--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2804,8 +2804,1496 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Lets Rent Bristol</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Letting agent</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>St Werburghs, Bristol BS2</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://letsrentbristol.co.uk</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>info@letsrentbristol.co.uk</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>0117 254 1133</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Adil Ayub &amp; Usman Ayub</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Family-run since 2009; manages HMOs/student/corporate lets across 7 postcodes - recurring management fees make each landlord worth thousands over time</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>ARLA Propertymark, CMP badges; portal listings</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Landlord acquisition dominated by bigger agencies and online agents (OpenRent) on search</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>'Landlords ask Google and ChatGPT who to trust with their Bristol BTL - own that answer'</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>Single office, established book - upsell landlord-focused content</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Bristol Property Centre</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Letting &amp; estate agent</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Chandos Rd, Redland, Bristol BS6</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bristolpropertycentre.co.uk</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>info@bristolpropertycentre.co.uk</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>0117 907 3577</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Alice Willmott (Head of Property Management)</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/bristol-property-centre</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning independent doing sales + lettings + student + commercial; Redland/BS6 is prime landlord territory</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Award mentions; LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Competes with national brands and Boardwalk-style digital independents for valuations</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>Local-SEO audit of 'letting agent Redland/Bishopston' - show the gap vs OpenRent and corporates</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>Confirm director name via Companies House (07695593) before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Caswell House</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Brize Norton, Oxfordshire (Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://caswellhouse.co.uk</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>kirsten@caswellhouse.co.uk</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>01993 701064</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Kirsten Jones (General Manager)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive-use 15th-century barn venue, 140 seated/200 evening; weddings worth £15-30k each - one booking pays for years of SEO</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Bridebook/Guides for Brides listings; professional photography</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Couples now ask ChatGPT for 'barn wedding venues Cotswolds' shortlists - directories get cited, venues don't</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>'Get on the AI shortlist: couples ask ChatGPT before they open Bridebook'</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Named GM with direct email - easiest warm route in batch 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Hyde House</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Stow-on-the-Wold, Gloucestershire</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://hyde-house.uk</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>hello@hyde-house.uk</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>01451 830354</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/HydeHouse (via page)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Exclusive-use Victorian house + barn with 20 bedrooms; premium Cotswolds weddings; relies on directory listings for discovery</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Bridebook/Coco Wedding Venues listings</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>Heavy dependence on paid directories that take commission or fees</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>Reduce directory dependence: rank + get AI-recommended directly and keep the margin</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Clifton Cosmetics</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Cosmetic clinic (injectables)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>The Body Centre, Alma Rd, Clifton, Bristol</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://cliftoncosmetics.co.uk</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Dr James Hesford (Founder)</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/cliftoncosmetics</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Doctor-led injectables clinic in affluent Clifton; repeat-treatment clients worth £1k+/year; local trust is the whole sales pitch</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Facebook page; WhatClinic listing</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Nurse-led and chain clinics outrank him; no clear local SEO presence</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>'Patients Google the injector before they book - make Dr Hesford the name Bristol finds first'</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>Doctor-led = strong E-E-A-T story for AEO content</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Zafra Medical</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Cosmetic/anti-ageing clinic</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Litfield House, Clifton Down, Bristol BS8</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zaframedical.co.uk</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Dr Jorge Zafra (Medical Director &amp; Owner)</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/zaframedical</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Owner-led anti-ageing clinic in prestige Litfield House medical centre; Vaser surgeon = high-ticket procedures</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>ConsultingRoom profile; Fresha booking</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Squarespace-style site with weak local SEO; invisible for 'botox Bristol' money terms</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>Free AI-visibility check for 'best aesthetic doctor Bristol' + one-page fix plan</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Yoganand Studio</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Yoga &amp; reformer pilates studio</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Clifton Triangle, Bristol BS8</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.yoganand.co.uk</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Jade (Founder)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/yoganand-studio</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/yoganandstudio</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Boutique studio in prime Clifton Triangle; memberships = recurring revenue; reformer pilates demand exploding in Bristol</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Active Instagram; ClassPass listing</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>Discovery happens on ClassPass (commission) rather than direct search</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>'Fill classes without paying ClassPass commission - own the local reformer searches'</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Smaller budget - fits entry £249 tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>The Reformer Space</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Reformer pilates studio</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Coldharbour Rd, Westbury Park, Bristol</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://thereformerspace.co.uk</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>info@thereformerspace.co.uk</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com (The reformer space page)</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>New (2024) dedicated reformer/tower studio in affluent Westbury Park/Redland; needs to build visibility fast to fill classes</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>ClassPass/Wellhub listings</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Brand-new domain with no authority; rivals (Soul Pilates, M.O) have head start</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>Ground-floor pitch: build search presence now while the studio is new</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>New business - keen but validate budget early</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Frazer James Financial Advisers</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Financial adviser / wealth management</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Berkeley Square, Bristol BS8</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://frazerjames.co.uk</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>james@frazerjames.co.uk</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>0117 990 2602</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>James Mackay (Founder/MD)</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/frazer-james</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning IFA for professionals/business owners; client lifetime value tens of thousands; founder already writes content</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>VouchedFor profile; content marketing on site; awards</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Content ranks for some terms but AI engines cite unbiased-looking directories instead of his articles</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>'Your guides rank on Google - here's how to make ChatGPT cite them too'</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>Direct founder email; marketing-literate buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ifamax Wealth Management</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Wealth management</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Bristol (clients Bristol/Bath/London)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ifamax.com</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>0117 332 2626</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Max Tennant</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/ifamax-limited</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Boutique firm targeting £400k+ investors; ultra-high client value; already runs keyword landing pages so believes in search</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Multiple SEO landing pages (wealth management Bristol etc.) - active investment</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Paying for SEO already; AEO/GEO layer missing; high-net-worth clients increasingly use AI research</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>Agency-upgrade pitch: add AI-search visibility to an already-working SEO base</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>Likely has an agency - displacement/upsell only</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Kensington &amp; Chelsea Tutors</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Private tuition agency</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Queens Gate Terrace, London SW7</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kctutors.co.uk</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>learn@kctutors.co.uk</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>020 7584 7987</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Nevil Chiles (MD &amp; Co-founder)</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/KensingtonandChelseaTutors</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Established 2002, serves ultra-wealthy SW London families; a single family client can be worth £10k+/year in tuition</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>Long-standing directory presence; celebrity client name-drops</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Newer polished agencies (Keystone, Ivy) dominate search and AI recommendations</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>'When parents ask ChatGPT for a Kensington tutor agency, Keystone comes up - not you'</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>Enquiries filter directly to MD Nevil - fast decision loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Ivy Education</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Private tuition &amp; education consultancy</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>London (Fulham office)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ivyeducation.co.uk</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>020 7736 6977</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Alastair Delafield (Founder &amp; CEO)</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/ivy-education</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Premium consultancy (tuition + school placement); wealthy international families; high fees per engagement</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>Award mentions; polished site; likely some agency spend</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>11+/school-admissions searches increasingly answered by AI Overviews citing content-rich competitors</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>AEO content play: own the questions parents ask AI about London school entry</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Wimbledon Osteopathic Clinic</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Osteopath</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Wimbledon/Raynes Park, London</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wimbledonosteopaths.co.uk</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>020 8946 6103</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>David Rowland (Principal)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>39 years established in affluent Wimbledon; self-pay treatments with long courses; loyal base but ageing digital presence</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Dated website; younger clinics and physio chains capture all new-patient searches</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>'Your reputation is 39 years strong - your Google presence isn't. Fix it for £249/month'</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>Classic modernisation candidate; confirm appetite to grow</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>West Dulwich Osteopaths</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Park Hall Rd, West Dulwich, London SE21</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://westdulwichosteopaths.com</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>westdulwichosteopaths@gmail.com</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>07779 262055</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Hollie Carter (Principal)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>7-practitioner clinic in affluent Dulwich Village catchment; still using a Gmail address and a legacy Weebly site - huge digital gap</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>None - organic/word-of-mouth only</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Multi-practitioner payroll but almost zero search visibility; losing new patients to marketed rivals</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>'A 7-practitioner clinic running on word-of-mouth: here's what you're leaving on the table'</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>Gmail contact = no marketing infrastructure at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Excellence Living</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Design &amp; build / home renovation</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Cheddar/Bristol &amp; North Somerset</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>https://excellenceliving.co.uk</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>hello@excellenceliving.co.uk</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>0117 212 0130</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Paul (Founder, 30+ yrs experience)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/ExcellenceLivingLtd</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Extensions/lofts/renovations worth £50-200k per job; already builds location landing pages (Bristol, Clevedon) so search-aware</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Location landing pages; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Location pages exist but thin; AI engines recommend FMB directory results instead of firms</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>'One extension job pays for 20 years of our fee - and your Clevedon page isn't even ranking'</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>High ticket + existing SEO intent = prime £249+ upsell</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Hallett Construction</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Builders / building contractor</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Hanham, Bristol BS15</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://hallettconstruction.co.uk</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>info@hallettconstruction.co.uk</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>0117 251 0179</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Jason Hallett (Director)</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/hallettconstruction.co.uk</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>FMB-member design &amp; build firm doing extensions with in-house planning service; already publishing postcode landing pages (BS40 etc.)</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>FMB membership; postcode landing pages = DIY SEO effort</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>DIY postcode pages show intent but lack authority to rank; no AEO strategy</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>'You're already building postcode pages - let us make them actually rank and get cited by AI'</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>Owner-led; DIY SEO effort = proven willingness to invest</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T25"/>
+  <autoFilter ref="A1:T41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2816,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2836,7 +4324,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2889,17 +4377,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2909,7 +4397,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2919,7 +4407,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2929,7 +4417,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2939,7 +4427,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2949,7 +4437,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2959,7 +4447,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2969,7 +4457,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2979,7 +4467,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2989,7 +4477,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2999,7 +4487,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3009,7 +4497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3019,7 +4507,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3029,10 +4517,160 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Independent vet (24/7 emergency)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Interior design studio</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Letting agent</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Letting &amp; estate agent</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cosmetic clinic (injectables)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cosmetic/anti-ageing clinic</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Yoga &amp; reformer pilates studio</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Reformer pilates studio</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Financial adviser / wealth management</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wealth management</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Private tuition agency</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Private tuition &amp; education consultancy</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Osteopath</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Design &amp; build / home renovation</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Builders / building contractor</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4292,8 +4292,1308 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Beard Medical Practice</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Litfield House, Clifton, Bristol BS8</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beardmedical.com</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>0117 973 1323</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Dr John Beard &amp; Dr Henry Beard (Founders)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Family-run private GP practice in Clifton; consultations + repeat memberships; self-pay healthcare demand booming as NHS waits grow</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Established listing presence; little visible content marketing</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Chains (Nuffield, HCA) and online GPs (DocTap) dominate 'private GP Bristol' searches</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>'NHS waits are sending patients to Google - make sure Bristol finds the Beards first'</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Family name practice = strong trust story for AEO content</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Broadgate GP</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>65 London Wall, City of London EC2</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.broadgategp.co.uk</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>doctor@broadgategp.co.uk</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>020 7638 4330</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Independent same-day private GP in the City since 2009; corporate workers self-pay £100+ per visit; high repeat and corporate-account value</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Twitter/X presence; Doctify profile</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>DocTap's 11 clinics and hospital brands outrank a single-site independent</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>'City workers ask ChatGPT where to get a same-day GP near Liverpool St - we checked who it names'</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Mayfield Clinic</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Redland, Bristol (+ Oxford HQ)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayfieldclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Growing private GP group already building 'nearby location' SEO pages (Keynsham, Bradley Stoke); blog answering patient questions = AEO-ready mindset</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>Location pages + patient-question blog posts = active SEO strategy</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>Content exists but thin authority; not cited by AI engines for Bristol private GP queries</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>Upgrade pitch: turn their existing location/blog strategy into AI citations</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>May have in-house/agency SEO - qualify first</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Nicola Roofing Ltd</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Roofer</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Longwell Green, Bristol</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nicolaroofing.co.uk</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>info@nicolaroofing.co.uk</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>0117 985 9882</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/Nicola-Roofing-Limited</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>30+ years established, covers Bristol &amp; Bath; re-roofs worth £5-15k; glowing reviews but weak digital presence</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Yell/TrustATrader listings</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Lead-gen platforms (Bark, TrustATrader) charge per lead for searches they could own</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>'30 years of great roofs, invisible on Google - own "roofer Bristol" instead of renting it from Bark'</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Westex Heating</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating / boilers</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Queen Square, Bath</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>https://westexheating.co.uk</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>services@westexheating.com</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>01225 331 091</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Bath-based Gas Safe firm; boiler installs £2.5-5k plus recurring service plans; affluent Bath housing stock</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>None visible beyond directories</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>British Gas and national installers (BOXT, Heatable) take the high-intent boiler searches</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>'When a Bath boiler dies, the owner Googles once. Here's how to be the answer'</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Bristol Boiler Company</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating / boilers</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>https://bristolboiler.co.uk</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>0117 939 6202</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Boiler installs + landlord gas certificates = recurring B2B revenue from letting agents/landlords; emergency repairs are high-intent searches</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>Dated site losing emergency and landlord work to slicker rivals</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>Quick-win pitch: emergency + landlord-certificate keywords they could own in months</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Rygol Electrical</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>https://rygol.co.uk</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>0117 313 7644</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>NICEIC contractor 20+ years; rewires worth £4-8k; also runs solar arm (solar.rygol.co.uk) - two service lines to market</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>Keyword landing pages (house rewiring Bristol) - some SEO effort</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Split web presence (rygol.co.uk + solar subdomain) dilutes authority</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>Consolidation + AEO pitch across both electrical and solar arms</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T48" s="3" t="inlineStr">
+        <is>
+          <t>One relationship, two revenue lines (electrical + solar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>MJP Electrical Services</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Warmley, Bristol (covers Bath, S Wales, Glos, Swindon)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mjpelectrical.com</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>info@mjpelectrical.com</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>0117 450 0124</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Mark Parry (Founder/Director)</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/MJPELECTRICALSW</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Family firm, 4.9-star rated, multi-region coverage; domestic + commercial; founder ex-British Gas senior engineer</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>Multiple regional Facebook pages; separate Bath site</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Regional microsites (mjpelectricalbath.com) split domain authority - classic old-SEO setup</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>'Your Bath site and main site are competing with each other on Google - here's the fix'</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Social Pantry</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Event &amp; wedding caterer</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Battersea, London</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://socialpantry.co.uk</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Alex Head (Founder &amp; Owner)</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/in/alex-head-49744865</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>High-profile B Corp caterer; weddings/corporate events worth £5-50k; founder has strong press profile ripe for AEO citation leverage</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>PR agency coverage (Sainsbury's Mag, podcasts); £1.1M investment 2023</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>Press profile doesn't convert to AI-answer visibility for 'wedding caterer London' queries</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>Turn press authority into AI citations; compete on answers not just aesthetics</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>Well-funded - bigger budget but may have agency already</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Kitchen Party</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Event &amp; wedding caterer</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Deptford, SE London</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://kitchen-party.co.uk</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Clem &amp; Joss (Co-founders, sisters)</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Farm-to-fork caterer since 2015; weddings and corporate events; recommended-supplier listings at venues = referral-dependent</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>Venue recommended-supplier listings (Asylum Chapel)</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Dependent on venue lists and word-of-mouth; near-zero search presence</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>'Couples shortlist caterers on ChatGPT now - venue lists alone won't fill your calendar'</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Featherbed Home Care</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Home care / live-in care</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Keynsham, Bristol &amp; Bath</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>https://featherbedhomecare.co.uk</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>featherbedcare@gmail.com</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>0117 986 1948</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Sally Carpenter (Manager)</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned since 1986; live-in care clients worth £50k+/year each; competes with nationals for the same searches</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>None - Gmail contact address signals zero marketing infrastructure</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Agincare/Bluebird/Helping Hands dominate every care search; families ask AI who to trust</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>'One live-in care client is worth £50k/year. Your Gmail address is costing you several'</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T52" s="3" t="inlineStr">
+        <is>
+          <t>Gmail tell again - same wedge as West Dulwich Osteopaths</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Snapdragons Nurseries</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Private day nurseries</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Redland/Horfield/Shirehampton Bristol + Bath &amp; Wiltshire</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.snapdragonsnursery.com</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>redland@snapdragonsnursery.com</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>0117 907 4032</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Rosemary &amp; Paul Collard (Founders)</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com/company/snapdragons-nurseries-limited</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Independent group since 1998 with Outstanding-rated settings; a nursery place is worth £12-15k/year and parents research obsessively</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>Established brand; council directory listings</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Parents now ask ChatGPT 'best nursery near Redland' - chains (Kids Planet, Busy Bees) invest heavily in search</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>'Your Outstanding rating should be the first thing AI tells parents - right now it isn't'</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>Multi-site independent = ideal mid-market client</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Terra Hale</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Personal training studio</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Chelsea &amp; Notting Hill, London</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>https://terrahale.com</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Private 1:1 longevity/PT studios in prime West London; clients pay £70-120/session on ongoing packages; 'longevity' positioning is search-trend gold</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>Location landing pages (personal training in Chelsea) - SEO aware</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Longevity-fitness searches exploding; bigger brands (KX, Third Space) absorb the demand</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>Own the emerging 'longevity training London' AI answers before the big clubs do</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>The Kensington Studio</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Personal training studio</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Kensington, London</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://thekensingtonstudio.com</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Exclusive private PT studio in ultra-affluent Kensington; high-ticket ongoing client relationships</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Boutique studio invisible next to KX and Harbour Club in local searches</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>Boutique-vs-big-club angle: be the AI answer for 'private personal trainer Kensington'</t>
+        </is>
+      </c>
+      <c r="R55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>nmotion London</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Personal training &amp; wellness studio</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Chelsea, London</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nmotionlondon.com</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Private fitness/wellbeing studio for professionals in Chelsea; tailored packages = high client lifetime value</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>Small brand fighting for visibility in London's most competitive fitness postcode</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>Entry-tier pitch: £249/mo to start appearing in local + AI search results</t>
+        </is>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T56" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T41"/>
+  <autoFilter ref="A1:T56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4304,7 +5604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4324,7 +5624,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -4347,17 +5647,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4367,7 +5667,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4377,7 +5677,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4387,57 +5687,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4447,7 +5747,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4457,7 +5757,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4467,7 +5767,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -4477,7 +5777,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -4487,7 +5787,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -4497,7 +5797,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -4507,7 +5807,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -4517,7 +5817,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4527,7 +5827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4537,7 +5837,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4547,7 +5847,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4557,7 +5857,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4567,7 +5867,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4577,7 +5877,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4587,7 +5887,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4597,7 +5897,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4607,7 +5907,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -4617,7 +5917,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4627,7 +5927,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -4637,7 +5937,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -4647,7 +5947,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -4657,7 +5957,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -4667,10 +5967,100 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Private tuition agency</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Private tuition &amp; education consultancy</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Osteopath</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Design &amp; build / home renovation</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Builders / building contractor</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Roofer</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Home care / live-in care</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Private day nurseries</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Personal training &amp; wellness studio</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5592,8 +5592,1212 @@
       </c>
       <c r="T56" s="4" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Edwards Family Law</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Family law firm</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Southampton Buildings, London WC2</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.edwardsfamilylaw.co.uk</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>contact@edwardsfamilylaw.co.uk</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>020 3983 1818</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Kelly Edwards (Managing Partner)</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/EdwardsFamilyLawLondon</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Boutique divorce firm handling complex/high-net-worth cases worth £20k+ in fees each; Chambers-ranked but digitally quiet</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>Chambers UK profile; directory listings</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>HNW divorce clients research discreetly via search/AI - big firms and content-rich rivals get found first</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>'People research divorce lawyers before telling anyone. Be the name Google and ChatGPT give them'</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Peters May</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Family law firm</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Brook Street, Mayfair, London W1</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.petersmay.com</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@petersmay.com</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>020 3036 0058</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Juliette Peters &amp; Jessica May (Founders)</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Mayfair divorce boutique; ultra-high-value cases; two-founder firm with fast decision making</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>Chambers profile</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Mayfair positioning but thin content vs Vardags/Stewarts who dominate HNW divorce searches</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>AEO for the questions HNW spouses actually ask AI about UK divorce</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Pickwick Estates</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Dulwich Village &amp; Honor Oak, London SE22</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pickwickestates.co.uk</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>adam.shea@pickwickestates.com</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Adam Shea (Director)</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 2002 in affluent Dulwich; premium family homes = high fees; dated .aspx website vs polished corporate rivals</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>Portal listings only</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Knight Frank/Foxtons/Pedder dominate Dulwich searches; dated site erodes valuation-lead credibility</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>'Dulwich sellers shortlist agents online before calling - your website is costing you instructions'</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>Legacy .aspx site = instant credibility for a modernisation pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Fulham Road Dental</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>725 Fulham Rd, London SW6</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fulhamroaddental.com</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@fulhamroaddental.com</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>020 4542 5555</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Dr George Cheetham</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Modern private practice selling implants + Invisalign in affluent SW6; every implant case £3k+; surrounded by chains (Perfect Smile, MyHealthcare)</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Polished new site; likely some marketing spend</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>New-ish practice building patient base against established chains with bigger budgets</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>AI-visibility race: be what ChatGPT recommends for 'Invisalign Fulham' before the chains lock it up</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Natural Health Chiropractic</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Chiropractor</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Hampstead Village, London NW3</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.naturalhealthchiro.co.uk</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>020 7431 4882</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Matt Murray (Chiropractor)</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Solo/small chiropractic clinic in one of London's wealthiest villages; treatment courses worth £500-1500 per patient</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Local visibility battle vs physio chains and osteopaths for the same back-pain searches</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>'Hampstead residents ask AI who can fix their back - the answer should be you'</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Hampstead Chiropractic Clinic</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Chiropractor</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>O2 Centre, Finchley Rd, London NW3</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>https://hampsteadchiropractic.co.uk</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/HCCgettreated</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Established BCA-member clinic treating all ages in affluent NW3; located inside Virgin Active = footfall + referral potential</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>Facebook page; WhatClinic reviews</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>Generic clinic name + weak site = losing 'chiropractor near me' to newer rivals</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>Quick local-SEO wins: reviews, GBP optimisation, then AEO layer</t>
+        </is>
+      </c>
+      <c r="R62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Rent A Home</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Letting agent</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Stoke Newington, London N16</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rentahome-uk.com</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Independent lettings/management since 1994 across N16/Hackney/Islington - dense landlord market with high management LTV</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>Portal listings (OnTheMarket)</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>Dated site; landlords choosing agents via search find Dexters/Winkworth/OpenRent first</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>'Hackney landlords are worth £1000s/year each in management fees - and they can't find you'</t>
+        </is>
+      </c>
+      <c r="R63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Steve Mears Independent Mortgage Services</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Mortgage broker</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stevemears.com</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>info@stevemears.com</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>0117 973 4300</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Steve Mears (Founder)</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>One of Bristol's longest-established brokers (1995); whole-of-market; every case worth £500-2k in proc fees + repeat remortgages</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>Long-standing brand; directory presence</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>Online brokers (Habito, L&amp;C) and Clifton Private Finance's strong SEO squeeze the middle</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>'Bristol homeowners ask ChatGPT whether to use a broker - the answer names your competitors'</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Vesta Mortgages</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Mortgage broker</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vestamortgages.co.uk</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@vestamortgages.co.uk</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>0117 363 7575</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Independent whole-of-market adviser in a hot property market; strong fit for local-intent search plays</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Smaller brand fighting Clifton PF and Fox Davidson who both invest in SEO</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>Underdog local-SEO pitch for specific niches (first-time buyer Bristol, BTL Bristol)</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Mellow Financial</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Mortgage &amp; insurance broker</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mellowfinancial.co.uk</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>hello@mellowfinancial.co.uk</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>0117 251 0544</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Young friendly-brand broker; protection cross-sales boost per-client value; brandable for content marketing</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>Modern brand suggests marketing awareness</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>New brand with little search authority in competitive market</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>Entry-tier: £249/mo to build the search foundation while the brand is young</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Holcombe Associates</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Business consultancy</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Dursley (serves Bristol/Glos/Somerset)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.holcombeassociate.com</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>jwasdell@holcombeassociate.com</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>07796 195495</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>James Wadsell (Founder)</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>SME growth/exit consultancy; engagements worth £10k+; already builds county landing pages (Bristol, Somerset, Glos, Worcs) = SEO believer</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>County landing pages = active DIY SEO</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Landing pages exist but thin; consultancy searches increasingly answered by AI</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>'Your county pages show the intent - here's how to make them actually win clients'</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Fernlea Vets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Hanham &amp; Kingswood, Bristol</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>https://fernleavets.co.uk</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>0117 967 7067</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Privately run two-site practice since 1986 in a city where IVC (corporate HQ'd in Bristol!) owns most rivals; independence is a differentiator</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>Corporate groups dominate 'vet Bristol' searches with big budgets</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>Independence story + AEO: be the answer to 'independent vet Bristol'</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Avenue Veterinary Centre</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>https://avenue-vets.com</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@avenue-vets.com</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>0117 956 9038</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Independent practice with 100+ years heritage; loyal client base but heritage doesn't rank on Google</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Same corporate-vs-independent squeeze as Fernlea</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>Heritage + independence content play for local and AI search</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Burnside Chartered Accountants</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Queen Square, Bristol BS1</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>https://burnside.biz</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>0845 071 7676</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Independent firm in prime Queen Square address serving Bristol SMEs; recurring-fee client model</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>'.biz' domain and dated site vs cloud-first rivals chasing the same SME clients</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>Modernisation pitch: site + local SEO before the online accountants take the market</t>
+        </is>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T70" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T56"/>
+  <autoFilter ref="A1:T70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5604,7 +6808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5624,7 +6828,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -5641,13 +6845,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5657,37 +6861,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5697,7 +6901,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5707,7 +6911,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5717,7 +6921,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5727,7 +6931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5737,67 +6941,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5807,7 +7011,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5817,7 +7021,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5827,7 +7031,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5837,7 +7041,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5847,7 +7051,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5857,7 +7061,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5867,7 +7071,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -5877,7 +7081,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5887,7 +7091,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5897,7 +7101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5907,7 +7111,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5917,7 +7121,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -5927,7 +7131,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5937,7 +7141,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5947,7 +7151,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5957,7 +7161,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5967,7 +7171,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5977,7 +7181,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5987,7 +7191,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5997,7 +7201,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6007,7 +7211,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6017,7 +7221,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6027,7 +7231,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6037,7 +7241,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6047,7 +7251,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6057,10 +7261,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Home care / live-in care</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Private day nurseries</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mortgage &amp; insurance broker</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Business consultancy</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6796,8 +6796,2620 @@
       </c>
       <c r="T70" s="4" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Etons of Bath</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Interior designer (period homes)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Walcot Street, Bath</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.etonsofbath.com</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sarah@etonsofbath.com</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>01225 639002</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Latham (Founder)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Specialist in Georgian/listed Bath properties - projects worth £50k+; showroom presence; already builds city landing pages (Bristol)</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Location landing pages; showroom; established brand since 2009</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Period-home niche is perfect AEO territory but AI engines don't yet cite them for it</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>'Own the answer to "interior designer for Georgian homes" across Google and ChatGPT'</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>Founder email published - direct route</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Bluefish Landscaping</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Landscape design &amp; build</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Farnham, Surrey (covers Weybridge/Guildford)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bluefishlandscapes.co.uk</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@bluefishlandscapes.co.uk</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>01252 321511</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>James Fish (Founder)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Luxury gardens, pools and outdoor kitchens for Surrey estates - projects £50-500k; BALI member; one client pays for a decade of SEO</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>BALI membership; case-study content</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Surrey's wealthiest postcodes research online; national design directories soak up the searches</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>'One Weybridge garden project is worth 100x our fee - be the name Surrey finds'</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Cobb Farr Estate Agents</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent (premium)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Bath (+ Bradford-on-Avon)</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cobbfarr.com</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Philip Cobb (Co-founder &amp; MD)</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Premium Bath independent since 1989; high-value Georgian stock = large fees per instruction</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>Portal listings; established brand</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>Knight Frank/Savills/Fine &amp; Country dominate premium Bath searches</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>'Bath sellers of £1m+ homes shortlist 3 agents online - make sure you're one of them'</t>
+        </is>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Nash &amp; Co Estate Agents</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>http://www.nashandcobath.co.uk</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@nashandcobath.co.uk</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>01225 444 800</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Independent Bath agency, 80+ years combined experience; dated website vs national rivals</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>HTTP-only dated site actively hurts trust for valuation leads</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>Website + local SEO rebuild pitch: table stakes to compete in Bath</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T74" s="3" t="inlineStr">
+        <is>
+          <t>Site still on http:// - instant credibility opener</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>@Home Estate Agents</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.athomebath.co.uk</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Toby Knight (Founder)</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 2013, founder with 33 years local experience; boutique service positioning</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>Rightmove profile</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>Small independent squeezed by corporates and Bath &amp; Rural boutiques alike</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>Local-hero content play: founder's 33 years of Bath knowledge as AEO material</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>The Brace Orthodontic Practice</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Orthodontist</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Artillery Passage, London E1</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thebrace.com</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>020 7247 5768</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Specialist orthodontists near Liverpool St; Invisalign/braces cases £3-6k; City workers self-pay</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>Some review cultivation</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Chain clinics and Harley St brands dominate 'Invisalign London' searches</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>City-worker angle: own 'orthodontist near Liverpool Street' + AI answers</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>The London Orthodontic Group</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Orthodontist</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>https://londonlovesbraces.com</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Dr Richard Hennebry &amp; Dr Vivi Grigoriou-Hennebry (Owners)</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Husband-and-wife US-trained specialists - rare credential in UK; high-value cases; memorable brand domain</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>Branded domain (londonlovesbraces) suggests marketing intent</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>US-trained differentiation invisible in search results and AI answers</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>'You have the best credentials story in London orthodontics - nobody can find it'</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TW10 Architects</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Richmond, London TW10</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>https://find-an-architect.architecture.com/tw10-architects/richmond</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>via RIBA directory / website</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>RIBA practice, 15+ years, residential focus in affluent Richmond; extensions/refurbs worth £100k+</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>RIBA directory listing</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Homeowners find architects via Houzz/directories that charge for leads</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>'Richmond homeowners ask ChatGPT how to find an architect - be the named answer'</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S78" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>Get direct website/email before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Scenario Architecture</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>London &amp; Surrey</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>https://scenarioarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Ran Ankory &amp; Maya Carni (Founders)</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>RIBA practice with strong brand; already runs location landing pages ('architects Surrey') = active SEO spend</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>Location landing pages; polished site; likely agency</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>Paying for SEO but AEO/GEO layer missing in a design-literate market</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>Agency-upgrade pitch: add AI-search visibility to existing SEO investment</t>
+        </is>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S79" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Malcolm Jenkins Associates</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Shepperton, Surrey</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>http://www.architectinguildford.co.uk</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>enquiries@malcolmjenkins.co.uk</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>01932 225344</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Malcolm Jenkins (Principal)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Established Surrey practice with keyword domain but very dated site; residential project values high in TW/GU postcodes</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>Keyword domain shows old SEO effort</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>1990s-era website undermines premium project credibility</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>Modernise + rank: the domain has history, the site squanders it</t>
+        </is>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S80" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Clair Strong Interior Design</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Bath (+ London)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.clairstrong.co.uk</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Clair Strong (Founder)</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Established 2006, Bath + London projects; residential and commercial; solo-led studio with strong portfolio</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>Etons of Bath and bigger studios out-market her in the same city</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>Entry-tier local SEO: own 'interior designer Bath' long-tail queries</t>
+        </is>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Graduate Gardeners</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Garden design &amp; landscaping</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Bisley, Gloucestershire (Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.graduategardeners.co.uk</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>office@graduategardeners.co.uk</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>01452 770273</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>BALI award winners, 50+ years, serving Cotswolds wealth; garden builds worth £30-150k</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>BALI awards; established reputation</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Award pedigree doesn't surface in AI answers for 'garden designer Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>Turn 50 years + BALI awards into the AI-cited Cotswolds authority</t>
+        </is>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S82" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Hitchen Legal</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Legal recruitment</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hitchenlegal.com</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>kate@hitchenlegal.com</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Kate Hitchen (Founder/Director)</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/katehitchen</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Boutique legal search firm since 2013; placement fees £15-30k; founder active on LinkedIn</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>Founder LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>Law firms ask AI to name legal recruiters - big brands (Michael Page, Robert Walters) get cited</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>Boutique-vs-giant AEO play in legal recruitment</t>
+        </is>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S83" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Workout Bristol</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Independent gym &amp; health club</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Harbourside + Ashton, Bristol</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.workoutbristol.co.uk</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ashton@workoutbristol.co.uk</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Bristol's longest-established independent club (1982), two sites, classes + PT; memberships = recurring revenue</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>PureGym/Anytime chains carpet-bomb 'gym Bristol' searches</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>Independent-community angle vs chains; own 'independent gym Bristol'</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S84" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Fitness</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Independent gym</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Kingswood, Bristol</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>https://mofgym.co.uk</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>11,000 sq ft biggest independent gym in Bristol; four training areas; membership volume model</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>Budget chains undercut on price; needs differentiation in search</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>Local-SEO + review engine to defend Kingswood catchment</t>
+        </is>
+      </c>
+      <c r="R85" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S85" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Bristol Physiotherapy Clinic</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>3 sites: Harbourside, Redland, Whiteladies Rd Bristol</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>https://bristolphysiotherapyclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>info@bristolphysiotherapyclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>0117 973 8319</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Three-site evidence-based practice since 2007; self-pay + insurance work; sites inside gyms/clubs = referral flow</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>Multi-site practice with single-site search visibility</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>Per-location Google/AI visibility: 3 sites should mean 3x the search presence</t>
+        </is>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S86" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>McFerran Physio</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Physiotherapy (sports)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Clifton Rugby Club, Bristol</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>https://mcferranphysio.co.uk</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Alan McFerran (Founder)</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Ex-Bristol City FC physio - elite-sport credibility; self-pay sports injury market in North Bristol</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>Pro-football story buried; generic rivals outrank him</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>'11 years with Bristol City's players - make that the answer to "sports physio Bristol"'</t>
+        </is>
+      </c>
+      <c r="R87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S87" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Parkgate Estate Agents</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Eton St, Richmond TW9</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.parkgate.co.uk</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>info@parkgate.co.uk</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>020 8940 2991</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Truly independent Richmond agency since 1976; already builds service landing pages (letting agents Richmond, property managers Twickenham)</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>Service landing pages = active SEO</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>Foxtons/Savills/Hamptons saturate Richmond; AEO is the open flank</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade pitch: their landing pages + our AEO layer = AI-recommended independent</t>
+        </is>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S88" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Antony Roberts</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Richmond, Kew, East Sheen</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.antonyroberts.co.uk</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Antony Roberts (Founder)</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Leading independent in Richmond/Kew with founder-name brand and local landlord roots; premium stock</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>Established multi-office brand</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>Corporate agents dominate search for Richmond property despite AR's local standing</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>'Richmond's leading independent should be Google's answer too'</t>
+        </is>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S89" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Griffin Stevens</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Twickenham</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>https://griffinstevens.co.uk</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Independent sales + lettings in Twickenham's family-home market</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>Portal listings</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>Smaller brand in Foxtons territory</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>Hyperlocal content: own Twickenham micro-neighbourhood searches</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Jo &amp; Co Property Management</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Letting agent / property management</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Richmond &amp; Kingston, London</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.joandcoprop.com</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Jo (Founder)</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Modern management-focused agency across SW London suburbs; recurring management fees per landlord</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>Modern brand/site</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>Young brand lacking search authority vs Parkgate/Antony Roberts</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>Landlord-focused content + local SEO from the ground up</t>
+        </is>
+      </c>
+      <c r="R91" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S91" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Sharp Family Law</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Family law firm</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Bath (+ Bristol)</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sharpfamilylaw.com</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>info@sharpfamilylaw.com</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Richard Sharp (Managing Partner)</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Specialist divorce firm in Bath; complex/relocation cases worth £15k+ fees; named MP with direct email</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>Directory profiles</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Regional giants (Thrings, Battens) and national brands crowd Bath family-law searches</t>
+        </is>
+      </c>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>'Divorcing spouses in Bath research lawyers at midnight - be the answer they find'</t>
+        </is>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S92" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Awdry Law</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Law firm</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Bath (+ Wiltshire offices)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>https://awdry.law</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>info@awdry.law</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>01225 417111</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Multi-office independent covering Bath/Wiltshire; conveyancing + private client = search-driven work</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>Modern .law domain rebrand suggests marketing awareness</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>Conveyancing comparison sites intercept their clients</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>Local-intent SEO for 'solicitor Bath/Chippenham' money terms</t>
+        </is>
+      </c>
+      <c r="R93" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S93" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Thames Skin Clinic</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Twickenham (serves Richmond/Teddington)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thamesskin.co.uk</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Dr Anna Hemming (Founder)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Doctor-led clinic in affluent SW London villages; repeat injectable clients worth £1k+/yr; founder has media presence</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>Save Face/Safety in Beauty profiles; PR</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>Central-London brands pull Richmond patients into town</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>'Keep Richmond's aesthetic patients local - be the AI answer for SW London skin clinics'</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>The Real You Clinic</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Twickenham/Richmond</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>https://realyouclinic.com</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Established medical aesthetics clinic in wealthy TW postcodes</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>Competing with Thames Skin and central London for same patients</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>Local reviews + AEO for 'aesthetics clinic Richmond'</t>
+        </is>
+      </c>
+      <c r="R95" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S95" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>HSA Dermal Clinic</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Skin clinic</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Richmond upon Thames</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hsadermalclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Advanced skin treatments in Richmond; Save Face accredited</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>Save Face accreditation</t>
+        </is>
+      </c>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>Weak differentiation in crowded local market</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>Accreditation-led trust content for local + AI search</t>
+        </is>
+      </c>
+      <c r="R96" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S96" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Solarsmith</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Solar installer</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Surrey, London &amp; South East</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.solarsmith.co.uk</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>team@solarsmith.co.uk</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>020 8050 2285</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>MCS installer covering Surrey's large-roof housing stock; installs £8-20k in wealthy postcodes</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>Bookable-online model suggests marketing awareness</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>Sunsave/EDF/Octopus muscling into domestic solar search</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>'Surrey homeowners ask AI if solar is worth it - be the installer in the answer'</t>
+        </is>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S97" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Solar Generation</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Solar installer</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Surrey (Leatherhead area)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>http://discoversolar.co.uk/directory/mcs-installer/surrey/surrey-solar-generation-ltd/</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>info@surreysolargeneration.com</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>01372 457750</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Simon Prichard (Director)</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>MCS-certified since 2011; long track record in affluent Surrey</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>Directory listings only</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>Minimal web presence in a market being taken by national brands</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>Ground-up local SEO: 14 years of installs as review/content ammunition</t>
+        </is>
+      </c>
+      <c r="R98" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S98" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>Confirm current website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Bristol Tuition</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Private tuition agency</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>https://bristoltuition.co.uk</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>enquiries@bristoltuition.co.uk</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>0117 457 6645</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>100+ registered tutors; 11+/GCSE demand from Bristol's grammar-adjacent families; per-family LTV high</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>National platforms (Tutorful, MyTutor) absorb local searches</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>'Bristol parents ask ChatGPT how to find a tutor - the answer is a national platform, not you'</t>
+        </is>
+      </c>
+      <c r="R99" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S99" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Greenhouse Learning</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Tutoring company</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>https://greenhouselearning.co.uk</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>rach@greenhouselearning.co.uk</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Rachel (Founder)</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>Personalised 1:1 and small-group tutoring at home/school/centre across Bristol; named founder email</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>Same national-platform squeeze; SEN/personalisation niche underexploited in search</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>Niche AEO: own 'SEN tutor Bristol' and personalised-tuition queries</t>
+        </is>
+      </c>
+      <c r="R100" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S100" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>3A Tutors</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Tutorial college &amp; exam centre</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.3at.org.uk</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>Independent exam centre + tutorial college; private candidates (home-ed, retakes) pay hundreds per exam sitting</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>Home-ed exam-centre searches are high-intent and poorly served locally</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>'Own "sit GCSE privately Bristol" - a high-intent niche nobody optimises for'</t>
+        </is>
+      </c>
+      <c r="R101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S101" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T101" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T70"/>
+  <autoFilter ref="A1:T101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6808,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6828,7 +9440,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -6845,23 +9457,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6871,7 +9483,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6881,7 +9493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6891,57 +9503,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6951,7 +9563,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6961,7 +9573,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6971,7 +9583,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6981,7 +9593,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6991,7 +9603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7001,67 +9613,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7071,7 +9683,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7081,7 +9693,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7091,7 +9703,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7101,7 +9713,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7111,7 +9723,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7121,7 +9733,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7131,7 +9743,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -7141,7 +9753,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7151,7 +9763,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7161,7 +9773,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7171,7 +9783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7181,7 +9793,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7191,7 +9803,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7201,7 +9813,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7211,7 +9823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7221,7 +9833,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7231,7 +9843,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7241,7 +9853,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7251,7 +9863,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7261,7 +9873,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7271,7 +9883,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7281,7 +9893,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7291,7 +9903,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7301,10 +9913,180 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Home care / live-in care</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Private day nurseries</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Personal training &amp; wellness studio</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mortgage &amp; insurance broker</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Business consultancy</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Interior designer (period homes)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Landscape design &amp; build</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Estate agent (premium)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Garden design &amp; landscaping</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Legal recruitment</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Independent gym &amp; health club</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Independent gym</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Physiotherapy (sports)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Letting agent / property management</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Skin clinic</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tutoring company</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tutorial college &amp; exam centre</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9408,8 +9408,2328 @@
       </c>
       <c r="T101" s="4" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Elizabeth Wightwick</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon Village, London SW19</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.elizabeth-wightwick.co.uk</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Elizabeth Wightwick (Founder)</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>Family-run independent in Wimbledon Village's premium market; instructions worth £10k+ in fees</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>Portal listings</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>Savills/Hamptons/Foxtons own Wimbledon search results</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>'Village sellers want a village agent - make Google and ChatGPT agree'</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S102" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>C James &amp; Co</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Wimbledon, London SW19</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cjames.co.uk</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Suzanne (Founder)</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>Wimbledon's longest-established solely independent agent (1991); sales + lettings + management</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>Portal listings</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>30-year reputation invisible in modern search</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>Heritage-into-authority content play</t>
+        </is>
+      </c>
+      <c r="R103" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S103" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Nunn &amp; Associates</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Chiswick / Bedford Park, London W4</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.andrewnunnassociates.co.uk</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Nunn (Owner)</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>Owner-run independent in affluent Bedford Park conservation area; premium period stock</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>Local reputation</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>Corporate agents flood W4 searches; independents rely on word-of-mouth</t>
+        </is>
+      </c>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>'Bedford Park owners ask AI who knows their conservation area best - be the answer'</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S104" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>BDBF LLP</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Employment law firm</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bdbf.co.uk</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Independent employment/partnership law boutique; exec severance cases worth £10-50k in fees; City catchment</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>Professional site; directory rankings</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>Executives research severance rights via AI before choosing lawyers - big firms get cited</t>
+        </is>
+      </c>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>AEO for the questions executives ask AI about exit packages</t>
+        </is>
+      </c>
+      <c r="R105" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S105" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Doyle Clayton</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Employment law firm</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>London &amp; Reading</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.doyleclayton.co.uk</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>info@doyleclayton.co.uk</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>020 7329 9090</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>UK's largest specialist workplace law firm yet still independent; both employer and employee work</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>Established content/brand</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>Specialist positioning under-leveraged in AI answers vs generalist giants</t>
+        </is>
+      </c>
+      <c r="Q106" s="3" t="inlineStr">
+        <is>
+          <t>'The workplace-law specialists should be the AI's specialist answer'</t>
+        </is>
+      </c>
+      <c r="R106" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S106" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>didlaw</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Employment law (disability discrimination)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>https://didlaw.com</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Karen Jackson (MD &amp; Founder)</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>Niche leader in disability/health discrimination - perfect defensible AEO niche; award-winning</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>Awards; founder profile</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr">
+        <is>
+          <t>Niche authority not yet translated into AI-answer dominance</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="inlineStr">
+        <is>
+          <t>Own every AI answer about workplace disability discrimination</t>
+        </is>
+      </c>
+      <c r="R107" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S107" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Anderson &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Chelsea/Kensington, London</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.andersonandsons.co.uk</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>Family firm since 1966 serving prime central London; emergency + renovation plumbing at premium rates; location landing pages already built</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>Location landing pages (Chelsea, Kensington) = active SEO</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>Aggregators (AllService4U, Checkatrade) intercept emergency searches</t>
+        </is>
+      </c>
+      <c r="Q108" s="3" t="inlineStr">
+        <is>
+          <t>'55 years in Chelsea should beat any aggregator - in AI answers it doesn't yet'</t>
+        </is>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S108" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Pippo Plumbers</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Kensington &amp; Chelsea, London</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>https://pippoplumbers.co.uk</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Growing K&amp;C plumbing firm since 2018; premium postcode = premium job values</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>Area landing pages</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr">
+        <is>
+          <t>Young brand competing with 50-year incumbents and aggregators</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="inlineStr">
+        <is>
+          <t>Ground-floor local SEO + review engine</t>
+        </is>
+      </c>
+      <c r="R109" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S109" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>The Pure Practice</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Central Bath</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>https://thepurepractice.co.uk</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Sonja Bass (Founder)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Founder with 20+ years Bath experience; central clinic; self-pay physio in affluent city</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>Online booking</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr">
+        <is>
+          <t>Hospital brands (Sulis, Ascenti) and Team Bath absorb physio searches</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>'Bath's independent physio should be Bath's AI answer'</t>
+        </is>
+      </c>
+      <c r="R110" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S110" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid Health Clinic</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Sports physio &amp; massage</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Milsom Street, Bath</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hybridhealthphysio.com</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Prime Milsom Street location; sports injury + massage; 20+ years experience</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>Same hospital-brand squeeze; thin differentiation online</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="inlineStr">
+        <is>
+          <t>Local + AEO for 'sports physio Bath'</t>
+        </is>
+      </c>
+      <c r="R111" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S111" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Arkenstone Wealth Management</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Financial adviser / wealth management</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon Village, London SW19</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arkenstonewealth.co.uk</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>advice@arkenstonewealth.co.uk</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>020 8323 8881</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>IFA practice in Wimbledon Village serving SW London professionals; client LTV in tens of thousands</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>Directory profiles (Unbiased)</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>Unbiased/VouchedFor intercept advice-seekers before they find local firms</t>
+        </is>
+      </c>
+      <c r="Q112" s="3" t="inlineStr">
+        <is>
+          <t>'Bypass the directories: be the direct AI answer for "IFA Wimbledon"'</t>
+        </is>
+      </c>
+      <c r="R112" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S112" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Harding Chartered Surveyors</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Chartered surveyors (party wall/building)</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Piccadilly + offices across London</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>https://hardingsurveyors.co.uk</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@hardingsurveyors.co.uk</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>020 7736 2383</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>RICS firm with party-wall specialism; London's renovation boom = constant high-intent searches; already builds location pages</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>Location pages (Piccadilly office etc.) = SEO investment</t>
+        </is>
+      </c>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>Party-wall queries increasingly answered by AI summaries citing content-rich rivals</t>
+        </is>
+      </c>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>'Every London extension needs a party wall surveyor - own that AI answer'</t>
+        </is>
+      </c>
+      <c r="R113" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S113" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Peter Barry Surveyors</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Chartered surveyors</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Fulham, SW London</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.peterbarry.co.uk</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>surveying@peterbarry.co.uk</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>020 7471 8932</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>Established SW London surveyors; party wall + building surveys tied to the extension boom</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>Office landing pages</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>Competing with Harding etc. for identical high-intent searches</t>
+        </is>
+      </c>
+      <c r="Q114" s="3" t="inlineStr">
+        <is>
+          <t>Local-borough AEO: own Wandsworth/Fulham survey queries</t>
+        </is>
+      </c>
+      <c r="R114" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S114" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Tayross Associates</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Chartered building surveyors</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>West London</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tayross.com</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>carl@tayross.com</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>020 8426 1448</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Carl (Principal)</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>RICS/CIOB consultancy - surveys, party wall, disputes; direct principal email</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P115" s="4" t="inlineStr">
+        <is>
+          <t>Small firm invisible next to bigger survey brands</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="inlineStr">
+        <is>
+          <t>Niche content: boundary disputes + EWS1 as AEO wedges</t>
+        </is>
+      </c>
+      <c r="R115" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S115" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>MGN Events</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Event management agency</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>London &amp; Surrey</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mgnevents.co.uk</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning creative agency for corporate + private events worth £20-200k each</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>Awards; polished site</t>
+        </is>
+      </c>
+      <c r="P116" s="4" t="inlineStr">
+        <is>
+          <t>Agency discovery moving to AI shortlists; referral-dependent</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>'CMOs ask ChatGPT for event agency shortlists - get on them'</t>
+        </is>
+      </c>
+      <c r="R116" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S116" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Eventify</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Event management agency</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eventifyuk.com</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Independent venue-finding + events agency; explicitly unbiased positioning = good content angle</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="inlineStr">
+        <is>
+          <t>Venue-finding is being eaten by AI directly - must become the cited source</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="inlineStr">
+        <is>
+          <t>Position as the transparent venue-data source AI engines cite</t>
+        </is>
+      </c>
+      <c r="R117" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S117" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Bristol Osteopaths</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Osteopathy clinics</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>3 sites: Wells Rd, Queen Charlotte St, Sneyd Park Bristol</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>https://bristolosteopaths.com</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>wellsroad@bristolosteopaths.com</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>0117 971 0221</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>Three-site osteopathy group; multi-decade presence; self-pay treatment courses</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>Three locations but one weak web presence; physios and chiros take the same back-pain searches</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>Per-site local SEO: 3 clinics should own 3 catchments</t>
+        </is>
+      </c>
+      <c r="R118" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S118" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Chandos Clinic Osteopaths</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>https://chandosclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>0117 974 5084</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>Established holistic clinic in Bristol; loyal patient base</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P119" s="4" t="inlineStr">
+        <is>
+          <t>Same local-visibility battle as peers</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="inlineStr">
+        <is>
+          <t>Quick-win local SEO + reviews</t>
+        </is>
+      </c>
+      <c r="R119" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S119" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Bath Spa Dentistry</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>James St West, Bath</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bathspadentistry.com</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>reception@bathspadentistry.com</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>01225 464346</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>Multi-award-winning private practice in Bath; cosmetic + implant work at Bath prices</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>Award wins promoted on site</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>Awards don't show up in AI answers; Bristol clinics pull Bath patients</t>
+        </is>
+      </c>
+      <c r="Q120" s="3" t="inlineStr">
+        <is>
+          <t>'Multi-award-winning should mean AI-recommended - let's close that gap'</t>
+        </is>
+      </c>
+      <c r="R120" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S120" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Edgar Buildings Dental &amp; Implant Clinic</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Edgar Buildings, Bath</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.smileofconfidence.com</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>Implant-focused practice in prestige George St address; £3-10k cases</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>Implant searches in Bath poorly contested - winnable</t>
+        </is>
+      </c>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>'Own "dental implants Bath" before anyone else wakes up'</t>
+        </is>
+      </c>
+      <c r="R121" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S121" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Widcombe Dental Practice</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Widcombe, Bath</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>https://widcombedentalpractice.co.uk</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>01225 317 681</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>Neighbourhood private practice in affluent Widcombe</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr">
+        <is>
+          <t>Village practice with village-scale visibility</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>Entry-tier local SEO package</t>
+        </is>
+      </c>
+      <c r="R122" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S122" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Hogs Back Builders</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Design &amp; build</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hogsbackbuilders.co.uk</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr"/>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="4" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>Bespoke design &amp; build across Surrey/Hampshire borders; project values £100k+</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P123" s="4" t="inlineStr">
+        <is>
+          <t>Checkatrade/MyBuilder soak up Surrey extension searches</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="inlineStr">
+        <is>
+          <t>'One Guildford extension pays for 30 years of our fee'</t>
+        </is>
+      </c>
+      <c r="R123" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S123" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Hills Build &amp; Design</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Design &amp; build</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Guildford &amp; Godalming, Surrey</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>http://www.surreyhillsbuild.co.uk</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Trevor Steyne (MD)</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>MD with 30+ years craft background; affluent Surrey Hills catchment</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P124" s="4" t="inlineStr">
+        <is>
+          <t>Dated site undersells premium work</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>Site modernisation + local SEO bundle</t>
+        </is>
+      </c>
+      <c r="R124" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S124" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Godman Construction</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Builders / renovations</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>https://godmanconstruction.co.uk</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>info@godmanconstruction.co.uk</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>01483 494 651</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>Renovations, extensions and new builds across Surrey; already publishing location blog content</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>Location blog posts = DIY SEO</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>DIY content lacks authority to rank</t>
+        </is>
+      </c>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>'You're writing the right pages - let's make them win'</t>
+        </is>
+      </c>
+      <c r="R125" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S125" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>CMD Recruitment</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Recruitment agency</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Bath (+ Wiltshire offices)</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>https://cmdrecruitment.com</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Bath@cmdrecruitment.com</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>01225 800000</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>Independent multi-office agency since 2004; permanent/interim placements across Bath/Wiltshire</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>Multi-office landing pages</t>
+        </is>
+      </c>
+      <c r="P126" s="4" t="inlineStr">
+        <is>
+          <t>Reed/Indeed and nationals dominate; local independent invisible in AI answers</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>'Bath employers ask AI for local recruiters - the answer is Reed. Fix that'</t>
+        </is>
+      </c>
+      <c r="R126" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S126" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Juice Recruitment</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Recruitment agency</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Bath &amp; South West</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>https://juicerecruitment.com</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr"/>
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>Established SW independent with Bath specialism and location landing pages</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>Location landing pages</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>Same national-brand squeeze</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>AEO layer on existing location-page strategy</t>
+        </is>
+      </c>
+      <c r="R127" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S127" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Marmalade Schools</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Private nursery schools</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Fulham, Wandsworth Common &amp; Clapham South, London</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.marmaladeschools.co.uk</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Rozzy Roberts (Founder)</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>Three-site independent nursery group founded by former teacher; nursery fees £15k+/year in SW London</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>Press mentions (Sotheby's journal, My Baba lists)</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>Parents shortlist via AI + listicles; corporate groups (Grandir, Dukes) spend big</t>
+        </is>
+      </c>
+      <c r="Q128" s="3" t="inlineStr">
+        <is>
+          <t>'SW London parents ask ChatGPT for nursery shortlists - be on all of them'</t>
+        </is>
+      </c>
+      <c r="R128" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S128" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Parsons Green Nursery</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Private day nursery</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Fulham Road, London SW6</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>https://parsonsgreennursery.com</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>admissions@parsonsgreennursery.com</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>020 3943 4678</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>Ofsted Outstanding nursery in prime SW6; waitlist-driven but competition for premium families is fierce</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>Ofsted Outstanding badge</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>Outstanding rating under-marketed; chains outrank them</t>
+        </is>
+      </c>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>'Outstanding-rated should be the first answer parents get - it isn't'</t>
+        </is>
+      </c>
+      <c r="R129" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S129" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T129" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T101"/>
+  <autoFilter ref="A1:T129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9420,7 +11740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9440,7 +11760,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -9457,13 +11777,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -9473,37 +11793,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -9513,7 +11833,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -9523,7 +11843,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -9533,7 +11853,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -9543,7 +11863,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -9553,11 +11873,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -9593,7 +11913,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -9603,7 +11923,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -9613,7 +11933,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -9623,7 +11943,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -9633,7 +11953,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -9643,7 +11963,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -9653,7 +11973,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -9663,7 +11983,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -9673,67 +11993,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -9743,7 +12063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -9753,7 +12073,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -9763,7 +12083,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -9773,7 +12093,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -9783,7 +12103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -9793,7 +12113,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -9803,7 +12123,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -9813,7 +12133,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -9823,7 +12143,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -9833,7 +12153,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -9843,7 +12163,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -9853,7 +12173,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -9863,7 +12183,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -9873,7 +12193,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -9883,7 +12203,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -9893,7 +12213,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -9903,7 +12223,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -9913,7 +12233,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -9923,7 +12243,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -9933,7 +12253,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -9943,7 +12263,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -9953,7 +12273,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -9963,7 +12283,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -9973,7 +12293,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -9983,7 +12303,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -9993,7 +12313,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -10003,7 +12323,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -10013,7 +12333,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -10023,7 +12343,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -10033,7 +12353,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -10043,7 +12363,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -10053,7 +12373,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -10063,7 +12383,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -10073,7 +12393,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -10083,10 +12403,170 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Physiotherapy (sports)</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Letting agent / property management</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Skin clinic</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tutoring company</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Employment law (disability discrimination)</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sports physio &amp; massage</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chartered surveyors (party wall/building)</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chartered surveyors</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chartered building surveyors</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Osteopathy clinics</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Builders / renovations</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Private nursery schools</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Private day nursery</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T129"/>
+  <dimension ref="A1:T160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11728,8 +11728,2636 @@
       </c>
       <c r="T129" s="3" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Associates</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Montpellier Exchange, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.morgan-associates.co.uk</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>01242 354692</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>Independent agency in prestige Montpellier address covering Cheltenham/Cotswolds; premium instructions worth thousands in fees</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>Portal listings</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>Fine &amp; Country/Knight Frank corporate brands dominate Cheltenham premium search</t>
+        </is>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>'Montpellier sellers shortlist online before calling - be on that shortlist'</t>
+        </is>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S130" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Beyond Dental Cheltenham</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Rodney Road, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>https://beyond-dental.co.uk/cheltenham</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>01296 730260</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr"/>
+      <c r="H131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>Luxury private dental brand with multi-location model; implants/Invisalign cases £3-6k in wealthy Cheltenham</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>Multi-location brand site</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>Local Cheltenham searches split with Cheltenham &amp; Cotswold Dental, Pittville Lawn - AEO could tip the balance</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>'Own the AI answer for "Invisalign Cheltenham" before your closest rival does'</t>
+        </is>
+      </c>
+      <c r="R131" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S131" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham &amp; Cotswold Dental</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>https://cheltenhamandcotswolddental.com</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>01242 269 498</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Dr Imran Nasser &amp; Dr Samantha Stewart (Principals)</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning practice with named principals; also runs facial aesthetics arm = two revenue lines</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>Facial aesthetics cross-sell page; awards</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>Two service lines (dental + aesthetics) competing for the same searches without a unified strategy</t>
+        </is>
+      </c>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>Consolidate dental + aesthetics AEO under one authority-building plan</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S132" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>JCP Estate Agents</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Oxford (Jericho/Summertown/Marston/East Oxford)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jamescpenny.co.uk</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning independent covering 'Prime Central Oxford' across 4 postcodes; academic-city premium market</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>Award mentions</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>Breckon &amp; Breckon and scottfraser also fight for the same Oxford postcodes</t>
+        </is>
+      </c>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>'Oxford buyers/sellers now ask AI which agent knows Jericho best - claim it'</t>
+        </is>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S133" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Breckon &amp; Breckon</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Summertown, North Oxford</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.breckon.co.uk</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr"/>
+      <c r="G134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1947 covering Summertown/Wolvercote/Jericho; heritage brand with high-value North Oxford stock</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>Long-established brand</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>80 years of trust doesn't automatically appear in AI search answers</t>
+        </is>
+      </c>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>Turn 'established 1947' into the AI-cited trust signal for North Oxford</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S134" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Otus Mortgages</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Mortgage broker</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Oxford &amp; Warwick</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>https://otusoxford.co.uk</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>hello@otus.uk.com</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>Neil Yeoman (Director)</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>Independent whole-of-market broker; Oxford's academic/professional buyers = high-value cases</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M135" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>Two-site brand (Oxford/Warwick)</t>
+        </is>
+      </c>
+      <c r="P135" s="4" t="inlineStr">
+        <is>
+          <t>Oxford Mortgages and Bright Money compete for the same 'mortgage broker Oxford' searches</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="inlineStr">
+        <is>
+          <t>Own the local-intent long tail before the other Oxford brokers do</t>
+        </is>
+      </c>
+      <c r="R135" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S135" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Linbury Doctors</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Private GP (membership model)</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Cotswolds/Oxfordshire/Gloucestershire (Broadway HQ)</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linburydoctors.co.uk</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>0333 050 7338</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Dr Hala &amp; Dr Lucy (Medical Directors)</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>Membership-based private GP covering 6 counties; recurring membership fees = high LTV per patient</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>Multi-county location pages</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>Membership model needs constant new-patient acquisition across a huge rural catchment</t>
+        </is>
+      </c>
+      <c r="Q136" s="3" t="inlineStr">
+        <is>
+          <t>'Cotswold families ask AI for a private GP - be the membership they find first'</t>
+        </is>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S136" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>The Guildford Vet</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Worplesdon Road, Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theguildfordvet.co.uk</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>info@theguildfordvet.co.uk</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>01483 610292</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Rob, Amber, Chris &amp; Lucy (Founders); Christian Gray (Director)</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/theguildfordvet</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>Founded 2022, proudly independent in affluent Guildford; 24/7 emergency = highest-intent local searches</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>Corporate vet groups (IVC, CVS) dominate Surrey vet searches with huge budgets</t>
+        </is>
+      </c>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>'New, independent, and invisible on Google - let's fix that before the chains notice'</t>
+        </is>
+      </c>
+      <c r="R137" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S137" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>The Cape Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>https://capevets.co.uk</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>Douglas Hall (Owner)</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Family-run independent, increasingly rare model in Surrey; loyal client base</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr">
+        <is>
+          <t>Independence story under-leveraged vs corporate-owned rivals</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>Independence-as-differentiator AEO content</t>
+        </is>
+      </c>
+      <c r="R138" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S138" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Cotswold Face &amp; Body Clinic</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>https://cotswoldfabclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>Luxury clinic with Harley Street surgeon association; high-ticket surgical-adjacent consultations</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>Harley St association promoted</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>Association with prestige name not translating into local/AI search dominance</t>
+        </is>
+      </c>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>Turn the Harley Street link into the AI-cited authority signal for Cotswold aesthetics</t>
+        </is>
+      </c>
+      <c r="R139" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S139" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Iris Medical Aesthetics</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.irismedicalaesthetics.com</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+      <c r="G140" s="4" t="inlineStr"/>
+      <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" s="4" t="inlineStr"/>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>Discreet boutique clinic in central Cheltenham; repeat injectable clients</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P140" s="4" t="inlineStr">
+        <is>
+          <t>Generic positioning in a market with several named-doctor rivals</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>Local + AEO package to compete with named-practitioner clinics</t>
+        </is>
+      </c>
+      <c r="R140" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S140" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Ashleigh Clarke Architects</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Upper Rissington, Cheltenham/Cotswolds</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>https://ashleighclarkearchitects.com</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>info@ashleighclarkearchitects.com</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>01451 828 419</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Ashleigh Clarke (Founder &amp; Lead Architect)</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>RIBA/ARB residential practice across the Cotswolds; project values £100k+; named founder with direct email</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>RIBA directory listing</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>Cotswold second-home owners search nationally; local firm needs to compete with London-based rivals</t>
+        </is>
+      </c>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>'Cotswold clients ask AI for a local architect who knows the planning rules - be that answer'</t>
+        </is>
+      </c>
+      <c r="R141" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S141" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Lewis Critchley Architects</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Tewkesbury/Cheltenham, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>https://lewiscritchleyarchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>lmc@lewiscritchleyarchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>01684 295473</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Lewis Critchley (Founder)</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>RIBA chartered, established 2019; direct founder email; growing Cotswolds residential practice</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>Professional site</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>Young practice needs to build authority fast against established Cotswold firms</t>
+        </is>
+      </c>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>Ground-floor local SEO + AEO while building reputation</t>
+        </is>
+      </c>
+      <c r="R142" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S142" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Gray Architecture</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham/Cotswolds</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>https://grayarchitecture.co.uk</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>info@grayarchitecture.co.uk</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>07855 348 625</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Chris Gray (Founder)</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr"/>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>Established 2021, 15+ years experience; solo-led practice with direct founder contact</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P143" s="4" t="inlineStr">
+        <is>
+          <t>New practice with minimal search visibility</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="inlineStr">
+        <is>
+          <t>Entry package: build local authority from a clean slate</t>
+        </is>
+      </c>
+      <c r="R143" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S143" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Hawkes &amp; Son</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Sash window restoration</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Melksham (serves Bath)</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>http://www.hawkes-sash.co.uk</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@hawkes-sash.co.uk</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>01225 791229</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Michael Hawkes (Founder)</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>Heritage-joinery specialist for Bath's Georgian housing stock; restoration jobs £3-10k; highly defensible niche</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>Dated site undersells a genuinely rare, high-value heritage-trade skill</t>
+        </is>
+      </c>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>'Own "sash window restoration Bath" - a high-value niche almost nobody optimises for'</t>
+        </is>
+      </c>
+      <c r="R144" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S144" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Clifton IT</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>IT support / MSP</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Whiteladies Rd, Bristol</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cliftonit.co.uk</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>info@cliftonit.co.uk</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>01179 595143</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>MSP serving Bristol/Bath/Exeter/Plymouth SMEs; recurring monthly contracts = high LTV per client</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>Multi-region service pages</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>SMEs searching for IT support see nationals (Solutions4IT etc.) first</t>
+        </is>
+      </c>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>'When a Bristol business Googles "IT support near me" at 9am on a bad day - be the answer'</t>
+        </is>
+      </c>
+      <c r="R145" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S145" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Three Cherries</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>IT support / MSP</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.threecherries.co.uk</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="inlineStr"/>
+      <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>Independent MSP since 1999 - one of the longest-standing in the region; SME contracts are sticky and high-value</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>25+ years trading</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>Longevity doesn't automatically win modern local/AI search</t>
+        </is>
+      </c>
+      <c r="Q146" s="3" t="inlineStr">
+        <is>
+          <t>'25 years of Bristol IT trust - let's make sure Google and AI both know it'</t>
+        </is>
+      </c>
+      <c r="R146" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S146" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Alchemy 16</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Personal training studio</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Imperial Square, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alchemy16.com</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Patrick (Founder)</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>Bespoke luxury 1:1 studio in a Grade II* listed building overlooking Imperial Gardens; premium ongoing PT packages</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>Polished brand/site</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>Boutique studio invisible next to gym chains in 'personal trainer Cheltenham' searches</t>
+        </is>
+      </c>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>'Cheltenham's most exclusive PT studio should be Cheltenham's top AI answer'</t>
+        </is>
+      </c>
+      <c r="R147" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S147" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Rob Ingram Fitness</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Personal training (1:1)</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.robingramfitness.com</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>Rob Ingram (Founder)</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr"/>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham's only dedicated 1:1 PT gym - strong differentiation story; high per-client value from ongoing sessions</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="inlineStr">
+        <is>
+          <t>'Only 1:1 gym in Cheltenham' claim isn't surfaced in local search</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="inlineStr">
+        <is>
+          <t>Own the 'private personal trainer Cheltenham' niche outright</t>
+        </is>
+      </c>
+      <c r="R148" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S148" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Infinite Balance</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Personal training &amp; nutrition coaching</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Hatherley, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>https://infinitebalance.co.uk</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>kirsty@infinitebalance.co.uk</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Kirsty Ellson (Founder)</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Solo-led PT + nutrition coaching; ongoing client relationships worth £150-300/month each</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P149" s="4" t="inlineStr">
+        <is>
+          <t>Solo practitioner competing with studio brands for visibility</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="inlineStr">
+        <is>
+          <t>Entry-tier local SEO to build a client base efficiently</t>
+        </is>
+      </c>
+      <c r="R149" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S149" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>The Avenue Pre-Prep &amp; Nursery</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Private nursery/pre-prep school</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Highgate, London N6</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>https://avenuepreprep.co.uk</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>020 8348 6815</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>Independent pre-prep serving Highgate/Hampstead/Muswell Hill; fees £15-20k/year, waitlist-driven demand</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>Established local reputation</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>Competing with Channing, Highgate Junior School feeder nurseries for the same wealthy families</t>
+        </is>
+      </c>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>'Highgate parents research nurseries on Google before they call - be the first result'</t>
+        </is>
+      </c>
+      <c r="R150" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S150" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>The Gower School</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Independent nursery (Montessori)</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Islington, North London</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thegowerschool.co.uk</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="4" t="inlineStr"/>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>Montessori nursery serving Islington/Angel/Camden/Highbury; premium early-years fees</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M151" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="inlineStr">
+        <is>
+          <t>Montessori niche under-marketed vs bigger nursery chains</t>
+        </is>
+      </c>
+      <c r="Q151" s="4" t="inlineStr">
+        <is>
+          <t>Own 'Montessori nursery Islington' AEO content</t>
+        </is>
+      </c>
+      <c r="R151" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S151" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Independent People Homecare</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Live-in care agency</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Guildford (serves Surrey/Oxfordshire)</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>via Oxfordshire family info service listing</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>0330 053 5014</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>Live-in care across two wealthy counties; clients worth £50-80k/year each</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>Council directory listing</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>Bigger national brands (Agincare, Helping Hands) dominate the same searches</t>
+        </is>
+      </c>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>'One live-in care client is worth £60k/year - and families are asking AI, not just Google'</t>
+        </is>
+      </c>
+      <c r="R152" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S152" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T152" s="3" t="inlineStr">
+        <is>
+          <t>Confirm website URL before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Solton Manor</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>East Langdon, Dover, Kent</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.soltonmanor.com</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>info@soltonmanor.com</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>01304 448 844</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr"/>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>Grade II listed 9-acre manor/barn venue in Kent; weddings worth £15-30k each</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>Multiple directory listings (Guides for Brides, Bridebook, Married in Kent)</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>Heavy directory dependence; couples increasingly ask AI for shortlists directly</t>
+        </is>
+      </c>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>'Reduce commission paid to wedding directories - own the AI-recommended shortlist instead'</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S153" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>The Oak Barn, Frame Farm</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Kent/Sussex border</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.the-oak-barn.co.uk</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>The Maw family (Owners)</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>Family-run barn venue in AONB; personalised-service positioning; high per-booking value</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>Directory listings</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>Family-run charm doesn't show up in generic 'barn wedding venue Kent' searches</t>
+        </is>
+      </c>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>'Your family story is the differentiator - make it the AI-cited one'</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S154" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Rivervale Barn</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Yateley, Hampshire</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rivervalebarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr"/>
+      <c r="G155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>Riverside barn venue in Hampshire; multiple barn options = flexible high-value bookings</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>Directory listings</t>
+        </is>
+      </c>
+      <c r="P155" s="4" t="inlineStr">
+        <is>
+          <t>Hampshire wedding-venue searches split across many similar barn venues</t>
+        </is>
+      </c>
+      <c r="Q155" s="4" t="inlineStr">
+        <is>
+          <t>Differentiate via riverside setting in AEO content</t>
+        </is>
+      </c>
+      <c r="R155" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S155" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T155" s="4" t="inlineStr">
+        <is>
+          <t>Verify site URL and contact before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Watkins Solicitors</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing/family)</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Bristol, Bath, Hereford, Evesham</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.watkinssolicitors.co.uk</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>info@watkinssolicitors.co.uk</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>Multi-office regional independent; conveyancing volume + family law = steady high-value pipeline</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>Multi-office site</t>
+        </is>
+      </c>
+      <c r="P156" s="4" t="inlineStr">
+        <is>
+          <t>Comparison sites (Compare My Move) intercept conveyancing searches before firms are found</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr">
+        <is>
+          <t>Local-office AEO: own 'conveyancing solicitor Bath' per branch</t>
+        </is>
+      </c>
+      <c r="R156" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S156" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T156" s="4" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Battrick Clark Solicitors</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Law firm</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Whiteladies Rd, Clifton, Bristol</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.battrickclark.co.uk</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>info@battrickclark.co.uk</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>0117 973 1391</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr"/>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>Established 1997, full-service firm on Bristol's professional strip; conveyancing + family + private client</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M157" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>Established brand</t>
+        </is>
+      </c>
+      <c r="P157" s="4" t="inlineStr">
+        <is>
+          <t>Generalist positioning competes with both boutiques and volume conveyancers</t>
+        </is>
+      </c>
+      <c r="Q157" s="4" t="inlineStr">
+        <is>
+          <t>Pick one high-value practice area to own in AI answers first</t>
+        </is>
+      </c>
+      <c r="R157" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S157" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T157" s="4" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Danielle Cohen Immigration Law Solicitors</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Immigration law firm</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Camden, London NW1</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>https://daniellecohenimmigration.com</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>danielle.cohen@daniellecohen.co.uk</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>020 7267 4133</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>Danielle Cohen (Founder)</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/daniellecohensolicitors</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>20+ year specialist niche firm; visa/immigration cases worth £2-10k in fees; founder name = brand</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
+          <t>YouTube channel; Facebook page - content-aware</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>Content exists but AI engines cite bigger immigration brands (IAS, Migrate) for generic queries</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>Turn founder's 20-year expertise into the AI-cited answer for complex visa questions</t>
+        </is>
+      </c>
+      <c r="R158" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S158" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Garth Coates Solicitors</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Immigration law firm</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Holborn, London WC1</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>https://garthcoates.com</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>020 7799 1600</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Garth Coates (Founder)</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/garthcoatessol</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>Est. 2008 boutique immigration specialist; high-value work visa and citizenship cases</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>Generic 'immigration solicitor London' searches won by volume firms with bigger ad spend</t>
+        </is>
+      </c>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>AEO for specific high-value queries (Innovator visa, Global Talent) where boutiques can win</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S159" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa Ganguin Immigration Law</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Immigration law firm</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>https://vanessaganguin.com</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr"/>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa Ganguin (Founder)</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>Partner-led boutique with decades of experience; multi-city presence (also lists Bristol)</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>Multi-city professional site</t>
+        </is>
+      </c>
+      <c r="P160" s="4" t="inlineStr">
+        <is>
+          <t>Boutique quality buried under bigger firms' search spend</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>Position as the boutique alternative in AI-generated shortlists</t>
+        </is>
+      </c>
+      <c r="R160" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S160" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T160" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T129"/>
+  <autoFilter ref="A1:T160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11740,7 +14368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11760,7 +14388,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
@@ -11777,7 +14405,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -11787,93 +14415,93 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -11883,57 +14511,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -11943,7 +14571,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -11953,7 +14581,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -11963,7 +14591,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -11973,7 +14601,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -11983,7 +14611,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -11993,7 +14621,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -12003,7 +14631,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -12013,7 +14641,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -12023,7 +14651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -12033,7 +14661,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -12043,7 +14671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -12053,27 +14681,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -12083,7 +14711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -12093,7 +14721,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -12103,7 +14731,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -12113,7 +14741,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -12123,7 +14751,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -12133,7 +14761,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -12143,7 +14771,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -12153,7 +14781,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -12163,7 +14791,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -12173,7 +14801,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -12183,7 +14811,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -12193,7 +14821,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -12203,7 +14831,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -12213,7 +14841,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -12223,7 +14851,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -12233,7 +14861,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -12243,7 +14871,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -12253,7 +14881,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -12263,7 +14891,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -12273,7 +14901,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -12283,7 +14911,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -12293,7 +14921,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -12303,7 +14931,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -12313,7 +14941,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -12323,7 +14951,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -12333,7 +14961,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -12343,7 +14971,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -12353,7 +14981,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -12363,7 +14991,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -12373,7 +15001,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -12383,7 +15011,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -12393,7 +15021,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -12403,7 +15031,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12413,7 +15041,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12423,7 +15051,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12433,7 +15061,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12443,7 +15071,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12453,7 +15081,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -12463,7 +15091,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -12473,7 +15101,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -12483,7 +15111,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -12493,7 +15121,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -12503,7 +15131,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -12513,7 +15141,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -12523,7 +15151,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -12533,7 +15161,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -12543,7 +15171,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -12553,7 +15181,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -12563,10 +15191,110 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Builders / renovations</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Private nursery schools</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Private day nursery</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Private GP (membership model)</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sash window restoration</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Personal training (1:1)</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Personal training &amp; nutrition coaching</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Private nursery/pre-prep school</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Independent nursery (Montessori)</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Live-in care agency</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing/family)</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T160"/>
+  <dimension ref="A1:T175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14356,8 +14356,1292 @@
       </c>
       <c r="T160" s="4" t="inlineStr"/>
     </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Philip Booth Esq</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Henley-on-Thames &amp; Marlow</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.philipboothesq.com</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr"/>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>Phil Booth (Director, 37+ yrs experience)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/PhilipBoothesq</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>Leading independent across two of the Thames Valley's wealthiest towns; premium riverside/village property fees</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>Ballards and Stowhill compete for the same Henley/Marlow searches</t>
+        </is>
+      </c>
+      <c r="Q161" s="3" t="inlineStr">
+        <is>
+          <t>'Henley sellers ask AI who knows the river towns best - be that answer'</t>
+        </is>
+      </c>
+      <c r="R161" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S161" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Ballards Estate Agents</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Henley-on-Thames, Marlow, Twyford</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>https://ballards-uk.com</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>nicky@ballards-uk.com</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>01491 411 055</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>Chris (Founder, opened 1990)</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned since 1990, award-winning, three-office Thames Valley coverage; instructions worth thousands each</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
+          <t>Award mentions; multi-office presence</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>Three offices but fragmented digital visibility vs single-minded corporate rivals</t>
+        </is>
+      </c>
+      <c r="Q162" s="3" t="inlineStr">
+        <is>
+          <t>Per-office local SEO + unified AEO strategy across all three towns</t>
+        </is>
+      </c>
+      <c r="R162" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S162" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Stowhill Estates Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent (premium)</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Marlow, South Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>https://stowhillbucks.co.uk</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr"/>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>David &amp; Sara (Founders, husband &amp; wife)</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>Boutique premium-only agency in one of the UK's wealthiest commuter belts; explicit premium positioning</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
+          <t>Premium brand positioning</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>Niche premium focus not yet AI-search dominant vs bigger names</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="inlineStr">
+        <is>
+          <t>'Premium-only' as the AEO hook: own that exact positioning in AI answers</t>
+        </is>
+      </c>
+      <c r="R163" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S163" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Comber &amp; Company</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Blackheath Village, London SE3</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.comberandco.co.uk</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>020 3641 5310</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Comber (Founder, since 1993)</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>Independent family firm in affluent Blackheath Village since 1993; sales+lettings+surveying under one roof</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>30+ years reputation</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>Winkworth/FJLord/Truepenny's all fight for the same Blackheath searches</t>
+        </is>
+      </c>
+      <c r="Q164" s="3" t="inlineStr">
+        <is>
+          <t>'32 years in Blackheath Village - make Google and ChatGPT say so too'</t>
+        </is>
+      </c>
+      <c r="R164" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S164" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Rigby &amp; Marchant</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Notting Hill, London W10/W11</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>https://rigbyandmarchant.co.uk</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>sales@rigbyandmarchant.co.uk</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>020 7221 7210</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Keith Rigby, Matt Marchant &amp; Fraser Clark (Founders, 1996)</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1996 in one of London's priciest postcodes; instructions worth substantial fees each</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
+          <t>Established local brand</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>Domus Nova and corporate giants (Knight Frank, Marsh &amp; Parsons) dominate W11 search</t>
+        </is>
+      </c>
+      <c r="Q165" s="3" t="inlineStr">
+        <is>
+          <t>'Notting Hill sellers now ask AI, not just Rightmove - own that answer'</t>
+        </is>
+      </c>
+      <c r="R165" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S165" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>St Cuthbert's Dental Surgery</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Newburgh St, Winchester, Hampshire</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.stcuthbertsdentalsurgery.co.uk</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>info@stcuthbertsdentalsurgery.co.uk</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>01962 853135</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/StCuthbertsDentalSurgery</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>Private practice in Winchester city centre; senior team with long tenure; affluent cathedral-city catchment</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>Facebook page</t>
+        </is>
+      </c>
+      <c r="P166" s="4" t="inlineStr">
+        <is>
+          <t>Bupa and newer clinics (Solutions Dental) outspend on Winchester dental search</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>'Winchester patients ask AI for a dentist near the cathedral - be the answer'</t>
+        </is>
+      </c>
+      <c r="R166" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S166" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Solutions Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Winchester, Hampshire</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.solutionsdentalclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>01962 864 655</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>Implant-focused private clinic in Winchester; £3-10k implant cases in a wealthy cathedral city</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated implants landing page</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>Implant searches contested locally but AI-answer visibility still open</t>
+        </is>
+      </c>
+      <c r="Q167" s="3" t="inlineStr">
+        <is>
+          <t>'Own "dental implants Winchester" - a high-value niche with room at the top'</t>
+        </is>
+      </c>
+      <c r="R167" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S167" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>YK Design</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Architect &amp; interior designer</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Henley-on-Thames</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ykdesign.co.uk</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Yasemin Kirkpatrick (Founder, RIBA, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/yasemin-kirkpatrick-93533369</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>20-year practice combining architecture + interiors for Thames Valley homes; project values £100k-1m+</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
+          <t>Professional portfolio site</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>Combined architecture+interiors offering underexploited in local AI search</t>
+        </is>
+      </c>
+      <c r="Q168" s="3" t="inlineStr">
+        <is>
+          <t>'One Henley client is worth years of our fee - be the AI's Henley architect'</t>
+        </is>
+      </c>
+      <c r="R168" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S168" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Trace Architects</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>London &amp; Henley-on-Thames</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>https://tracearchitects.format.com</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Giles Lovegrove &amp; Kristian Rapallini (Founders)</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>Two-studio practice (London + Henley) for high-end residential; decades of combined experience at leading firms</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>Portfolio site referencing prior firm pedigree</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>Pedigree from previous firms not yet built into their own AI-search authority</t>
+        </is>
+      </c>
+      <c r="Q169" s="3" t="inlineStr">
+        <is>
+          <t>Turn founders' prior-firm credentials into the new practice's AEO content</t>
+        </is>
+      </c>
+      <c r="R169" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S169" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Francis Associates</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Architects / project management</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Medmenham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.francis-associates.co.uk</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr"/>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Julian Francis FRICS (Founder, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>Established 1988, RICS-qualified; project management + architecture for Thames Valley estates</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P170" s="4" t="inlineStr">
+        <is>
+          <t>37 years of trust not converted into digital-era search visibility</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr">
+        <is>
+          <t>Heritage-into-authority AEO play for high-value estate projects</t>
+        </is>
+      </c>
+      <c r="R170" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S170" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T170" s="4" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Austyn Smith Associates</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>IFA / wealth management</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Henley-on-Thames, Beaconsfield, High Wycombe, Marlow</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>https://austynsmith.com</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>info@austynsmith.com</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>01494 578 100</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>Austyn (Founder, 25+ years)</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>25-year independent IFA across 4 wealthy Bucks/Oxon towns; already builds per-town landing pages</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O171" s="3" t="inlineStr">
+        <is>
+          <t>Per-town SEO landing pages = active investment</t>
+        </is>
+      </c>
+      <c r="P171" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist across 4 towns but none dominate AI answers yet</t>
+        </is>
+      </c>
+      <c r="Q171" s="3" t="inlineStr">
+        <is>
+          <t>AEO layer across all 4 existing town pages - multiply an existing strategy</t>
+        </is>
+      </c>
+      <c r="R171" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S171" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>The Guildford Private General Practice</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Central Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thegpgp.co.uk</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@thegpgp.co.uk</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>01483 826367</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>Dr Selby, Dr Ballance, Dr Hendley (Partners)</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/thegpgp</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>Established 2013, three named GP partners with 15-20 years' experience each; self-pay consultations in wealthy Guildford</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O172" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>Circle Health/Mount Alvernia hospital brand competes for the same Guildford private-GP searches</t>
+        </is>
+      </c>
+      <c r="Q172" s="3" t="inlineStr">
+        <is>
+          <t>'Guildford professionals ask AI for a private GP - beat the hospital brand to the answer'</t>
+        </is>
+      </c>
+      <c r="R172" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S172" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Manor Farm Barn (Tythe)</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Bicester, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.manorfarmtythebarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr"/>
+      <c r="G173" s="3" t="inlineStr"/>
+      <c r="H173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>16th-century barn venue near Bicester; Oxfordshire weddings worth £15-25k each</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated wedding microsite</t>
+        </is>
+      </c>
+      <c r="P173" s="3" t="inlineStr">
+        <is>
+          <t>Directory-dependent discovery same as other venues in the database</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr">
+        <is>
+          <t>'Own the AI-recommended shortlist for Oxfordshire barn weddings'</t>
+        </is>
+      </c>
+      <c r="R173" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S173" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Dovecote Events</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Rural Oxfordshire (Cotswolds edge)</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dovecoteevents.uk</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr"/>
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr"/>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>Grade II listed barn on the Cotswolds/Oxfordshire border; exclusive-use bookings</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M174" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P174" s="4" t="inlineStr">
+        <is>
+          <t>Listed-building charm undersold in generic wedding-venue search</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr">
+        <is>
+          <t>Grade II heritage story as AEO differentiator</t>
+        </is>
+      </c>
+      <c r="R174" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S174" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T174" s="4" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Cornwell Manor</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Chipping Norton, Oxfordshire/Gloucestershire border</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>https://cornwellmanor.com</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr"/>
+      <c r="G175" s="3" t="inlineStr"/>
+      <c r="H175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>2,000-acre estate venue; ultra-premium Cotswolds weddings worth £30k+</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>Polished estate branding</t>
+        </is>
+      </c>
+      <c r="P175" s="3" t="inlineStr">
+        <is>
+          <t>Ultra-premium positioning needs to win the highest-value AI-search queries specifically</t>
+        </is>
+      </c>
+      <c r="Q175" s="3" t="inlineStr">
+        <is>
+          <t>Target 'luxury Cotswolds wedding venue' AEO exclusively - don't compete on volume terms</t>
+        </is>
+      </c>
+      <c r="R175" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S175" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T175" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T160"/>
+  <autoFilter ref="A1:T175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14368,7 +15652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14388,7 +15672,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5">
@@ -14405,43 +15689,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -14491,7 +15775,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -14501,17 +15785,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -14521,7 +15805,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -14641,7 +15925,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -14651,7 +15935,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -14661,7 +15945,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -14671,7 +15955,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -14681,7 +15965,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -14691,7 +15975,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -14701,27 +15985,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -14731,7 +16015,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -14741,7 +16025,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -14751,7 +16035,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -14761,7 +16045,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -14771,7 +16055,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -14781,7 +16065,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -14791,7 +16075,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -14801,7 +16085,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -14811,7 +16095,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -14821,7 +16105,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -14831,7 +16115,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -14841,7 +16125,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -14851,7 +16135,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -14861,7 +16145,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -14871,7 +16155,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -14881,7 +16165,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -14891,7 +16175,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -14901,7 +16185,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -14911,7 +16195,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -14921,7 +16205,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -14931,7 +16215,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -14941,7 +16225,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -14951,7 +16235,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -14961,7 +16245,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -14971,7 +16255,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -14981,7 +16265,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -14991,7 +16275,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -15001,7 +16285,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -15011,7 +16295,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -15021,7 +16305,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -15031,7 +16315,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -15041,7 +16325,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -15051,7 +16335,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -15061,7 +16345,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -15071,7 +16355,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -15081,7 +16365,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -15091,7 +16375,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -15101,7 +16385,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -15111,7 +16395,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -15121,7 +16405,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -15131,7 +16415,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -15141,7 +16425,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -15151,7 +16435,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -15161,7 +16445,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -15171,7 +16455,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -15181,7 +16465,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -15295,6 +16579,36 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Architect &amp; interior designer</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Architects / project management</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>IFA / wealth management</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T175"/>
+  <dimension ref="A1:T187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15640,8 +15640,1036 @@
       </c>
       <c r="T175" s="3" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Kings Estates</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kings-estates.co.uk</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>01892 533367</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>Mike Heath (lettings) &amp; Gemma Collins (sales) - siblings, since 1985</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>Owner-led independent since 1985; sibling founders handle every client personally; premium marketing for Tunbridge Wells/Kent/Sussex homes</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
+          <t>Area-guide content pages (Tunbridge Wells guide) = active SEO effort</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>Content exists but competes with Savills/Hamptons/Fine &amp; Country's bigger budgets</t>
+        </is>
+      </c>
+      <c r="Q176" s="3" t="inlineStr">
+        <is>
+          <t>'You built the area guides - let's make AI cite them, not just Google index them'</t>
+        </is>
+      </c>
+      <c r="R176" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S176" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Druce &amp; Partners</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>St Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>https://druce-partners.co.uk</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>sales@druce-partners.co.uk</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>01727 855 232</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Darryl Druce (Founder, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>Independent family firm since 1988; 50+ years combined local experience; premium St Albans period-home fees</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t>Long-established brand</t>
+        </is>
+      </c>
+      <c r="P177" s="3" t="inlineStr">
+        <is>
+          <t>Cassidy &amp; Tate and Heartwood Homes both fight for the same St Albans premium searches</t>
+        </is>
+      </c>
+      <c r="Q177" s="3" t="inlineStr">
+        <is>
+          <t>'St Albans buyers now ask AI before Rightmove - be the answer they get'</t>
+        </is>
+      </c>
+      <c r="R177" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S177" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>Woodbury Park Dental Surgery</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>https://woodburyparkdentalsurgery.com</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>info@woodburyparkdentalsurgery.com</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>01892 522297</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>Dr Alanna Gardiner (Principal)</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/WoodburyParkDentalSurgery</t>
+        </is>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>Independent, non-corporate, family-run practice - explicit differentiation from chains; named principal dentist</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>'Non-corporate' story not yet leveraged as an AI-search differentiator vs Bupa/mydentist</t>
+        </is>
+      </c>
+      <c r="Q178" s="3" t="inlineStr">
+        <is>
+          <t>'Own the AI answer for "independent dentist Tunbridge Wells" - it's your exact positioning'</t>
+        </is>
+      </c>
+      <c r="R178" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S178" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>The Dental Box</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Southborough, Tunbridge Wells</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thedentalbox.co.uk</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr"/>
+      <c r="G179" s="3" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>Private-only practice in a newly regenerated civic centre; no NHS dilution means fully self-pay client base</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>Private-only positioning is a strong differentiator currently invisible in local search</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="inlineStr">
+        <is>
+          <t>'Private-only' AEO content: own the self-pay dental searches in Southborough/TW</t>
+        </is>
+      </c>
+      <c r="R179" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S179" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Lewis &amp; Co Accountants &amp; Tax Advisors</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Southborough, Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lewisandco.biz</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>info@lewisandco.biz</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>01892 513 515</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Barney Lewis (Principal &amp; MD, FCA)</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/LewisandCoAccountantsandTaxAdvisors</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 1986, serving Kent/Sussex SMEs; recurring-fee clients across decades of trading</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P180" s="4" t="inlineStr">
+        <is>
+          <t>Perrys and S&amp;W (150-year-old firm) dominate Tunbridge Wells accountant searches with scale</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="inlineStr">
+        <is>
+          <t>'The small firm that's big on personal service' - own that exact AEO positioning</t>
+        </is>
+      </c>
+      <c r="R180" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S180" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Gilberts Chartered Accountants</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>St Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>https://gilberts.uk.com</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr"/>
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>Medium-sized independent firm with roots to 1921; serves St Albans SMEs and private clients</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M181" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O181" s="4" t="inlineStr">
+        <is>
+          <t>Century-old heritage promoted</t>
+        </is>
+      </c>
+      <c r="P181" s="4" t="inlineStr">
+        <is>
+          <t>Heritage brand not translated into modern local/AI search dominance</t>
+        </is>
+      </c>
+      <c r="Q181" s="4" t="inlineStr">
+        <is>
+          <t>'103 years in St Albans - let's make AI say so when clients ask for an accountant'</t>
+        </is>
+      </c>
+      <c r="R181" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S181" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Culverden Vets</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Wadhurst &amp; Crowborough, Kent</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>https://culverden.co.uk</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr"/>
+      <c r="G182" s="3" t="inlineStr"/>
+      <c r="H182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>One of Kent &amp; Sussex's longest-running independent vets, 3 sites; loyal multi-generation client base</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O182" s="3" t="inlineStr">
+        <is>
+          <t>Multi-site established brand</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>Corporate groups (IVC, CVS) and Vets Now dominate local + emergency vet search</t>
+        </is>
+      </c>
+      <c r="Q182" s="3" t="inlineStr">
+        <is>
+          <t>'3 sites, decades of trust - none of it shows up when pet owners ask AI'</t>
+        </is>
+      </c>
+      <c r="R182" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S182" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Carewell Vets</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Kent &amp; Surrey (Edenbridge area)</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>https://carewellvets.co.uk</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>reception@carewellvets.co.uk</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>01342 612103</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr"/>
+      <c r="H183" s="3" t="inlineStr"/>
+      <c r="I183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>Explicitly '100% independent', family-run across the Kent/Surrey border; strong differentiation story</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>'100% independent' claim isn't yet an AI-search asset</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr">
+        <is>
+          <t>Own the AI answer for '100% independent vet Kent/Surrey' - it's their own tagline</t>
+        </is>
+      </c>
+      <c r="R183" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S183" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Sevenoaks Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Manor Clinic, Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>https://sevenoaksphysiotherapy.co.uk</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>info@7oaksphysio.co.uk</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>01732 464 400</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>30 practitioners under one roof in affluent Sevenoaks; self-pay physio + multiple specialisms = high patient LTV</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>Multi-practitioner scale</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>Scale not reflected in 'physio Sevenoaks' search visibility vs newer boutique rivals</t>
+        </is>
+      </c>
+      <c r="Q184" s="3" t="inlineStr">
+        <is>
+          <t>'30 practitioners deserve to dominate the search, not just the waiting room'</t>
+        </is>
+      </c>
+      <c r="R184" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S184" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Orchard Clinic</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Physiotherapy &amp; clinical Pilates</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>St Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>https://www.orchardphysio.co.uk</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>01727 855 414</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>Paul Carnell (Clinic Director &amp; Head Physiotherapist)</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>Established 1987, named director; St Albans' longest-running physio brand</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>40 years trading</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>Heritage brand losing 'physio St Albans' searches to newer entrants (Redrock, Ann Physiocare)</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>'Founded 1987 - make that longevity the AI's answer, not just a footnote'</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Simon Knight Architects</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>St Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>https://simonknightarchitects.com</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>Simon Knight (Founder, 15+ years)</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>RIBA chartered practice in historic St Albans; residential + larger projects across Herts</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O186" s="4" t="inlineStr">
+        <is>
+          <t>Professional portfolio site</t>
+        </is>
+      </c>
+      <c r="P186" s="4" t="inlineStr">
+        <is>
+          <t>Competing with London-based AURA and Scenario for the same Herts clients</t>
+        </is>
+      </c>
+      <c r="Q186" s="4" t="inlineStr">
+        <is>
+          <t>'St Albans' own architect vs London firms parachuting in - own that local-first AEO angle'</t>
+        </is>
+      </c>
+      <c r="R186" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S186" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>Seth White Architects</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>St Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>via RIBA directory listing</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr"/>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>Seth White (Founder)</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr"/>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>Design-led RIBA practice for St Albans new builds/extensions/refurbs; residential project values £100k+</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M187" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O187" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P187" s="4" t="inlineStr">
+        <is>
+          <t>Small practice needs differentiated content to compete for Herts residential work</t>
+        </is>
+      </c>
+      <c r="Q187" s="4" t="inlineStr">
+        <is>
+          <t>Local-first AEO content targeting St Albans conservation-area planning queries</t>
+        </is>
+      </c>
+      <c r="R187" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S187" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T187" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website URL before outreach</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T175"/>
+  <autoFilter ref="A1:T187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15652,7 +16680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15672,7 +16700,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -15689,37 +16717,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -15729,7 +16757,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -15739,33 +16767,33 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -15775,7 +16803,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -15785,7 +16813,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -15795,17 +16823,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -16609,6 +17637,16 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Physiotherapy &amp; clinical Pilates</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T187"/>
+  <dimension ref="A1:T198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16668,8 +16668,960 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Davies Property Partners</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Cobham, Surrey</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>https://daviespropertypartners.co.uk</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>01932 588 288</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Gareth &amp; Claire Davies (2nd generation, since 2021); founded by Ian Davies 2002</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/daviespropertypartners</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned since 2002, recent generational handover to siblings; premium Cobham/Surrey stock, high fees per instruction</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 20+ years trading</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>New generation running the business - a natural moment to modernise marketing</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="inlineStr">
+        <is>
+          <t>'New leadership, same trust - let's make sure your digital presence matches your reputation'</t>
+        </is>
+      </c>
+      <c r="R188" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S188" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Buckinghams</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Virginia Water, Surrey</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>https://www.buckinghams.com</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>01344 933898</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt family (Owners, since 1991)</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/BuckinghamsEstateAgents</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1991 in one of the UK's wealthiest villages (Virginia Water); very high average property values</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 30+ years trading</t>
+        </is>
+      </c>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>Savills/Knight Frank corporate offices also based in Virginia Water compete for the same ultra-high-value stock</t>
+        </is>
+      </c>
+      <c r="Q189" s="3" t="inlineStr">
+        <is>
+          <t>'Virginia Water sellers ask AI before Rightmove now - be the independent name it gives'</t>
+        </is>
+      </c>
+      <c r="R189" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S189" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Peter Scott Estate Agents</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Chalfont St Giles (serves Beaconsfield/Gerrards Cross)</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>https://www.peterscottproperty.co.uk</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>peter@peterscottproperty.co.uk</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>01494 870 633</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>Peter Scott (Founder, est. 1982)</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/peterscottproperty</t>
+        </is>
+      </c>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1982 across South Bucks' wealthiest villages; long-term repeat clients (sold same client 10 homes)</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O190" s="3" t="inlineStr">
+        <is>
+          <t>YouTube channel; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>40+ years of repeat-client trust not converted into modern digital dominance</t>
+        </is>
+      </c>
+      <c r="Q190" s="3" t="inlineStr">
+        <is>
+          <t>'You've sold one client 10 houses - let's make sure the next one finds you on Google first'</t>
+        </is>
+      </c>
+      <c r="R190" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S190" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge Dental Care</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge High St, Surrey</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>https://weybridge-dental-care.co.uk</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>weybridgedentalcare@gmail.com</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>01932 842 838</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Rashi Soin (Principal Dentist &amp; Owner)</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="inlineStr"/>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>20+ year established practice in affluent Weybridge; named owner-principal; general + cosmetic private work</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O191" s="3" t="inlineStr">
+        <is>
+          <t>Gmail contact address - low marketing infrastructure</t>
+        </is>
+      </c>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>Bupa Dental Care Weybridge and MyoDental compete for the same high-value searches</t>
+        </is>
+      </c>
+      <c r="Q191" s="3" t="inlineStr">
+        <is>
+          <t>'20 years of trust in Weybridge deserves better than a Gmail inbox - let's fix the whole funnel'</t>
+        </is>
+      </c>
+      <c r="R191" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S191" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T191" s="3" t="inlineStr">
+        <is>
+          <t>Gmail tell - same infrastructure-gap wedge as other rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>The Specialist Dental Practice</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>https://thespecialistdentalpractice.com</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>info@weybridgedentist.co.uk</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>01932 857 585</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t>Specialist-branded practice in wealthy Weybridge; positioning suggests referral/specialist work at premium fees</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O192" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>'Specialist' branding underexploited in local search - genuinely differentiated in NLP terms</t>
+        </is>
+      </c>
+      <c r="Q192" s="3" t="inlineStr">
+        <is>
+          <t>Own 'specialist dentist Weybridge' - the branding practically writes the AEO content</t>
+        </is>
+      </c>
+      <c r="R192" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S192" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>MyoDental</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>https://myodental.co.uk/surrey</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr"/>
+      <c r="G193" s="4" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>Serving Surrey since 2008; accepting new private patients; competitive £80 check-up pricing suggests volume model</t>
+        </is>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M193" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O193" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P193" s="4" t="inlineStr">
+        <is>
+          <t>Volume private model needs constant new-patient search visibility to sustain growth</t>
+        </is>
+      </c>
+      <c r="Q193" s="4" t="inlineStr">
+        <is>
+          <t>Local-intent SEO to keep the new-patient pipeline full</t>
+        </is>
+      </c>
+      <c r="R193" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S193" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge Vets</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>York Road, Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.weybridgevets.co.uk</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>01932 855 856</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr">
+        <is>
+          <t>Explicitly independent 'family vets for family pets' serving Weybridge/Leatherhead/Cobham - three wealthy towns from one site</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O194" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>Multi-town catchment but single-location search visibility</t>
+        </is>
+      </c>
+      <c r="Q194" s="3" t="inlineStr">
+        <is>
+          <t>'Family vets for family pets' - turn that tagline into the AI-cited answer across 3 towns</t>
+        </is>
+      </c>
+      <c r="R194" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S194" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T194" s="3" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Concept Eight Architects</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>via RIBA directory listing</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr"/>
+      <c r="G195" s="3" t="inlineStr"/>
+      <c r="H195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
+          <t>RIBA chartered since 2006, based in Weybridge; residential specialism in one of Surrey's wealthiest commuter towns</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O195" s="3" t="inlineStr">
+        <is>
+          <t>RIBA chartered practice</t>
+        </is>
+      </c>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>Established credentials not converted into local AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q195" s="3" t="inlineStr">
+        <is>
+          <t>Own 'architect Weybridge/Cobham' - direct geographic match to their office</t>
+        </is>
+      </c>
+      <c r="R195" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S195" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T195" s="3" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Dr Cat Aesthetics</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>https://drcataesthetics.com</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr"/>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Dr Cat (Founder, practising NHS GP)</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr"/>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>Doctor-led (practising GP) aesthetics clinic; strong trust credential; repeat injectable clients in wealthy Weybridge</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="inlineStr">
+        <is>
+          <t>Professional site</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>GP credential is a strong differentiator not yet leveraged for AI-search trust signals</t>
+        </is>
+      </c>
+      <c r="Q196" s="3" t="inlineStr">
+        <is>
+          <t>'A real GP doing your Botox' - own that credibility angle in AEO content</t>
+        </is>
+      </c>
+      <c r="R196" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S196" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>The Norup Clinic</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics &amp; skin clinic</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Esher, Surrey (serves Cobham/Weybridge/Walton)</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thenorupclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr"/>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Dr Mette Norup (Founder)</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr"/>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>Named-doctor clinic covering 4 wealthy Surrey towns from one base; high-value repeat skin/aesthetic clients</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O197" s="3" t="inlineStr">
+        <is>
+          <t>Multi-town service area</t>
+        </is>
+      </c>
+      <c r="P197" s="3" t="inlineStr">
+        <is>
+          <t>Single clinic serving 4 towns needs 4x the local search presence it currently has</t>
+        </is>
+      </c>
+      <c r="Q197" s="3" t="inlineStr">
+        <is>
+          <t>Per-town local SEO + AEO to match the multi-town service claim</t>
+        </is>
+      </c>
+      <c r="R197" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S197" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>Light Touch Clinic</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>https://lighttouchclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr"/>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>Dr Natalie Geary (Medical Lead)</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr"/>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning medical team; doctor-led positioning in a competitive Surrey aesthetics market</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M198" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O198" s="4" t="inlineStr">
+        <is>
+          <t>Awards promoted</t>
+        </is>
+      </c>
+      <c r="P198" s="4" t="inlineStr">
+        <is>
+          <t>Awards don't automatically appear in AI-search answers</t>
+        </is>
+      </c>
+      <c r="Q198" s="4" t="inlineStr">
+        <is>
+          <t>Turn award-winning status into the AI-cited trust signal for Weybridge aesthetics</t>
+        </is>
+      </c>
+      <c r="R198" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S198" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T198" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T187"/>
+  <autoFilter ref="A1:T198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16680,7 +17632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16700,7 +17652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
@@ -16717,7 +17669,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -16727,7 +17679,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -16737,13 +17689,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -16753,11 +17705,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -16773,17 +17725,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -16793,17 +17745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -16813,7 +17765,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -16823,7 +17775,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -17647,6 +18599,16 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Aesthetics &amp; skin clinic</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T198"/>
+  <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17620,8 +17620,760 @@
       </c>
       <c r="T198" s="4" t="inlineStr"/>
     </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>The Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Recruitment agency</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Guildford (+ Worthing)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>https://therecruitmentconsultancy.com</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>01483 456465</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>Sharon Ellis (Managing Director)</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 1997, 2 offices across Surrey/Sussex; placement fees + repeat SME client relationships</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M199" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O199" s="4" t="inlineStr">
+        <is>
+          <t>Established 2-office brand</t>
+        </is>
+      </c>
+      <c r="P199" s="4" t="inlineStr">
+        <is>
+          <t>Michael Page/Robert Half corporate brands dominate Guildford recruitment search</t>
+        </is>
+      </c>
+      <c r="Q199" s="4" t="inlineStr">
+        <is>
+          <t>'Guildford SMEs ask AI for a recruiter who knows the local market - be that answer'</t>
+        </is>
+      </c>
+      <c r="R199" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S199" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>Price Ferguson Wealth Management</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Wealth management / IFA</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Guildford (+ Farnham)</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>https://priceferguson.com</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>info@priceferguson.com</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>01483 456 477</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Michael Price (Founder, est. 1997)</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr"/>
+      <c r="I200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>Established 1997, multi-office Surrey wealth manager; client AUM relationships worth tens of thousands in fees</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="inlineStr">
+        <is>
+          <t>Multi-office landing pages</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>Rathbones/HFMC/Chapters all compete for the same affluent Guildford searches</t>
+        </is>
+      </c>
+      <c r="Q200" s="3" t="inlineStr">
+        <is>
+          <t>'27 years managing Guildford's wealth - let's make sure AI knows it'</t>
+        </is>
+      </c>
+      <c r="R200" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S200" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Pembroke Consulting</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>IFA / financial planning</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pembroke.uk.net</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Tony Jaume (Founder, est. 1996)</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr"/>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1996 in wealthy Weybridge; long-tenured founder-adviser relationships</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>Nearly 30 years of trust invisible in modern local/AI search</t>
+        </is>
+      </c>
+      <c r="Q201" s="3" t="inlineStr">
+        <is>
+          <t>Turn three decades of Weybridge trust into the AI-cited local IFA answer</t>
+        </is>
+      </c>
+      <c r="R201" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S201" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>Rosan Helmsley</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Wealth management &amp; employee benefits</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rosan-ifa.com</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr"/>
+      <c r="G202" s="3" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 2001; advisers average 20+ years' experience; corporate benefits arm = B2B revenue line too</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O202" s="3" t="inlineStr">
+        <is>
+          <t>Professional site</t>
+        </is>
+      </c>
+      <c r="P202" s="3" t="inlineStr">
+        <is>
+          <t>Two service lines (personal wealth + corporate benefits) competing for attention without unified AEO strategy</t>
+        </is>
+      </c>
+      <c r="Q202" s="3" t="inlineStr">
+        <is>
+          <t>Split content strategy: separate AEO tracks for personal wealth vs corporate benefits searches</t>
+        </is>
+      </c>
+      <c r="R202" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S202" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>RH Electrical Services</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Weybridge (serves Surrey/SW London)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rh-electrical.co.uk</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr"/>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>Andy Hedges (Owner, NICEIC since 2007)</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr"/>
+      <c r="I203" s="4" t="inlineStr"/>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>Established 1976 - nearly 50 years trading; NICEIC member; rewires/consumer units in premium Surrey homes</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M203" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P203" s="4" t="inlineStr">
+        <is>
+          <t>Half a century of trust doesn't show up in 'electrician Weybridge' searches</t>
+        </is>
+      </c>
+      <c r="Q203" s="4" t="inlineStr">
+        <is>
+          <t>'49 years wiring Weybridge homes - time AI knew it too'</t>
+        </is>
+      </c>
+      <c r="R203" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S203" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>Surrey Roofing Specialists</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Roofer</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Addlestone (serves Weybridge/Esher/Cobham/Guildford)</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>https://www.surreyroofingspecialists.co.uk</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>07946 640262</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>Carl (Director)</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr"/>
+      <c r="I204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>Covers 10+ wealthy Surrey/SW London towns from one base; roof jobs £5-20k in premium housing stock</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="inlineStr">
+        <is>
+          <t>CORC membership (Confederation of Roofing Contractors)</t>
+        </is>
+      </c>
+      <c r="P204" s="3" t="inlineStr">
+        <is>
+          <t>Wide catchment but thin per-town search visibility - opportunity to dominate several towns at once</t>
+        </is>
+      </c>
+      <c r="Q204" s="3" t="inlineStr">
+        <is>
+          <t>Multi-town local SEO campaign covering the whole Surrey Roofing Specialists service area</t>
+        </is>
+      </c>
+      <c r="R204" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S204" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Barford Park Barn</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Downton, near Salisbury, Wiltshire</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>https://barfordparkweddings.co.uk</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr"/>
+      <c r="G205" s="3" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr"/>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t>300-acre family farm wedding venue, seats 150-200; Wiltshire weddings worth £15-25k each</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O205" s="3" t="inlineStr">
+        <is>
+          <t>Multiple directory listings (Guides for Brides, Bridebook, Confetti)</t>
+        </is>
+      </c>
+      <c r="P205" s="3" t="inlineStr">
+        <is>
+          <t>Heavy directory dependence - same commission-middleman pattern as other venues</t>
+        </is>
+      </c>
+      <c r="Q205" s="3" t="inlineStr">
+        <is>
+          <t>'Own the AI-recommended shortlist for South Wiltshire barn weddings directly'</t>
+        </is>
+      </c>
+      <c r="R205" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S205" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>Manor Estate</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Wiltshire</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>https://manorestate.co.uk</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr"/>
+      <c r="G206" s="3" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>Grade II* listed manor house + barn, privately owned; premium exclusive-use weddings</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="inlineStr">
+        <is>
+          <t>Polished dedicated wedding site</t>
+        </is>
+      </c>
+      <c r="P206" s="3" t="inlineStr">
+        <is>
+          <t>Grade II* listing not leveraged as an AI-search authority/trust signal</t>
+        </is>
+      </c>
+      <c r="Q206" s="3" t="inlineStr">
+        <is>
+          <t>Heritage-listing content as the AEO differentiator vs generic barn venues</t>
+        </is>
+      </c>
+      <c r="R206" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S206" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>Wellington Barn</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Wiltshire</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wellingtonbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr"/>
+      <c r="G207" s="4" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr"/>
+      <c r="I207" s="4" t="inlineStr"/>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>'Wiltshire's original authentic barn venue' - strong positioning claim; countryside views</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M207" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O207" s="4" t="inlineStr">
+        <is>
+          <t>Branded positioning ('original authentic')</t>
+        </is>
+      </c>
+      <c r="P207" s="4" t="inlineStr">
+        <is>
+          <t>Positioning claim not yet the AI-cited answer for 'original barn venue Wiltshire'</t>
+        </is>
+      </c>
+      <c r="Q207" s="4" t="inlineStr">
+        <is>
+          <t>Own the 'original authentic barn' AEO positioning outright</t>
+        </is>
+      </c>
+      <c r="R207" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S207" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T207" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T198"/>
+  <autoFilter ref="A1:T207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17632,7 +18384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17652,7 +18404,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -17685,27 +18437,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -17795,7 +18547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -17805,7 +18557,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -17815,7 +18567,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -17825,27 +18577,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -17855,7 +18607,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -17865,7 +18617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -17875,7 +18627,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -17885,7 +18637,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -17895,7 +18647,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -17905,7 +18657,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -17915,7 +18667,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -17925,7 +18677,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -17935,7 +18687,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -17945,7 +18697,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -17955,7 +18707,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -17965,7 +18717,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -17975,7 +18727,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -17985,17 +18737,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -18005,7 +18757,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -18015,7 +18767,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -18025,7 +18777,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -18035,7 +18787,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -18045,7 +18797,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -18055,7 +18807,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -18065,7 +18817,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -18075,7 +18827,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -18085,7 +18837,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -18095,7 +18847,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -18105,7 +18857,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -18115,7 +18867,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -18125,7 +18877,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -18135,7 +18887,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -18145,7 +18897,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -18155,7 +18907,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -18165,7 +18917,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -18175,7 +18927,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -18185,7 +18937,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -18195,7 +18947,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -18609,6 +19361,36 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Wealth management / IFA</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IFA / financial planning</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Wealth management &amp; employee benefits</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T207"/>
+  <dimension ref="A1:T215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18372,8 +18372,684 @@
       </c>
       <c r="T207" s="4" t="inlineStr"/>
     </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>Cavender Estate Agent</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Guildford &amp; Godalming, Surrey</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cavenders.co.uk</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>info@cavenders.co.uk</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>01483 457 728</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t>Truly independent since 2012 across two Surrey towns; residential sales/lettings for professional-family stock</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O208" s="3" t="inlineStr">
+        <is>
+          <t>Two-office presence</t>
+        </is>
+      </c>
+      <c r="P208" s="3" t="inlineStr">
+        <is>
+          <t>Bourne/Curchods/Clarke Gammon corporate-scale rivals dominate Guildford search</t>
+        </is>
+      </c>
+      <c r="Q208" s="3" t="inlineStr">
+        <is>
+          <t>'Guildford's genuinely independent agent should win the AI answer, not the network brands'</t>
+        </is>
+      </c>
+      <c r="R208" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S208" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>Ralph James</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Reigate, Redhill, Dorking, Banstead, Surrey</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ralphjames.co.uk</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>reigate@ralphjames.co.uk</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>01737 333 677</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Cullum Cina &amp; Paul Cooney (Senior management)</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr"/>
+      <c r="I209" s="3" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 2015, 4-office growth in premium Surrey towns; outperforming rivals in Redhill/Reigate per their own claim</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O209" s="3" t="inlineStr">
+        <is>
+          <t>Per-office landing pages; growth-stage marketing awareness</t>
+        </is>
+      </c>
+      <c r="P209" s="3" t="inlineStr">
+        <is>
+          <t>Rapid 4-office growth needs matching search-visibility growth across all locations</t>
+        </is>
+      </c>
+      <c r="Q209" s="3" t="inlineStr">
+        <is>
+          <t>'You outperform rivals locally - let's make sure AI says so across all 4 towns'</t>
+        </is>
+      </c>
+      <c r="R209" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S209" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>White &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Dorking, Reigate, Horley, Oxted, Leatherhead</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>https://www.whiteandsons.co.uk</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr"/>
+      <c r="G210" s="3" t="inlineStr"/>
+      <c r="H210" s="3" t="inlineStr"/>
+      <c r="I210" s="3" t="inlineStr"/>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t>Established 1817 - over 200 years trading; 5-office coverage of Surrey's wealthiest towns</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O210" s="3" t="inlineStr">
+        <is>
+          <t>Multi-office; 'cutting edge technology' self-description</t>
+        </is>
+      </c>
+      <c r="P210" s="3" t="inlineStr">
+        <is>
+          <t>200 years of heritage vastly under-leveraged as an AI-search trust signal</t>
+        </is>
+      </c>
+      <c r="Q210" s="3" t="inlineStr">
+        <is>
+          <t>'207 years in Surrey property - the AI answer should reflect that, not just Rightmove'</t>
+        </is>
+      </c>
+      <c r="R210" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S210" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>Rochford Stokes</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Battersea/Clapham/Wandsworth/Balham, London</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rochfordstokes.com</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr"/>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Founders with 35+ years combined experience each (est. 2006)</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t>Founder-run since 2006 across SW11/SW4 postcodes; high property values, repeat-client relationships</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O211" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P211" s="3" t="inlineStr">
+        <is>
+          <t>Marsh &amp; Parsons/Jacksons corporate-scale rivals dominate the same postcodes</t>
+        </is>
+      </c>
+      <c r="Q211" s="3" t="inlineStr">
+        <is>
+          <t>35 years' combined experience as the AEO trust signal vs bigger network brands</t>
+        </is>
+      </c>
+      <c r="R211" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S211" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>C. Scott &amp; Co</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Wandsworth Common, London SW18</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cscottandco.com</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>carrie@cscottandco.com</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr"/>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Carrie Scott (Founder)</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/carriescottcscottandco</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/c.scottandco_estateagents</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning independent, 25+ years serving Wandsworth/Balham/Earlsfield/Streatham/Tooting</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O212" s="3" t="inlineStr">
+        <is>
+          <t>Active Instagram presence; awards</t>
+        </is>
+      </c>
+      <c r="P212" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning but competing with Jacksons/Porters/Realm for the same dense SW London postcodes</t>
+        </is>
+      </c>
+      <c r="Q212" s="3" t="inlineStr">
+        <is>
+          <t>'25 years and an award - now make sure ChatGPT recommends you over the corporate chains'</t>
+        </is>
+      </c>
+      <c r="R212" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S212" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>Porters Estate Agents</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Balham, London SW17</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>https://portersbalham.com</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr"/>
+      <c r="G213" s="4" t="inlineStr"/>
+      <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Family-owned, 40 years trading, 100+ years combined team experience in Balham/Wandsworth</t>
+        </is>
+      </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O213" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P213" s="4" t="inlineStr">
+        <is>
+          <t>Longevity claim buried; newer branded independents (C.Scott, Patrick Henry) out-market them digitally</t>
+        </is>
+      </c>
+      <c r="Q213" s="4" t="inlineStr">
+        <is>
+          <t>Turn '100 years combined experience' into the AI-cited local-expert answer</t>
+        </is>
+      </c>
+      <c r="R213" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S213" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>Colin Bibra Estate Agents</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Ealing, London W5</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.colinbibra.com</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>020 8566 3333</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>Colin Bibra (Founder, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr"/>
+      <c r="I214" s="4" t="inlineStr"/>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 1988, founder's namesake brand; 35+ years in Ealing's premium property market</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M214" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O214" s="4" t="inlineStr">
+        <is>
+          <t>Established namesake brand</t>
+        </is>
+      </c>
+      <c r="P214" s="4" t="inlineStr">
+        <is>
+          <t>Corporate brands (Savills, haart) and Grimshaw/Robertson Smith &amp; Kempson compete for Ealing search visibility</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="inlineStr">
+        <is>
+          <t>'The Ealing agent named after its founder - make AI say his name when clients search'</t>
+        </is>
+      </c>
+      <c r="R214" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S214" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>Grimshaw and Co</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Ealing, London W5</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>https://www.grimshawhomes.co.uk</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr"/>
+      <c r="G215" s="4" t="inlineStr"/>
+      <c r="H215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>Independent 50+ years in Ealing; deep local market knowledge, residential sales specialism</t>
+        </is>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M215" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O215" s="4" t="inlineStr">
+        <is>
+          <t>Half-century heritage promoted</t>
+        </is>
+      </c>
+      <c r="P215" s="4" t="inlineStr">
+        <is>
+          <t>50 years untranslated into digital-era search dominance</t>
+        </is>
+      </c>
+      <c r="Q215" s="4" t="inlineStr">
+        <is>
+          <t>'50 years knowing Ealing - it's time Google and AI knew it as well as your clients do'</t>
+        </is>
+      </c>
+      <c r="R215" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S215" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T215" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T207"/>
+  <autoFilter ref="A1:T215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18404,7 +19080,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -18421,7 +19097,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T215"/>
+  <dimension ref="A1:T221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19048,8 +19048,528 @@
       </c>
       <c r="T215" s="4" t="inlineStr"/>
     </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>Balham Gateway Dental Practice</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Balham High Rd, London SW12</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>https://www.balhamgatewaydental.com</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>balham-gateway-dental@dentallymail.co.uk</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>020 8673 7887</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Dr Panos Angelopoulos (Principal, acquired 2021)</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/panos-angelopoulos-78647a41</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr"/>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1950s, new owner-principal with implant/oral surgery specialism; Invisalign provider since 2015</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O216" s="3" t="inlineStr">
+        <is>
+          <t>Doctify profile</t>
+        </is>
+      </c>
+      <c r="P216" s="3" t="inlineStr">
+        <is>
+          <t>70-year heritage + new specialist owner not yet converted into AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q216" s="3" t="inlineStr">
+        <is>
+          <t>'70 years in Balham, new implant expertise - let's make sure Google and AI both know both halves of the story'</t>
+        </is>
+      </c>
+      <c r="R216" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S216" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>Chiswick Dental</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Chiswick High Road, London W4</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chiswickdental.co.uk</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>info@chiswickdental.co.uk</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>020 8994 6202</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Dr Gajen Pathmanathan (Principal, Implant &amp; Cosmetic Dentist)</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr"/>
+      <c r="I217" s="3" t="inlineStr"/>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t>Named implant/cosmetic specialist principal on Chiswick's main high street; premium W4 client base</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O217" s="3" t="inlineStr">
+        <is>
+          <t>Detailed referral/fees pages - marketing-aware</t>
+        </is>
+      </c>
+      <c r="P217" s="3" t="inlineStr">
+        <is>
+          <t>Referral infrastructure built but AI-answer visibility for 'implants Chiswick' still open</t>
+        </is>
+      </c>
+      <c r="Q217" s="3" t="inlineStr">
+        <is>
+          <t>'You built the referral pages - let's make sure ChatGPT recommends you to patients too'</t>
+        </is>
+      </c>
+      <c r="R217" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S217" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Juliet Moss &amp; Associates Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Thurleigh Rd, Balham, London SW12</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.julietmossphysio.co.uk</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>info@julietmossphysio.co.uk</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>020 8675 5633</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>Juliet Moss (Founder)</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr"/>
+      <c r="I218" s="4" t="inlineStr"/>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>Established practice serving Clapham/Balham/Wandsworth; insurance + self-pay mix in dense affluent SW postcodes</t>
+        </is>
+      </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L218" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M218" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O218" s="4" t="inlineStr">
+        <is>
+          <t>BUPA/CSP directory listings</t>
+        </is>
+      </c>
+      <c r="P218" s="4" t="inlineStr">
+        <is>
+          <t>Excellence Physiotherapy and reCentre Health compete for the same dense-postcode searches</t>
+        </is>
+      </c>
+      <c r="Q218" s="4" t="inlineStr">
+        <is>
+          <t>'Own the AI answer for physio across Clapham, Balham AND Wandsworth - not just one'</t>
+        </is>
+      </c>
+      <c r="R218" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S218" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T218" s="4" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>Armstrong Simmonds Architects</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Battersea, London SW11</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>https://www.as-architects.co.uk</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>projects@as-architects.co.uk</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>020 7228 1324</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>John Armstrong (Founder, est. 2010)</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr"/>
+      <c r="I219" s="3" t="inlineStr"/>
+      <c r="J219" s="3" t="inlineStr">
+        <is>
+          <t>RIBA practice with dedicated per-borough landing pages (Wandsworth/Clapham/Battersea) - genuine SEO investment</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
+          <t>Per-area landing pages = active SEO strategy</t>
+        </is>
+      </c>
+      <c r="P219" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist across 3+ areas but AI-answer citations still open</t>
+        </is>
+      </c>
+      <c r="Q219" s="3" t="inlineStr">
+        <is>
+          <t>'You've built the SEO pages for 3 boroughs - add the AEO layer to make AI cite them too'</t>
+        </is>
+      </c>
+      <c r="R219" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S219" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Quartet Architecture</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Wandsworth, London</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.quartetarchitecture.com</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr"/>
+      <c r="G220" s="4" t="inlineStr"/>
+      <c r="H220" s="4" t="inlineStr"/>
+      <c r="I220" s="4" t="inlineStr"/>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>RIBA-chartered, 20+ years delivering bespoke residences in Wandsworth; high project values</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M220" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O220" s="4" t="inlineStr">
+        <is>
+          <t>Professional portfolio site</t>
+        </is>
+      </c>
+      <c r="P220" s="4" t="inlineStr">
+        <is>
+          <t>20 years' delivery record not translated into modern local AI-search authority</t>
+        </is>
+      </c>
+      <c r="Q220" s="4" t="inlineStr">
+        <is>
+          <t>Portfolio-driven AEO content: let 20 years of projects answer AI queries directly</t>
+        </is>
+      </c>
+      <c r="R220" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S220" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Browning Architects</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Earlsfield, Wandsworth, London</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>via RIBA directory listing</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr"/>
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="4" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr"/>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning SW London practice, deep council/planning relationships in Wandsworth</t>
+        </is>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L221" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M221" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O221" s="4" t="inlineStr">
+        <is>
+          <t>Awards; planning-department relationships</t>
+        </is>
+      </c>
+      <c r="P221" s="4" t="inlineStr">
+        <is>
+          <t>Planning expertise is a strong differentiator invisible in generic architect searches</t>
+        </is>
+      </c>
+      <c r="Q221" s="4" t="inlineStr">
+        <is>
+          <t>'We know Wandsworth planning inside out' - own that exact AEO angle</t>
+        </is>
+      </c>
+      <c r="R221" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S221" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T221" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live site before outreach</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T215"/>
+  <autoFilter ref="A1:T221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19080,7 +19600,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
@@ -19103,31 +19623,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -19143,7 +19663,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -19153,7 +19673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -19163,11 +19683,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -19213,17 +19733,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -19233,7 +19753,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -19243,7 +19763,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -19253,7 +19773,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -19263,7 +19783,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -19273,17 +19793,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -19293,7 +19813,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -19303,7 +19823,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -19313,7 +19833,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -19323,7 +19843,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -19333,7 +19853,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -19343,7 +19863,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -19353,7 +19873,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -19363,7 +19883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -19373,7 +19893,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -19383,7 +19903,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -19393,7 +19913,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B36" t="n">

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$229</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T221"/>
+  <dimension ref="A1:T229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19568,8 +19568,692 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>Auerbach &amp; Steele</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Independent optician</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>King's Road, Chelsea, London SW3</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>https://www.auerbach-steele.com</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>info@auerbach-steele.com</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>020 7349 0001</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>Gail Steele (Founder, est. 1996)</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr"/>
+      <c r="I222" s="3" t="inlineStr"/>
+      <c r="J222" s="3" t="inlineStr">
+        <is>
+          <t>Premium design-led eyewear on King's Road since 1996; repeat prescription clients worth £300-1000+ per visit</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O222" s="3" t="inlineStr">
+        <is>
+          <t>Design-led branding; 28 years trading</t>
+        </is>
+      </c>
+      <c r="P222" s="3" t="inlineStr">
+        <is>
+          <t>Independent eyewear boutiques increasingly squeezed by Specsavers/Vision Express search dominance</t>
+        </is>
+      </c>
+      <c r="Q222" s="3" t="inlineStr">
+        <is>
+          <t>'Chelsea's design-literate opticians deserve to beat the chains in AI answers too'</t>
+        </is>
+      </c>
+      <c r="R222" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S222" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>CULT VISION</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Independent optician</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Clerkenwell, London EC1</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>https://cultvision.com</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr"/>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>Panos (Founder, 20+ years)</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Curated independent-designer eyewear boutique; strong niche positioning against mass-market chains</t>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L223" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M223" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O223" s="4" t="inlineStr">
+        <is>
+          <t>Curated-brand positioning</t>
+        </is>
+      </c>
+      <c r="P223" s="4" t="inlineStr">
+        <is>
+          <t>Niche 'independent designer eyewear' story not yet the AI-cited Clerkenwell answer</t>
+        </is>
+      </c>
+      <c r="Q223" s="4" t="inlineStr">
+        <is>
+          <t>Own the AI answer for 'independent eyewear designer London' - genuinely defensible niche</t>
+        </is>
+      </c>
+      <c r="R223" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S223" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T223" s="4" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Aristone Optical</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Independent optician</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>Fulham, London SW6</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aristoneopticians.com</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr"/>
+      <c r="G224" s="4" t="inlineStr"/>
+      <c r="H224" s="4" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>Family-run for 70 years - one of West London's most established independents; multi-generation trust</t>
+        </is>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M224" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N224" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O224" s="4" t="inlineStr">
+        <is>
+          <t>70-year heritage promoted</t>
+        </is>
+      </c>
+      <c r="P224" s="4" t="inlineStr">
+        <is>
+          <t>Heritage brand invisible against Specsavers/Boots Opticians in modern local search</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="inlineStr">
+        <is>
+          <t>'70 years of Fulham trust - let's make AI recommend you, not just the high-street chains'</t>
+        </is>
+      </c>
+      <c r="R224" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S224" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T224" s="4" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Charles Bainbridge Estate Agents</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Canterbury, Kent</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>https://www.charlesbainbridge.com</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>charlie@charlesbainbridge.com</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>01227 780 227</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>Andrea Dann (Founding team)</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr"/>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/charlesbainbridgeea</t>
+        </is>
+      </c>
+      <c r="J225" s="3" t="inlineStr">
+        <is>
+          <t>Proudly independent family-run agency in Canterbury's premium period-home market; strong local reputation for integrity</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O225" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P225" s="3" t="inlineStr">
+        <is>
+          <t>Wards/Fine &amp; Country corporate-scale rivals dominate Canterbury searches</t>
+        </is>
+      </c>
+      <c r="Q225" s="3" t="inlineStr">
+        <is>
+          <t>'Canterbury sellers value integrity - make sure AI recommends the independent, not just the network brand'</t>
+        </is>
+      </c>
+      <c r="R225" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S225" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>Simon Miller &amp; Company</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Maidstone &amp; the Weald, Kent</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>https://simonmiller.co.uk</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>01622 691 255</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr"/>
+      <c r="H226" s="3" t="inlineStr"/>
+      <c r="I226" s="3" t="inlineStr"/>
+      <c r="J226" s="3" t="inlineStr">
+        <is>
+          <t>Truly independent, multi-office coverage of Maidstone/Malling/the Weald; strong local-knowledge positioning</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O226" s="3" t="inlineStr">
+        <is>
+          <t>Multi-office network</t>
+        </is>
+      </c>
+      <c r="P226" s="3" t="inlineStr">
+        <is>
+          <t>Independent claim not converted into AI-search dominance vs Wards/Foundation</t>
+        </is>
+      </c>
+      <c r="Q226" s="3" t="inlineStr">
+        <is>
+          <t>'Truly independent' as the exact AEO positioning to own in Kent property search</t>
+        </is>
+      </c>
+      <c r="R226" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S226" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>Heritage Estate Agents</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Portishead, Nailsea, Clevedon, Yatton (North Somerset)</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>https://heritage4homes.co.uk</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>01275 840 610</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr"/>
+      <c r="H227" s="3" t="inlineStr"/>
+      <c r="I227" s="3" t="inlineStr"/>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>North Somerset's largest independent, 5-town coverage; steady commuter-belt Bristol demand</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O227" s="3" t="inlineStr">
+        <is>
+          <t>Multi-office coverage</t>
+        </is>
+      </c>
+      <c r="P227" s="3" t="inlineStr">
+        <is>
+          <t>Largest independent claim not leveraged as AI-search trust signal across all 5 towns</t>
+        </is>
+      </c>
+      <c r="Q227" s="3" t="inlineStr">
+        <is>
+          <t>'Largest independent in North Somerset - own that claim in every AI answer, not just the tagline'</t>
+        </is>
+      </c>
+      <c r="R227" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S227" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Westcoast Properties</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Weston-super-Mare, Portishead, Nailsea, Patchway (North Somerset/Bristol)</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>https://www.westcoast-properties.co.uk</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr"/>
+      <c r="H228" s="4" t="inlineStr"/>
+      <c r="I228" s="4" t="inlineStr"/>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 1995, 4-office North Somerset/North Bristol coverage; 30 years trading</t>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M228" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N228" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O228" s="4" t="inlineStr">
+        <is>
+          <t>Multi-office established brand</t>
+        </is>
+      </c>
+      <c r="P228" s="4" t="inlineStr">
+        <is>
+          <t>30-year trading history under-leveraged for search trust vs Heritage/Connells</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="inlineStr">
+        <is>
+          <t>Turn 3 decades of trading into the AI-cited local-authority answer</t>
+        </is>
+      </c>
+      <c r="R228" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S228" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>London Dermatology Centre</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Dermatology clinic</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Wimpole Street, London W1</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>https://www.london-dermatology-centre.co.uk</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>reception@the-dermatology-centre.co.uk</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>020 7467 3720</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>Dr Sunil Chopra (Founder &amp; Clinical Director, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/drsunilchopra</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr"/>
+      <c r="J229" s="3" t="inlineStr">
+        <is>
+          <t>20-year-established consultant dermatology clinic; skin cancer/acne/rosacea cases worth £200-500+ per consultation with repeat visits</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O229" s="3" t="inlineStr">
+        <is>
+          <t>Doctify reviews; established brand</t>
+        </is>
+      </c>
+      <c r="P229" s="3" t="inlineStr">
+        <is>
+          <t>Newer, more aggressively-marketed dermatology brands (Skin55, Eudelo) may be winning AI-search share from established players</t>
+        </is>
+      </c>
+      <c r="Q229" s="3" t="inlineStr">
+        <is>
+          <t>'20 years of consultant-level expertise - make sure that outranks newer, flashier competitors in AI answers too'</t>
+        </is>
+      </c>
+      <c r="R229" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S229" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T229" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T221"/>
+  <autoFilter ref="A1:T229"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19580,7 +20264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -19600,7 +20284,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
@@ -19617,7 +20301,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -19803,17 +20487,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -19823,7 +20507,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -19833,7 +20517,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -19843,7 +20527,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -19853,7 +20537,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -19863,7 +20547,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -19873,7 +20557,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -19883,7 +20567,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -19893,7 +20577,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -19903,7 +20587,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -19913,7 +20597,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -19923,7 +20607,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -19933,7 +20617,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -19943,17 +20627,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -19963,7 +20647,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -19973,7 +20657,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -19983,7 +20667,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -19993,7 +20677,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -20003,7 +20687,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -20013,7 +20697,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -20023,7 +20707,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -20033,7 +20717,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -20043,7 +20727,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -20053,7 +20737,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -20063,7 +20747,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -20073,7 +20757,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -20083,7 +20767,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -20093,7 +20777,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -20103,7 +20787,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -20113,7 +20797,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -20123,7 +20807,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -20133,7 +20817,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -20143,7 +20827,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -20153,7 +20837,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -20163,7 +20847,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -20173,7 +20857,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20183,7 +20867,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -20193,7 +20877,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -20203,7 +20887,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -20213,7 +20897,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -20223,7 +20907,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20233,7 +20917,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20243,7 +20927,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20253,7 +20937,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20263,7 +20947,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20273,7 +20957,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20283,7 +20967,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -20293,7 +20977,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -20303,7 +20987,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -20313,7 +20997,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -20323,7 +21007,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -20333,7 +21017,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -20343,7 +21027,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -20353,7 +21037,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -20363,7 +21047,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -20373,7 +21057,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -20383,7 +21067,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -20393,7 +21077,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -20403,7 +21087,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -20413,7 +21097,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -20423,7 +21107,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -20433,7 +21117,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -20443,7 +21127,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -20453,7 +21137,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -20463,7 +21147,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -20473,7 +21157,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -20483,7 +21167,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -20493,7 +21177,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -20503,7 +21187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -20513,7 +21197,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -20523,7 +21207,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -20533,7 +21217,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -20543,7 +21227,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -20553,7 +21237,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -20563,7 +21247,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -20573,7 +21257,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -20583,10 +21267,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>IFA / financial planning</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Dermatology clinic</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T229"/>
+  <dimension ref="A1:T236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20252,8 +20252,616 @@
       </c>
       <c r="T229" s="3" t="inlineStr"/>
     </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Bass Estate Agents</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Primrose Hill, London NW1</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jeremybass.co.uk</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>info@jeremybass.co.uk</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>020 7722 8686</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>Jeremy Bass (Founder &amp; Director, est. 2000)</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr"/>
+      <c r="I230" s="3" t="inlineStr"/>
+      <c r="J230" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 2000 in ultra-premium Primrose Hill village; founder personally known in the area for 30+ years</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O230" s="3" t="inlineStr">
+        <is>
+          <t>Local press interviews (I Love Primrose Hill blog)</t>
+        </is>
+      </c>
+      <c r="P230" s="3" t="inlineStr">
+        <is>
+          <t>Corporate giants (John D Wood, Knight Frank) also operate in Primrose Hill and outspend on digital</t>
+        </is>
+      </c>
+      <c r="Q230" s="3" t="inlineStr">
+        <is>
+          <t>'Primrose Hill's own agent for 25 years - make sure AI says his name, not just the corporates'</t>
+        </is>
+      </c>
+      <c r="R230" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S230" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T230" s="3" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>Laurence Leigh</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>St John's Wood, Maida Vale, Regent's Park, Primrose Hill, Hampstead</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>https://laurenceleigh.com</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr"/>
+      <c r="G231" s="3" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr"/>
+      <c r="I231" s="3" t="inlineStr"/>
+      <c r="J231" s="3" t="inlineStr">
+        <is>
+          <t>Independent, 50+ years combined team experience across 5 of London's wealthiest villages</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O231" s="3" t="inlineStr">
+        <is>
+          <t>Multi-village coverage claim</t>
+        </is>
+      </c>
+      <c r="P231" s="3" t="inlineStr">
+        <is>
+          <t>Broad coverage claim not matched by dominant per-village search visibility</t>
+        </is>
+      </c>
+      <c r="Q231" s="3" t="inlineStr">
+        <is>
+          <t>Per-village AEO content to actually own all 5 areas claimed</t>
+        </is>
+      </c>
+      <c r="R231" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S231" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T231" s="3" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>McKee &amp; Co</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>South Kensington, London SW7</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mckee.co.uk</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>020 8022 7161</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>David McKee (2nd generation, family firm since 1979)</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr"/>
+      <c r="I232" s="3" t="inlineStr"/>
+      <c r="J232" s="3" t="inlineStr">
+        <is>
+          <t>45+ year independent niche agency in Prime Central London; family firm with deep multi-generation local knowledge</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O232" s="3" t="inlineStr">
+        <is>
+          <t>Area-guide content (South Kensington/Kensington guides)</t>
+        </is>
+      </c>
+      <c r="P232" s="3" t="inlineStr">
+        <is>
+          <t>Area guides exist but Knight Frank/Strutt &amp; Parker corporate scale dominates PCL search</t>
+        </is>
+      </c>
+      <c r="Q232" s="3" t="inlineStr">
+        <is>
+          <t>'Second-generation local knowledge vs corporate scale - AEO is the equaliser'</t>
+        </is>
+      </c>
+      <c r="R232" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S232" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T232" s="3" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>Pilates Hub Weybridge</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>Queens Rd, Weybridge, Surrey</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pilateshubweybridge.co.uk</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>info@pilateshubweybridge.co.uk</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>07961 740302</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>Sara Noon (Founder &amp; Director)</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/sara-noon-61066253</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/pilates_hub_weybridge</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>Founder-led boutique studio in affluent Weybridge; memberships + 1:1 sessions = strong recurring revenue per client</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L233" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M233" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N233" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O233" s="4" t="inlineStr">
+        <is>
+          <t>Active Instagram; Mindbody/Wellhub listings</t>
+        </is>
+      </c>
+      <c r="P233" s="4" t="inlineStr">
+        <is>
+          <t>Discovery via booking platforms (Mindbody) means paying commission on the studio's own clients</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="inlineStr">
+        <is>
+          <t>'Stop paying Mindbody for leads you could own directly via local + AI search'</t>
+        </is>
+      </c>
+      <c r="R233" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S233" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T233" s="4" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>Guildford Pilates Place</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>High Street, Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>https://guildfordpilatesplace.co.uk</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>pilates@guildfordpilatesplace.co.uk</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>01483 506 113</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr"/>
+      <c r="H234" s="4" t="inlineStr"/>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/guildfordpilates</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>Guildford's original dedicated Pilates studio since 2010 - first-mover positioning in the town centre</t>
+        </is>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M234" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>Instagram presence; Mindbody listing</t>
+        </is>
+      </c>
+      <c r="P234" s="4" t="inlineStr">
+        <is>
+          <t>'Original' claim undefended in local search against newer entrants (HiP Studio, The Pilates Movement)</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="inlineStr">
+        <is>
+          <t>'Guildford's original Pilates studio' - own that exact AEO positioning before newer rivals claim it</t>
+        </is>
+      </c>
+      <c r="R234" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S234" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>HiP Studio</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Shalford, Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hipstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F235" s="4" t="inlineStr"/>
+      <c r="G235" s="4" t="inlineStr"/>
+      <c r="H235" s="4" t="inlineStr"/>
+      <c r="I235" s="4" t="inlineStr"/>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>Boutique reformer studio with premium STOTT equipment in Shalford village near Guildford</t>
+        </is>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M235" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N235" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O235" s="4" t="inlineStr">
+        <is>
+          <t>Premium equipment branding</t>
+        </is>
+      </c>
+      <c r="P235" s="4" t="inlineStr">
+        <is>
+          <t>Boutique/premium positioning invisible against bigger Guildford studios in search</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="inlineStr">
+        <is>
+          <t>Own 'STOTT reformer Guildford' - equipment-brand AEO niche nobody else claims</t>
+        </is>
+      </c>
+      <c r="R235" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S235" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T235" s="4" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>The Pilates Movement</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Pilates studio (multi-site)</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>4 studios across Surrey incl. Guildford</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>https://thepilatesmovementstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>guildford@thepilatesmovementstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>01483 399 149</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Jeff &amp; Jane (Founders, husband &amp; wife)</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr"/>
+      <c r="J236" s="3" t="inlineStr">
+        <is>
+          <t>4-studio Surrey group; couple-founded; multi-site scale gives real cross-sell/membership revenue</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O236" s="3" t="inlineStr">
+        <is>
+          <t>Per-studio booking pages = active marketing</t>
+        </is>
+      </c>
+      <c r="P236" s="3" t="inlineStr">
+        <is>
+          <t>4 studios but not yet 4x the search dominance in each catchment</t>
+        </is>
+      </c>
+      <c r="Q236" s="3" t="inlineStr">
+        <is>
+          <t>Per-studio local SEO + AEO push to match the scale they've already built</t>
+        </is>
+      </c>
+      <c r="R236" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S236" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T236" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T229"/>
+  <autoFilter ref="A1:T236"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20264,7 +20872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -20284,7 +20892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -20301,7 +20909,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -20497,17 +21105,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -20517,7 +21125,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -20527,7 +21135,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -20537,7 +21145,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -20547,7 +21155,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -20557,7 +21165,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -20567,7 +21175,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -20577,7 +21185,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -20587,7 +21195,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -20597,7 +21205,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -20607,7 +21215,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -20617,7 +21225,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -20627,7 +21235,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -20637,17 +21245,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -20657,7 +21265,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -20667,7 +21275,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -20677,7 +21285,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -20687,7 +21295,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -20697,7 +21305,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -20707,7 +21315,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -20717,7 +21325,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -20727,7 +21335,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -20737,7 +21345,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -20747,7 +21355,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -20757,7 +21365,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -20767,7 +21375,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -20777,7 +21385,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -20787,7 +21395,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -20797,7 +21405,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -20807,7 +21415,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -20817,7 +21425,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -20827,7 +21435,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -20837,7 +21445,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -20847,7 +21455,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -20857,7 +21465,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20867,7 +21475,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -20877,7 +21485,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -20887,7 +21495,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -20897,7 +21505,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -20907,7 +21515,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -20917,7 +21525,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -20927,7 +21535,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -20937,7 +21545,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -20947,7 +21555,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -20957,7 +21565,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -20967,7 +21575,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -20977,7 +21585,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -20987,7 +21595,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -20997,7 +21605,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -21007,7 +21615,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -21017,7 +21625,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -21027,7 +21635,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -21037,7 +21645,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -21047,7 +21655,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -21057,7 +21665,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -21067,7 +21675,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -21077,7 +21685,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -21087,7 +21695,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -21097,7 +21705,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -21107,7 +21715,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -21117,7 +21725,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -21127,7 +21735,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -21137,7 +21745,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -21147,7 +21755,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -21157,7 +21765,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -21167,7 +21775,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -21177,7 +21785,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -21187,7 +21795,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -21197,7 +21805,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -21207,7 +21815,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -21217,7 +21825,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -21227,7 +21835,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -21237,7 +21845,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -21247,7 +21855,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -21257,7 +21865,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -21267,7 +21875,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -21277,7 +21885,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -21287,10 +21895,30 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Wealth management &amp; employee benefits</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Dermatology clinic</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pilates studio (multi-site)</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T236"/>
+  <dimension ref="A1:T242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20860,8 +20860,520 @@
       </c>
       <c r="T236" s="3" t="inlineStr"/>
     </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>Christopher Robin Day Nurseries</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Private nursery (Montessori, multi-site)</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Cranleigh &amp; Woking, Surrey</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>https://www.daynurseriessurrey.co.uk</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>admin@christopherrobin.co.uk</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>01483 339 406</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr"/>
+      <c r="I237" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/christopherrobinnurseries</t>
+        </is>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t>Family-run Montessori group, 30+ years, 4+ sites across Surrey; nursery fees £15k+/year per child with sibling/multi-year retention</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O237" s="3" t="inlineStr">
+        <is>
+          <t>Facebook page; per-site listings</t>
+        </is>
+      </c>
+      <c r="P237" s="3" t="inlineStr">
+        <is>
+          <t>Corporate nursery chains (Bright Horizons, N Family, Grandir) heavily outspend on search in the same towns</t>
+        </is>
+      </c>
+      <c r="Q237" s="3" t="inlineStr">
+        <is>
+          <t>'30 years family-run Montessori vs corporate chains - own the AI answer for "independent nursery Guildford"'</t>
+        </is>
+      </c>
+      <c r="R237" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S237" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T237" s="3" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>Ramsac</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>IT support / MSP</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Guildford (Old Portsmouth Rd)</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ramsac.com</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>01483 412 040</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr"/>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/ramsac.ltd</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning Surrey MSP with cybersecurity specialism; recurring SME contracts = high client LTV</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning brand; thought-leadership positioning</t>
+        </is>
+      </c>
+      <c r="P238" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning status not automatically an AI-search citation advantage over Akita/Wessex IT</t>
+        </is>
+      </c>
+      <c r="Q238" s="3" t="inlineStr">
+        <is>
+          <t>'Award-winning Guildford IT support - make sure that's what AI says when SMEs ask'</t>
+        </is>
+      </c>
+      <c r="R238" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S238" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T238" s="3" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>LP Networks</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>IT support / MSP</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Woking (serves Surrey: Reigate/Redhill/Guildford/Morden)</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>https://lpnetworks.com</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr"/>
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="4" t="inlineStr"/>
+      <c r="I239" s="4" t="inlineStr"/>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>Fixed-price MSP model across 5+ Surrey towns; recurring monthly contracts</t>
+        </is>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M239" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N239" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O239" s="4" t="inlineStr">
+        <is>
+          <t>Fixed-price packaging = marketing-aware</t>
+        </is>
+      </c>
+      <c r="P239" s="4" t="inlineStr">
+        <is>
+          <t>Multi-town coverage but generic 'IT support Surrey' searches won by bigger regional players</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="inlineStr">
+        <is>
+          <t>Per-town local SEO to match the fixed-price, multi-town service promise</t>
+        </is>
+      </c>
+      <c r="R239" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S239" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Wessex IT</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>IT support / MSP</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wessexit.com</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr"/>
+      <c r="G240" s="4" t="inlineStr"/>
+      <c r="H240" s="4" t="inlineStr"/>
+      <c r="I240" s="4" t="inlineStr"/>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>Supports 250+ Guildford-area businesses; established SME-focused MSP</t>
+        </is>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L240" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M240" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N240" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O240" s="4" t="inlineStr">
+        <is>
+          <t>250+ client claim promoted</t>
+        </is>
+      </c>
+      <c r="P240" s="4" t="inlineStr">
+        <is>
+          <t>Client-base size claim not leveraged as an AI-search trust signal</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="inlineStr">
+        <is>
+          <t>'250+ Surrey businesses trust us' - turn that into the AEO-cited proof point</t>
+        </is>
+      </c>
+      <c r="R240" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S240" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T240" s="4" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Huggins Lewis Foskett Solicitors</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Law firm (wills &amp; probate)</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>South Woodford, East London</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hugginslaw.co.uk</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>020 8989 3000</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>Simon Huggins (Partner, Head of Wills &amp; Probate)</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr"/>
+      <c r="I241" s="4" t="inlineStr"/>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>Long-established East London firm; contentious probate specialism = high-value, high-stress client searches</t>
+        </is>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M241" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N241" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O241" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P241" s="4" t="inlineStr">
+        <is>
+          <t>Contentious probate searches are high-intent but dominated by London-wide specialist brands (Osbornes, Russell-Cooke)</t>
+        </is>
+      </c>
+      <c r="Q241" s="4" t="inlineStr">
+        <is>
+          <t>'When families fight over an estate, they Google fast - be the East London name that comes up'</t>
+        </is>
+      </c>
+      <c r="R241" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S241" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Waymont Consulting</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Business/technical consultancy</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Research Park, Guildford</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>https://surrey-research-park.com/company/waymont-consulting</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr"/>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>Dave Waymont (Founder, est. 2000)</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr"/>
+      <c r="I242" s="4" t="inlineStr"/>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>25-year technical/business consultancy based at Surrey Research Park; established B2B relationships</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M242" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O242" s="4" t="inlineStr">
+        <is>
+          <t>Research Park location = credibility signal</t>
+        </is>
+      </c>
+      <c r="P242" s="4" t="inlineStr">
+        <is>
+          <t>Prestigious location not converted into search-driven new client acquisition</t>
+        </is>
+      </c>
+      <c r="Q242" s="4" t="inlineStr">
+        <is>
+          <t>Location + longevity as the AEO trust signal for Surrey SME consultancy searches</t>
+        </is>
+      </c>
+      <c r="R242" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S242" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T242" s="4" t="inlineStr">
+        <is>
+          <t>Confirm direct website/contact before outreach</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T236"/>
+  <autoFilter ref="A1:T242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20872,7 +21384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -20892,7 +21404,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -20995,17 +21507,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -21015,7 +21527,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -21025,7 +21537,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -21035,17 +21547,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -21055,7 +21567,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -21065,7 +21577,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -21075,7 +21587,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -21085,7 +21597,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -21095,7 +21607,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -21105,7 +21617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -21115,17 +21627,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -21135,7 +21647,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -21145,7 +21657,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -21155,7 +21667,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -21165,7 +21677,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -21175,7 +21687,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -21185,7 +21697,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -21195,7 +21707,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -21205,7 +21717,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -21215,7 +21727,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -21225,7 +21737,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -21235,7 +21747,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -21245,7 +21757,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -21919,6 +22431,36 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Private nursery (Montessori, multi-site)</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Law firm (wills &amp; probate)</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Business/technical consultancy</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$246</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T242"/>
+  <dimension ref="A1:T246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -21372,8 +21372,376 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Brock Taylor</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Horsham &amp; Haywards Heath, West Sussex</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>https://brocktaylor.co.uk</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>horshamsales@brocktaylor.co.uk</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>01403 272 022</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Peter &amp; Lucy Maskell (Owners, since 2007); founded 1992</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/brock-taylor</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/brocktaylor.estate.agents</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>'Best Agent in West Sussex' 12 years running; 2-office independent with award pedigree and active social presence</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>Instagram/YouTube presence; 12 consecutive award wins</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning status not fully converted into AI-search citation dominance</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>'12 years as West Sussex's best agent - make AI say so, not just the award ceremony'</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
+          <t>Strong existing marketing awareness = easy upsell conversation</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>Clark &amp; Company</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Haywards Heath, West Sussex</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>https://clarkandcompany.co.uk</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>mclark2302@aol.com</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>01444 416 376</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>Mitch Clark (Founder &amp; Managing Partner, 2nd generation)</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/clark-&amp;-co</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr"/>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t>Second-generation family accountancy firm covering Haywards Heath to Brighton/Crawley/Oxted - wide recurring-fee catchment</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="inlineStr">
+        <is>
+          <t>AOL email address - low marketing infrastructure</t>
+        </is>
+      </c>
+      <c r="P244" s="3" t="inlineStr">
+        <is>
+          <t>Wide geographic coverage undermined by dated digital presence (AOL email is the tell)</t>
+        </is>
+      </c>
+      <c r="Q244" s="3" t="inlineStr">
+        <is>
+          <t>'You cover 12 towns but your email address is stuck in 2005 - let's fix the whole funnel'</t>
+        </is>
+      </c>
+      <c r="R244" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S244" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T244" s="3" t="inlineStr">
+        <is>
+          <t>AOL email = same infrastructure-gap wedge as Gmail-contact prospects elsewhere in the database</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>Rose Chapman Architects</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Architects &amp; interior design</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Haywards Heath, West Sussex</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>https://rosechapmanarchitects.com</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>nicholas@rosechapmanarchitects.com</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>07429 074995</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>Rose Chapman / Nicholas (Founders)</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr"/>
+      <c r="I245" s="4" t="inlineStr"/>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>Combined architecture + interior design studio covering listed buildings across Sussex/Brighton/London; young practice building reputation</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N245" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O245" s="4" t="inlineStr">
+        <is>
+          <t>Active journal/blog content</t>
+        </is>
+      </c>
+      <c r="P245" s="4" t="inlineStr">
+        <is>
+          <t>New practice (2022) needs to build search authority fast in a competitive Sussex market</t>
+        </is>
+      </c>
+      <c r="Q245" s="4" t="inlineStr">
+        <is>
+          <t>Ground-floor AEO investment while the practice is still establishing its market position</t>
+        </is>
+      </c>
+      <c r="R245" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S245" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T245" s="4" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>DHP Dental Healthcare Practice</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Private/NHS dentist</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>North Heath Lane, Horsham, Sussex</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>https://dhp.dental</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>info@dhp.dental</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>01403 259 717</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr"/>
+      <c r="H246" s="4" t="inlineStr"/>
+      <c r="I246" s="4" t="inlineStr"/>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>Modern family dental practice in Horsham; mixed private/NHS model with upsell potential to cosmetic/implant work</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L246" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O246" s="4" t="inlineStr">
+        <is>
+          <t>Rebranded domain (dhp.dental) suggests marketing awareness</t>
+        </is>
+      </c>
+      <c r="P246" s="4" t="inlineStr">
+        <is>
+          <t>New domain/brand needs search authority built from scratch</t>
+        </is>
+      </c>
+      <c r="Q246" s="4" t="inlineStr">
+        <is>
+          <t>Early-mover AEO advantage while rebrand is still fresh</t>
+        </is>
+      </c>
+      <c r="R246" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S246" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T246" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T242"/>
+  <autoFilter ref="A1:T246"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21384,7 +21752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21404,7 +21772,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
@@ -21467,17 +21835,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -21487,7 +21855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -21497,11 +21865,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -22461,6 +22829,26 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Architects &amp; interior design</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Private/NHS dentist</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$254</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T246"/>
+  <dimension ref="A1:T254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -21740,8 +21740,700 @@
       </c>
       <c r="T246" s="4" t="inlineStr"/>
     </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Bath Kitchen Company</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; bathroom design</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Bath, Somerset</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>https://bathkitchencompany.co.uk</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr"/>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>James Horsfall (Owner)</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/james-horsfall-6b71a711</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr"/>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>Independent handmade-kitchen specialist, 30+ years trading in Bath; bespoke kitchen projects worth £20-80k each</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O247" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P247" s="3" t="inlineStr">
+        <is>
+          <t>National kitchen chains (Wren, Magnet) outspend on 'kitchen design Bath' search terms</t>
+        </is>
+      </c>
+      <c r="Q247" s="3" t="inlineStr">
+        <is>
+          <t>'A £40k bespoke kitchen deserves a bespoke marketing plan, not just a showroom visit'</t>
+        </is>
+      </c>
+      <c r="R247" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S247" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T247" s="3" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Somerset Kitchens Design Studio</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; bathroom design</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Wrington (serves Bristol/Bath)</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>https://www.somersetkitchendesignstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr"/>
+      <c r="G248" s="4" t="inlineStr"/>
+      <c r="H248" s="4" t="inlineStr"/>
+      <c r="I248" s="4" t="inlineStr"/>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>Family-run bespoke kitchen/bathroom designer serving Bristol and Bath from one Somerset base</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O248" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P248" s="4" t="inlineStr">
+        <is>
+          <t>Two-city catchment but single-location search visibility limits reach</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="inlineStr">
+        <is>
+          <t>Own both 'kitchen designer Bristol' and 'kitchen designer Bath' from one business</t>
+        </is>
+      </c>
+      <c r="R248" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S248" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>BK11 (Bathroom &amp; Kitchen 11)</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; bathroom design</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Long Ditton, Surrey (serves Esher/Cobham/Surbiton)</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>https://bathroomandkitcheneleven.co.uk</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr"/>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>Ben (Managing Director)</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr"/>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning luxury bathroom/kitchen showroom in the heart of wealthy Surrey; projects £30-100k+</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O249" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning branding</t>
+        </is>
+      </c>
+      <c r="P249" s="3" t="inlineStr">
+        <is>
+          <t>Awards not converted into AI-search dominance for Esher/Cobham searches</t>
+        </is>
+      </c>
+      <c r="Q249" s="3" t="inlineStr">
+        <is>
+          <t>'Award-winning Surrey design should be the AI's answer, not just the showroom's trophy cabinet'</t>
+        </is>
+      </c>
+      <c r="R249" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S249" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>AJM Removals Bristol</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Removals company</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Fishponds Rd, Bristol</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>https://ajm-removals-bristol.co.uk</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>contact@ajmremovals.co.uk</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>0117 251 0113</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>Artjom "AJ" (Founder, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr"/>
+      <c r="I250" s="4" t="inlineStr"/>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>Owner personally oversees every move since 2011; £1m public liability insurance signals a serious, insured operation worth more than budget rivals</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O250" s="4" t="inlineStr">
+        <is>
+          <t>Insurance credentials promoted</t>
+        </is>
+      </c>
+      <c r="P250" s="4" t="inlineStr">
+        <is>
+          <t>Man-and-van budget competitors and national brands (Bishop's Move) both crowd 'removals Bristol' search</t>
+        </is>
+      </c>
+      <c r="Q250" s="4" t="inlineStr">
+        <is>
+          <t>'Fully insured, owner-managed removals vs a stranger with a van - own that trust gap in AI answers'</t>
+        </is>
+      </c>
+      <c r="R250" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S250" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T250" s="4" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>Clarkson's Independent Funeral Directors</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Funeral directors</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Bath, Frome &amp; Saltford (Bristol)</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>https://www.clarksonsfuneraldirectors.co.uk</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>01225 426 822</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>Carol Spalding &amp; Sophie May (mother &amp; daughter, Owners)</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr"/>
+      <c r="I251" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/ClarksonsBathFromeSaltford</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>Family-run across 3 sites; funerals are high-emotion, high-value, once-only decisions researched urgently online</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O251" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; multi-site coverage</t>
+        </is>
+      </c>
+      <c r="P251" s="3" t="inlineStr">
+        <is>
+          <t>Corporate funeral groups (Dignity, Co-op Funeralcare) dominate search visibility despite worse reputations</t>
+        </is>
+      </c>
+      <c r="Q251" s="3" t="inlineStr">
+        <is>
+          <t>'Grieving families search fast and trust local - be the independent name Google and AI recommend over the corporates'</t>
+        </is>
+      </c>
+      <c r="R251" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S251" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T251" s="3" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Hebden Pople Independent Funerals</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Funeral directors</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>Stockwood, South Bristol</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>https://hebdenpople.co.uk</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>01275 563 422</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr"/>
+      <c r="H252" s="4" t="inlineStr"/>
+      <c r="I252" s="4" t="inlineStr"/>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>Family-run independent serving Bristol/Bath/South Gloucestershire; approachable positioning differentiates from corporate chains</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N252" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O252" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P252" s="4" t="inlineStr">
+        <is>
+          <t>Same corporate-chain search dominance problem as Clarkson's</t>
+        </is>
+      </c>
+      <c r="Q252" s="4" t="inlineStr">
+        <is>
+          <t>'Approachable, independent, local' - own that AEO positioning against Dignity/Co-op</t>
+        </is>
+      </c>
+      <c r="R252" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S252" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T252" s="4" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>Guildford Chiropractic Centre</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Chiropractor</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>https://www.guildfordchiropractic.co.uk</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>info@guildfordchiropractic.co.uk</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>01483 562 830</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>Founded by Donald &amp; Elizabeth Bennett, 1953 (multi-generation family)</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr"/>
+      <c r="I253" s="3" t="inlineStr"/>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>70+ years trading, multi-generational chiropractic family - genuinely rare heritage in a competitive Surrey market</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O253" s="3" t="inlineStr">
+        <is>
+          <t>70-year heritage</t>
+        </is>
+      </c>
+      <c r="P253" s="3" t="inlineStr">
+        <is>
+          <t>Decades of trust invisible against newer, better-marketed rivals (Health in Motion, GW Osteopathy)</t>
+        </is>
+      </c>
+      <c r="Q253" s="3" t="inlineStr">
+        <is>
+          <t>'70 years and three generations of Bennetts - the AI answer should reflect that, not just Google Maps'</t>
+        </is>
+      </c>
+      <c r="R253" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S253" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Health In Motion</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Guildford &amp; Surbiton, Surrey</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>https://healthinmotiononline.co.uk</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>01483 310 440</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>Dominic Malone (Founder, 10+ years)</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr"/>
+      <c r="I254" s="4" t="inlineStr"/>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>Two-town osteopathy/wellness practice; founder-led with over a decade of trading</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L254" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M254" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N254" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O254" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P254" s="4" t="inlineStr">
+        <is>
+          <t>Two-town coverage undermined by single-location search visibility</t>
+        </is>
+      </c>
+      <c r="Q254" s="4" t="inlineStr">
+        <is>
+          <t>Own both Guildford AND Surbiton osteopathy searches from one founder-led brand</t>
+        </is>
+      </c>
+      <c r="R254" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S254" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T254" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T246"/>
+  <autoFilter ref="A1:T254"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21752,7 +22444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21772,7 +22464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5">
@@ -21935,7 +22627,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -21945,7 +22637,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -21955,7 +22647,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -21965,7 +22657,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -21975,7 +22667,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -21985,7 +22677,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -21995,7 +22687,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -22005,37 +22697,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Kitchen &amp; bathroom design</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -22045,7 +22737,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -22055,7 +22747,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -22065,7 +22757,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -22075,7 +22767,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -22085,7 +22777,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -22095,7 +22787,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -22105,7 +22797,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -22115,7 +22807,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -22125,7 +22817,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -22135,27 +22827,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -22165,7 +22857,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -22175,7 +22867,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -22185,7 +22877,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -22195,7 +22887,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -22205,7 +22897,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -22215,7 +22907,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -22225,7 +22917,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -22235,7 +22927,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -22245,7 +22937,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -22255,7 +22947,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -22265,7 +22957,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -22275,7 +22967,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -22285,7 +22977,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -22295,7 +22987,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -22305,7 +22997,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -22315,7 +23007,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -22325,7 +23017,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -22335,7 +23027,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -22345,7 +23037,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -22355,7 +23047,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -22365,7 +23057,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -22375,7 +23067,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -22385,7 +23077,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -22395,7 +23087,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -22405,7 +23097,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -22415,7 +23107,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -22425,7 +23117,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -22435,7 +23127,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -22445,7 +23137,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -22455,7 +23147,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -22465,7 +23157,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -22475,7 +23167,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -22485,7 +23177,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -22495,7 +23187,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -22505,7 +23197,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -22515,7 +23207,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -22525,7 +23217,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -22535,7 +23227,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -22545,7 +23237,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -22555,7 +23247,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -22565,7 +23257,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -22575,7 +23267,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -22585,7 +23277,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -22595,7 +23287,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -22605,7 +23297,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -22615,7 +23307,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -22625,7 +23317,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -22635,7 +23327,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -22645,7 +23337,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -22655,7 +23347,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -22665,7 +23357,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -22675,7 +23367,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -22685,7 +23377,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -22695,7 +23387,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -22705,7 +23397,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -22715,7 +23407,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -22725,7 +23417,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -22735,7 +23427,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -22745,7 +23437,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -22755,7 +23447,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -22765,7 +23457,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -22775,7 +23467,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -22785,7 +23477,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -22795,7 +23487,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -22805,7 +23497,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -22815,7 +23507,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -22825,7 +23517,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -22835,7 +23527,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -22845,10 +23537,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>Business/technical consultancy</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Architects &amp; interior design</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>Private/NHS dentist</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Removals company</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T254"/>
+  <dimension ref="A1:T261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22432,8 +22432,604 @@
       </c>
       <c r="T254" s="4" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Little Green Rooms</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Garden rooms / outbuildings</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Gloucester Road, Bishopston, Bristol</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>https://littlegreenrooms.co.uk</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr"/>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>Jack (Founder, launched during lockdown)</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/little_green_rooms</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability-led garden room maker with a Bristol showroom; work-from-home boom drove strong demand, projects £15-40k</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M255" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N255" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O255" s="4" t="inlineStr">
+        <is>
+          <t>Instagram presence; showroom</t>
+        </is>
+      </c>
+      <c r="P255" s="4" t="inlineStr">
+        <is>
+          <t>National garden-room brands (Crane, Cabin Master) outspend on generic search terms</t>
+        </is>
+      </c>
+      <c r="Q255" s="4" t="inlineStr">
+        <is>
+          <t>'Sustainable, Bristol-made garden rooms deserve to beat national brands in local search'</t>
+        </is>
+      </c>
+      <c r="R255" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S255" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T255" s="4" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>Garden Rooms by Drumbeat</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Garden rooms / outbuildings</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Surrey &amp; South East</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>https://gardenroomsbydrumbeat.co.uk</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>01483 768 273</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr"/>
+      <c r="H256" s="3" t="inlineStr"/>
+      <c r="I256" s="3" t="inlineStr"/>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>30 years' design &amp; build experience in Surrey's wealthy commuter belt; premium garden offices/studios</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O256" s="3" t="inlineStr">
+        <is>
+          <t>30-year heritage promoted</t>
+        </is>
+      </c>
+      <c r="P256" s="3" t="inlineStr">
+        <is>
+          <t>Three decades of trust not converted into AI-search dominance vs newer brands</t>
+        </is>
+      </c>
+      <c r="Q256" s="3" t="inlineStr">
+        <is>
+          <t>'30 years building Surrey's garden rooms - make sure AI still recommends the original'</t>
+        </is>
+      </c>
+      <c r="R256" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S256" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T256" s="3" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>S&amp;D Paving &amp; Landscaping</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Driveways &amp; landscaping</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Epsom, Surrey</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sanddpaving.co.uk</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr"/>
+      <c r="G257" s="4" t="inlineStr"/>
+      <c r="H257" s="4" t="inlineStr"/>
+      <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>Established 2008, FSB/Tobermore/Bradstone accredited; driveway/patio jobs £5-20k in premium Surrey postcodes</t>
+        </is>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N257" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O257" s="4" t="inlineStr">
+        <is>
+          <t>Trade accreditations</t>
+        </is>
+      </c>
+      <c r="P257" s="4" t="inlineStr">
+        <is>
+          <t>Checkatrade/MyBuilder intercept driveway searches before firms are found directly</t>
+        </is>
+      </c>
+      <c r="Q257" s="4" t="inlineStr">
+        <is>
+          <t>'Stop paying Checkatrade for leads to your own jobs - own "driveways Epsom" outright'</t>
+        </is>
+      </c>
+      <c r="R257" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S257" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T257" s="4" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Midelney Manor</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Langport, Somerset</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.midelneymanor.co.uk</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>01458 252 377</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Alice &amp; Jeremy (Family owners, 500-year family estate)</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>Elizabethan manor in family hands for 500 years; deliberately limited to ~10 weddings/summer = ultra-premium exclusivity</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>Bespoke/exclusive positioning; multiple directory listings</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>500-year family story is an extraordinary AEO asset currently used only for directory listings</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>'500 years in one family - the rarest wedding-venue story in Somerset deserves to be the AI's answer too'</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional, hard-to-replicate brand story - high-value low-effort AEO win</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>Ash Barton Estate</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ashbarton.com</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr"/>
+      <c r="G259" s="3" t="inlineStr"/>
+      <c r="H259" s="3" t="inlineStr"/>
+      <c r="I259" s="3" t="inlineStr"/>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>Grade II* listed 15th-century manor on 25 acres; flexible format (marquee/barn/festival/chapel) suits multiple wedding styles</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
+          <t>Polished dedicated wedding site</t>
+        </is>
+      </c>
+      <c r="P259" s="3" t="inlineStr">
+        <is>
+          <t>Format flexibility not leveraged as a distinct AEO angle vs single-format rivals</t>
+        </is>
+      </c>
+      <c r="Q259" s="3" t="inlineStr">
+        <is>
+          <t>'One venue, four wedding styles' - own that flexibility positioning in AI answers</t>
+        </is>
+      </c>
+      <c r="R259" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S259" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>Huntsham Court</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Wedding &amp; event venue</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Devon (Exmoor border)</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>https://www.huntshamcourt.co.uk</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr"/>
+      <c r="G260" s="3" t="inlineStr"/>
+      <c r="H260" s="3" t="inlineStr"/>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning private-hire estate sleeping 100 across 42 bedrooms; ultra-high-value multi-day event bookings</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O260" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning branding</t>
+        </is>
+      </c>
+      <c r="P260" s="3" t="inlineStr">
+        <is>
+          <t>Scale (100 guests, 42 bedrooms) undersold as the AEO differentiator vs smaller venues</t>
+        </is>
+      </c>
+      <c r="Q260" s="3" t="inlineStr">
+        <is>
+          <t>Target 'large wedding venue Devon' AEO specifically - most rivals can't match the capacity</t>
+        </is>
+      </c>
+      <c r="R260" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S260" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T260" s="3" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>AV Trinity</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>IFA &amp; mortgage broker</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avtrinity.com</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>info@avtrinity.com</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>01892 612 500</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>Karen Vidler (Co-founder, est. 1986)</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/AVTrinity</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr"/>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1986 - nearly 40 years serving Kent/Sussex; combined IFA + mortgage broker = higher per-client value</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O261" s="3" t="inlineStr">
+        <is>
+          <t>Community page; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P261" s="3" t="inlineStr">
+        <is>
+          <t>40 years of trust competing with newer, more search-savvy brokers for the same Kent/Sussex clients</t>
+        </is>
+      </c>
+      <c r="Q261" s="3" t="inlineStr">
+        <is>
+          <t>'40 years of independent advice in Tunbridge Wells - the AI answer should say so, not just Unbiased.co.uk'</t>
+        </is>
+      </c>
+      <c r="R261" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S261" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T261" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T254"/>
+  <autoFilter ref="A1:T261"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22444,7 +23040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22464,7 +23060,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -22487,7 +23083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -22497,21 +23093,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -22847,17 +23443,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -22867,7 +23463,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -22877,7 +23473,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -22887,7 +23483,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -22897,7 +23493,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -22907,7 +23503,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -22917,7 +23513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -22927,7 +23523,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -22937,7 +23533,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -22947,7 +23543,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -22957,7 +23553,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -22967,7 +23563,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -22977,7 +23573,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -22987,7 +23583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -22997,7 +23593,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -23007,7 +23603,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -23017,7 +23613,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -23027,7 +23623,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -23037,7 +23633,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -23047,7 +23643,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -23057,7 +23653,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -23067,7 +23663,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23077,7 +23673,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23087,7 +23683,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23097,7 +23693,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23107,7 +23703,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23117,7 +23713,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23127,7 +23723,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23137,7 +23733,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23147,7 +23743,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23157,7 +23753,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23167,7 +23763,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -23177,7 +23773,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -23187,7 +23783,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -23197,7 +23793,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -23207,7 +23803,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -23217,7 +23813,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -23227,7 +23823,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -23237,7 +23833,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -23247,7 +23843,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -23257,7 +23853,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -23267,7 +23863,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -23277,7 +23873,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -23287,7 +23883,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -23297,7 +23893,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -23307,7 +23903,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -23317,7 +23913,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -23327,7 +23923,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -23337,7 +23933,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -23347,7 +23943,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -23357,7 +23953,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -23367,7 +23963,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -23377,7 +23973,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -23387,7 +23983,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -23397,7 +23993,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -23407,7 +24003,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -23417,7 +24013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -23427,7 +24023,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -23437,7 +24033,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -23447,7 +24043,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -23457,7 +24053,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -23467,7 +24063,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -23477,7 +24073,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -23487,7 +24083,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -23497,7 +24093,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -23507,7 +24103,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -23517,7 +24113,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -23527,7 +24123,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -23537,7 +24133,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -23547,7 +24143,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -23557,7 +24153,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -23567,10 +24163,50 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>Private/NHS dentist</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>Removals company</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Driveways &amp; landscaping</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Wedding &amp; event venue</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IFA &amp; mortgage broker</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T261"/>
+  <dimension ref="A1:T266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23028,8 +23028,444 @@
       </c>
       <c r="T261" s="3" t="inlineStr"/>
     </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>The Private GP Clinic</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Underriver, Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theprivategpclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>info@theprivategpclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>01732 835 212</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr"/>
+      <c r="H262" s="3" t="inlineStr"/>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>Independent private GP in rural Sevenoaks catchment; self-pay consultations with Saturday availability = strong convenience differentiator</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O262" s="3" t="inlineStr">
+        <is>
+          <t>Weekend opening hours promoted</t>
+        </is>
+      </c>
+      <c r="P262" s="3" t="inlineStr">
+        <is>
+          <t>KIMS Hospital and Nuffield Health private-GP brands dominate Kent private-GP search with hospital-scale marketing</t>
+        </is>
+      </c>
+      <c r="Q262" s="3" t="inlineStr">
+        <is>
+          <t>'Saturday appointments, no hospital wait - own that convenience story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R262" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S262" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>Dr Anita Aesthetics</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Mount Ephraim Rd, Tunbridge Wells (serves Sevenoaks)</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dranitaaesthetics.com</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr"/>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Dr Anita Madi (Founder, GMC public health specialist)</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr"/>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>Doctor-led, GMC-registered aesthetic doctor serving two wealthy Kent towns from one clinic; genuine medical credential differentiator</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="inlineStr">
+        <is>
+          <t>Dual-town service pages (Tunbridge Wells + Sevenoaks)</t>
+        </is>
+      </c>
+      <c r="P263" s="3" t="inlineStr">
+        <is>
+          <t>Dual-town SEO pages exist but AI-answer citations still open for either town</t>
+        </is>
+      </c>
+      <c r="Q263" s="3" t="inlineStr">
+        <is>
+          <t>'A GMC-registered doctor doing your Botox' - the exact trust signal AEO content should carry</t>
+        </is>
+      </c>
+      <c r="R263" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S263" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Priory Lodge Vets</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Pembury Road, Tonbridge, Kent</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>https://www.plvet.co.uk</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>info@plvet.co.uk</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>01732 353 668</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr"/>
+      <c r="H264" s="4" t="inlineStr"/>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Priory-Lodge-Vets-100057128660958</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>Firmly independent small-animal practice in Tonbridge; explicit independence positioning vs corporate rivals</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M264" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N264" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O264" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P264" s="4" t="inlineStr">
+        <is>
+          <t>'Firmly independent' claim not yet the AI-cited answer against corporate vet groups</t>
+        </is>
+      </c>
+      <c r="Q264" s="4" t="inlineStr">
+        <is>
+          <t>Own 'independent vet Tonbridge' - their own positioning statement as the AEO target</t>
+        </is>
+      </c>
+      <c r="R264" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S264" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T264" s="4" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Hollow Rock Fitness</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Personal training gym</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>London Road, Riverhead, Sevenoaks</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hollowrockfitness.com</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>JFARMER101@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>07887 711664</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>James Farmer (Founder, 24+ years training experience)</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr"/>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/hollowrockfitness</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>Founder-led PT gym with nearly a quarter-century of coaching experience; ongoing client packages in affluent Sevenoaks</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L265" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M265" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N265" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O265" s="4" t="inlineStr">
+        <is>
+          <t>ClassPass/Fresha booking listings</t>
+        </is>
+      </c>
+      <c r="P265" s="4" t="inlineStr">
+        <is>
+          <t>Booking-platform discovery means paying commission on clients the gym could own directly</t>
+        </is>
+      </c>
+      <c r="Q265" s="4" t="inlineStr">
+        <is>
+          <t>'24 years of coaching experience - stop renting your leads from ClassPass, own the search instead'</t>
+        </is>
+      </c>
+      <c r="R265" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S265" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T265" s="4" t="inlineStr">
+        <is>
+          <t>Personal iCloud email - confirm before outreach, may prefer phone contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Thrive Personal Training</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Personal training gym</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thrive-personaltraining.co.uk</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr"/>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Luke French (Owner)</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr"/>
+      <c r="I266" s="4" t="inlineStr"/>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>Owner-led, second Tunbridge Wells location opened - proven growth and reinvestment in the local market</t>
+        </is>
+      </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L266" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M266" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N266" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O266" s="4" t="inlineStr">
+        <is>
+          <t>Two-site expansion</t>
+        </is>
+      </c>
+      <c r="P266" s="4" t="inlineStr">
+        <is>
+          <t>Second-site growth not matched by dominant local search share</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="inlineStr">
+        <is>
+          <t>'You've proven the model works twice - now make sure AI recommends both locations'</t>
+        </is>
+      </c>
+      <c r="R266" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S266" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T266" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T261"/>
+  <autoFilter ref="A1:T266"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23040,7 +23476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -23060,7 +23496,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
@@ -23117,7 +23553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -23133,17 +23569,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -23153,7 +23589,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -23163,7 +23599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -23173,17 +23609,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -23193,7 +23629,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -23453,17 +23889,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -23473,7 +23909,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -23483,7 +23919,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -23493,7 +23929,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -23503,7 +23939,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -23513,7 +23949,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -23523,7 +23959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -23533,7 +23969,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -23543,7 +23979,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -23553,7 +23989,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -23563,7 +23999,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -23573,7 +24009,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -23583,7 +24019,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -23593,7 +24029,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -23603,7 +24039,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -23613,7 +24049,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -23623,7 +24059,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -23633,7 +24069,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -23643,7 +24079,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -23653,7 +24089,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -23663,7 +24099,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -23673,7 +24109,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -23683,7 +24119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -23693,7 +24129,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -23703,7 +24139,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -23713,7 +24149,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -23723,7 +24159,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -23733,7 +24169,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -23743,7 +24179,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -23753,7 +24189,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -23763,7 +24199,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -23773,7 +24209,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -23783,7 +24219,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -23793,7 +24229,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -23803,7 +24239,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -23813,7 +24249,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -23823,7 +24259,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -23833,7 +24269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -23843,7 +24279,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -23853,7 +24289,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -23863,7 +24299,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -23873,7 +24309,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -23883,7 +24319,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -23893,7 +24329,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -23903,7 +24339,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -23913,7 +24349,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -23923,7 +24359,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -23933,7 +24369,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -23943,7 +24379,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -23953,7 +24389,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -23963,7 +24399,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -23973,7 +24409,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -23983,7 +24419,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -23993,7 +24429,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -24003,7 +24439,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -24013,7 +24449,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -24023,7 +24459,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -24033,7 +24469,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -24043,7 +24479,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -24053,7 +24489,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -24063,7 +24499,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -24073,7 +24509,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -24083,7 +24519,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -24093,7 +24529,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -24103,7 +24539,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -24113,7 +24549,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -24123,7 +24559,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -24133,7 +24569,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -24143,7 +24579,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -24153,7 +24589,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -24163,7 +24599,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -24173,7 +24609,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -24183,7 +24619,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -24193,7 +24629,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -24203,10 +24639,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>Wedding &amp; event venue</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B120" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T266"/>
+  <dimension ref="A1:T270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23464,8 +23464,364 @@
       </c>
       <c r="T266" s="4" t="inlineStr"/>
     </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>Tayler and Fletcher</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent &amp; chartered surveyors</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Stow-on-the-Wold, Bourton-on-the-Water, Chipping Norton</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>https://www.taylerandfletcher.co.uk</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>01451 798 056</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr"/>
+      <c r="H267" s="3" t="inlineStr"/>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/TaylerandFletcher</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>Leading independent covering the Cotswolds' most tourist-famous villages; residential + rural/agricultural property = high average fees</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O267" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 3-office coverage</t>
+        </is>
+      </c>
+      <c r="P267" s="3" t="inlineStr">
+        <is>
+          <t>Corporate premium brands (Knight Frank, Savills) also target Stow/Bourton for second-home buyers</t>
+        </is>
+      </c>
+      <c r="Q267" s="3" t="inlineStr">
+        <is>
+          <t>'Cotswolds second-home buyers research online for months - be the independent name AI recommends'</t>
+        </is>
+      </c>
+      <c r="R267" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S267" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T267" s="3" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>Birkmyre Property Consultants</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Marlborough, Wiltshire</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>https://www.birkmyrepc.co.uk</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>info@birkmyrepc.co.uk</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>01672 516 619</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>Dominic Birkmyre (Founder, MRICS, est. 2009)</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr"/>
+      <c r="I268" s="3" t="inlineStr"/>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>RICS-qualified founder with 25 years' experience; village/country property specialism across Wiltshire/Hampshire/Berkshire</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P268" s="3" t="inlineStr">
+        <is>
+          <t>Fine &amp; Country and Winkworth national brands dominate Marlborough search visibility</t>
+        </is>
+      </c>
+      <c r="Q268" s="3" t="inlineStr">
+        <is>
+          <t>'RICS-qualified, 25 years of country property expertise - the AI answer should say so'</t>
+        </is>
+      </c>
+      <c r="R268" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S268" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T268" s="3" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Films London</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Wedding photography &amp; videography</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>South London (serves London/Surrey/Kent/Herts/Essex)</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>https://weddingfilmslondon.co.uk</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr"/>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>Founder &amp; Kate (husband-and-wife team, est. 2008)</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/wedding.films.london</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr"/>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning team, 300+ weddings filmed since 2008; premium packages £2-5k+ per wedding across a huge catchment</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L269" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M269" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N269" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O269" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning branding; wide-area coverage</t>
+        </is>
+      </c>
+      <c r="P269" s="4" t="inlineStr">
+        <is>
+          <t>Wide catchment claim not matched by per-county search dominance</t>
+        </is>
+      </c>
+      <c r="Q269" s="4" t="inlineStr">
+        <is>
+          <t>Per-county AEO content to actually own the whole claimed coverage area</t>
+        </is>
+      </c>
+      <c r="R269" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S269" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T269" s="4" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>Estate Legal</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Commercial property litigation law firm</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Whiteladies Road, Clifton, Bristol (+ London)</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>https://estatelegal.co.uk</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>amyrudrum@estatelegal.co.uk</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>07825 336 680</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Bonnie Martin &amp; Amy Rudrum (Founders, ex-national-firm partners)</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr"/>
+      <c r="I270" s="3" t="inlineStr"/>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>Boutique property litigation specialists with 50+ years combined experience; niche expertise (Pubs Code, rent review) = high-value instructions</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O270" s="3" t="inlineStr">
+        <is>
+          <t>Detailed niche-service SEO pages (Pubs Code, dilapidations, rent review)</t>
+        </is>
+      </c>
+      <c r="P270" s="3" t="inlineStr">
+        <is>
+          <t>Deep niche content exists but AI-answer citations for these specific legal queries still open</t>
+        </is>
+      </c>
+      <c r="Q270" s="3" t="inlineStr">
+        <is>
+          <t>'You've written the definitive pages on Pubs Code disputes - let's make AI cite them, not just index them'</t>
+        </is>
+      </c>
+      <c r="R270" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S270" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T270" s="3" t="inlineStr">
+        <is>
+          <t>Sophisticated, marketing-literate founders - lead with AEO specifics, not basics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T266"/>
+  <autoFilter ref="A1:T270"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23476,7 +23832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -23496,7 +23852,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -23513,7 +23869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -24653,6 +25009,36 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estate agent &amp; chartered surveyors</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Wedding photography &amp; videography</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Commercial property litigation law firm</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$277</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T270"/>
+  <dimension ref="A1:T277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23820,8 +23820,620 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>Spiller Brooks Estate Agents</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Whitstable, Kent</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>https://spillerbrooks.co.uk</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>info@spillerbrooks.co.uk</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>01227 272 155</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Nikki Spiller (Owner, 17+ years experience)</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/SpillerbrooksEstateAgents</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>Truly independent, rebranded from Mark Smith Estate Agents; named 'one of the best in the UK'; coastal Kent premium market</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O271" s="3" t="inlineStr">
+        <is>
+          <t>National award recognition; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P271" s="3" t="inlineStr">
+        <is>
+          <t>National award status not converted into local/AI-search dominance for Whitstable searches</t>
+        </is>
+      </c>
+      <c r="Q271" s="3" t="inlineStr">
+        <is>
+          <t>'Named one of the UK's best agents - make sure that's what AI says for "estate agent Whitstable"'</t>
+        </is>
+      </c>
+      <c r="R271" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S271" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>County Estate Agents</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Whitstable (serves Tankerton/Herne Bay/Faversham/Canterbury)</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>https://www.countyestateagents.co.uk</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr"/>
+      <c r="G272" s="4" t="inlineStr"/>
+      <c r="H272" s="4" t="inlineStr"/>
+      <c r="I272" s="4" t="inlineStr"/>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>Long-established independent covering 4 East Kent coastal/market towns; residential, coastal and commercial property</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N272" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O272" s="4" t="inlineStr">
+        <is>
+          <t>Multi-town coverage</t>
+        </is>
+      </c>
+      <c r="P272" s="4" t="inlineStr">
+        <is>
+          <t>Wide catchment but single-brand search visibility thin per town</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own all 4 claimed markets</t>
+        </is>
+      </c>
+      <c r="R272" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S272" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T272" s="4" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Breadings</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Whitstable/East Kent</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr"/>
+      <c r="G273" s="4" t="inlineStr"/>
+      <c r="H273" s="4" t="inlineStr"/>
+      <c r="I273" s="4" t="inlineStr"/>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>Private independent trading 70+ years - genuinely rare longevity in East Kent property market</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M273" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N273" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O273" s="4" t="inlineStr">
+        <is>
+          <t>70-year heritage</t>
+        </is>
+      </c>
+      <c r="P273" s="4" t="inlineStr">
+        <is>
+          <t>Decades of trust untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q273" s="4" t="inlineStr">
+        <is>
+          <t>'70 years of Kentish property trust deserves to be the AI's answer too'</t>
+        </is>
+      </c>
+      <c r="R273" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S273" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T273" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Clifton Architects</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>Cliftonwood, Bristol</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>http://www.cliftonarchitects.com</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr"/>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>Amanda Webb (Founder, 30+ years experience)</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/amanda-webb-052b455a</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr"/>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>Founder with 20 years at a prior Bristol practice before establishing her own; deep local residential experience</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M274" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N274" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O274" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P274" s="4" t="inlineStr">
+        <is>
+          <t>30 years of Bristol residential expertise invisible in modern search</t>
+        </is>
+      </c>
+      <c r="Q274" s="4" t="inlineStr">
+        <is>
+          <t>Portfolio-driven AEO content leveraging three decades of local project history</t>
+        </is>
+      </c>
+      <c r="R274" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S274" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T274" s="4" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>Sussex Solar</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Solar installer</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Horsham, West Sussex (serves Sussex/Surrey/Kent/Hampshire)</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>https://sussexsolar.com</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>01403 371 000</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Andy Baxter (Founder, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Sussex-Solar-Ltd-100043388126281</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr"/>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned since 2005, MCS-certified across 4 counties; solar installs £8-20k each in a booming demand market</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O275" s="3" t="inlineStr">
+        <is>
+          <t>20-year trading history; Facebook page</t>
+        </is>
+      </c>
+      <c r="P275" s="3" t="inlineStr">
+        <is>
+          <t>National lead-gen platforms (Sunsave, Solar Guide) intercept searches across all 4 counties</t>
+        </is>
+      </c>
+      <c r="Q275" s="3" t="inlineStr">
+        <is>
+          <t>'Stop paying national lead-gen sites for leads in your own 4-county patch'</t>
+        </is>
+      </c>
+      <c r="R275" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S275" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T275" s="3" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>i2i Recruitment</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Recruitment agency</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham (South West)</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>https://i2irecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>richard@i2irecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>01242 771 021</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>Charlie (Founder); Richard Ogden-Metherell (CEO)</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/i2i-recruitment</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/i2irecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t>Certified B Corp independent recruiter with a personal, relationship-led positioning; placement fees + repeat SME clients</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="inlineStr">
+        <is>
+          <t>B Corp certification; active socials</t>
+        </is>
+      </c>
+      <c r="P276" s="3" t="inlineStr">
+        <is>
+          <t>B Corp status is a strong ethical differentiator not yet leveraged in AI-search answers</t>
+        </is>
+      </c>
+      <c r="Q276" s="3" t="inlineStr">
+        <is>
+          <t>'B Corp-certified recruitment - own the AI answer for "ethical recruiter Cheltenham"'</t>
+        </is>
+      </c>
+      <c r="R276" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S276" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T276" s="3" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>The Burford Recruitment Company</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Recruitment agency (boutique)</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>Burford, West Oxfordshire (Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.burfordrecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+      <c r="G277" s="4" t="inlineStr"/>
+      <c r="H277" s="4" t="inlineStr"/>
+      <c r="I277" s="4" t="inlineStr"/>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning boutique agency est. 2016 covering office/professional/creative/finance roles across the Cotswolds</t>
+        </is>
+      </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N277" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O277" s="4" t="inlineStr">
+        <is>
+          <t>Award-winning branding</t>
+        </is>
+      </c>
+      <c r="P277" s="4" t="inlineStr">
+        <is>
+          <t>Boutique positioning in a rural catchment with less digital competition than cities - genuinely winnable</t>
+        </is>
+      </c>
+      <c r="Q277" s="4" t="inlineStr">
+        <is>
+          <t>Own 'recruitment agency Cotswolds' outright - thin competition for this exact query</t>
+        </is>
+      </c>
+      <c r="R277" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S277" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T277" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T270"/>
+  <autoFilter ref="A1:T277"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23832,7 +24444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -23852,7 +24464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5">
@@ -23869,23 +24481,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -23955,7 +24567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -23965,7 +24577,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -23975,17 +24587,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -24005,17 +24617,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -24025,7 +24637,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -24035,7 +24647,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -24045,7 +24657,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -24055,7 +24667,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -24065,7 +24677,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -25039,6 +25651,16 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Recruitment agency (boutique)</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$277</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$283</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T277"/>
+  <dimension ref="A1:T283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24432,8 +24432,532 @@
       </c>
       <c r="T277" s="4" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>Airwave AV</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Home cinema &amp; smart home installer</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Surrey &amp; Greater London</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>https://airwaveav.co.uk</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>020 8243 8547</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr"/>
+      <c r="H278" s="3" t="inlineStr"/>
+      <c r="I278" s="3" t="inlineStr"/>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t>Control4 smart-home specialist for premium Surrey/London homes; installs £10-50k+ per project with ongoing service contracts</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
+          <t>Control4 dealer accreditation</t>
+        </is>
+      </c>
+      <c r="P278" s="3" t="inlineStr">
+        <is>
+          <t>Multiple similar-positioned rivals (Vertex AV, Lighthouse, New Wave AV) compete for identical high-net-worth clients</t>
+        </is>
+      </c>
+      <c r="Q278" s="3" t="inlineStr">
+        <is>
+          <t>'Own the AI answer for "Control4 installer Surrey" before the next AV firm does'</t>
+        </is>
+      </c>
+      <c r="R278" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S278" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T278" s="3" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Lighthouse</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Home cinema installer</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Thames Ditton, Surrey (serves London/South East)</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lighthouse-ltd.co.uk</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>020 3696 5257</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr"/>
+      <c r="H279" s="4" t="inlineStr"/>
+      <c r="I279" s="4" t="inlineStr"/>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>Luxury bespoke home cinema specialist in wealthy Surrey; project values easily £20-100k for full builds</t>
+        </is>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M279" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N279" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O279" s="4" t="inlineStr">
+        <is>
+          <t>Luxury brand positioning</t>
+        </is>
+      </c>
+      <c r="P279" s="4" t="inlineStr">
+        <is>
+          <t>Crowded 'home cinema installer London/Surrey' niche with many similarly-positioned rivals</t>
+        </is>
+      </c>
+      <c r="Q279" s="4" t="inlineStr">
+        <is>
+          <t>Differentiate via AEO on bespoke/luxury build specifics vs generic AV installers</t>
+        </is>
+      </c>
+      <c r="R279" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S279" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T279" s="4" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Ionaida</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Curtains, blinds &amp; upholstery</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>North Somerset &amp; Bristol</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ionaida.com</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>Rebecca Fawcett (Founder)</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr"/>
+      <c r="I280" s="4" t="inlineStr"/>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>Solo interior specialist with strong retail/design pedigree (ex-Bentalls, Monkwell Fabrics); bespoke curtain projects £2-10k per home</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M280" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N280" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O280" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P280" s="4" t="inlineStr">
+        <is>
+          <t>National made-to-measure chains (Hillarys, Style Studio) outspend on generic curtain-search terms</t>
+        </is>
+      </c>
+      <c r="Q280" s="4" t="inlineStr">
+        <is>
+          <t>'A design pedigree from Bentalls and Monkwell deserves better than losing to national chains on Google'</t>
+        </is>
+      </c>
+      <c r="R280" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S280" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T280" s="4" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Curtain Flair</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Bespoke curtains &amp; soft furnishings</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Bristol &amp; Bath</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.curtainflairltd.com</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>0117 986 7277</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>Alison (Principal)</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/curtainflairltd</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr"/>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 2003, hand-making in-house across Bristol/Bath; premium made-to-measure projects</t>
+        </is>
+      </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L281" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M281" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N281" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O281" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P281" s="4" t="inlineStr">
+        <is>
+          <t>20+ years of craftsmanship not converted into search-driven client acquisition</t>
+        </is>
+      </c>
+      <c r="Q281" s="4" t="inlineStr">
+        <is>
+          <t>'20 years of hand-made curtains vs a national chain's factory line - own that story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R281" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S281" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T281" s="4" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>Averys of Bristol</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Wine merchant</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Culver Street, Bristol</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>via directory/press coverage</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr"/>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>Mimi Avery (5th generation owner)</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr"/>
+      <c r="I282" s="3" t="inlineStr"/>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>227-year-old family wine merchant with historic vaulted cellar; extraordinary heritage story, high-value repeat/gifting clients</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O282" s="3" t="inlineStr">
+        <is>
+          <t>Historic brand; press coverage</t>
+        </is>
+      </c>
+      <c r="P282" s="3" t="inlineStr">
+        <is>
+          <t>227 years of history is an exceptional, almost un-copyable AEO asset currently underused for search</t>
+        </is>
+      </c>
+      <c r="Q282" s="3" t="inlineStr">
+        <is>
+          <t>'227 years and five generations - the rarest wine-merchant story in Bristol should be AI's answer too'</t>
+        </is>
+      </c>
+      <c r="R282" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S282" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T282" s="3" t="inlineStr">
+        <is>
+          <t>Confirm current live website before outreach - one of the most compelling heritage stories in the database</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>Janie Richardson School Search &amp; Placement</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Education consultancy (school placement)</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Fulham, London SW6</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>https://jrschoolsearch.com</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>janie@jrschoolsearch.co.uk</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>020 7731 0695</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>Janie Richardson (Founder)</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/janie-richardson-95557737</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr"/>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>Independent school-search consultant for relocating/international families; fees run into thousands per placement</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O283" s="3" t="inlineStr">
+        <is>
+          <t>Professional site; LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P283" s="3" t="inlineStr">
+        <is>
+          <t>Bigger consultancies (William Clarence, Keystone) outspend on 'school consultant London' search</t>
+        </is>
+      </c>
+      <c r="Q283" s="3" t="inlineStr">
+        <is>
+          <t>'Discreet, personal school placement vs a big consultancy brand - own that AEO positioning'</t>
+        </is>
+      </c>
+      <c r="R283" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S283" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T283" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T277"/>
+  <autoFilter ref="A1:T283"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24444,7 +24968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -24464,7 +24988,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -25661,6 +26185,66 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Home cinema &amp; smart home installer</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Home cinema installer</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Curtains, blinds &amp; upholstery</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bespoke curtains &amp; soft furnishings</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Wine merchant</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Education consultancy (school placement)</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$289</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T283"/>
+  <dimension ref="A1:T289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24956,8 +24956,528 @@
       </c>
       <c r="T283" s="3" t="inlineStr"/>
     </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>V&amp;H Homes</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; letting agent</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Ashtead (serves Epsom/Fetcham), Surrey</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>https://vhhomes.co.uk</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>sales@vhhomes.co.uk</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>01372 221 678</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>Paul Aboud (Founder, est. 2009)</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/VHHomes.EstateAgents</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>Family-run, 16 years established, leading agent in Ashtead; premium Surrey commuter-belt property fees</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O284" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P284" s="3" t="inlineStr">
+        <is>
+          <t>Cairds/Davies Property Partners compete for the same Epsom/Ashtead/Leatherhead searches</t>
+        </is>
+      </c>
+      <c r="Q284" s="3" t="inlineStr">
+        <is>
+          <t>'Leading agent in Ashtead - make AI say so, not just the local reputation'</t>
+        </is>
+      </c>
+      <c r="R284" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S284" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T284" s="3" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Cairds Estate Agents</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Epsom &amp; Ashtead, Surrey</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cairds.co.uk</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F285" s="4" t="inlineStr"/>
+      <c r="G285" s="4" t="inlineStr"/>
+      <c r="H285" s="4" t="inlineStr"/>
+      <c r="I285" s="4" t="inlineStr"/>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>Independent local business, 40+ years' experience in Epsom/Ashtead property market</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L285" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M285" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N285" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O285" s="4" t="inlineStr">
+        <is>
+          <t>40-year heritage</t>
+        </is>
+      </c>
+      <c r="P285" s="4" t="inlineStr">
+        <is>
+          <t>Four decades of trust untranslated into modern AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q285" s="4" t="inlineStr">
+        <is>
+          <t>'40 years in Epsom deserves to be the AI's answer, not just word-of-mouth'</t>
+        </is>
+      </c>
+      <c r="R285" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S285" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T285" s="4" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>Jackie Quinn Estate Agents</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Letting agent</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Ashtead/Epsom/Leatherhead/Dorking/Clapham/Balham</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jackiequinn.co.uk</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F286" s="4" t="inlineStr"/>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>Jackie Quinn (Founder)</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr"/>
+      <c r="I286" s="4" t="inlineStr"/>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>Wide-catchment independent letting specialist spanning Surrey and South London; landlord management fees recur</t>
+        </is>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M286" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N286" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O286" s="4" t="inlineStr">
+        <is>
+          <t>Multi-area coverage</t>
+        </is>
+      </c>
+      <c r="P286" s="4" t="inlineStr">
+        <is>
+          <t>Broad geographic claim not matched by per-area search dominance</t>
+        </is>
+      </c>
+      <c r="Q286" s="4" t="inlineStr">
+        <is>
+          <t>Per-town landlord-focused AEO content across the whole claimed footprint</t>
+        </is>
+      </c>
+      <c r="R286" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S286" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T286" s="4" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>Elite Tuition Collective</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Private tuition agency</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Chertsey, Surrey (serves Staines/Weybridge/Egham/Virginia Water)</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>https://elitetuitioncollective.com</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>info@elitetuitioncollective.com</t>
+        </is>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>07843 934 949</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>Lauren Bowles (Founder, ex-primary teacher)</t>
+        </is>
+      </c>
+      <c r="H287" s="4" t="inlineStr"/>
+      <c r="I287" s="4" t="inlineStr"/>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>Founder-led, teacher-credentialed tutoring group across 5 wealthy Surrey towns; per-family tuition spend can run thousands/year</t>
+        </is>
+      </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L287" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M287" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N287" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O287" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P287" s="4" t="inlineStr">
+        <is>
+          <t>National tutoring platforms (MyTutor, Tutorful) absorb the same local searches</t>
+        </is>
+      </c>
+      <c r="Q287" s="4" t="inlineStr">
+        <is>
+          <t>'A qualified teacher's tuition agency vs an anonymous national platform - own that trust gap'</t>
+        </is>
+      </c>
+      <c r="R287" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S287" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>The Cotswold Caterer</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Wedding &amp; event caterer</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Quedgeley, Gloucester (serves Cotswolds/Gloucestershire)</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>https://thecotswoldcaterer.co.uk</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>hello@thecotswoldcaterer.co.uk</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>01452 905 106</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr"/>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/thecotswoldcaterergloucestershire</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr"/>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>Family business with 15+ years catering experience across weddings/corporate/funerals - three revenue lines from one kitchen</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O288" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; dedicated event-type landing pages</t>
+        </is>
+      </c>
+      <c r="P288" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist per event type but AI-answer citations for 'wedding caterer Cotswolds' still open</t>
+        </is>
+      </c>
+      <c r="Q288" s="3" t="inlineStr">
+        <is>
+          <t>'You built pages for weddings, corporate AND funerals - let's make AI cite all three'</t>
+        </is>
+      </c>
+      <c r="R288" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S288" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T288" s="3" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>Bennett &amp; Friends</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Wedding &amp; event caterer</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Rural Cotswolds (Gloucestershire/Oxfordshire)</t>
+        </is>
+      </c>
+      <c r="D289" s="4" t="inlineStr">
+        <is>
+          <t>https://bennettandfriends.co.uk</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>sam@bennettandfriends.co.uk</t>
+        </is>
+      </c>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>01386 575 840</t>
+        </is>
+      </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>Sam (Founder)</t>
+        </is>
+      </c>
+      <c r="H289" s="4" t="inlineStr"/>
+      <c r="I289" s="4" t="inlineStr"/>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>Friendly, flexible independent caterer serving the wider Cotswolds; repeat venue partnerships drive referral business</t>
+        </is>
+      </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L289" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M289" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N289" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O289" s="4" t="inlineStr">
+        <is>
+          <t>Venue-partner relationships</t>
+        </is>
+      </c>
+      <c r="P289" s="4" t="inlineStr">
+        <is>
+          <t>Referral-dependent growth model vulnerable if venue partnerships shift; direct search presence would diversify</t>
+        </is>
+      </c>
+      <c r="Q289" s="4" t="inlineStr">
+        <is>
+          <t>'Stop relying only on venue referrals - build a direct search presence as backup income'</t>
+        </is>
+      </c>
+      <c r="R289" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S289" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T289" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T283"/>
+  <autoFilter ref="A1:T289"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24968,7 +25488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -24988,7 +25508,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
@@ -25005,7 +25525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -25055,7 +25575,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -25161,7 +25681,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -25171,7 +25691,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -25181,7 +25701,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -25191,7 +25711,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -25201,7 +25721,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -25211,7 +25731,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -25221,7 +25741,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -25231,7 +25751,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -25241,7 +25761,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kitchen &amp; bathroom design</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -25251,27 +25771,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Kitchen &amp; bathroom design</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -25391,17 +25911,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -25411,7 +25931,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -25421,7 +25941,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -25431,7 +25951,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -25441,7 +25961,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -25451,7 +25971,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -25461,7 +25981,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -25471,7 +25991,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -25481,7 +26001,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -25491,7 +26011,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -25501,7 +26021,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -25511,7 +26031,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -25521,7 +26041,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -25531,7 +26051,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -25541,7 +26061,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -25551,7 +26071,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -25561,7 +26081,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -25571,7 +26091,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -25581,7 +26101,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -25591,7 +26111,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -25601,7 +26121,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -25611,7 +26131,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -25621,7 +26141,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -25631,7 +26151,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -25641,7 +26161,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -25651,7 +26171,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -25661,7 +26181,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -25671,7 +26191,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -25681,7 +26201,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -25691,7 +26211,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -25701,7 +26221,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -25711,7 +26231,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -25721,7 +26241,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -25731,7 +26251,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -25741,7 +26261,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -25751,7 +26271,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -25761,7 +26281,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -25771,7 +26291,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -25781,7 +26301,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -25791,7 +26311,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -25801,7 +26321,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -25811,7 +26331,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -25821,7 +26341,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -25831,7 +26351,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -25841,7 +26361,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -25851,7 +26371,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -25861,7 +26381,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -25871,7 +26391,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -25881,7 +26401,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -25891,7 +26411,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -25901,7 +26421,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -25911,7 +26431,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -25921,7 +26441,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -25931,7 +26451,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -25941,7 +26461,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -25951,7 +26471,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -25961,7 +26481,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -25971,7 +26491,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -25981,7 +26501,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -25991,7 +26511,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -26001,7 +26521,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -26011,7 +26531,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -26021,7 +26541,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -26031,7 +26551,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -26041,7 +26561,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -26051,7 +26571,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -26061,7 +26581,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -26071,7 +26591,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -26081,7 +26601,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -26091,7 +26611,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -26101,7 +26621,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -26111,7 +26631,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -26121,7 +26641,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -26131,7 +26651,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -26141,7 +26661,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -26151,7 +26671,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -26161,7 +26681,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -26171,7 +26691,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -26181,7 +26701,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -26191,7 +26711,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -26201,7 +26721,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -26211,7 +26731,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -26221,7 +26741,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -26231,7 +26751,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -26241,10 +26761,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>Wine merchant</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Education consultancy (school placement)</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B131" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$296</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T289"/>
+  <dimension ref="A1:T296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -25476,8 +25476,612 @@
       </c>
       <c r="T289" s="4" t="inlineStr"/>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Milestone &amp; Collis</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Estate agent &amp; surveyors</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Church Street, Twickenham (+ Teddington)</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.milestone-collis.com</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Sales@milestone-collis.com</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>020 8892 1313</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>Est. 1890; current principals B. Dinnage &amp; D. Dunlop lineage</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/milestone.collis</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/milestonecollis</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>135-year-old independent firm - extraordinary heritage in Twickenham/Teddington property; surveying arm adds a second revenue line</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>135 years of trust is an exceptional AEO asset currently underused against modern digital-first rivals</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>'135 years in Twickenham - the longest-established name should be AI's answer too'</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>Rare, hard-to-replicate heritage story - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>Websters Estate Agents</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Twickenham &amp; Teddington, London</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mywebsters.co.uk</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>020 8892 3343</t>
+        </is>
+      </c>
+      <c r="G291" s="4" t="inlineStr"/>
+      <c r="H291" s="4" t="inlineStr"/>
+      <c r="I291" s="4" t="inlineStr"/>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>Two-office independent covering 9+ SW London postcodes (Twickenham, St Margaret's, Whitton, Hampton, etc.)</t>
+        </is>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M291" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N291" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O291" s="4" t="inlineStr">
+        <is>
+          <t>Two-office coverage</t>
+        </is>
+      </c>
+      <c r="P291" s="4" t="inlineStr">
+        <is>
+          <t>Wide postcode claim not matched by per-area search dominance</t>
+        </is>
+      </c>
+      <c r="Q291" s="4" t="inlineStr">
+        <is>
+          <t>Per-postcode AEO content to actually own the 9 areas claimed</t>
+        </is>
+      </c>
+      <c r="R291" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S291" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>Devenports Estate Agents</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Twickenham &amp; Hampton, London</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>https://devenports.co.uk</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F292" s="4" t="inlineStr"/>
+      <c r="G292" s="4" t="inlineStr"/>
+      <c r="H292" s="4" t="inlineStr"/>
+      <c r="I292" s="4" t="inlineStr"/>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>Independent covering Twickenham/Hampton; sales and lettings for premium riverside property</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M292" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N292" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O292" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P292" s="4" t="inlineStr">
+        <is>
+          <t>Corporate brands (Dexters, Hamptons) dominate Twickenham search visibility</t>
+        </is>
+      </c>
+      <c r="Q292" s="4" t="inlineStr">
+        <is>
+          <t>Local-first AEO positioning vs the corporate-brand search dominance</t>
+        </is>
+      </c>
+      <c r="R292" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S292" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T292" s="4" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>Lebanon Park Dental Group</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Richmond Road, Twickenham</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lebanonparkdental.co.uk</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>info@lebanonparkdental.co.uk</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>020 8892 3803</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr"/>
+      <c r="H293" s="3" t="inlineStr"/>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/lebanonparkdentalgroup</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t>Private practice offering implants/Invisalign/hygiene in premium Twickenham; group model with named team page</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O293" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; BUPA finder listing</t>
+        </is>
+      </c>
+      <c r="P293" s="3" t="inlineStr">
+        <is>
+          <t>Perfect Smile/Complete Smile chains outspend on 'dental implants Twickenham' search</t>
+        </is>
+      </c>
+      <c r="Q293" s="3" t="inlineStr">
+        <is>
+          <t>'Own "dental implants Twickenham" before the multi-site chains lock it up'</t>
+        </is>
+      </c>
+      <c r="R293" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S293" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T293" s="3" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>The Complete Smile Twickenham</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>Twickenham, London</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thecompletesmile.co.uk</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr"/>
+      <c r="G294" s="3" t="inlineStr"/>
+      <c r="H294" s="3" t="inlineStr"/>
+      <c r="I294" s="3" t="inlineStr"/>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>10,000+ implants placed - genuinely exceptional volume claim; serves Twickenham/Richmond</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O294" s="3" t="inlineStr">
+        <is>
+          <t>Volume-of-implants claim promoted</t>
+        </is>
+      </c>
+      <c r="P294" s="3" t="inlineStr">
+        <is>
+          <t>Extraordinary track record (10,000+ implants) not yet the AI-cited proof point</t>
+        </is>
+      </c>
+      <c r="Q294" s="3" t="inlineStr">
+        <is>
+          <t>'10,000 implants placed - make that the number AI quotes back to patients'</t>
+        </is>
+      </c>
+      <c r="R294" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S294" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T294" s="3" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>Globe IFA</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Independent financial adviser</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>St Margarets, Twickenham</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>https://globeifa.co.uk</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>garry@globeifa.co.uk</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>020 8891 0711</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>Garry Haywood (Founder, est. 1994)</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr"/>
+      <c r="I295" s="3" t="inlineStr"/>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>30-year independent IFA in wealthy SW London; multi-adviser team with detailed fee transparency content</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O295" s="3" t="inlineStr">
+        <is>
+          <t>Transparent-fees content = marketing-aware</t>
+        </is>
+      </c>
+      <c r="P295" s="3" t="inlineStr">
+        <is>
+          <t>30 years of trust and transparent-fee positioning not yet the AI-cited local answer</t>
+        </is>
+      </c>
+      <c r="Q295" s="3" t="inlineStr">
+        <is>
+          <t>'30 years, transparent fees - the exact story AI should tell when Twickenham residents ask for an IFA'</t>
+        </is>
+      </c>
+      <c r="R295" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S295" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T295" s="3" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>Marguerite Murdoch Architects</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Teddington, London</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>https://mmurdocharchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr"/>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>Marguerite Murdoch (Founder, est. 2006)</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr"/>
+      <c r="I296" s="4" t="inlineStr"/>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>Founder-led practice, nearly 20 years in Teddington/Richmond residential architecture</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L296" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M296" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N296" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O296" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P296" s="4" t="inlineStr">
+        <is>
+          <t>Two decades of local project history not converted into AI-search authority</t>
+        </is>
+      </c>
+      <c r="Q296" s="4" t="inlineStr">
+        <is>
+          <t>Portfolio-driven AEO leveraging 20 years of Teddington-area projects</t>
+        </is>
+      </c>
+      <c r="R296" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S296" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T296" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T289"/>
+  <autoFilter ref="A1:T296"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25488,7 +26092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -25508,7 +26112,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5">
@@ -25525,7 +26129,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -25535,13 +26139,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -25551,11 +26155,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -25631,7 +26235,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -25641,17 +26245,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -26775,6 +27379,26 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estate agent &amp; surveyors</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Independent financial adviser</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$303</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T296"/>
+  <dimension ref="A1:T303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26080,8 +26080,600 @@
       </c>
       <c r="T296" s="4" t="inlineStr"/>
     </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>Dr Shilpa Dave Health</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Teddington &amp; Twickenham, London</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>https://privategp.org</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>pa@privategp.org</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>0203 303 0326</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Dr Shilpa Dave (Founder &amp; Lead GP, 15+ yrs private/20+ yrs NHS)</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr"/>
+      <c r="I297" s="3" t="inlineStr"/>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>Two-site private GP with membership model; 6-day availability and deep dual NHS/private credentials = strong trust signal</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O297" s="3" t="inlineStr">
+        <is>
+          <t>Doctify profile; membership tiers</t>
+        </is>
+      </c>
+      <c r="P297" s="3" t="inlineStr">
+        <is>
+          <t>Membership-model private GPs increasingly compete for the same self-pay searches as hospital brands</t>
+        </is>
+      </c>
+      <c r="Q297" s="3" t="inlineStr">
+        <is>
+          <t>'20 years NHS + 15 years private - own that credibility in AI answers, not just Doctify'</t>
+        </is>
+      </c>
+      <c r="R297" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S297" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T297" s="3" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>The Richmond Doctor</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Richmond, London</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>https://therichmonddoctor.com</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr"/>
+      <c r="G298" s="4" t="inlineStr"/>
+      <c r="H298" s="4" t="inlineStr"/>
+      <c r="I298" s="4" t="inlineStr"/>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>Premium private GP serving local and international families in wealthy Richmond</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M298" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O298" s="4" t="inlineStr">
+        <is>
+          <t>International-family positioning</t>
+        </is>
+      </c>
+      <c r="P298" s="4" t="inlineStr">
+        <is>
+          <t>International-family niche is a distinct, under-optimised AEO angle vs generic private GP competitors</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="inlineStr">
+        <is>
+          <t>Own 'private GP for international families Richmond' - genuinely specific, defensible niche</t>
+        </is>
+      </c>
+      <c r="R298" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S298" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T298" s="4" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>King Street Vets</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>King Street, Twickenham</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kingstreetvets.co.uk</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>contact@kingstreetvets.co.uk</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>020 8963 3306</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Dr Karmen Webbe (Owner, MRCVS)</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr"/>
+      <c r="I299" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/KingStreetVets</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr">
+        <is>
+          <t>Owner-led independent small-animal practice in premium Twickenham; explicit independence positioning</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L299" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M299" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O299" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P299" s="3" t="inlineStr">
+        <is>
+          <t>Corporate vet groups (Medivet, CVS) heavily outspend on Twickenham/Richmond vet search</t>
+        </is>
+      </c>
+      <c r="Q299" s="3" t="inlineStr">
+        <is>
+          <t>'Owner-led and independent - own that AI answer against the corporate vet chains'</t>
+        </is>
+      </c>
+      <c r="R299" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S299" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T299" s="3" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>The Vet in St Margarets</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>St Margarets (serves Twickenham/Isleworth/Teddington/Richmond)</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>https://thevetinstmargarets.co.uk</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr"/>
+      <c r="G300" s="4" t="inlineStr"/>
+      <c r="H300" s="4" t="inlineStr"/>
+      <c r="I300" s="4" t="inlineStr"/>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>Proudly independent, 4-town catchment from one St Margarets base</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M300" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O300" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P300" s="4" t="inlineStr">
+        <is>
+          <t>4-town claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q300" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own the claimed catchment</t>
+        </is>
+      </c>
+      <c r="R300" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S300" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T300" s="4" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>Richmond Vets</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Richmond, London (between Kew Gardens and Richmond)</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>https://www.richmond-vets.co.uk</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr"/>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned since the 1970s</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr"/>
+      <c r="I301" s="3" t="inlineStr"/>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>50+ years family-owned in one of London's wealthiest boroughs - exceptional heritage for a competitive vet market</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L301" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M301" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O301" s="3" t="inlineStr">
+        <is>
+          <t>50-year heritage</t>
+        </is>
+      </c>
+      <c r="P301" s="3" t="inlineStr">
+        <is>
+          <t>Half a century of trust invisible against Medivet/CVS corporate marketing budgets</t>
+        </is>
+      </c>
+      <c r="Q301" s="3" t="inlineStr">
+        <is>
+          <t>'50 years family-owned in Richmond - the AI answer should say so, not just Google Maps'</t>
+        </is>
+      </c>
+      <c r="R301" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S301" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T301" s="3" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>Richmond Sports Conditioning (RSC)</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Personal training</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>Kew, Richmond, London</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rsc.coach</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr"/>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>Dan Matkin (Founder)</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="inlineStr"/>
+      <c r="I302" s="4" t="inlineStr"/>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>Strength &amp; conditioning specialist PT in affluent Kew/Richmond; ongoing client packages</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L302" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M302" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N302" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O302" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P302" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'personal trainer Richmond' searches won by bigger studio brands (Foundry, nmotion)</t>
+        </is>
+      </c>
+      <c r="Q302" s="4" t="inlineStr">
+        <is>
+          <t>Own the 'strength and conditioning coach Richmond' niche specifically</t>
+        </is>
+      </c>
+      <c r="R302" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S302" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T302" s="4" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>The Performance Works</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Personal training</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>Richmond Rugby Club &amp; Barnes (serves SW London)</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theperformanceworks-pt.com</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F303" s="4" t="inlineStr"/>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>Edward Stembridge (Founder, ex-professional rugby player)</t>
+        </is>
+      </c>
+      <c r="H303" s="4" t="inlineStr"/>
+      <c r="I303" s="4" t="inlineStr"/>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>Ex-pro rugby player credential is a rare, genuinely differentiating trust signal for a PT business</t>
+        </is>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M303" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N303" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O303" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P303" s="4" t="inlineStr">
+        <is>
+          <t>Ex-pro athlete credential not yet leveraged as the AI-cited differentiator</t>
+        </is>
+      </c>
+      <c r="Q303" s="4" t="inlineStr">
+        <is>
+          <t>'Trained by a professional rugby player' - own that exact positioning in AI answers</t>
+        </is>
+      </c>
+      <c r="R303" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S303" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T303" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T296"/>
+  <autoFilter ref="A1:T303"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26092,7 +26684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -26112,7 +26704,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
@@ -26169,7 +26761,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -26185,7 +26777,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -26195,17 +26787,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -26215,17 +26807,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -26525,17 +27117,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -26545,7 +27137,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -26555,7 +27147,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -26565,7 +27157,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -26575,7 +27167,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -26585,7 +27177,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -26595,7 +27187,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -26605,7 +27197,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -26615,7 +27207,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -26625,7 +27217,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -26635,7 +27227,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -26645,7 +27237,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -26655,7 +27247,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -26665,7 +27257,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -26675,7 +27267,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -26685,7 +27277,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -26695,7 +27287,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -26705,7 +27297,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -26715,7 +27307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -26725,7 +27317,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -26735,7 +27327,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -26745,7 +27337,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -26755,7 +27347,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -26765,7 +27357,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -26775,7 +27367,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -26785,7 +27377,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -26795,7 +27387,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -26805,7 +27397,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -26815,7 +27407,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -26825,7 +27417,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -26835,7 +27427,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -26845,7 +27437,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -26855,7 +27447,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -26865,7 +27457,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -26875,7 +27467,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -26885,7 +27477,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -26895,7 +27487,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -26905,7 +27497,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -26915,7 +27507,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -26925,7 +27517,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -26935,7 +27527,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -26945,7 +27537,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -26955,7 +27547,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -26965,7 +27557,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -26975,7 +27567,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -26985,7 +27577,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -26995,7 +27587,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -27005,7 +27597,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -27015,7 +27607,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -27025,7 +27617,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -27035,7 +27627,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -27045,7 +27637,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -27055,7 +27647,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -27065,7 +27657,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -27075,7 +27667,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -27085,7 +27677,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -27095,7 +27687,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -27105,7 +27697,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -27115,7 +27707,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -27125,7 +27717,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -27135,7 +27727,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -27145,7 +27737,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -27155,7 +27747,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -27165,7 +27757,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -27175,7 +27767,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -27185,7 +27777,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -27195,7 +27787,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -27205,7 +27797,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -27215,7 +27807,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -27225,7 +27817,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -27235,7 +27827,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -27245,7 +27837,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -27255,7 +27847,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -27265,7 +27857,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -27275,7 +27867,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -27285,7 +27877,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -27295,7 +27887,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -27305,7 +27897,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -27315,7 +27907,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -27325,7 +27917,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -27335,7 +27927,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -27345,7 +27937,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -27355,7 +27947,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -27365,7 +27957,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -27375,7 +27967,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -27385,7 +27977,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -27395,10 +27987,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>Estate agent &amp; surveyors</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>Independent financial adviser</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B134" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$310</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T303"/>
+  <dimension ref="A1:T310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26672,8 +26672,600 @@
       </c>
       <c r="T303" s="4" t="inlineStr"/>
     </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>Latimer</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>Kingston upon Thames, London</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>https://www.latimerandco.com</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>info@latimerandco.co.uk</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>020 3463 0274</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Carla Lester (Owner, 30+ years experience, est. 1989)</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr"/>
+      <c r="I304" s="3" t="inlineStr"/>
+      <c r="J304" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1989, owner-run for 35 years; premium Kingston/Surbiton border property fees</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M304" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O304" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P304" s="3" t="inlineStr">
+        <is>
+          <t>Corporate brands (Hamptons, Curchods) dominate Kingston search visibility</t>
+        </is>
+      </c>
+      <c r="Q304" s="3" t="inlineStr">
+        <is>
+          <t>'35 years owner-run in Kingston - make AI say so, not just Rightmove'</t>
+        </is>
+      </c>
+      <c r="R304" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S304" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T304" s="3" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>Saxon Kings</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>Kingston upon Thames, London</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>https://saxonkings.co.uk</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F305" s="4" t="inlineStr"/>
+      <c r="G305" s="4" t="inlineStr"/>
+      <c r="H305" s="4" t="inlineStr"/>
+      <c r="I305" s="4" t="inlineStr"/>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>Independent, owner-run since 2006; established local reputation in KT1/KT2</t>
+        </is>
+      </c>
+      <c r="K305" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L305" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M305" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N305" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O305" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P305" s="4" t="inlineStr">
+        <is>
+          <t>Newer independent competing with 100-year-old incumbents and corporate brands alike</t>
+        </is>
+      </c>
+      <c r="Q305" s="4" t="inlineStr">
+        <is>
+          <t>Ground-floor AEO investment to build search authority alongside reputation</t>
+        </is>
+      </c>
+      <c r="R305" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S305" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T305" s="4" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Carringtons</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>Kingston, Surbiton, New Malden, Kingston Vale</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>https://carringtonsproperty.com</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr"/>
+      <c r="G306" s="4" t="inlineStr"/>
+      <c r="H306" s="4" t="inlineStr"/>
+      <c r="I306" s="4" t="inlineStr"/>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>Family-led independent across 4 SW London towns; broad residential coverage</t>
+        </is>
+      </c>
+      <c r="K306" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N306" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O306" s="4" t="inlineStr">
+        <is>
+          <t>Multi-town coverage</t>
+        </is>
+      </c>
+      <c r="P306" s="4" t="inlineStr">
+        <is>
+          <t>Wide catchment claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own all 4 claimed markets</t>
+        </is>
+      </c>
+      <c r="R306" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S306" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T306" s="4" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>Thames Street Dental</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>Thames Street, Kingston upon Thames</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>https://thames-dental.co.uk</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>020 8546 6546</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr"/>
+      <c r="H307" s="4" t="inlineStr"/>
+      <c r="I307" s="4" t="inlineStr"/>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>Independent family-run clinic on Kingston's riverside high street; implant work = high per-case value</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L307" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M307" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N307" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O307" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P307" s="4" t="inlineStr">
+        <is>
+          <t>Chain dental brands and Aesthetika compete for the same Kingston implant searches</t>
+        </is>
+      </c>
+      <c r="Q307" s="4" t="inlineStr">
+        <is>
+          <t>'Family-run on the Thames - own "dental implants Kingston" before the chains do'</t>
+        </is>
+      </c>
+      <c r="R307" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S307" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T307" s="4" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetika Dental Studio</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>Kingston upon Thames</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>https://aesthetikadentalstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr"/>
+      <c r="G308" s="4" t="inlineStr"/>
+      <c r="H308" s="4" t="inlineStr"/>
+      <c r="I308" s="4" t="inlineStr"/>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>Established since 2011, private-only positioning with dedicated implants landing page</t>
+        </is>
+      </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L308" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M308" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N308" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O308" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated implants page = active SEO</t>
+        </is>
+      </c>
+      <c r="P308" s="4" t="inlineStr">
+        <is>
+          <t>Implants page exists but not yet the AI-cited answer for Kingston implant searches</t>
+        </is>
+      </c>
+      <c r="Q308" s="4" t="inlineStr">
+        <is>
+          <t>Upgrade existing implants SEO page into an AEO-optimised asset</t>
+        </is>
+      </c>
+      <c r="R308" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S308" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T308" s="4" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>Fletcher Crane Architects</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Union Street, Kingston upon Thames</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fletchercranearchitects.com</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>info@fletchercranearchitects.com</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>020 8977 4693</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>Carmine Bassi (Founder)</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr"/>
+      <c r="I309" s="3" t="inlineStr"/>
+      <c r="J309" s="3" t="inlineStr">
+        <is>
+          <t>RIBA award-winning practice, 20+ years across residential/education/hotel sectors - diverse high-value client base</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M309" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O309" s="3" t="inlineStr">
+        <is>
+          <t>RIBA awards</t>
+        </is>
+      </c>
+      <c r="P309" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning multi-sector practice not leveraging that range as an AEO differentiator</t>
+        </is>
+      </c>
+      <c r="Q309" s="3" t="inlineStr">
+        <is>
+          <t>'From homes to hotels - own the AI answer for versatile Kingston architecture'</t>
+        </is>
+      </c>
+      <c r="R309" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S309" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T309" s="3" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>Tax Affinity Accountants</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>Tolworth, Kingston upon Thames</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>https://www.taxaffinity.com</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>0800 043 4051</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>Founder (ex-top-tier accountancy firm advisor)</t>
+        </is>
+      </c>
+      <c r="H310" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/TaxAffinity</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr"/>
+      <c r="J310" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 2012; founder's big-firm pedigree serving SME/sole trader clients; self-described 'No 1 rated'</t>
+        </is>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M310" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N310" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O310" s="4" t="inlineStr">
+        <is>
+          <t>'Independently rated No 1' claim; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P310" s="4" t="inlineStr">
+        <is>
+          <t>Rating claim not converted into the AI-cited answer for 'accountant Kingston'</t>
+        </is>
+      </c>
+      <c r="Q310" s="4" t="inlineStr">
+        <is>
+          <t>'Independently rated No 1 - make sure AI repeats that, not just the website banner'</t>
+        </is>
+      </c>
+      <c r="R310" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S310" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T310" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T303"/>
+  <autoFilter ref="A1:T310"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26704,7 +27296,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5">
@@ -26721,7 +27313,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -26731,7 +27323,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -26741,7 +27333,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -26777,7 +27369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -26787,7 +27379,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -26797,17 +27389,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -26817,17 +27409,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B17" t="n">

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T310"/>
+  <dimension ref="A1:T318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27264,8 +27264,712 @@
       </c>
       <c r="T310" s="4" t="inlineStr"/>
     </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>Capital Estate Agents</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>Beckenham Lane, Bromley, Kent</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>https://capitalestateagents.com</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>info@capitalestateagents.com</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>020 8313 0010</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Rob Tancred (Managing Director, est. 1996)</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr"/>
+      <c r="I311" s="3" t="inlineStr"/>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>Independent since 1996, leading agent positioning in Bromley/Beckenham; premium SE London commuter-belt fees</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M311" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O311" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P311" s="3" t="inlineStr">
+        <is>
+          <t>Alan de Maid (est. 1953) and Mann corporate brands dominate Bromley search visibility</t>
+        </is>
+      </c>
+      <c r="Q311" s="3" t="inlineStr">
+        <is>
+          <t>'Leading independent agent since 1996 - make AI say so, not just Rightmove'</t>
+        </is>
+      </c>
+      <c r="R311" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S311" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T311" s="3" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>Sinclair Hammelton</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Bromley, Beckenham &amp; Hayes, Kent</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sinclairhammelton.co.uk</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr"/>
+      <c r="G312" s="4" t="inlineStr"/>
+      <c r="H312" s="4" t="inlineStr"/>
+      <c r="I312" s="4" t="inlineStr"/>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>Independently owned across 3 SE London/Kent towns; residential sales and lettings</t>
+        </is>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O312" s="4" t="inlineStr">
+        <is>
+          <t>Multi-town coverage</t>
+        </is>
+      </c>
+      <c r="P312" s="4" t="inlineStr">
+        <is>
+          <t>3-town claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own all 3 claimed markets</t>
+        </is>
+      </c>
+      <c r="R312" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S312" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T312" s="4" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>Grafton Estate Agents</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>Beckenham, Kent</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>https://www.graftonestateagents.co.uk</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F313" s="4" t="inlineStr"/>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>Tariq Gabr (Owner, 18+ years experience)</t>
+        </is>
+      </c>
+      <c r="H313" s="4" t="inlineStr"/>
+      <c r="I313" s="4" t="inlineStr"/>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>Proudly independent, family-run; founder-led with nearly two decades of local experience</t>
+        </is>
+      </c>
+      <c r="K313" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L313" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M313" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N313" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O313" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P313" s="4" t="inlineStr">
+        <is>
+          <t>Family-run positioning invisible against bigger Bromley-area agents in search</t>
+        </is>
+      </c>
+      <c r="Q313" s="4" t="inlineStr">
+        <is>
+          <t>'Family-run since day one - own that AEO positioning against the bigger brands'</t>
+        </is>
+      </c>
+      <c r="R313" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S313" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T313" s="4" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>Kelsey Park Dental</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>Kelsey Park Road, Beckenham, Kent</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>https://kelseyparkdental.co.uk</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>frontdesk@kelseyparkdental.co.uk</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>020 8650 7677</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Monica Moreira De Smith (Principal Owner)</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/monica-moreira-36607673</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/kelseyparkdental</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr">
+        <is>
+          <t>70+ years independent practice serving Beckenham/Bromley/West Wickham; named owner-principal with implant specialism</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M314" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O314" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; LinkedIn</t>
+        </is>
+      </c>
+      <c r="P314" s="3" t="inlineStr">
+        <is>
+          <t>70 years of trust invisible against national dental chains dominating Beckenham search</t>
+        </is>
+      </c>
+      <c r="Q314" s="3" t="inlineStr">
+        <is>
+          <t>'70 years in Beckenham - the AI answer should reflect that heritage, not just Google Maps'</t>
+        </is>
+      </c>
+      <c r="R314" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S314" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T314" s="3" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>Premier Dental Clinic</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Beckenham Lane, Bromley, Kent</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>https://premierdentalclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>reception@premierdentalclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>020 8460 9150</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Dr Louie (Implant specialist)</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr"/>
+      <c r="I315" s="3" t="inlineStr"/>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t>Named implant specialist offering digital surgical planning and guided surgery - genuine clinical differentiation</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M315" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O315" s="3" t="inlineStr">
+        <is>
+          <t>Digital surgical planning promoted</t>
+        </is>
+      </c>
+      <c r="P315" s="3" t="inlineStr">
+        <is>
+          <t>Advanced technique not yet leveraged as the AI-cited differentiator vs generic implant clinics</t>
+        </is>
+      </c>
+      <c r="Q315" s="3" t="inlineStr">
+        <is>
+          <t>'Digital-guided implant surgery - own that specific AEO niche in Bromley'</t>
+        </is>
+      </c>
+      <c r="R315" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S315" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T315" s="3" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>Culverhouse &amp; Co</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; financial planners</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>Farnborough Village, Orpington (Bromley/Kent)</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>https://www.culverhouse-accountants.co.uk</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>info@culverhouse-accountants.co.uk</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>01689 862 211</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>John Culverhouse (Founder)</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr"/>
+      <c r="I316" s="3" t="inlineStr"/>
+      <c r="J316" s="3" t="inlineStr">
+        <is>
+          <t>Combined accountancy + financial planning firm - two revenue lines per client relationship, high LTV</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L316" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M316" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N316" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O316" s="3" t="inlineStr">
+        <is>
+          <t>Detailed service-specific SEO pages (HMRC enquiries, savings &amp; investments)</t>
+        </is>
+      </c>
+      <c r="P316" s="3" t="inlineStr">
+        <is>
+          <t>Many individual service pages exist but AI-answer citations for specific queries still open</t>
+        </is>
+      </c>
+      <c r="Q316" s="3" t="inlineStr">
+        <is>
+          <t>'You've written pages for every service - let's make AI cite them, not just index them'</t>
+        </is>
+      </c>
+      <c r="R316" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S316" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T316" s="3" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>Gary Arnold Architects</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Bromley, Kent (serves Beckenham/Croydon)</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>https://garyarnoldarchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>07595 916 171</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>Gary Arnold (Founder, 15+ years)</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr"/>
+      <c r="I317" s="3" t="inlineStr"/>
+      <c r="J317" s="3" t="inlineStr">
+        <is>
+          <t>5-star rated chartered architect, per-area landing pages (Beckenham, South Croydon) = active SEO investment</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L317" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M317" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N317" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O317" s="3" t="inlineStr">
+        <is>
+          <t>Per-area landing pages; 5-star reviews</t>
+        </is>
+      </c>
+      <c r="P317" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist across multiple areas but AI-answer citations still open</t>
+        </is>
+      </c>
+      <c r="Q317" s="3" t="inlineStr">
+        <is>
+          <t>'You built pages for every area you serve - add the AEO layer to make AI cite them'</t>
+        </is>
+      </c>
+      <c r="R317" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S317" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T317" s="3" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>Brouard Architects</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Chislehurst, Kent (serves Bromley/Beckenham/Keston)</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>01689 857 253</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>Philip Brouard (Founder, est. 1999)</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr"/>
+      <c r="I318" s="3" t="inlineStr"/>
+      <c r="J318" s="3" t="inlineStr">
+        <is>
+          <t>25-year practice across residential/education/healthcare/hotel sectors - diverse, high-value client base</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L318" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M318" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N318" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O318" s="3" t="inlineStr">
+        <is>
+          <t>Multi-sector portfolio</t>
+        </is>
+      </c>
+      <c r="P318" s="3" t="inlineStr">
+        <is>
+          <t>Diverse sector experience not leveraged as an AEO differentiator vs residential-only rivals</t>
+        </is>
+      </c>
+      <c r="Q318" s="3" t="inlineStr">
+        <is>
+          <t>'From homes to hotels - one practice, own the AI answer for every project type'</t>
+        </is>
+      </c>
+      <c r="R318" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S318" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T318" s="3" t="inlineStr">
+        <is>
+          <t>Confirm current live website before outreach</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T310"/>
+  <autoFilter ref="A1:T318"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27276,7 +27980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -27296,7 +28000,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
@@ -27313,7 +28017,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -27323,7 +28027,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -27369,17 +28073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -27389,7 +28093,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -27399,17 +28103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -28593,6 +29297,16 @@
         </is>
       </c>
       <c r="B134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; financial planners</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$327</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T318"/>
+  <dimension ref="A1:T327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27968,8 +27968,768 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>ShineRocks</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Purley, Surrey/Croydon</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shinerocks.co.uk</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>020 3745 3493</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>Paul &amp; Claire Shinerock (Family owners, 35+ yr local brand)</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/ShinerocksPurley</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr"/>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t>Family name recognised locally for 35+ years (originally soft-furnishing retail); leading independent in mid/upper Purley market</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M319" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N319" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O319" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 35-year local brand</t>
+        </is>
+      </c>
+      <c r="P319" s="3" t="inlineStr">
+        <is>
+          <t>Frost (est. 1862) and corporate agents also compete hard for Purley/Croydon search</t>
+        </is>
+      </c>
+      <c r="Q319" s="3" t="inlineStr">
+        <is>
+          <t>'35 years of the Shinerocks name in Purley - make AI say it, not just word of mouth'</t>
+        </is>
+      </c>
+      <c r="R319" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S319" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T319" s="3" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Frost Estate Agents</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Purley, Surrey</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.frostproperty.co.uk</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr"/>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>Independent since 1862 - extraordinary 160+ year heritage; multiple 'Best Agent in Purley' awards since 2017</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>Multiple industry awards</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>160 years of history + repeated awards not yet the AI-cited answer for Purley property search</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>'160 years and multiple Best Agent awards - the AI answer should say both, not just one'</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional heritage + award combination - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>David Bright Estates</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>Purley/Kenley/Coulsdon/Croydon, Surrey</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.davidbrightestates.co.uk</t>
+        </is>
+      </c>
+      <c r="E321" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F321" s="4" t="inlineStr"/>
+      <c r="G321" s="4" t="inlineStr"/>
+      <c r="H321" s="4" t="inlineStr"/>
+      <c r="I321" s="4" t="inlineStr"/>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>35+ years combined experience across a 4-town South Croydon/Surrey catchment</t>
+        </is>
+      </c>
+      <c r="K321" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L321" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M321" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N321" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O321" s="4" t="inlineStr">
+        <is>
+          <t>Multi-town coverage</t>
+        </is>
+      </c>
+      <c r="P321" s="4" t="inlineStr">
+        <is>
+          <t>35 years' experience claim not converted into per-town AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q321" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own all 4 claimed markets</t>
+        </is>
+      </c>
+      <c r="R321" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S321" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>The Artemis Clinic</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>West Wickham (serves Beckenham/Bromley/Hayes/Orpington)</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>https://www.artemisclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>office@artemisclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>020 8777 1500</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr"/>
+      <c r="H322" s="3" t="inlineStr"/>
+      <c r="I322" s="3" t="inlineStr"/>
+      <c r="J322" s="3" t="inlineStr">
+        <is>
+          <t>Independent private GP covering 4 SE London/Kent towns from one base; self-pay consultations</t>
+        </is>
+      </c>
+      <c r="K322" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L322" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M322" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N322" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O322" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P322" s="3" t="inlineStr">
+        <is>
+          <t>4-town catchment claim not matched by per-town search visibility</t>
+        </is>
+      </c>
+      <c r="Q322" s="3" t="inlineStr">
+        <is>
+          <t>Per-town AEO content for 'private GP' across the whole claimed service area</t>
+        </is>
+      </c>
+      <c r="R322" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S322" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T322" s="3" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>The Blackwell Clinic</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>Private GP &amp; dermatology</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>Bromley (serves Blackheath)</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>https://theblackwellclinic.com</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>0808 189 5666</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr"/>
+      <c r="H323" s="3" t="inlineStr"/>
+      <c r="I323" s="3" t="inlineStr"/>
+      <c r="J323" s="3" t="inlineStr">
+        <is>
+          <t>Combined GP + dermatologist + aesthetics + skin surgery under one roof - multiple revenue lines per client relationship</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M323" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N323" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O323" s="3" t="inlineStr">
+        <is>
+          <t>Circle Health booking platform integration</t>
+        </is>
+      </c>
+      <c r="P323" s="3" t="inlineStr">
+        <is>
+          <t>Multi-service offering not unified into one strong AEO strategy across all 4 service lines</t>
+        </is>
+      </c>
+      <c r="Q323" s="3" t="inlineStr">
+        <is>
+          <t>Consolidate 4 service lines into one coherent AEO content plan</t>
+        </is>
+      </c>
+      <c r="R323" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S323" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T323" s="3" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>Anderson Veterinary Surgery</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>Burnt Ash Lane, Bromley North, Kent</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>https://andersonvets.co.uk</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>info@andersonvets.co.uk</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>020 8290 1698</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>Katie Mercer MRCVS (Managing Partner, since 2013)</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr"/>
+      <c r="I324" s="3" t="inlineStr"/>
+      <c r="J324" s="3" t="inlineStr">
+        <is>
+          <t>Proudly independent, named managing partner since 2013; strong professionalism/care positioning</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M324" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N324" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O324" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P324" s="3" t="inlineStr">
+        <is>
+          <t>Medivet's Bromley presence (Open Saturdays branding) outspends on local vet search</t>
+        </is>
+      </c>
+      <c r="Q324" s="3" t="inlineStr">
+        <is>
+          <t>'Proudly independent, named vet you can trust - own that vs the Medivet chain in AI answers'</t>
+        </is>
+      </c>
+      <c r="R324" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S324" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T324" s="3" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>Tender Paws Vets</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>West Wickham (Bromley/Beckenham)</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>https://tenderpaws.vet</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>mail@tenderpaws.vet</t>
+        </is>
+      </c>
+      <c r="F325" s="4" t="inlineStr"/>
+      <c r="G325" s="4" t="inlineStr"/>
+      <c r="H325" s="4" t="inlineStr"/>
+      <c r="I325" s="4" t="inlineStr"/>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>40+ years as a popular local vet - genuine multi-decade community fixture</t>
+        </is>
+      </c>
+      <c r="K325" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L325" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M325" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N325" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O325" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P325" s="4" t="inlineStr">
+        <is>
+          <t>40 years of community trust invisible against corporate vet marketing budgets</t>
+        </is>
+      </c>
+      <c r="Q325" s="4" t="inlineStr">
+        <is>
+          <t>'40 years as West Wickham's local vet - the AI answer should say so too'</t>
+        </is>
+      </c>
+      <c r="R325" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S325" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T325" s="4" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Great Tangley Manor</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Wonersh, Surrey (Surrey Hills AONB)</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greattangleymanor.co.uk</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>info@greattangleymanor.co.uk</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>020 7526 4852</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr"/>
+      <c r="H326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr"/>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>Grade I listed, reputedly Britain's oldest house (1,000 years) - among the most extraordinary heritage stories in the whole database</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>Detailed visual tour/local venues content</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>'Britain's oldest house' claim is an exceptional AEO asset barely leveraged beyond the website itself</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>'Britain's oldest house as a wedding venue - that claim alone should dominate every AI answer for Surrey manor weddings'</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>Among the strongest heritage-story assets found in the whole database</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>Kingswood Manor</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Hills</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kingswood-manor.co.uk</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F327" s="4" t="inlineStr"/>
+      <c r="G327" s="4" t="inlineStr"/>
+      <c r="H327" s="4" t="inlineStr"/>
+      <c r="I327" s="4" t="inlineStr"/>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Hills setting with mature gardens; premium exclusive-use weddings</t>
+        </is>
+      </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L327" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M327" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O327" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P327" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'Surrey Hills wedding venue' searches split across many similar venues</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="inlineStr">
+        <is>
+          <t>Differentiate via specific garden/landscape AEO content vs generic rivals</t>
+        </is>
+      </c>
+      <c r="R327" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S327" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T327" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T318"/>
+  <autoFilter ref="A1:T327"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27980,7 +28740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -28000,7 +28760,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5">
@@ -28017,7 +28777,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -28033,21 +28793,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -28057,13 +28817,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -28073,7 +28833,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -28083,17 +28843,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -29307,6 +30067,16 @@
         </is>
       </c>
       <c r="B135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Private GP &amp; dermatology</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$333</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T327"/>
+  <dimension ref="A1:T333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28728,8 +28728,528 @@
       </c>
       <c r="T327" s="4" t="inlineStr"/>
     </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>Mi-Move</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>Sutton, Surrey</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mi-move.com</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>info@mi-move.com</t>
+        </is>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>020 3538 0558</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr"/>
+      <c r="H328" s="4" t="inlineStr"/>
+      <c r="I328" s="4" t="inlineStr"/>
+      <c r="J328" s="4" t="inlineStr">
+        <is>
+          <t>Independent covering Sutton/Cheam/Carshalton/Wallington/Banstead; 35+ years combined local sales experience</t>
+        </is>
+      </c>
+      <c r="K328" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L328" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M328" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N328" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O328" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P328" s="4" t="inlineStr">
+        <is>
+          <t>Belvoir/Cubitt &amp; West corporate brands compete for the same Sutton searches</t>
+        </is>
+      </c>
+      <c r="Q328" s="4" t="inlineStr">
+        <is>
+          <t>'35 years of local sales experience deserves to be the AI's answer for Sutton property'</t>
+        </is>
+      </c>
+      <c r="R328" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S328" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T328" s="4" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>Cromwells Estate Agents</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>Wallington/Carshalton/Sutton/Croydon</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cromwellsestateagents.com</t>
+        </is>
+      </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F329" s="4" t="inlineStr"/>
+      <c r="G329" s="4" t="inlineStr"/>
+      <c r="H329" s="4" t="inlineStr"/>
+      <c r="I329" s="4" t="inlineStr"/>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>Privately owned, explicitly not bank/insurance-owned; wide 5-town South London/Surrey catchment</t>
+        </is>
+      </c>
+      <c r="K329" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L329" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M329" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N329" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O329" s="4" t="inlineStr">
+        <is>
+          <t>Independence explicitly promoted</t>
+        </is>
+      </c>
+      <c r="P329" s="4" t="inlineStr">
+        <is>
+          <t>'Not owned by a bank' positioning is a strong trust angle unused in AI-search content</t>
+        </is>
+      </c>
+      <c r="Q329" s="4" t="inlineStr">
+        <is>
+          <t>'Not owned by a bank or insurer' - own that exact independence positioning in AI answers</t>
+        </is>
+      </c>
+      <c r="R329" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S329" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>Cheam Dental Practice</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>London Road, Sutton (Cheam)</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>cheamdental@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>020 8337 2886</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr"/>
+      <c r="H330" s="4" t="inlineStr"/>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Cheam-Dental-Practice-100041375306012</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>Long-standing local practice in affluent Cheam; Hotmail contact address signals low marketing infrastructure</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L330" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M330" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N330" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O330" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P330" s="4" t="inlineStr">
+        <is>
+          <t>Hotmail email is the classic infrastructure-gap tell seen throughout this database</t>
+        </is>
+      </c>
+      <c r="Q330" s="4" t="inlineStr">
+        <is>
+          <t>'A Hotmail address is costing you patients - let's modernise the whole digital front door'</t>
+        </is>
+      </c>
+      <c r="R330" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S330" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T330" s="4" t="inlineStr">
+        <is>
+          <t>Hotmail tell - same infrastructure-gap wedge pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>Ninety 2 Dental</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>Worcester Park (serves Sutton/Cheam/Raynes Park/Wimbledon)</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ninety2dental.co.uk</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>020 8337 1168</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="inlineStr"/>
+      <c r="H331" s="4" t="inlineStr"/>
+      <c r="I331" s="4" t="inlineStr"/>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>Free-consultation implant offer across 4 SW London towns; volume-oriented private model</t>
+        </is>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L331" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M331" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N331" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O331" s="4" t="inlineStr">
+        <is>
+          <t>Free-consultation offer promoted</t>
+        </is>
+      </c>
+      <c r="P331" s="4" t="inlineStr">
+        <is>
+          <t>4-town catchment claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q331" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own the 4 areas served</t>
+        </is>
+      </c>
+      <c r="R331" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S331" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T331" s="4" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>The Recruiters Room</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Recruitment agency</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Bracknell, Berkshire (serves Basingstoke/Hampshire/Surrey)</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>https://therecruitersroom.co.uk</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>info@therecruitersroom.co.uk</t>
+        </is>
+      </c>
+      <c r="F332" s="4" t="inlineStr"/>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>Two founders known as 'the two Lauras' (35+ yrs combined, est. 2016)</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/the-recruiters-room</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr"/>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>Founder-led boutique with a distinctive brand identity and 35 years' combined recruitment experience</t>
+        </is>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L332" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M332" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N332" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O332" s="4" t="inlineStr">
+        <is>
+          <t>Distinctive branding; LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P332" s="4" t="inlineStr">
+        <is>
+          <t>Distinctive brand identity not yet converted into AI-search dominance for Berkshire/Hampshire recruitment</t>
+        </is>
+      </c>
+      <c r="Q332" s="4" t="inlineStr">
+        <is>
+          <t>'The two Lauras' - own that memorable branding in AI-search answers too</t>
+        </is>
+      </c>
+      <c r="R332" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S332" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T332" s="4" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>Olympia Finance</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Mortgage broker</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>Covent Garden, London (serves Eltham/Sidcup/Bexley/Woolwich/Dartford/Lewisham/Essex)</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>https://olympiafinance.co.uk</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>info@olympiafinance.co.uk</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="inlineStr">
+        <is>
+          <t>0207 096 1988</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Ashan Sarkar (Director)</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/olympiafinance</t>
+        </is>
+      </c>
+      <c r="I333" s="3" t="inlineStr"/>
+      <c r="J333" s="3" t="inlineStr">
+        <is>
+          <t>Whole-of-market broker with per-area landing pages across 8+ SE London/Essex towns - genuine SEO investment</t>
+        </is>
+      </c>
+      <c r="K333" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L333" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M333" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N333" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O333" s="3" t="inlineStr">
+        <is>
+          <t>Extensive per-area landing pages = active SEO strategy</t>
+        </is>
+      </c>
+      <c r="P333" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist across 8+ areas but AI-answer citations still open for most of them</t>
+        </is>
+      </c>
+      <c r="Q333" s="3" t="inlineStr">
+        <is>
+          <t>'You've built pages for 8 areas - the AEO layer could multiply that investment overnight'</t>
+        </is>
+      </c>
+      <c r="R333" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S333" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T333" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T327"/>
+  <autoFilter ref="A1:T333"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28760,7 +29280,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
@@ -28777,7 +29297,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -28793,7 +29313,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -28803,11 +29323,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -28823,17 +29343,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -28843,7 +29363,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -28883,7 +29403,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -28893,7 +29413,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -28903,21 +29423,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$340</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T333"/>
+  <dimension ref="A1:T340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -29248,8 +29248,604 @@
       </c>
       <c r="T333" s="3" t="inlineStr"/>
     </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>Bespoke Estate Agents</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire (+ South Oxfordshire)</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mybespokeagent.com</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr"/>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>Mark Heneghan MNAEA (Founder, 30+ years)</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr"/>
+      <c r="I334" s="3" t="inlineStr"/>
+      <c r="J334" s="3" t="inlineStr">
+        <is>
+          <t>Founder personally involved with every client for 30 years; local-knowledge positioning across Berkshire/South Oxon</t>
+        </is>
+      </c>
+      <c r="K334" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L334" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M334" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N334" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O334" s="3" t="inlineStr">
+        <is>
+          <t>Alumni/community directory presence</t>
+        </is>
+      </c>
+      <c r="P334" s="3" t="inlineStr">
+        <is>
+          <t>30 years of personal service invisible against Winkworth/Chancellors corporate brands in Reading search</t>
+        </is>
+      </c>
+      <c r="Q334" s="3" t="inlineStr">
+        <is>
+          <t>'A founder who personally guides every client for 30 years - own that story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R334" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S334" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T334" s="3" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>Quarters</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>Rose Street, Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>https://www.quarters.agency</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>hello@quarters.agency</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="inlineStr">
+        <is>
+          <t>0118 466 0292</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>Co-founders with 40+ years combined experience (est. 2003)</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/QuartersResidential</t>
+        </is>
+      </c>
+      <c r="I335" s="3" t="inlineStr"/>
+      <c r="J335" s="3" t="inlineStr">
+        <is>
+          <t>Deliberately boutique - only partners with a small handful of families at a time; bespoke marketing per home</t>
+        </is>
+      </c>
+      <c r="K335" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L335" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M335" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N335" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O335" s="3" t="inlineStr">
+        <is>
+          <t>Journal/values content = active brand marketing</t>
+        </is>
+      </c>
+      <c r="P335" s="3" t="inlineStr">
+        <is>
+          <t>Boutique-by-design positioning not yet the AI-cited answer for premium Wokingham property</t>
+        </is>
+      </c>
+      <c r="Q335" s="3" t="inlineStr">
+        <is>
+          <t>'Deliberately small, deliberately bespoke - own that AEO positioning against volume agents'</t>
+        </is>
+      </c>
+      <c r="R335" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S335" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T335" s="3" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>Wentworth Estate Agents</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>Twyford/Woodley (serves Reading), Berkshire</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wentworthestateagents.com</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F336" s="4" t="inlineStr"/>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>Adrian Laflin (Founder, est. 2000)</t>
+        </is>
+      </c>
+      <c r="H336" s="4" t="inlineStr"/>
+      <c r="I336" s="4" t="inlineStr"/>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 2000, founder actively involved day-to-day across the Reading commuter belt</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L336" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M336" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N336" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O336" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P336" s="4" t="inlineStr">
+        <is>
+          <t>24 years of active founder involvement untranslated into modern search presence</t>
+        </is>
+      </c>
+      <c r="Q336" s="4" t="inlineStr">
+        <is>
+          <t>'A founder still hands-on after 24 years - own that trust story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R336" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S336" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T336" s="4" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>Reading Dental Spa</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>Wokingham Road, Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>https://www.readingdentalspa.co.uk</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>01183 272 322</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr"/>
+      <c r="H337" s="3" t="inlineStr"/>
+      <c r="I337" s="3" t="inlineStr"/>
+      <c r="J337" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated implant-offer landing page shows active SEO investment; spa-style premium positioning</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L337" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M337" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N337" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O337" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated implant-offer page = active SEO</t>
+        </is>
+      </c>
+      <c r="P337" s="3" t="inlineStr">
+        <is>
+          <t>Implant offer page exists but AI-answer citations for 'dental implants Reading' still open</t>
+        </is>
+      </c>
+      <c r="Q337" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade the existing implant-offer SEO page into an AEO-optimised asset</t>
+        </is>
+      </c>
+      <c r="R337" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S337" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T337" s="3" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>Earley Dental Practice</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Earley, Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>https://earleydentist.co.uk</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr"/>
+      <c r="G338" s="4" t="inlineStr"/>
+      <c r="H338" s="4" t="inlineStr"/>
+      <c r="I338" s="4" t="inlineStr"/>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>Well-established private practice with dedicated implants category page</t>
+        </is>
+      </c>
+      <c r="K338" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L338" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M338" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N338" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O338" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated implants category page</t>
+        </is>
+      </c>
+      <c r="P338" s="4" t="inlineStr">
+        <is>
+          <t>Reading Dental Spa and Puresmile Earley compete for the same implant searches</t>
+        </is>
+      </c>
+      <c r="Q338" s="4" t="inlineStr">
+        <is>
+          <t>Differentiate via specific implant-technique AEO content vs generic rivals</t>
+        </is>
+      </c>
+      <c r="R338" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S338" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T338" s="4" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>Heritage Revival</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Architects (heritage specialism)</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>Broad Street, Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>https://heritagerevival.uk</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>info@heritagerevival.uk</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>0118 403 2885</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr"/>
+      <c r="H339" s="3" t="inlineStr"/>
+      <c r="I339" s="3" t="inlineStr"/>
+      <c r="J339" s="3" t="inlineStr">
+        <is>
+          <t>Heritage/listed-building architecture specialism - genuinely defensible niche vs generic residential architects</t>
+        </is>
+      </c>
+      <c r="K339" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L339" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M339" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N339" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O339" s="3" t="inlineStr">
+        <is>
+          <t>Niche name/positioning ('Heritage Revival')</t>
+        </is>
+      </c>
+      <c r="P339" s="3" t="inlineStr">
+        <is>
+          <t>Heritage specialism is a strong AEO niche barely contested in Berkshire search</t>
+        </is>
+      </c>
+      <c r="Q339" s="3" t="inlineStr">
+        <is>
+          <t>Own 'listed building architect Berkshire' - a specific, low-competition AEO target</t>
+        </is>
+      </c>
+      <c r="R339" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S339" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T339" s="3" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>Millward, May &amp; Co</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Peach Street, Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>https://www.millwardmay.co.uk</t>
+        </is>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>emma@millwardmay.co.uk</t>
+        </is>
+      </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>0118 380 0363</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>Emma May &amp; Ben Hicks (Partners)</t>
+        </is>
+      </c>
+      <c r="H340" s="4" t="inlineStr"/>
+      <c r="I340" s="4" t="inlineStr"/>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>Independent firm for business owners; named partners with direct emails; recurring-fee SME client base</t>
+        </is>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M340" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N340" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O340" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P340" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'accountant Wokingham' searches won by TaxAssist/national franchise brands</t>
+        </is>
+      </c>
+      <c r="Q340" s="4" t="inlineStr">
+        <is>
+          <t>'For business owners' positioning - own that specific AEO angle vs generic accountancy search</t>
+        </is>
+      </c>
+      <c r="R340" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S340" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T340" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T333"/>
+  <autoFilter ref="A1:T340"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29260,7 +29856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -29280,7 +29876,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
@@ -29297,7 +29893,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -29347,13 +29943,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -29363,7 +29959,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Estate &amp; letting agent</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -29373,11 +29969,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Estate &amp; letting agent</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -30597,6 +31193,16 @@
         </is>
       </c>
       <c r="B136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Architects (heritage specialism)</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$348</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T340"/>
+  <dimension ref="A1:T348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -29844,8 +29844,708 @@
       </c>
       <c r="T340" s="4" t="inlineStr"/>
     </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>Jacobs Properties</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jacobs.properties</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>info@jacobs.properties</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>01256 781 300</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>Jon Coombs (Owner, est. 1999)</t>
+        </is>
+      </c>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jon-coombs</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr"/>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>Independent since 1999, self-described 'people's estate agent'; friendly-service positioning in Basingstoke commuter belt</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L341" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M341" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N341" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O341" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P341" s="4" t="inlineStr">
+        <is>
+          <t>'People's estate agent' branding not yet the AI-cited answer for Basingstoke property search</t>
+        </is>
+      </c>
+      <c r="Q341" s="4" t="inlineStr">
+        <is>
+          <t>Own the friendly/people-first AEO positioning against corporate Basingstoke rivals</t>
+        </is>
+      </c>
+      <c r="R341" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S341" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>Barons Estate Agents</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>Winton Square, Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>https://www.viewagents.com/estate-agent/Basingstoke/Barons-Estate-Agents</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F342" s="4" t="inlineStr"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>Kevin Penfold &amp; Trevor Lee (Founders, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H342" s="4" t="inlineStr"/>
+      <c r="I342" s="4" t="inlineStr"/>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>36-year independent firm still trading from its original office; long local heritage</t>
+        </is>
+      </c>
+      <c r="K342" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L342" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M342" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N342" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O342" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P342" s="4" t="inlineStr">
+        <is>
+          <t>36 years of continuous trading undersold as an AEO trust signal</t>
+        </is>
+      </c>
+      <c r="Q342" s="4" t="inlineStr">
+        <is>
+          <t>'Same office, same name, 36 years - make AI say so, not just Companies House'</t>
+        </is>
+      </c>
+      <c r="R342" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S342" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>Sansome and George</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sansomeandgeorge.co.uk</t>
+        </is>
+      </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F343" s="4" t="inlineStr"/>
+      <c r="G343" s="4" t="inlineStr"/>
+      <c r="H343" s="4" t="inlineStr"/>
+      <c r="I343" s="4" t="inlineStr"/>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>Family-run independent providing personal service across Basingstoke</t>
+        </is>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M343" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N343" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O343" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P343" s="4" t="inlineStr">
+        <is>
+          <t>Family-run positioning invisible against Fine &amp; Country/corporate rivals in Basingstoke search</t>
+        </is>
+      </c>
+      <c r="Q343" s="4" t="inlineStr">
+        <is>
+          <t>Own the family-run/personal-service AEO positioning outright</t>
+        </is>
+      </c>
+      <c r="R343" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S343" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T343" s="4" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>Bounty Road Dental</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bountyroaddental.co.uk</t>
+        </is>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>info@bountyroaddental.co.uk</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>01256 465 764</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr"/>
+      <c r="H344" s="4" t="inlineStr"/>
+      <c r="I344" s="4" t="inlineStr"/>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>Friendly, affordable-positioned implant/cosmetic private practice in Basingstoke</t>
+        </is>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L344" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M344" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N344" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O344" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P344" s="4" t="inlineStr">
+        <is>
+          <t>'Affordable + high-quality' positioning not yet the AI-cited local answer</t>
+        </is>
+      </c>
+      <c r="Q344" s="4" t="inlineStr">
+        <is>
+          <t>Own the value-conscious implant-patient AEO segment in Basingstoke</t>
+        </is>
+      </c>
+      <c r="R344" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S344" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>Gwynne Dental</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>Private cosmetic dentist / implants</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>https://gwynnedental.co.uk</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>office@gwynnedental.co.uk</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="inlineStr">
+        <is>
+          <t>01256 321 945</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>Dr Sophie Clark-Lipscomb (Oral Surgeon)</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr"/>
+      <c r="I345" s="3" t="inlineStr"/>
+      <c r="J345" s="3" t="inlineStr">
+        <is>
+          <t>Named oral surgeon providing implant treatment; leading private cosmetic dentist positioning</t>
+        </is>
+      </c>
+      <c r="K345" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L345" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M345" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N345" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O345" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P345" s="3" t="inlineStr">
+        <is>
+          <t>Named-surgeon credential not leveraged as the AI-cited trust signal for implant searches</t>
+        </is>
+      </c>
+      <c r="Q345" s="3" t="inlineStr">
+        <is>
+          <t>'A named oral surgeon doing your implants' - own that credibility angle in AEO content</t>
+        </is>
+      </c>
+      <c r="R345" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S345" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T345" s="3" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>The Hampshire Vet</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>Beggarwood, Basingstoke, Hampshire</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thehampshirevet.co.uk</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>info@thehampshirevet.co.uk</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>01256 639 707</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>Emily &amp; Jamie (Founders, both head vets)</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/thehampshirevet</t>
+        </is>
+      </c>
+      <c r="I346" s="3" t="inlineStr"/>
+      <c r="J346" s="3" t="inlineStr">
+        <is>
+          <t>New independent practice with onsite overnight care - genuine differentiator vs corporate day-only branches</t>
+        </is>
+      </c>
+      <c r="K346" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M346" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N346" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O346" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; onsite-care positioning</t>
+        </is>
+      </c>
+      <c r="P346" s="3" t="inlineStr">
+        <is>
+          <t>New practice needs fast search-authority building against established corporate Basingstoke vets</t>
+        </is>
+      </c>
+      <c r="Q346" s="3" t="inlineStr">
+        <is>
+          <t>'Overnight care onsite - own that AEO differentiator before corporate chains copy it'</t>
+        </is>
+      </c>
+      <c r="R346" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S346" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T346" s="3" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>Wokingham Solar</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>Solar installer</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wokinghamsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>hello@wokinghamsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="inlineStr">
+        <is>
+          <t>0118 449 2824</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>Paul &amp; Simon (Founders)</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Wokingham-Solar-61568618596545</t>
+        </is>
+      </c>
+      <c r="I347" s="3" t="inlineStr"/>
+      <c r="J347" s="3" t="inlineStr">
+        <is>
+          <t>MCS installer with dedicated case-studies page - active SEO/proof-point investment</t>
+        </is>
+      </c>
+      <c r="K347" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L347" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M347" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N347" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O347" s="3" t="inlineStr">
+        <is>
+          <t>Case studies page = active content marketing</t>
+        </is>
+      </c>
+      <c r="P347" s="3" t="inlineStr">
+        <is>
+          <t>Case studies exist but AI-answer citations for 'solar installer Wokingham' still open</t>
+        </is>
+      </c>
+      <c r="Q347" s="3" t="inlineStr">
+        <is>
+          <t>Turn existing case studies into AEO-optimised proof-point content</t>
+        </is>
+      </c>
+      <c r="R347" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S347" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T347" s="3" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>FlexiFlame</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Heating engineer / plumbing</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Tilehurst, Reading (serves Berkshire)</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flexiflame.co.uk</t>
+        </is>
+      </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>0118 945 1999</t>
+        </is>
+      </c>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>Michael Pearse (Founder, 20+ years, Gas Safe)</t>
+        </is>
+      </c>
+      <c r="H348" s="4" t="inlineStr"/>
+      <c r="I348" s="4" t="inlineStr"/>
+      <c r="J348" s="4" t="inlineStr">
+        <is>
+          <t>20-year independent Gas Safe engineer; boiler/appliance repairs across Berkshire homes and businesses</t>
+        </is>
+      </c>
+      <c r="K348" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L348" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M348" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N348" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O348" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P348" s="4" t="inlineStr">
+        <is>
+          <t>MyBuilder/Checkatrade intercept heating-engineer searches before independents are found directly</t>
+        </is>
+      </c>
+      <c r="Q348" s="4" t="inlineStr">
+        <is>
+          <t>'20 years Gas Safe registered - stop paying Checkatrade for leads to your own patch'</t>
+        </is>
+      </c>
+      <c r="R348" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S348" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T348" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T340"/>
+  <autoFilter ref="A1:T348"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29856,7 +30556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B137"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -29876,7 +30576,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5">
@@ -29893,7 +30593,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -29919,7 +30619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -29929,11 +30629,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -29943,7 +30643,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -29999,17 +30699,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Solar installer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solar installer</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -31203,6 +31903,26 @@
         </is>
       </c>
       <c r="B137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Private cosmetic dentist / implants</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Heating engineer / plumbing</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$356</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T348"/>
+  <dimension ref="A1:T356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -30544,8 +30544,692 @@
       </c>
       <c r="T348" s="4" t="inlineStr"/>
     </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>Downer &amp; Co</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>Cheap Street, Newbury, Berkshire</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>https://www.downer.co.uk</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>simon.downer@downer.co.uk</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>01635 523 777</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>Simon Downer (Founder, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr"/>
+      <c r="I349" s="3" t="inlineStr"/>
+      <c r="J349" s="3" t="inlineStr">
+        <is>
+          <t>36-year entirely independent firm; founder still directly contactable; premium West Berkshire property fees</t>
+        </is>
+      </c>
+      <c r="K349" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L349" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M349" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N349" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O349" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P349" s="3" t="inlineStr">
+        <is>
+          <t>Savills/Carter Jonas corporate brands dominate Newbury premium search</t>
+        </is>
+      </c>
+      <c r="Q349" s="3" t="inlineStr">
+        <is>
+          <t>'36 years independent, founder still answering emails - own that AEO trust story'</t>
+        </is>
+      </c>
+      <c r="R349" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S349" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T349" s="3" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>Cricketts Estate Agent</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>Newbury, West Berkshire</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cricketts.co.uk</t>
+        </is>
+      </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F350" s="4" t="inlineStr"/>
+      <c r="G350" s="4" t="inlineStr"/>
+      <c r="H350" s="4" t="inlineStr"/>
+      <c r="I350" s="4" t="inlineStr"/>
+      <c r="J350" s="4" t="inlineStr">
+        <is>
+          <t>60+ years combined team experience, dedicated property manager per client - genuine service differentiator</t>
+        </is>
+      </c>
+      <c r="K350" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L350" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M350" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N350" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O350" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P350" s="4" t="inlineStr">
+        <is>
+          <t>'Dedicated property manager' positioning invisible in generic Newbury agent searches</t>
+        </is>
+      </c>
+      <c r="Q350" s="4" t="inlineStr">
+        <is>
+          <t>Own that specific personal-service AEO angle vs volume-focused rivals</t>
+        </is>
+      </c>
+      <c r="R350" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S350" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>Emmett Bloom</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent (boutique)</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>West Berkshire</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E351" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F351" s="4" t="inlineStr"/>
+      <c r="G351" s="4" t="inlineStr"/>
+      <c r="H351" s="4" t="inlineStr"/>
+      <c r="I351" s="4" t="inlineStr"/>
+      <c r="J351" s="4" t="inlineStr">
+        <is>
+          <t>Boutique independent with bespoke marketing for distinctive homes - premium niche positioning</t>
+        </is>
+      </c>
+      <c r="K351" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L351" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M351" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N351" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O351" s="4" t="inlineStr">
+        <is>
+          <t>Bespoke-marketing positioning</t>
+        </is>
+      </c>
+      <c r="P351" s="4" t="inlineStr">
+        <is>
+          <t>Boutique/bespoke claim not yet the AI-cited answer for premium West Berkshire property</t>
+        </is>
+      </c>
+      <c r="Q351" s="4" t="inlineStr">
+        <is>
+          <t>Own 'boutique estate agent West Berkshire' - a specific, defensible niche</t>
+        </is>
+      </c>
+      <c r="R351" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S351" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T351" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Combe Manor</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>Hungerford, West Berkshire</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.combemanor.com</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>01488 668 931</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>Sybille Russell (Family owner, since 1960s)</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr"/>
+      <c r="I352" s="2" t="inlineStr"/>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>Russell family estate for 60+ years, 30 years running weddings from the barns - deep, genuine multi-generation story</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>Multiple directory listings (Guides for Brides, Bridebook, Cvent)</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>60-year family story is an exceptional AEO asset barely used beyond directory blurbs</t>
+        </is>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>'One family, one estate, 60 years - own that story in every AI answer for Berkshire barn weddings'</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>Strong multi-generational heritage story - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="inlineStr">
+        <is>
+          <t>The Post Barn</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>Snelsmore Common, Newbury, Berkshire</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thepostbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E353" s="4" t="inlineStr">
+        <is>
+          <t>info@thepostbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>01635 881 800</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="inlineStr"/>
+      <c r="H353" s="4" t="inlineStr"/>
+      <c r="I353" s="4" t="inlineStr"/>
+      <c r="J353" s="4" t="inlineStr">
+        <is>
+          <t>Barn venue set within Snelsmore Common's protected countryside - distinctive natural setting</t>
+        </is>
+      </c>
+      <c r="K353" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L353" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M353" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N353" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O353" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P353" s="4" t="inlineStr">
+        <is>
+          <t>Protected-countryside setting undersold as a differentiator vs generic Berkshire barn venues</t>
+        </is>
+      </c>
+      <c r="Q353" s="4" t="inlineStr">
+        <is>
+          <t>'Weddings on protected common land' - own that unusual, specific AEO positioning</t>
+        </is>
+      </c>
+      <c r="R353" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S353" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="inlineStr">
+        <is>
+          <t>Lillibrooke Manor</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>Maidenhead, Berkshire</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>https://lillibrookemanor.co.uk</t>
+        </is>
+      </c>
+      <c r="E354" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F354" s="4" t="inlineStr"/>
+      <c r="G354" s="4" t="inlineStr"/>
+      <c r="H354" s="4" t="inlineStr"/>
+      <c r="I354" s="4" t="inlineStr"/>
+      <c r="J354" s="4" t="inlineStr">
+        <is>
+          <t>Family-run barn wedding venue in Berkshire's Maidenhead commuter belt</t>
+        </is>
+      </c>
+      <c r="K354" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L354" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M354" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N354" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O354" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated estate/venue content pages</t>
+        </is>
+      </c>
+      <c r="P354" s="4" t="inlineStr">
+        <is>
+          <t>Family-run story not yet leveraged as the AI-cited local differentiator</t>
+        </is>
+      </c>
+      <c r="Q354" s="4" t="inlineStr">
+        <is>
+          <t>Turn the family-run story into AEO content vs corporate-feeling rivals</t>
+        </is>
+      </c>
+      <c r="R354" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S354" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>The Berkshire Clinic</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Private GP</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>Reading &amp; Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>https://theberkshireclinic.com</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F355" s="3" t="inlineStr">
+        <is>
+          <t>0118 304 5920</t>
+        </is>
+      </c>
+      <c r="G355" s="3" t="inlineStr"/>
+      <c r="H355" s="3" t="inlineStr"/>
+      <c r="I355" s="3" t="inlineStr"/>
+      <c r="J355" s="3" t="inlineStr">
+        <is>
+          <t>Two-town private GP with urgent-consultation phone line - convenience differentiator</t>
+        </is>
+      </c>
+      <c r="K355" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M355" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N355" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O355" s="3" t="inlineStr">
+        <is>
+          <t>Urgent-line promoted</t>
+        </is>
+      </c>
+      <c r="P355" s="3" t="inlineStr">
+        <is>
+          <t>Two-town coverage claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q355" s="3" t="inlineStr">
+        <is>
+          <t>Per-town AEO content for both Reading and Wokingham private GP searches</t>
+        </is>
+      </c>
+      <c r="R355" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S355" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T355" s="3" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>Absolute Architecture</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>Architects &amp; interior design</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>Newbury, Berkshire (40-mile radius)</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>https://absolute-architecture.co.uk</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="inlineStr">
+        <is>
+          <t>01635 528 188</t>
+        </is>
+      </c>
+      <c r="G356" s="3" t="inlineStr">
+        <is>
+          <t>Kate Cooper &amp; Jennie Lunn (Directors, est. 2008)</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kate-cooper-a92a1420</t>
+        </is>
+      </c>
+      <c r="I356" s="3" t="inlineStr"/>
+      <c r="J356" s="3" t="inlineStr">
+        <is>
+          <t>Combined architecture + interior design for a 40-mile radius across 4 counties; named studio manager for client onboarding</t>
+        </is>
+      </c>
+      <c r="K356" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L356" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M356" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N356" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O356" s="3" t="inlineStr">
+        <is>
+          <t>Press coverage (Hamptons brochure feature)</t>
+        </is>
+      </c>
+      <c r="P356" s="3" t="inlineStr">
+        <is>
+          <t>Press feature exists but not yet converted into AI-search citation authority</t>
+        </is>
+      </c>
+      <c r="Q356" s="3" t="inlineStr">
+        <is>
+          <t>Turn existing press coverage into the AI-cited authority for Berkshire/Hampshire residential architecture</t>
+        </is>
+      </c>
+      <c r="R356" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S356" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T356" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T348"/>
+  <autoFilter ref="A1:T356"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30556,7 +31240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -30576,7 +31260,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5">
@@ -30593,13 +31277,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -30609,17 +31293,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -30629,7 +31313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -30649,17 +31333,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -30949,7 +31633,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -30959,7 +31643,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -30969,7 +31653,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -30979,7 +31663,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -30989,7 +31673,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -30999,17 +31683,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -31019,7 +31703,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -31029,7 +31713,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -31039,7 +31723,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -31049,7 +31733,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -31059,7 +31743,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -31069,7 +31753,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -31079,7 +31763,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -31089,7 +31773,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -31099,7 +31783,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -31109,7 +31793,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -31119,7 +31803,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -31129,7 +31813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -31139,7 +31823,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -31149,7 +31833,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -31159,7 +31843,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -31169,7 +31853,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -31179,7 +31863,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -31189,7 +31873,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -31199,7 +31883,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -31209,7 +31893,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -31219,7 +31903,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -31229,7 +31913,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -31239,7 +31923,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -31249,7 +31933,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -31259,7 +31943,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -31269,7 +31953,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -31279,7 +31963,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -31289,7 +31973,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -31299,7 +31983,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -31309,7 +31993,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -31319,7 +32003,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -31329,7 +32013,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -31339,7 +32023,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -31349,7 +32033,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -31359,7 +32043,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -31369,7 +32053,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -31379,7 +32063,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -31389,7 +32073,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -31399,7 +32083,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -31409,7 +32093,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -31419,7 +32103,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -31429,7 +32113,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -31439,7 +32123,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -31449,7 +32133,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -31459,7 +32143,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -31469,7 +32153,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -31479,7 +32163,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -31489,7 +32173,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -31499,7 +32183,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -31509,7 +32193,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -31519,7 +32203,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -31529,7 +32213,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -31539,7 +32223,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -31549,7 +32233,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -31559,7 +32243,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -31569,7 +32253,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -31579,7 +32263,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -31589,7 +32273,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -31599,7 +32283,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -31609,7 +32293,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -31619,7 +32303,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -31629,7 +32313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -31639,7 +32323,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -31649,7 +32333,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -31659,7 +32343,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -31669,7 +32353,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -31679,7 +32363,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -31689,7 +32373,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -31699,7 +32383,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -31923,6 +32607,16 @@
         </is>
       </c>
       <c r="B139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Estate agent (boutique)</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T356"/>
+  <dimension ref="A1:T364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -31228,8 +31228,712 @@
       </c>
       <c r="T356" s="3" t="inlineStr"/>
     </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>Martyn Cox &amp; Company</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>Corn Street, Witney, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>https://www.martyncox.com</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>property@martyncox.com</t>
+        </is>
+      </c>
+      <c r="F357" s="3" t="inlineStr">
+        <is>
+          <t>01993 779 020</t>
+        </is>
+      </c>
+      <c r="G357" s="3" t="inlineStr">
+        <is>
+          <t>Martyn Cox (Founder, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H357" s="3" t="inlineStr"/>
+      <c r="I357" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/martyncoxco</t>
+        </is>
+      </c>
+      <c r="J357" s="3" t="inlineStr">
+        <is>
+          <t>36-year independent in West Oxfordshire's market towns; town &amp; country property specialism</t>
+        </is>
+      </c>
+      <c r="K357" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L357" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M357" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N357" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O357" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P357" s="3" t="inlineStr">
+        <is>
+          <t>Corporate brands (scottfraser, Hamptons) compete for the same Witney searches</t>
+        </is>
+      </c>
+      <c r="Q357" s="3" t="inlineStr">
+        <is>
+          <t>'36 years of Witney town &amp; country property - own the AI answer, not just Rightmove'</t>
+        </is>
+      </c>
+      <c r="R357" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S357" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T357" s="3" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Merrifield</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>Witney/Abingdon/Wantage, Oxfordshire (8 offices)</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="inlineStr"/>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>Philip Miller &amp; Stuart Wallsworth (Directors, 30+ years each)</t>
+        </is>
+      </c>
+      <c r="H358" s="3" t="inlineStr"/>
+      <c r="I358" s="3" t="inlineStr"/>
+      <c r="J358" s="3" t="inlineStr">
+        <is>
+          <t>8-office independent group across West Oxfordshire market towns; high-energy proactive positioning</t>
+        </is>
+      </c>
+      <c r="K358" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L358" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M358" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N358" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O358" s="3" t="inlineStr">
+        <is>
+          <t>Multi-office scale</t>
+        </is>
+      </c>
+      <c r="P358" s="3" t="inlineStr">
+        <is>
+          <t>8-office claim not matched by per-town search dominance</t>
+        </is>
+      </c>
+      <c r="Q358" s="3" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own all 8 claimed markets</t>
+        </is>
+      </c>
+      <c r="R358" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S358" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T358" s="3" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="inlineStr">
+        <is>
+          <t>Simpsons Property</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>Witney (+ Abingdon), Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>https://www.simpsonsproperty.com</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F359" s="4" t="inlineStr"/>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>Tom Mizen (Witney branch manager)</t>
+        </is>
+      </c>
+      <c r="H359" s="4" t="inlineStr"/>
+      <c r="I359" s="4" t="inlineStr"/>
+      <c r="J359" s="4" t="inlineStr">
+        <is>
+          <t>60 years combined team experience across Witney/Abingdon offices</t>
+        </is>
+      </c>
+      <c r="K359" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L359" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M359" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N359" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O359" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P359" s="4" t="inlineStr">
+        <is>
+          <t>60 years' combined experience untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q359" s="4" t="inlineStr">
+        <is>
+          <t>'60 years combined experience - the AI answer should reflect it, not just staff bios'</t>
+        </is>
+      </c>
+      <c r="R359" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S359" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="inlineStr">
+        <is>
+          <t>Rejoice Dental Care</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>Ock Street, Abingdon, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>https://rejoicedental.co.uk</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>info@rejoicedental.co.uk</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>01235 550 855</t>
+        </is>
+      </c>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>Grace Addanki (Principal Dentist)</t>
+        </is>
+      </c>
+      <c r="H360" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/grace-addanki-94325b203</t>
+        </is>
+      </c>
+      <c r="I360" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/rejoicedc.sm</t>
+        </is>
+      </c>
+      <c r="J360" s="4" t="inlineStr">
+        <is>
+          <t>Named principal dentist, welcomes patients across South Oxfordshire including Witney; implant + whitening services</t>
+        </is>
+      </c>
+      <c r="K360" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L360" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M360" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N360" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O360" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence; LinkedIn</t>
+        </is>
+      </c>
+      <c r="P360" s="4" t="inlineStr">
+        <is>
+          <t>Wide catchment claim (South Oxon + Witney) not matched by per-area search dominance</t>
+        </is>
+      </c>
+      <c r="Q360" s="4" t="inlineStr">
+        <is>
+          <t>Per-area AEO content to actually own the wider claimed catchment</t>
+        </is>
+      </c>
+      <c r="R360" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S360" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T360" s="4" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>Buttercross Dental Practice</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>Corn Street, Witney, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>https://www.buttercrossdp.co.uk</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F361" s="4" t="inlineStr">
+        <is>
+          <t>01993 402 402</t>
+        </is>
+      </c>
+      <c r="G361" s="4" t="inlineStr"/>
+      <c r="H361" s="4" t="inlineStr"/>
+      <c r="I361" s="4" t="inlineStr"/>
+      <c r="J361" s="4" t="inlineStr">
+        <is>
+          <t>Advanced dentistry with dedicated implants treatment page in Witney town centre</t>
+        </is>
+      </c>
+      <c r="K361" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L361" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M361" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N361" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O361" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated implants page = active SEO</t>
+        </is>
+      </c>
+      <c r="P361" s="4" t="inlineStr">
+        <is>
+          <t>Implants page exists but AI-answer citations for 'dental implants Witney' still open</t>
+        </is>
+      </c>
+      <c r="Q361" s="4" t="inlineStr">
+        <is>
+          <t>Upgrade existing implants SEO page into an AEO-optimised asset</t>
+        </is>
+      </c>
+      <c r="R361" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S361" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>Anderson Orr Architects</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="inlineStr">
+        <is>
+          <t>Oxfordshire (+ London/Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>https://www.andersonorr.com</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="inlineStr"/>
+      <c r="G362" s="3" t="inlineStr">
+        <is>
+          <t>Est. 2000, 4th-generation design-led practice</t>
+        </is>
+      </c>
+      <c r="H362" s="3" t="inlineStr"/>
+      <c r="I362" s="3" t="inlineStr"/>
+      <c r="J362" s="3" t="inlineStr">
+        <is>
+          <t>High-end private residential + developer + commercial work spanning London to the Cotswolds - very high project values</t>
+        </is>
+      </c>
+      <c r="K362" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L362" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M362" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N362" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O362" s="3" t="inlineStr">
+        <is>
+          <t>Multi-region portfolio</t>
+        </is>
+      </c>
+      <c r="P362" s="3" t="inlineStr">
+        <is>
+          <t>Broad geographic reach not matched by per-region AEO dominance</t>
+        </is>
+      </c>
+      <c r="Q362" s="3" t="inlineStr">
+        <is>
+          <t>Per-region AEO content leveraging the 4th-generation design pedigree</t>
+        </is>
+      </c>
+      <c r="R362" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S362" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T362" s="3" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="inlineStr">
+        <is>
+          <t>SWA Architects</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>Eynsham, near Oxford, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>http://www.swa-architects.co.uk</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F363" s="4" t="inlineStr"/>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>Est. 1985 (Stanhope Wilkinson Associates)</t>
+        </is>
+      </c>
+      <c r="H363" s="4" t="inlineStr"/>
+      <c r="I363" s="4" t="inlineStr"/>
+      <c r="J363" s="4" t="inlineStr">
+        <is>
+          <t>40-year established practice near Oxford; efficient, value-for-money positioning</t>
+        </is>
+      </c>
+      <c r="K363" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L363" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M363" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N363" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O363" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P363" s="4" t="inlineStr">
+        <is>
+          <t>40 years of trust untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q363" s="4" t="inlineStr">
+        <is>
+          <t>'40 years near Oxford - the AI answer should reflect that heritage'</t>
+        </is>
+      </c>
+      <c r="R363" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S363" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T363" s="4" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>Ridgefield Consulting</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>Chartered accountants</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="inlineStr">
+        <is>
+          <t>Oxford (Church Way)</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ridgefieldconsulting.co.uk</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>simon@ridgefieldconsulting.co.uk</t>
+        </is>
+      </c>
+      <c r="F364" s="3" t="inlineStr">
+        <is>
+          <t>01491 578 207</t>
+        </is>
+      </c>
+      <c r="G364" s="3" t="inlineStr">
+        <is>
+          <t>Simon Thomas (Founder &amp; MD) &amp; Brian Thomas (Director, father-son)</t>
+        </is>
+      </c>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/simonthomasoxford</t>
+        </is>
+      </c>
+      <c r="I364" s="3" t="inlineStr"/>
+      <c r="J364" s="3" t="inlineStr">
+        <is>
+          <t>Father-son independent firm since 2010; press-featured (Independent Oxford interview) - marketing-aware</t>
+        </is>
+      </c>
+      <c r="K364" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M364" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N364" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O364" s="3" t="inlineStr">
+        <is>
+          <t>Press interview coverage; detailed team page</t>
+        </is>
+      </c>
+      <c r="P364" s="3" t="inlineStr">
+        <is>
+          <t>Press coverage exists but not yet converted into AI-search citation authority</t>
+        </is>
+      </c>
+      <c r="Q364" s="3" t="inlineStr">
+        <is>
+          <t>Turn the Independent Oxford press feature into AI-cited local authority content</t>
+        </is>
+      </c>
+      <c r="R364" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S364" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T364" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T356"/>
+  <autoFilter ref="A1:T364"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31260,7 +31964,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -31277,23 +31981,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wedding venue</t>
+          <t>Architects</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architects</t>
+          <t>Wedding venue</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -31327,13 +32031,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Private GP</t>
+          <t>Chartered accountants</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -31343,11 +32047,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chartered accountants</t>
+          <t>Private GP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$372</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T364"/>
+  <dimension ref="A1:T372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -31932,8 +31932,696 @@
       </c>
       <c r="T364" s="3" t="inlineStr"/>
     </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>Anker and Partners</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent &amp; chartered surveyors</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>High Street, Banbury, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ankerandpartners.co.uk</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>post@ankerandpartners.co.uk</t>
+        </is>
+      </c>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>01295 271 414</t>
+        </is>
+      </c>
+      <c r="G365" s="3" t="inlineStr">
+        <is>
+          <t>Est. 1984</t>
+        </is>
+      </c>
+      <c r="H365" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/anker-and-partners</t>
+        </is>
+      </c>
+      <c r="I365" s="3" t="inlineStr"/>
+      <c r="J365" s="3" t="inlineStr">
+        <is>
+          <t>40-year independent covering sales/lettings/surveying in North Oxfordshire; surveying arm adds a second revenue line</t>
+        </is>
+      </c>
+      <c r="K365" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L365" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M365" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N365" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O365" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P365" s="3" t="inlineStr">
+        <is>
+          <t>Fine &amp; Country and Chancellors corporate brands compete for Banbury premium search</t>
+        </is>
+      </c>
+      <c r="Q365" s="3" t="inlineStr">
+        <is>
+          <t>'40 years in Banbury property - own the AI answer, not just the high street presence'</t>
+        </is>
+      </c>
+      <c r="R365" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S365" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T365" s="3" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>Mark David Estate Agents</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="inlineStr">
+        <is>
+          <t>North Oxfordshire &amp; Cotswolds</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F366" s="3" t="inlineStr"/>
+      <c r="G366" s="3" t="inlineStr"/>
+      <c r="H366" s="3" t="inlineStr"/>
+      <c r="I366" s="3" t="inlineStr"/>
+      <c r="J366" s="3" t="inlineStr">
+        <is>
+          <t>Leading independent for village/country/equestrian homes in North Oxfordshire and the Cotswolds - high-value niche stock</t>
+        </is>
+      </c>
+      <c r="K366" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L366" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M366" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N366" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O366" s="3" t="inlineStr">
+        <is>
+          <t>Equestrian/country-home niche positioning</t>
+        </is>
+      </c>
+      <c r="P366" s="3" t="inlineStr">
+        <is>
+          <t>Niche property type (equestrian/country) is a strong AEO angle barely contested</t>
+        </is>
+      </c>
+      <c r="Q366" s="3" t="inlineStr">
+        <is>
+          <t>Own 'equestrian property agent Oxfordshire' - a specific, high-value niche</t>
+        </is>
+      </c>
+      <c r="R366" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S366" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T366" s="3" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>41 South Bar Dental Practice</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>South Bar, Banbury, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>https://www.41southbar.com</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>info@41southbar.com</t>
+        </is>
+      </c>
+      <c r="F367" s="3" t="inlineStr">
+        <is>
+          <t>01295 262 008</t>
+        </is>
+      </c>
+      <c r="G367" s="3" t="inlineStr">
+        <is>
+          <t>Dr Tom Donnelly (Owner since 1989)</t>
+        </is>
+      </c>
+      <c r="H367" s="3" t="inlineStr"/>
+      <c r="I367" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/41southbar</t>
+        </is>
+      </c>
+      <c r="J367" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning practice, same owner for 35+ years; deep local reputation for implants/cosmetic dentistry</t>
+        </is>
+      </c>
+      <c r="K367" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L367" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M367" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N367" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O367" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning branding; Facebook presence</t>
+        </is>
+      </c>
+      <c r="P367" s="3" t="inlineStr">
+        <is>
+          <t>35 years of ownership continuity is a strong AEO trust signal currently underused</t>
+        </is>
+      </c>
+      <c r="Q367" s="3" t="inlineStr">
+        <is>
+          <t>'Same owner, 35 years, award-winning - own that continuity story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R367" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S367" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T367" s="3" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="inlineStr">
+        <is>
+          <t>Bicester Dental Care &amp; Implant Centre</t>
+        </is>
+      </c>
+      <c r="B368" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>Sheep Street, Bicester, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E368" s="4" t="inlineStr">
+        <is>
+          <t>bicesterdental@gmail.com</t>
+        </is>
+      </c>
+      <c r="F368" s="4" t="inlineStr">
+        <is>
+          <t>01869 252 788</t>
+        </is>
+      </c>
+      <c r="G368" s="4" t="inlineStr"/>
+      <c r="H368" s="4" t="inlineStr"/>
+      <c r="I368" s="4" t="inlineStr"/>
+      <c r="J368" s="4" t="inlineStr">
+        <is>
+          <t>Free implant consultation offer in a growing Oxfordshire commuter town</t>
+        </is>
+      </c>
+      <c r="K368" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L368" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M368" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N368" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O368" s="4" t="inlineStr">
+        <is>
+          <t>Gmail contact address - low marketing infrastructure</t>
+        </is>
+      </c>
+      <c r="P368" s="4" t="inlineStr">
+        <is>
+          <t>Gmail address signals minimal digital marketing investment despite Bicester's fast-growing population</t>
+        </is>
+      </c>
+      <c r="Q368" s="4" t="inlineStr">
+        <is>
+          <t>'Bicester is growing fast - a Gmail address won't win the new-resident dental searches'</t>
+        </is>
+      </c>
+      <c r="R368" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S368" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T368" s="4" t="inlineStr">
+        <is>
+          <t>Gmail tell - same infrastructure-gap wedge pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>Hilltop Vets</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>Hinksey Heights, Oxford</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>https://hilltopvets.co.uk</t>
+        </is>
+      </c>
+      <c r="E369" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F369" s="4" t="inlineStr"/>
+      <c r="G369" s="4" t="inlineStr"/>
+      <c r="H369" s="4" t="inlineStr"/>
+      <c r="I369" s="4" t="inlineStr"/>
+      <c r="J369" s="4" t="inlineStr">
+        <is>
+          <t>Proudly independent, distinctive 'The Barn' setting on Oxford's southern bypass</t>
+        </is>
+      </c>
+      <c r="K369" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L369" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M369" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N369" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O369" s="4" t="inlineStr">
+        <is>
+          <t>Distinctive branding ('proudly independent')</t>
+        </is>
+      </c>
+      <c r="P369" s="4" t="inlineStr">
+        <is>
+          <t>'Proudly independent' positioning not yet the AI-cited answer for Oxford vet search</t>
+        </is>
+      </c>
+      <c r="Q369" s="4" t="inlineStr">
+        <is>
+          <t>Own that exact independence positioning as the AEO target</t>
+        </is>
+      </c>
+      <c r="R369" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S369" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T369" s="4" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="4" t="inlineStr">
+        <is>
+          <t>Boundary Vets</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>Oxford Road, Abingdon, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>info@boundaryvets.co.uk</t>
+        </is>
+      </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>01235 538 721</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="inlineStr"/>
+      <c r="H370" s="4" t="inlineStr"/>
+      <c r="I370" s="4" t="inlineStr"/>
+      <c r="J370" s="4" t="inlineStr">
+        <is>
+          <t>Independent Abingdon practice serving a fast-growing Oxfordshire commuter town</t>
+        </is>
+      </c>
+      <c r="K370" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L370" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M370" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N370" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O370" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P370" s="4" t="inlineStr">
+        <is>
+          <t>Corporate vet chains outspend on Abingdon-area vet search</t>
+        </is>
+      </c>
+      <c r="Q370" s="4" t="inlineStr">
+        <is>
+          <t>'Independent in a growing town - own the AI answer before the chains do'</t>
+        </is>
+      </c>
+      <c r="R370" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S370" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>Larkmead Veterinary Group</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Independent vet (mixed practice)</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr">
+        <is>
+          <t>Didcot, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E371" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F371" s="4" t="inlineStr"/>
+      <c r="G371" s="4" t="inlineStr"/>
+      <c r="H371" s="4" t="inlineStr"/>
+      <c r="I371" s="4" t="inlineStr"/>
+      <c r="J371" s="4" t="inlineStr">
+        <is>
+          <t>Independent 24/7 emergency practice covering pets, farm animals and equines - unusually broad mixed-practice model</t>
+        </is>
+      </c>
+      <c r="K371" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L371" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M371" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N371" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O371" s="4" t="inlineStr">
+        <is>
+          <t>24/7 emergency service</t>
+        </is>
+      </c>
+      <c r="P371" s="4" t="inlineStr">
+        <is>
+          <t>Mixed-practice (farm + equine + pets) breadth undersold as an AEO differentiator</t>
+        </is>
+      </c>
+      <c r="Q371" s="4" t="inlineStr">
+        <is>
+          <t>Own 'mixed animal vet Didcot' - a broader, less-contested niche than small-animal-only rivals</t>
+        </is>
+      </c>
+      <c r="R371" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S371" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T371" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>The Great Barn</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>Aynho, Oxfordshire/Northamptonshire border</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>https://thegreatbarn.net</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="inlineStr"/>
+      <c r="G372" s="3" t="inlineStr">
+        <is>
+          <t>Stephenson family (converted the barns in 1986)</t>
+        </is>
+      </c>
+      <c r="H372" s="3" t="inlineStr"/>
+      <c r="I372" s="3" t="inlineStr"/>
+      <c r="J372" s="3" t="inlineStr">
+        <is>
+          <t>18th-century barn converted for weddings by the founding family in 1986; recently professionalised operations via The Venue Group partnership</t>
+        </is>
+      </c>
+      <c r="K372" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L372" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M372" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N372" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O372" s="3" t="inlineStr">
+        <is>
+          <t>Multiple wedding-directory listings; professional venue-management partnership</t>
+        </is>
+      </c>
+      <c r="P372" s="3" t="inlineStr">
+        <is>
+          <t>New operational partnership is an opportunity to refresh the AEO strategy alongside it</t>
+        </is>
+      </c>
+      <c r="Q372" s="3" t="inlineStr">
+        <is>
+          <t>'Since the family converted it in 1986' - own that heritage story as the AI-cited differentiator</t>
+        </is>
+      </c>
+      <c r="R372" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S372" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T372" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T364"/>
+  <autoFilter ref="A1:T372"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31944,7 +32632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -31964,7 +32652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5">
@@ -31981,7 +32669,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -32001,37 +32689,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Private dentist</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Private dentist</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -32377,7 +33065,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -32387,7 +33075,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -32397,17 +33085,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -32417,7 +33105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -32427,7 +33115,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -32437,7 +33125,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -32447,7 +33135,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -32457,7 +33145,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -32467,7 +33155,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -32477,7 +33165,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -32487,7 +33175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -32497,7 +33185,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -32507,7 +33195,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -32517,7 +33205,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -32527,7 +33215,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -32537,7 +33225,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -32547,7 +33235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -32557,7 +33245,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -32567,7 +33255,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -32577,7 +33265,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -32587,7 +33275,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -32597,7 +33285,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -32607,7 +33295,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -32617,7 +33305,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -32627,7 +33315,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -32637,7 +33325,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -32647,7 +33335,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -32657,7 +33345,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -32667,7 +33355,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -32677,7 +33365,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -32687,7 +33375,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -32697,7 +33385,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -32707,7 +33395,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -32717,7 +33405,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -32727,7 +33415,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -32737,7 +33425,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -32747,7 +33435,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -32757,7 +33445,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -32767,7 +33455,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -32777,7 +33465,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -32787,7 +33475,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -32797,7 +33485,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -32807,7 +33495,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -32817,7 +33505,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -32827,7 +33515,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -32837,7 +33525,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -32847,7 +33535,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -32857,7 +33545,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -32867,7 +33555,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -32877,7 +33565,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -32887,7 +33575,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -32897,7 +33585,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -32907,7 +33595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -32917,7 +33605,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -32927,7 +33615,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -32937,7 +33625,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -32947,7 +33635,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -32957,7 +33645,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -32967,7 +33655,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -32977,7 +33665,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -32987,7 +33675,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -32997,7 +33685,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -33007,7 +33695,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -33017,7 +33705,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -33027,7 +33715,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -33037,7 +33725,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -33047,7 +33735,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -33057,7 +33745,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -33067,7 +33755,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -33077,7 +33765,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -33087,7 +33775,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -33097,7 +33785,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -33107,7 +33795,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -33117,7 +33805,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -33127,7 +33815,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -33137,7 +33825,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -33147,7 +33835,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -33321,6 +34009,16 @@
         </is>
       </c>
       <c r="B140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Independent vet (mixed practice)</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$380</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T372"/>
+  <dimension ref="A1:T380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -32620,8 +32620,692 @@
       </c>
       <c r="T372" s="3" t="inlineStr"/>
     </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>SLM Property</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>Windsor Town Centre, Berkshire</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>https://www.slmproperty.com</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F373" s="3" t="inlineStr"/>
+      <c r="G373" s="3" t="inlineStr">
+        <is>
+          <t>Lance Mordant &amp; Sophie Potter-Mordant (Father-daughter owners)</t>
+        </is>
+      </c>
+      <c r="H373" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/sophie-potter-mordant-09585a55</t>
+        </is>
+      </c>
+      <c r="I373" s="3" t="inlineStr"/>
+      <c r="J373" s="3" t="inlineStr">
+        <is>
+          <t>Family firm with 90 years of Central London property reputation now serving Windsor; ultra-premium royal-town property fees</t>
+        </is>
+      </c>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L373" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M373" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N373" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O373" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P373" s="3" t="inlineStr">
+        <is>
+          <t>90-year family reputation not yet converted into AI-search dominance for Windsor property searches</t>
+        </is>
+      </c>
+      <c r="Q373" s="3" t="inlineStr">
+        <is>
+          <t>'90 years of family reputation, now in Windsor - own that story in AI answers, not just testimonials'</t>
+        </is>
+      </c>
+      <c r="R373" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S373" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T373" s="3" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="4" t="inlineStr">
+        <is>
+          <t>Barker Stone</t>
+        </is>
+      </c>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>Cookham, Maidenhead, Berkshire</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>https://barkerstone.co.uk</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F374" s="4" t="inlineStr"/>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>Simon Stone (Director)</t>
+        </is>
+      </c>
+      <c r="H374" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/BarkerStoneUK</t>
+        </is>
+      </c>
+      <c r="I374" s="4" t="inlineStr"/>
+      <c r="J374" s="4" t="inlineStr">
+        <is>
+          <t>Bespoke personal service across Berkshire/Bucks/Surrey/London - wide, premium multi-county coverage</t>
+        </is>
+      </c>
+      <c r="K374" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L374" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M374" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N374" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O374" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P374" s="4" t="inlineStr">
+        <is>
+          <t>Wide multi-county claim not matched by per-area search dominance</t>
+        </is>
+      </c>
+      <c r="Q374" s="4" t="inlineStr">
+        <is>
+          <t>Per-town AEO content to actually own the claimed multi-county footprint</t>
+        </is>
+      </c>
+      <c r="R374" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S374" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T374" s="4" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>Marshalls Property Services</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>Windsor, Berkshire</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F375" s="4" t="inlineStr"/>
+      <c r="G375" s="4" t="inlineStr">
+        <is>
+          <t>Est. 1995</t>
+        </is>
+      </c>
+      <c r="H375" s="4" t="inlineStr"/>
+      <c r="I375" s="4" t="inlineStr"/>
+      <c r="J375" s="4" t="inlineStr">
+        <is>
+          <t>Family-owned since 1995, full estate management service in Windsor and surrounding villages</t>
+        </is>
+      </c>
+      <c r="K375" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L375" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M375" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N375" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O375" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P375" s="4" t="inlineStr">
+        <is>
+          <t>30 years of trust untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q375" s="4" t="inlineStr">
+        <is>
+          <t>'30 years managing Windsor estates - the AI answer should reflect that heritage'</t>
+        </is>
+      </c>
+      <c r="R375" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S375" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T375" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>Optima Dental Care</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / cosmetic</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>Boyn Valley Road, Maidenhead, Berkshire</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>https://optimadentalcare.co.uk</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>info@optimadentalcare.co.uk</t>
+        </is>
+      </c>
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>01628 777 552</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="inlineStr"/>
+      <c r="H376" s="4" t="inlineStr"/>
+      <c r="I376" s="4" t="inlineStr"/>
+      <c r="J376" s="4" t="inlineStr">
+        <is>
+          <t>Private + NHS cosmetic/implant practice also serving High Wycombe - two-town reach</t>
+        </is>
+      </c>
+      <c r="K376" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L376" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M376" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N376" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O376" s="4" t="inlineStr">
+        <is>
+          <t>Two-town service pages (Maidenhead + High Wycombe)</t>
+        </is>
+      </c>
+      <c r="P376" s="4" t="inlineStr">
+        <is>
+          <t>Two-town pages exist but AI-answer citations for either town still open</t>
+        </is>
+      </c>
+      <c r="Q376" s="4" t="inlineStr">
+        <is>
+          <t>Upgrade the existing two-town SEO pages into AEO-optimised assets</t>
+        </is>
+      </c>
+      <c r="R376" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S376" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T376" s="4" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>Portman Dental &amp; Implant Clinic</t>
+        </is>
+      </c>
+      <c r="B377" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>Maidenhead, Berkshire</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dentists-maidenhead.co.uk</t>
+        </is>
+      </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F377" s="4" t="inlineStr"/>
+      <c r="G377" s="4" t="inlineStr">
+        <is>
+          <t>Est. 2006</t>
+        </is>
+      </c>
+      <c r="H377" s="4" t="inlineStr"/>
+      <c r="I377" s="4" t="inlineStr"/>
+      <c r="J377" s="4" t="inlineStr">
+        <is>
+          <t>Specialist implant clinic playing a central Maidenhead role for nearly 20 years</t>
+        </is>
+      </c>
+      <c r="K377" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L377" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M377" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N377" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O377" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P377" s="4" t="inlineStr">
+        <is>
+          <t>20 years of specialist reputation untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q377" s="4" t="inlineStr">
+        <is>
+          <t>'Nearly 20 years of specialist implant care - own that AEO trust signal in Maidenhead'</t>
+        </is>
+      </c>
+      <c r="R377" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S377" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T377" s="4" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>Philip Wadge Architecture Studio</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="inlineStr">
+        <is>
+          <t>Berkshire (Ascot/Sunningdale/Windsor/Maidenhead/Newbury)</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>https://www.philipwadge.co.uk</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F378" s="3" t="inlineStr"/>
+      <c r="G378" s="3" t="inlineStr">
+        <is>
+          <t>Philip Wadge (Founder)</t>
+        </is>
+      </c>
+      <c r="H378" s="3" t="inlineStr"/>
+      <c r="I378" s="3" t="inlineStr"/>
+      <c r="J378" s="3" t="inlineStr">
+        <is>
+          <t>Extremely wide Berkshire coverage across 8+ named towns - genuinely broad reach for a single-founder practice</t>
+        </is>
+      </c>
+      <c r="K378" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L378" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M378" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N378" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O378" s="3" t="inlineStr">
+        <is>
+          <t>Per-town landing pages across many towns = major SEO investment</t>
+        </is>
+      </c>
+      <c r="P378" s="3" t="inlineStr">
+        <is>
+          <t>Landing pages exist for 8+ towns but AI-answer citations remain open across most of them</t>
+        </is>
+      </c>
+      <c r="Q378" s="3" t="inlineStr">
+        <is>
+          <t>'You built pages for 8 towns - the AEO layer could multiply that investment several times over'</t>
+        </is>
+      </c>
+      <c r="R378" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S378" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T378" s="3" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="inlineStr">
+        <is>
+          <t>TPA Studio</t>
+        </is>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>Architects</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>Maidenhead &amp; Thames Valley, Berkshire</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>https://tpa.studio</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F379" s="4" t="inlineStr"/>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>Natasha Gandhi, Ed Drysdale &amp; Peter Thomas (Partners, 30+ yrs combined)</t>
+        </is>
+      </c>
+      <c r="H379" s="4" t="inlineStr"/>
+      <c r="I379" s="4" t="inlineStr"/>
+      <c r="J379" s="4" t="inlineStr">
+        <is>
+          <t>Three-partner practice with 30+ years combined expertise across the Thames Valley</t>
+        </is>
+      </c>
+      <c r="K379" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L379" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M379" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N379" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O379" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P379" s="4" t="inlineStr">
+        <is>
+          <t>30 years' combined partner expertise untranslated into modern AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q379" s="4" t="inlineStr">
+        <is>
+          <t>Portfolio-driven AEO content leveraging the partners' combined decades of experience</t>
+        </is>
+      </c>
+      <c r="R379" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S379" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T379" s="4" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>SMA Wealth (Steven Mufti &amp; Associates)</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>Wealth management / IFA</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="inlineStr">
+        <is>
+          <t>Ascot, Berkshire</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>https://www.smawm.co.uk</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F380" s="3" t="inlineStr"/>
+      <c r="G380" s="3" t="inlineStr">
+        <is>
+          <t>Steven Mufti (Founder, Chartered Financial Planner, est. 2013)</t>
+        </is>
+      </c>
+      <c r="H380" s="3" t="inlineStr"/>
+      <c r="I380" s="3" t="inlineStr"/>
+      <c r="J380" s="3" t="inlineStr">
+        <is>
+          <t>Chartered founder serving the Home Counties from Ascot; detailed service-specific content (family wealth, professionals, corporate)</t>
+        </is>
+      </c>
+      <c r="K380" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L380" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M380" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N380" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O380" s="3" t="inlineStr">
+        <is>
+          <t>Multiple detailed service pages = active content marketing</t>
+        </is>
+      </c>
+      <c r="P380" s="3" t="inlineStr">
+        <is>
+          <t>Detailed service content exists but AI-answer citations for specific queries still open</t>
+        </is>
+      </c>
+      <c r="Q380" s="3" t="inlineStr">
+        <is>
+          <t>'You've written pages for every client type - let's make AI cite them, not just index them'</t>
+        </is>
+      </c>
+      <c r="R380" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S380" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T380" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T372"/>
+  <autoFilter ref="A1:T380"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32632,7 +33316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -32652,7 +33336,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5">
@@ -32669,7 +33353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -32679,7 +33363,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -32709,7 +33393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -33025,7 +33709,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -33035,7 +33719,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -33045,7 +33729,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -33055,7 +33739,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -33065,7 +33749,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -33075,7 +33759,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -33085,7 +33769,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -33095,17 +33779,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -33115,7 +33799,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -33125,7 +33809,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -33135,7 +33819,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -33145,7 +33829,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -33155,7 +33839,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -33165,7 +33849,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -33175,7 +33859,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -33185,7 +33869,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -33195,7 +33879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -33205,7 +33889,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -33215,7 +33899,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -33225,7 +33909,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -33235,7 +33919,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -33245,7 +33929,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -33255,7 +33939,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -33265,7 +33949,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -33275,7 +33959,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -33285,7 +33969,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -33295,7 +33979,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -33305,7 +33989,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -33315,7 +33999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -33325,7 +34009,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -33335,7 +34019,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -33345,7 +34029,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -33355,7 +34039,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -33365,7 +34049,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -33375,7 +34059,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -33385,7 +34069,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -33395,7 +34079,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -33405,7 +34089,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -33415,7 +34099,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -33425,7 +34109,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -33435,7 +34119,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -33445,7 +34129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -33455,7 +34139,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -33465,7 +34149,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -33475,7 +34159,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -33485,7 +34169,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -33495,7 +34179,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -33505,7 +34189,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -33515,7 +34199,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -33525,7 +34209,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -33535,7 +34219,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -33545,7 +34229,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -33555,7 +34239,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -33565,7 +34249,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -33575,7 +34259,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -33585,7 +34269,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -33595,7 +34279,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -33605,7 +34289,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -33615,7 +34299,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -33625,7 +34309,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -33635,7 +34319,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -33645,7 +34329,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -33655,7 +34339,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -33665,7 +34349,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -33675,7 +34359,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -33685,7 +34369,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -33695,7 +34379,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -33705,7 +34389,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -33715,7 +34399,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -34019,6 +34703,16 @@
         </is>
       </c>
       <c r="B141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Private dentist / cosmetic</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$387</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T380"/>
+  <dimension ref="A1:T387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -33304,8 +33304,616 @@
       </c>
       <c r="T380" s="3" t="inlineStr"/>
     </row>
+    <row r="381">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>Robsons Estate Agents</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>Amersham &amp; Chesham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>https://robsonsweb.com</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>Property@robsonsbucks.com</t>
+        </is>
+      </c>
+      <c r="F381" s="3" t="inlineStr">
+        <is>
+          <t>01494 724 999</t>
+        </is>
+      </c>
+      <c r="G381" s="3" t="inlineStr">
+        <is>
+          <t>Est. 1962, 9-office independent group</t>
+        </is>
+      </c>
+      <c r="H381" s="3" t="inlineStr"/>
+      <c r="I381" s="3" t="inlineStr"/>
+      <c r="J381" s="3" t="inlineStr">
+        <is>
+          <t>63-year independent group along the Metropolitan Line; 9-office scale gives serious cross-market fee volume</t>
+        </is>
+      </c>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L381" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M381" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N381" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O381" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P381" s="3" t="inlineStr">
+        <is>
+          <t>63 years of heritage across 9 offices untranslated into modern per-office AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q381" s="3" t="inlineStr">
+        <is>
+          <t>'63 years along the Met Line - own the AI answer for every office, not just Rightmove'</t>
+        </is>
+      </c>
+      <c r="R381" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S381" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T381" s="3" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="4" t="inlineStr">
+        <is>
+          <t>Binks Estate Agents</t>
+        </is>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t>Amersham/Chorleywood (Northwood to Chesham corridor)</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>https://binksweb.com</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F382" s="4" t="inlineStr"/>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>Est. 1994</t>
+        </is>
+      </c>
+      <c r="H382" s="4" t="inlineStr"/>
+      <c r="I382" s="4" t="inlineStr"/>
+      <c r="J382" s="4" t="inlineStr">
+        <is>
+          <t>31-year independent along the Metropolitan Line corridor; premium lettings/management specialism</t>
+        </is>
+      </c>
+      <c r="K382" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L382" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M382" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N382" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O382" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P382" s="4" t="inlineStr">
+        <is>
+          <t>Corporate rivals (Savills, Knight Frank) compete for the same Met Line searches</t>
+        </is>
+      </c>
+      <c r="Q382" s="4" t="inlineStr">
+        <is>
+          <t>'31 years along the Met Line - own the AI answer for Amersham/Chorleywood property'</t>
+        </is>
+      </c>
+      <c r="R382" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S382" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T382" s="4" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>Chess House Dental Practice</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>High Street, Chesham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chesshousedental.com</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>info@chesshousedental.com</t>
+        </is>
+      </c>
+      <c r="F383" s="3" t="inlineStr">
+        <is>
+          <t>01494 977 140</t>
+        </is>
+      </c>
+      <c r="G383" s="3" t="inlineStr">
+        <is>
+          <t>Dr Yash Ghevaria &amp; Dr Devang Patel (Implantology team)</t>
+        </is>
+      </c>
+      <c r="H383" s="3" t="inlineStr"/>
+      <c r="I383" s="3" t="inlineStr"/>
+      <c r="J383" s="3" t="inlineStr">
+        <is>
+          <t>Named implant specialists serving 4 Bucks towns (Chesham/Amersham/Chalfont/Bovingdon) from one practice</t>
+        </is>
+      </c>
+      <c r="K383" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L383" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M383" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N383" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O383" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated implants page = active SEO</t>
+        </is>
+      </c>
+      <c r="P383" s="3" t="inlineStr">
+        <is>
+          <t>4-town claim not matched by per-town search dominance for implant searches</t>
+        </is>
+      </c>
+      <c r="Q383" s="3" t="inlineStr">
+        <is>
+          <t>Per-town AEO content for 'dental implants' across all 4 claimed towns</t>
+        </is>
+      </c>
+      <c r="R383" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S383" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T383" s="3" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="4" t="inlineStr">
+        <is>
+          <t>The Dental &amp; Implant Centre</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>Private dentist / implants</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>Hill Avenue, Amersham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dentalandimplant.co.uk</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>01494 854 053</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr"/>
+      <c r="H384" s="4" t="inlineStr"/>
+      <c r="I384" s="4" t="inlineStr"/>
+      <c r="J384" s="4" t="inlineStr">
+        <is>
+          <t>Affordable-positioned implant specialist in Amersham; value-conscious implant patient segment</t>
+        </is>
+      </c>
+      <c r="K384" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L384" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M384" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N384" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O384" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P384" s="4" t="inlineStr">
+        <is>
+          <t>'Affordable' positioning not yet the AI-cited local answer for value-conscious implant searches</t>
+        </is>
+      </c>
+      <c r="Q384" s="4" t="inlineStr">
+        <is>
+          <t>Own the value-conscious implant-patient AEO segment in Amersham</t>
+        </is>
+      </c>
+      <c r="R384" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S384" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T384" s="4" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Evolution Properties</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>Ashford (+ Folkestone/Maidstone), Kent</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>https://evolutionproperties.co.uk</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>ashford@evolutionproperties.co.uk</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>01233 501 601</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Sharron (Founder, est. 2012)</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr"/>
+      <c r="I385" s="2" t="inlineStr"/>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>Gold Award-winning independent, invitation-only industry recognition, 130+ years combined staff experience</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>Gold Award status; polished agent-profile pages</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>Award status is a strong AEO trust signal not yet the AI-cited answer for Ashford property</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>'Gold Award-winning, invitation-only recognition - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>Award pedigree + founder story = strong AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>Geering &amp; Colyer</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>Ashford, Kent</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>https://www.geeringandcolyer.co.uk</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F386" s="3" t="inlineStr"/>
+      <c r="G386" s="3" t="inlineStr">
+        <is>
+          <t>Est. 1800s (Robert Geering &amp; Frank Colyer)</t>
+        </is>
+      </c>
+      <c r="H386" s="3" t="inlineStr"/>
+      <c r="I386" s="3" t="inlineStr"/>
+      <c r="J386" s="3" t="inlineStr">
+        <is>
+          <t>115+ year heritage firm - one of the oldest independent names in Kent property</t>
+        </is>
+      </c>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L386" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M386" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N386" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O386" s="3" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P386" s="3" t="inlineStr">
+        <is>
+          <t>115 years of history vastly underused as an AI-search trust signal</t>
+        </is>
+      </c>
+      <c r="Q386" s="3" t="inlineStr">
+        <is>
+          <t>'115 years in Kent property - the AI answer should say so, not just the company history page'</t>
+        </is>
+      </c>
+      <c r="R386" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S386" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T386" s="3" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>Cansdales</t>
+        </is>
+      </c>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; financial advisers</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>Little Chalfont &amp; Old Amersham, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cansdales.co.uk</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>01494 924 417</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>John Thornton (Director)</t>
+        </is>
+      </c>
+      <c r="H387" s="4" t="inlineStr"/>
+      <c r="I387" s="4" t="inlineStr"/>
+      <c r="J387" s="4" t="inlineStr">
+        <is>
+          <t>Combined accountancy + IFA firm across two Amersham-area offices - two revenue lines per client relationship</t>
+        </is>
+      </c>
+      <c r="K387" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L387" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M387" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N387" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O387" s="4" t="inlineStr">
+        <is>
+          <t>Two-office presence; SKS network member</t>
+        </is>
+      </c>
+      <c r="P387" s="4" t="inlineStr">
+        <is>
+          <t>Combined-service model not unified into one coherent AEO strategy across accountancy and IFA searches</t>
+        </is>
+      </c>
+      <c r="Q387" s="4" t="inlineStr">
+        <is>
+          <t>Consolidate accountancy + IFA services into one coherent local AEO content plan</t>
+        </is>
+      </c>
+      <c r="R387" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S387" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T387" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T380"/>
+  <autoFilter ref="A1:T387"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33316,7 +33924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -33336,7 +33944,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5">
@@ -33353,7 +33961,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -33379,17 +33987,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Independent vet</t>
+          <t>Private dentist / implants</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Private dentist / implants</t>
+          <t>Independent vet</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -34713,6 +35321,16 @@
         </is>
       </c>
       <c r="B142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; financial advisers</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$395</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T387"/>
+  <dimension ref="A1:T395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -33912,8 +33912,724 @@
       </c>
       <c r="T387" s="4" t="inlineStr"/>
     </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>Safehands Recruitment (Bristol)</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare recruitment agency</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>Castlemead, Bristol</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>https://www.safehandsrecruitment.co.uk/office/bristol/</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>info@safehandsrecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>0117 917 5777</t>
+        </is>
+      </c>
+      <c r="G388" s="3" t="inlineStr">
+        <is>
+          <t>Oli Yuille (Franchise owner, 25+ yrs recruitment experience)</t>
+        </is>
+      </c>
+      <c r="H388" s="3" t="inlineStr"/>
+      <c r="I388" s="3" t="inlineStr"/>
+      <c r="J388" s="3" t="inlineStr">
+        <is>
+          <t>Interim/permanent/temp staffing for social care and healthcare sector; care homes and NHS trusts pay premium day rates per placement</t>
+        </is>
+      </c>
+      <c r="K388" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L388" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M388" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N388" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O388" s="3" t="inlineStr">
+        <is>
+          <t>Franchise brand with national marketing support</t>
+        </is>
+      </c>
+      <c r="P388" s="3" t="inlineStr">
+        <is>
+          <t>Franchise model means local search visibility competes with sister branches for the same brand terms</t>
+        </is>
+      </c>
+      <c r="Q388" s="3" t="inlineStr">
+        <is>
+          <t>'Bristol's own Safehands - own the local AI answer, not just the national franchise site'</t>
+        </is>
+      </c>
+      <c r="R388" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S388" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T388" s="3" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>Moon Executive Search</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>Executive search / headhunting</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="inlineStr">
+        <is>
+          <t>Bristol &amp; London</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moonexecsearch.com</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>recruit@moonexecsearch.com</t>
+        </is>
+      </c>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>01275 371 200</t>
+        </is>
+      </c>
+      <c r="G389" s="3" t="inlineStr">
+        <is>
+          <t>Vanessa Moon &amp; Simon Quinn (Principals)</t>
+        </is>
+      </c>
+      <c r="H389" s="3" t="inlineStr"/>
+      <c r="I389" s="3" t="inlineStr"/>
+      <c r="J389" s="3" t="inlineStr">
+        <is>
+          <t>20+ years senior/board-level search; single placement fees run into tens of thousands; charity/corporate client mix</t>
+        </is>
+      </c>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L389" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M389" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N389" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O389" s="3" t="inlineStr">
+        <is>
+          <t>Press coverage (charity appointments)</t>
+        </is>
+      </c>
+      <c r="P389" s="3" t="inlineStr">
+        <is>
+          <t>High-value senior search queries increasingly researched via AI before a headhunter is contacted directly</t>
+        </is>
+      </c>
+      <c r="Q389" s="3" t="inlineStr">
+        <is>
+          <t>'When boards ask ChatGPT who handles senior search in the South West, be the answer'</t>
+        </is>
+      </c>
+      <c r="R389" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S389" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T389" s="3" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>Safe Haven Training</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>First aid &amp; health &amp; safety training</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="inlineStr">
+        <is>
+          <t>Cannock (nationwide UK delivery)</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>https://www.safehaventraining.co.uk</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>info@safehaventraining.co.uk</t>
+        </is>
+      </c>
+      <c r="F390" s="3" t="inlineStr">
+        <is>
+          <t>0800 260 6942</t>
+        </is>
+      </c>
+      <c r="G390" s="3" t="inlineStr">
+        <is>
+          <t>Ian Bryan (Founder, ex-NHS paramedic, est. 2012)</t>
+        </is>
+      </c>
+      <c r="H390" s="3" t="inlineStr"/>
+      <c r="I390" s="3" t="inlineStr"/>
+      <c r="J390" s="3" t="inlineStr">
+        <is>
+          <t>Nationwide certified first aid/H&amp;S training for businesses; corporate training contracts recur annually per client</t>
+        </is>
+      </c>
+      <c r="K390" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L390" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M390" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N390" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O390" s="3" t="inlineStr">
+        <is>
+          <t>Nationwide coverage claim; paramedic-credential branding</t>
+        </is>
+      </c>
+      <c r="P390" s="3" t="inlineStr">
+        <is>
+          <t>Nationwide reach means competing with dozens of similarly-positioned training providers in generic search</t>
+        </is>
+      </c>
+      <c r="Q390" s="3" t="inlineStr">
+        <is>
+          <t>'An ex-NHS paramedic teaching your team first aid' - own that credibility angle in AEO content</t>
+        </is>
+      </c>
+      <c r="R390" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S390" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T390" s="3" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>Education People</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>Teaching &amp; education recruitment agency</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>Bristol (South West England)</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>https://educationpeopleltd.com</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>nicole@educationpeopleltd.com</t>
+        </is>
+      </c>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>0117 325 2516</t>
+        </is>
+      </c>
+      <c r="G391" s="3" t="inlineStr">
+        <is>
+          <t>Nicole Dommett (Founder &amp; Director, est. 2008)</t>
+        </is>
+      </c>
+      <c r="H391" s="3" t="inlineStr"/>
+      <c r="I391" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/educationpeople</t>
+        </is>
+      </c>
+      <c r="J391" s="3" t="inlineStr">
+        <is>
+          <t>17-year independent education recruiter covering Bristol/BANES/Somerset/Gloucestershire; schools pay per-placement fees repeatedly each term</t>
+        </is>
+      </c>
+      <c r="K391" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L391" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M391" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N391" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O391" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; established regional brand</t>
+        </is>
+      </c>
+      <c r="P391" s="3" t="inlineStr">
+        <is>
+          <t>TeacherActive/Tradewind/Prospero national brands with bigger budgets dominate 'teaching agency Bristol' search</t>
+        </is>
+      </c>
+      <c r="Q391" s="3" t="inlineStr">
+        <is>
+          <t>'17 years placing South West teachers - own that AEO answer against the national chains'</t>
+        </is>
+      </c>
+      <c r="R391" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S391" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T391" s="3" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>Supply Education Alliance</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>Supply teaching agency</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>Taunton (serves Bristol/Bath/Somerset/Wiltshire)</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>https://supply-education-alliance.co.uk</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="inlineStr">
+        <is>
+          <t>admin@supply-education-alliance.co.uk</t>
+        </is>
+      </c>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>0117 990 3481</t>
+        </is>
+      </c>
+      <c r="G392" s="3" t="inlineStr">
+        <is>
+          <t>Marie &amp; Emma (Co-founders, 17+ yrs combined)</t>
+        </is>
+      </c>
+      <c r="H392" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/supplyeducationalliance</t>
+        </is>
+      </c>
+      <c r="I392" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/somerseteducationallianceltd</t>
+        </is>
+      </c>
+      <c r="J392" s="3" t="inlineStr">
+        <is>
+          <t>Independent supply-teaching specialist across 3 counties from a Somerset base; recurring termly school placements</t>
+        </is>
+      </c>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L392" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M392" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N392" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O392" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P392" s="3" t="inlineStr">
+        <is>
+          <t>3-county claim not matched by per-county search dominance vs bigger agencies</t>
+        </is>
+      </c>
+      <c r="Q392" s="3" t="inlineStr">
+        <is>
+          <t>Per-county AEO content to actually own Bristol/Bath/Wiltshire searches separately</t>
+        </is>
+      </c>
+      <c r="R392" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S392" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T392" s="3" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>Harper Construction Recruitment</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>Construction recruitment agency</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>Clevedon, Bristol (South West)</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>https://harperconstructionrecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>info@harpercr.co.uk</t>
+        </is>
+      </c>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>01275 873 664</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>Family-run, est. ~2006 (nearly 20 years)</t>
+        </is>
+      </c>
+      <c r="H393" s="4" t="inlineStr"/>
+      <c r="I393" s="4" t="inlineStr"/>
+      <c r="J393" s="4" t="inlineStr">
+        <is>
+          <t>Independent trades/labour supplier to South West building sites; placement fees plus ongoing temp-labour margin per worker per week</t>
+        </is>
+      </c>
+      <c r="K393" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L393" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M393" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N393" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O393" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P393" s="4" t="inlineStr">
+        <is>
+          <t>Time4Recruitment/national construction agencies compete for the same South West site-labour searches</t>
+        </is>
+      </c>
+      <c r="Q393" s="4" t="inlineStr">
+        <is>
+          <t>'20 years supplying South West sites - own the AI answer for "construction recruitment Bristol"'</t>
+        </is>
+      </c>
+      <c r="R393" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S393" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T393" s="4" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="inlineStr">
+        <is>
+          <t>Drayton Fox</t>
+        </is>
+      </c>
+      <c r="B394" s="4" t="inlineStr">
+        <is>
+          <t>Construction recruitment agency</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="inlineStr">
+        <is>
+          <t>Bristol (South West England)</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>https://www.draytonfox.com</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>alex.wyatt@draytonfox.com</t>
+        </is>
+      </c>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>07498 154 635</t>
+        </is>
+      </c>
+      <c r="G394" s="4" t="inlineStr"/>
+      <c r="H394" s="4" t="inlineStr"/>
+      <c r="I394" s="4" t="inlineStr"/>
+      <c r="J394" s="4" t="inlineStr">
+        <is>
+          <t>Independent built-environment recruiter; permanent/temp/contract placements across the South West construction sector</t>
+        </is>
+      </c>
+      <c r="K394" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L394" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M394" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N394" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O394" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P394" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'construction recruitment Bristol' searches split across several similar independents</t>
+        </is>
+      </c>
+      <c r="Q394" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific built-environment sub-niche (e.g. quantity surveyors, site managers) in AEO content</t>
+        </is>
+      </c>
+      <c r="R394" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S394" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T394" s="4" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>Evolve Hospitality Recruitment</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>Hospitality staffing agency</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="inlineStr">
+        <is>
+          <t>City of London (nationwide)</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>https://evolvehospitality.co.uk</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>london@evolvehospitality.co.uk</t>
+        </is>
+      </c>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>0207 397 1260</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>Ed Vokes (Director, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H395" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/ed-vokes-9a113433</t>
+        </is>
+      </c>
+      <c r="I395" s="4" t="inlineStr"/>
+      <c r="J395" s="4" t="inlineStr">
+        <is>
+          <t>14-year specialist hospitality staffing firm; caterers/hotels/venues pay recurring temp-staffing margins for events and shifts</t>
+        </is>
+      </c>
+      <c r="K395" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L395" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M395" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N395" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O395" s="4" t="inlineStr">
+        <is>
+          <t>Established multi-year brand</t>
+        </is>
+      </c>
+      <c r="P395" s="4" t="inlineStr">
+        <is>
+          <t>Crowded London hospitality-staffing market with many similarly-positioned independents</t>
+        </is>
+      </c>
+      <c r="Q395" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific hospitality-staffing niche (e.g. Michelin-standard chefs, prestige events) in AEO content</t>
+        </is>
+      </c>
+      <c r="R395" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S395" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T395" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T387"/>
+  <autoFilter ref="A1:T395"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33924,7 +34640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B143"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -33944,7 +34660,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5">
@@ -34397,17 +35113,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -34417,7 +35133,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -34427,7 +35143,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -34437,7 +35153,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -34447,7 +35163,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -34457,7 +35173,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -34467,7 +35183,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -34477,7 +35193,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -34487,7 +35203,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -34497,7 +35213,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -34507,7 +35223,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -34517,7 +35233,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -34527,7 +35243,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -34537,7 +35253,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -34547,7 +35263,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -34557,7 +35273,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -34567,7 +35283,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -34577,7 +35293,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -34587,7 +35303,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -34597,7 +35313,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -34607,7 +35323,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -34617,7 +35333,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -34627,7 +35343,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -34637,7 +35353,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -34647,7 +35363,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -34657,7 +35373,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -34667,7 +35383,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -34677,7 +35393,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -34687,7 +35403,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -34697,7 +35413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -34707,7 +35423,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -34717,7 +35433,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -34727,7 +35443,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -34737,7 +35453,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -34747,7 +35463,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -34757,7 +35473,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -34767,7 +35483,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -34777,7 +35493,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -34787,7 +35503,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -34797,7 +35513,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -34807,7 +35523,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -34817,7 +35533,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -34827,7 +35543,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -34837,7 +35553,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -34847,7 +35563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -34857,7 +35573,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -34867,7 +35583,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -34877,7 +35593,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -34887,7 +35603,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -34897,7 +35613,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -34907,7 +35623,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -34917,7 +35633,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -34927,7 +35643,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -34937,7 +35653,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -34947,7 +35663,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -34957,7 +35673,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -34967,7 +35683,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -34977,7 +35693,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -34987,7 +35703,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -34997,7 +35713,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -35007,7 +35723,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -35017,7 +35733,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -35027,7 +35743,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -35037,7 +35753,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -35047,7 +35763,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -35057,7 +35773,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -35067,7 +35783,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -35077,7 +35793,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -35087,7 +35803,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -35097,7 +35813,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -35107,7 +35823,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -35117,7 +35833,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -35127,7 +35843,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -35137,7 +35853,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -35147,7 +35863,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -35157,7 +35873,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -35167,7 +35883,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -35177,7 +35893,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -35187,7 +35903,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -35197,7 +35913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -35207,7 +35923,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -35217,7 +35933,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -35227,7 +35943,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -35237,7 +35953,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -35247,7 +35963,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -35257,7 +35973,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -35267,7 +35983,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -35277,7 +35993,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -35287,7 +36003,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -35297,7 +36013,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -35307,7 +36023,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -35317,7 +36033,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -35327,10 +36043,80 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>Private dentist / cosmetic</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Healthcare recruitment agency</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Executive search / headhunting</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>First aid &amp; health &amp; safety training</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Teaching &amp; education recruitment agency</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Supply teaching agency</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Hospitality staffing agency</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$401</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T395"/>
+  <dimension ref="A1:T401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34628,8 +34628,532 @@
       </c>
       <c r="T395" s="4" t="inlineStr"/>
     </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>Ashley Rees Associates</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>Finance &amp; accountancy recruitment agency</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="inlineStr">
+        <is>
+          <t>Henbury Road, Bristol</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ashleyreesassociates.co.uk</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F396" s="3" t="inlineStr"/>
+      <c r="G396" s="3" t="inlineStr">
+        <is>
+          <t>20-year independent South West specialist</t>
+        </is>
+      </c>
+      <c r="H396" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Ashley-Rees-Associates-100070959433536</t>
+        </is>
+      </c>
+      <c r="I396" s="3" t="inlineStr"/>
+      <c r="J396" s="3" t="inlineStr">
+        <is>
+          <t>REC-member independent recruiter for finance roles across SW England; placement fees on management-accountant-to-CFO roles are substantial</t>
+        </is>
+      </c>
+      <c r="K396" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L396" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M396" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N396" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O396" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; REC membership</t>
+        </is>
+      </c>
+      <c r="P396" s="3" t="inlineStr">
+        <is>
+          <t>Core3/national brands (Robert Walters, Morgan McKinley) dominate 'finance recruitment Bristol' search</t>
+        </is>
+      </c>
+      <c r="Q396" s="3" t="inlineStr">
+        <is>
+          <t>'20 years placing SW finance talent - own that AEO answer against the national brands'</t>
+        </is>
+      </c>
+      <c r="R396" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S396" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T396" s="3" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="inlineStr">
+        <is>
+          <t>Core3</t>
+        </is>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>Accounting &amp; finance recruitment agency</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F397" s="4" t="inlineStr"/>
+      <c r="G397" s="4" t="inlineStr"/>
+      <c r="H397" s="4" t="inlineStr"/>
+      <c r="I397" s="4" t="inlineStr"/>
+      <c r="J397" s="4" t="inlineStr">
+        <is>
+          <t>Bristol-headquartered specialist covering management accountants through to CFO placements</t>
+        </is>
+      </c>
+      <c r="K397" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L397" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M397" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N397" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O397" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P397" s="4" t="inlineStr">
+        <is>
+          <t>Same national-brand squeeze as other Bristol finance recruiters</t>
+        </is>
+      </c>
+      <c r="Q397" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific finance sub-niche (e.g. CFO/interim finance) in AEO content</t>
+        </is>
+      </c>
+      <c r="R397" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S397" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T397" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>HL Training Services</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>Forklift &amp; plant operator training</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="inlineStr">
+        <is>
+          <t>Barton Hill, Bristol</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hltraining.co.uk</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="inlineStr">
+        <is>
+          <t>sales@hltraining.co.uk</t>
+        </is>
+      </c>
+      <c r="F398" s="3" t="inlineStr">
+        <is>
+          <t>0117 952 5625</t>
+        </is>
+      </c>
+      <c r="G398" s="3" t="inlineStr">
+        <is>
+          <t>Vince Hueston Jr &amp; Angela Hueston (Family, est. 1988)</t>
+        </is>
+      </c>
+      <c r="H398" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/hl-training-services</t>
+        </is>
+      </c>
+      <c r="I398" s="3" t="inlineStr"/>
+      <c r="J398" s="3" t="inlineStr">
+        <is>
+          <t>37-year family business delivering RTITB/ITSSAR-accredited forklift and plant training on-site across the South West; corporate H&amp;S contracts recur</t>
+        </is>
+      </c>
+      <c r="K398" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L398" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M398" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N398" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O398" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; long trading history</t>
+        </is>
+      </c>
+      <c r="P398" s="3" t="inlineStr">
+        <is>
+          <t>National forklift-training franchises (Wallace School, Pegasus) outspend on generic 'forklift training Bristol' search</t>
+        </is>
+      </c>
+      <c r="Q398" s="3" t="inlineStr">
+        <is>
+          <t>'37 years training Bristol's forklift operators - own that AEO trust signal against national franchises'</t>
+        </is>
+      </c>
+      <c r="R398" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S398" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T398" s="3" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>Cuff Jones</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>Legal recruitment agency</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>Clerkenwell, London</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cuffjones.co.uk</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>steph@cuffjones.com</t>
+        </is>
+      </c>
+      <c r="F399" s="3" t="inlineStr"/>
+      <c r="G399" s="3" t="inlineStr">
+        <is>
+          <t>Jonathan Cuff (Director, est. 2010)</t>
+        </is>
+      </c>
+      <c r="H399" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jonathancuff1</t>
+        </is>
+      </c>
+      <c r="I399" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Cuff-Jones-Expert-Legal-Recruitment-100076873250336</t>
+        </is>
+      </c>
+      <c r="J399" s="3" t="inlineStr">
+        <is>
+          <t>Boutique legal recruiter to top law firms globally; single senior-solicitor placement fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K399" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L399" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M399" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N399" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O399" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; international client base</t>
+        </is>
+      </c>
+      <c r="P399" s="3" t="inlineStr">
+        <is>
+          <t>Boutique positioning invisible against Taylor Root/SSQ/Robert Walters in generic legal-recruitment search</t>
+        </is>
+      </c>
+      <c r="Q399" s="3" t="inlineStr">
+        <is>
+          <t>'Dedicated, personable legal recruitment vs a corporate agency conveyor belt - own that AEO positioning'</t>
+        </is>
+      </c>
+      <c r="R399" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S399" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T399" s="3" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>EJ Legal</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>Legal recruitment agency</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ejlegal.co.uk</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F400" s="4" t="inlineStr"/>
+      <c r="G400" s="4" t="inlineStr"/>
+      <c r="H400" s="4" t="inlineStr"/>
+      <c r="I400" s="4" t="inlineStr"/>
+      <c r="J400" s="4" t="inlineStr">
+        <is>
+          <t>London legal recruitment specialist placing solicitors/paralegals into law firms</t>
+        </is>
+      </c>
+      <c r="K400" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L400" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M400" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N400" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O400" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P400" s="4" t="inlineStr">
+        <is>
+          <t>Crowded London legal-recruitment market with many similarly-positioned boutiques</t>
+        </is>
+      </c>
+      <c r="Q400" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific legal practice-area niche (e.g. private client, litigation) in AEO content</t>
+        </is>
+      </c>
+      <c r="R400" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S400" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T400" s="4" t="inlineStr">
+        <is>
+          <t>Confirm live website before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>Pegasus Lift Truck Training</t>
+        </is>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>Forklift training</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>UK-wide (on-site delivery)</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>https://pegasuslifttrucktraining.co.uk</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F401" s="4" t="inlineStr"/>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>Dawn &amp; Giuseppe Girardi (Founders, 25+ yrs experience)</t>
+        </is>
+      </c>
+      <c r="H401" s="4" t="inlineStr"/>
+      <c r="I401" s="4" t="inlineStr"/>
+      <c r="J401" s="4" t="inlineStr">
+        <is>
+          <t>ITSSAR-accredited nationwide on-site training; corporate clients need repeat annual certification renewals</t>
+        </is>
+      </c>
+      <c r="K401" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L401" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M401" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N401" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O401" s="4" t="inlineStr">
+        <is>
+          <t>25-year trading history</t>
+        </is>
+      </c>
+      <c r="P401" s="4" t="inlineStr">
+        <is>
+          <t>National reach means competing with many similarly-positioned forklift trainers for the same generic searches</t>
+        </is>
+      </c>
+      <c r="Q401" s="4" t="inlineStr">
+        <is>
+          <t>'25 years of ITSSAR-accredited training - own the AEO answer for corporate renewal searches'</t>
+        </is>
+      </c>
+      <c r="R401" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S401" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T401" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T395"/>
+  <autoFilter ref="A1:T401"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34640,7 +35164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -34660,7 +35184,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -35123,17 +35647,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -35143,7 +35667,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -35153,7 +35677,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -35163,7 +35687,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -35173,7 +35697,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -35183,7 +35707,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -35193,7 +35717,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -35203,7 +35727,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -35213,7 +35737,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -35223,7 +35747,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -35233,7 +35757,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -35243,7 +35767,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -35253,7 +35777,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -35263,7 +35787,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -35273,7 +35797,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -35283,7 +35807,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -35293,7 +35817,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -35303,7 +35827,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -35313,7 +35837,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -35323,7 +35847,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -35333,7 +35857,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -35343,7 +35867,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -35353,7 +35877,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -35363,7 +35887,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -35373,7 +35897,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -35383,7 +35907,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -35393,7 +35917,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -35403,7 +35927,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -35413,7 +35937,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -35423,7 +35947,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -35433,7 +35957,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -35443,7 +35967,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -35453,7 +35977,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -35463,7 +35987,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -35473,7 +35997,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -35483,7 +36007,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -35493,7 +36017,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -35503,7 +36027,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -35513,7 +36037,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -35523,7 +36047,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -35533,7 +36057,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -35543,7 +36067,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -35553,7 +36077,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -35563,7 +36087,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -35573,7 +36097,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -35583,7 +36107,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -35593,7 +36117,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -35603,7 +36127,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -35613,7 +36137,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -35623,7 +36147,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -35633,7 +36157,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -35643,7 +36167,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -35653,7 +36177,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -35663,7 +36187,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -35673,7 +36197,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -35683,7 +36207,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -35693,7 +36217,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -35703,7 +36227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -35713,7 +36237,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -35723,7 +36247,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -35733,7 +36257,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -35743,7 +36267,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -35753,7 +36277,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -35763,7 +36287,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -35773,7 +36297,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -35783,7 +36307,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -35793,7 +36317,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -35803,7 +36327,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -35813,7 +36337,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -35823,7 +36347,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -35833,7 +36357,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -35843,7 +36367,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -35853,7 +36377,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -35863,7 +36387,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -35873,7 +36397,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -35883,7 +36407,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -35893,7 +36417,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -35903,7 +36427,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -35913,7 +36437,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -35923,7 +36447,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -35933,7 +36457,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -35943,7 +36467,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -35953,7 +36477,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -35963,7 +36487,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -35973,7 +36497,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -35983,7 +36507,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -35993,7 +36517,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -36003,7 +36527,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -36013,7 +36537,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -36023,7 +36547,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -36033,7 +36557,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -36043,7 +36567,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -36053,7 +36577,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -36063,7 +36587,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -36073,7 +36597,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -36083,7 +36607,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -36093,7 +36617,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -36103,7 +36627,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -36113,10 +36637,60 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>Supply teaching agency</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>Hospitality staffing agency</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Finance &amp; accountancy recruitment agency</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Accounting &amp; finance recruitment agency</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Forklift &amp; plant operator training</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Forklift training</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$407</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T401"/>
+  <dimension ref="A1:T407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35152,8 +35152,540 @@
       </c>
       <c r="T401" s="4" t="inlineStr"/>
     </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>Lewis School of English</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>Language school</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>Southampton (+ juniors/online)</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>https://lewis-school.co.uk</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>023 8022 8203</t>
+        </is>
+      </c>
+      <c r="G402" s="3" t="inlineStr">
+        <is>
+          <t>Alistair Walker MA (Director); est. 1976, 50th anniversary 2026</t>
+        </is>
+      </c>
+      <c r="H402" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/lewisschool</t>
+        </is>
+      </c>
+      <c r="I402" s="3" t="inlineStr"/>
+      <c r="J402" s="3" t="inlineStr">
+        <is>
+          <t>50-year independent language school; international students pay per-course/term fees, high LTV per enrolment</t>
+        </is>
+      </c>
+      <c r="K402" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L402" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M402" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N402" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O402" s="3" t="inlineStr">
+        <is>
+          <t>Established multi-decade brand; LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P402" s="3" t="inlineStr">
+        <is>
+          <t>50th-anniversary milestone is a strong AEO/PR hook not yet leveraged for AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q402" s="3" t="inlineStr">
+        <is>
+          <t>'Celebrating 50 years - turn the anniversary into the AI-cited answer for English language schools in the UK'</t>
+        </is>
+      </c>
+      <c r="R402" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S402" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T402" s="3" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>Sigma Recruitment</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>Engineering &amp; manufacturing recruitment</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>Cardiff (serves Bristol/Bath/South West)</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sigmarecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>rhys@sigmarecruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>029 2010 0790</t>
+        </is>
+      </c>
+      <c r="G403" s="3" t="inlineStr">
+        <is>
+          <t>Rhys Williams (Founder, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H403" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/rhyswilliamsigma</t>
+        </is>
+      </c>
+      <c r="I403" s="3" t="inlineStr"/>
+      <c r="J403" s="3" t="inlineStr">
+        <is>
+          <t>20-year independent engineering recruiter with a dedicated Bristol-market landing page - active SEO investment reaching into the South West despite a Cardiff HQ</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L403" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M403" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N403" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O403" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated Bristol/Bath location landing pages = active SEO</t>
+        </is>
+      </c>
+      <c r="P403" s="3" t="inlineStr">
+        <is>
+          <t>Bristol landing page exists but AI-answer citations for 'engineering recruitment Bristol' still open</t>
+        </is>
+      </c>
+      <c r="Q403" s="3" t="inlineStr">
+        <is>
+          <t>'You built the Bristol page - let's make sure AI cites it, not just Google'</t>
+        </is>
+      </c>
+      <c r="R403" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S403" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T403" s="3" t="inlineStr">
+        <is>
+          <t>HQ is Cardiff; targets Bristol/Bath market via dedicated pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>Kieran Perry</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>Business &amp; sales coaching</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="inlineStr">
+        <is>
+          <t>Sandbach/London (serves UK-wide)</t>
+        </is>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kieranperry.com</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="inlineStr">
+        <is>
+          <t>info@kieranperry.com</t>
+        </is>
+      </c>
+      <c r="F404" s="3" t="inlineStr">
+        <is>
+          <t>07912 846 492</t>
+        </is>
+      </c>
+      <c r="G404" s="3" t="inlineStr">
+        <is>
+          <t>Kieran Perry (Founder, 25+ yrs experience)</t>
+        </is>
+      </c>
+      <c r="H404" s="3" t="inlineStr"/>
+      <c r="I404" s="3" t="inlineStr"/>
+      <c r="J404" s="3" t="inlineStr">
+        <is>
+          <t>Solo executive/sales coach with published book and blog-driven content strategy; corporate coaching retainers worth thousands per client</t>
+        </is>
+      </c>
+      <c r="K404" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L404" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M404" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N404" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O404" s="3" t="inlineStr">
+        <is>
+          <t>Extensive blog/SEO content across many coaching topics = active SEO investment</t>
+        </is>
+      </c>
+      <c r="P404" s="3" t="inlineStr">
+        <is>
+          <t>Large content library exists but AI-answer citations for specific coaching queries still open</t>
+        </is>
+      </c>
+      <c r="Q404" s="3" t="inlineStr">
+        <is>
+          <t>'You've written the definitive guides - let's make AI cite them, not just index them'</t>
+        </is>
+      </c>
+      <c r="R404" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S404" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T404" s="3" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>Nolan Recruitment</t>
+        </is>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>Engineering &amp; energy recruitment</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>UK-wide</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nolanrecruitment.com</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F405" s="4" t="inlineStr"/>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>Sean Neary (Managing Director, est. 2016)</t>
+        </is>
+      </c>
+      <c r="H405" s="4" t="inlineStr"/>
+      <c r="I405" s="4" t="inlineStr"/>
+      <c r="J405" s="4" t="inlineStr">
+        <is>
+          <t>Independent specialist in engineering/energy sector placements since 2016; high-value technical placements</t>
+        </is>
+      </c>
+      <c r="K405" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L405" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M405" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N405" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O405" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P405" s="4" t="inlineStr">
+        <is>
+          <t>Crowded engineering-recruitment market with many similarly-positioned independents</t>
+        </is>
+      </c>
+      <c r="Q405" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific energy-sector sub-niche in AEO content vs generalist engineering recruiters</t>
+        </is>
+      </c>
+      <c r="R405" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S405" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T405" s="4" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>Hughes Driver Training</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>HGV driver training</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="inlineStr">
+        <is>
+          <t>Leicester (nationwide delivery)</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hughesdrivertraining.co.uk</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>info@hughesdrivertraining.co.uk</t>
+        </is>
+      </c>
+      <c r="F406" s="3" t="inlineStr">
+        <is>
+          <t>0800 177 7447</t>
+        </is>
+      </c>
+      <c r="G406" s="3" t="inlineStr">
+        <is>
+          <t>Bill Hughes (Founder); now 3rd generation family-run</t>
+        </is>
+      </c>
+      <c r="H406" s="3" t="inlineStr"/>
+      <c r="I406" s="3" t="inlineStr"/>
+      <c r="J406" s="3" t="inlineStr">
+        <is>
+          <t>Multi-generation family HGV training business; logistics firms need repeat driver certification and CPC training</t>
+        </is>
+      </c>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L406" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M406" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N406" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O406" s="3" t="inlineStr">
+        <is>
+          <t>Family-story branding ('Our Story' page)</t>
+        </is>
+      </c>
+      <c r="P406" s="3" t="inlineStr">
+        <is>
+          <t>3-generation family story is a strong AEO trust asset not yet leveraged against national franchises</t>
+        </is>
+      </c>
+      <c r="Q406" s="3" t="inlineStr">
+        <is>
+          <t>'3 generations training HGV drivers - own that family-trust story in AI answers'</t>
+        </is>
+      </c>
+      <c r="R406" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S406" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T406" s="3" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>Hartlip HGV Driving School</t>
+        </is>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>HGV driver training</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hartliphgv.co.uk</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F407" s="4" t="inlineStr"/>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>Family-run</t>
+        </is>
+      </c>
+      <c r="H407" s="4" t="inlineStr"/>
+      <c r="I407" s="4" t="inlineStr"/>
+      <c r="J407" s="4" t="inlineStr">
+        <is>
+          <t>Independent family-run HGV school in Kent; affordable, tailored training for career-changers and logistics firms</t>
+        </is>
+      </c>
+      <c r="K407" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L407" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M407" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N407" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O407" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P407" s="4" t="inlineStr">
+        <is>
+          <t>National HGV training brands with bigger ad budgets dominate generic 'HGV training Kent' search</t>
+        </is>
+      </c>
+      <c r="Q407" s="4" t="inlineStr">
+        <is>
+          <t>'Family-run and affordable' - own that exact AEO positioning vs national franchises</t>
+        </is>
+      </c>
+      <c r="R407" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S407" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T407" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T401"/>
+  <autoFilter ref="A1:T407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35164,7 +35696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -35184,7 +35716,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
@@ -35657,17 +36189,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -35677,7 +36209,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -35687,7 +36219,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -35697,7 +36229,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -35707,7 +36239,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -35717,7 +36249,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -35727,7 +36259,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -35737,7 +36269,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -35747,7 +36279,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -35757,7 +36289,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -35767,7 +36299,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -35777,7 +36309,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -35787,7 +36319,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -35797,7 +36329,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -35807,7 +36339,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -35817,7 +36349,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -35827,7 +36359,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -35837,7 +36369,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -35847,7 +36379,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -35857,7 +36389,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -35867,7 +36399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -35877,7 +36409,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -35887,7 +36419,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -35897,7 +36429,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -35907,7 +36439,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -35917,7 +36449,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -35927,7 +36459,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -35937,7 +36469,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -35947,7 +36479,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -35957,7 +36489,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -35967,7 +36499,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -35977,7 +36509,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -35987,7 +36519,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -35997,7 +36529,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -36007,7 +36539,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -36017,7 +36549,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -36027,7 +36559,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -36037,7 +36569,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -36047,7 +36579,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -36057,7 +36589,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -36067,7 +36599,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -36077,7 +36609,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -36087,7 +36619,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -36097,7 +36629,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -36107,7 +36639,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -36117,7 +36649,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -36127,7 +36659,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -36137,7 +36669,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -36147,7 +36679,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -36157,7 +36689,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -36167,7 +36699,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -36177,7 +36709,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -36187,7 +36719,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -36197,7 +36729,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -36207,7 +36739,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -36217,7 +36749,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -36227,7 +36759,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -36237,7 +36769,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -36247,7 +36779,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -36257,7 +36789,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -36267,7 +36799,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -36277,7 +36809,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -36287,7 +36819,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -36297,7 +36829,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -36307,7 +36839,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -36317,7 +36849,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -36327,7 +36859,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -36337,7 +36869,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -36347,7 +36879,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -36357,7 +36889,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -36367,7 +36899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -36377,7 +36909,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -36387,7 +36919,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -36397,7 +36929,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -36407,7 +36939,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -36417,7 +36949,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -36427,7 +36959,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -36437,7 +36969,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -36447,7 +36979,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -36457,7 +36989,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -36467,7 +36999,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -36477,7 +37009,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -36487,7 +37019,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -36497,7 +37029,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -36507,7 +37039,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -36517,7 +37049,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -36527,7 +37059,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -36537,7 +37069,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -36547,7 +37079,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -36557,7 +37089,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -36567,7 +37099,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -36577,7 +37109,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -36587,7 +37119,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -36597,7 +37129,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -36607,7 +37139,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -36617,7 +37149,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -36627,7 +37159,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -36637,7 +37169,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -36647,7 +37179,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -36657,7 +37189,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -36667,7 +37199,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -36677,7 +37209,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -36687,10 +37219,60 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>Forklift &amp; plant operator training</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>Forklift training</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Language school</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Engineering &amp; manufacturing recruitment</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Business &amp; sales coaching</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Engineering &amp; energy recruitment</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$411</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T407"/>
+  <dimension ref="A1:T411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35684,8 +35684,380 @@
       </c>
       <c r="T407" s="4" t="inlineStr"/>
     </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>TRIA Recruitment</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>Tech recruitment agency</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="inlineStr">
+        <is>
+          <t>Colston Tower, Bristol</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>https://www.triarecruitment.com</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>info@triarecruitment.com</t>
+        </is>
+      </c>
+      <c r="F408" s="3" t="inlineStr">
+        <is>
+          <t>0117 332 7000</t>
+        </is>
+      </c>
+      <c r="G408" s="3" t="inlineStr">
+        <is>
+          <t>Harriet Kirkpatrick, Lara Webb &amp; David Kirkpatrick (Co-founders, est. 2015)</t>
+        </is>
+      </c>
+      <c r="H408" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/tria-recruitment</t>
+        </is>
+      </c>
+      <c r="I408" s="3" t="inlineStr"/>
+      <c r="J408" s="3" t="inlineStr">
+        <is>
+          <t>Majority women-owned independent tech recruiter; placement fees on developer/engineering roles run into thousands per hire</t>
+        </is>
+      </c>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L408" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M408" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N408" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O408" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; established multi-founder brand</t>
+        </is>
+      </c>
+      <c r="P408" s="3" t="inlineStr">
+        <is>
+          <t>Peaple Talent/ISL Talent/Xist4 all compete for the same Bristol tech-recruitment searches</t>
+        </is>
+      </c>
+      <c r="Q408" s="3" t="inlineStr">
+        <is>
+          <t>'Majority women-owned, independent tech recruiter - own that distinct AEO positioning in Bristol'</t>
+        </is>
+      </c>
+      <c r="R408" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S408" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T408" s="3" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>Xist4</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>Data/tech/AI recruitment agency</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>Bristol &amp; London</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xist4.com</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F409" s="3" t="inlineStr"/>
+      <c r="G409" s="3" t="inlineStr">
+        <is>
+          <t>26 years combined sector experience</t>
+        </is>
+      </c>
+      <c r="H409" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/xist4-it-recruitment</t>
+        </is>
+      </c>
+      <c r="I409" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/XIST4</t>
+        </is>
+      </c>
+      <c r="J409" s="3" t="inlineStr">
+        <is>
+          <t>Specialist data/cyber/AI recruiter across 2 major cities; placement fees on senior tech/leadership roles are substantial</t>
+        </is>
+      </c>
+      <c r="K409" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L409" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M409" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N409" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O409" s="3" t="inlineStr">
+        <is>
+          <t>Sector-specific landing pages (fintech, startups, cyber) = active SEO</t>
+        </is>
+      </c>
+      <c r="P409" s="3" t="inlineStr">
+        <is>
+          <t>Sector pages exist but AI-answer citations for specific niche tech-recruitment queries still open</t>
+        </is>
+      </c>
+      <c r="Q409" s="3" t="inlineStr">
+        <is>
+          <t>'You built pages for fintech, cyber and AI recruitment - let's make AI cite them'</t>
+        </is>
+      </c>
+      <c r="R409" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S409" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T409" s="3" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Ray Cochrane Beauty Aesthetics Academy</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Beauty/aesthetics training academy</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>Baker Street, London W1</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.raycochrane.co.uk</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>admission@raycochrane.co.uk</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>020 7486 6291</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>Founded 1954 by Mrs Ray Cochrane; longest-established CIDESCO school in the UK</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/raycochranebeautyaestheticsacademy</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/raycochraneacademy</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>71-year heritage academy training beauty therapists who go on to open their own high-value clinics; course fees run into thousands per student</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>CIDESCO prestige accreditation promoted</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>71 years of heritage + prestigious accreditation not yet the AI-cited answer for 'beauty academy London'</t>
+        </is>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>'The UK's longest-established CIDESCO school - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional 71-year heritage story - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="inlineStr">
+        <is>
+          <t>Omni Academy of Hair, Beauty &amp; Aesthetics</t>
+        </is>
+      </c>
+      <c r="B411" s="4" t="inlineStr">
+        <is>
+          <t>Beauty/hair training academy</t>
+        </is>
+      </c>
+      <c r="C411" s="4" t="inlineStr">
+        <is>
+          <t>Walton-on-Thames, Surrey</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="inlineStr">
+        <is>
+          <t>https://www.omniacademy.co.uk</t>
+        </is>
+      </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F411" s="4" t="inlineStr"/>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>Carolyne Cross (Founder, est. 2008); Rianna (current lead, since 2022)</t>
+        </is>
+      </c>
+      <c r="H411" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/omniacademy1</t>
+        </is>
+      </c>
+      <c r="I411" s="4" t="inlineStr"/>
+      <c r="J411" s="4" t="inlineStr">
+        <is>
+          <t>17-year independent academy in wealthy Surrey; students pay course fees for hair/beauty/aesthetics/massage qualifications</t>
+        </is>
+      </c>
+      <c r="K411" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L411" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M411" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N411" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O411" s="4" t="inlineStr">
+        <is>
+          <t>Instagram presence</t>
+        </is>
+      </c>
+      <c r="P411" s="4" t="inlineStr">
+        <is>
+          <t>Local Surrey students search generically for 'beauty course near me' - academy not yet the AI-cited local answer</t>
+        </is>
+      </c>
+      <c r="Q411" s="4" t="inlineStr">
+        <is>
+          <t>Own 'beauty training course Surrey' - a specific, winnable local AEO target</t>
+        </is>
+      </c>
+      <c r="R411" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S411" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="T411" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T407"/>
+  <autoFilter ref="A1:T411"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35696,7 +36068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -35716,7 +36088,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5">
@@ -37273,6 +37645,46 @@
         </is>
       </c>
       <c r="B160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Tech recruitment agency</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Data/tech/AI recruitment agency</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Beauty/aesthetics training academy</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Beauty/hair training academy</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$414</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T411"/>
+  <dimension ref="A1:T414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -36056,8 +36056,276 @@
       </c>
       <c r="T411" s="4" t="inlineStr"/>
     </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Interface Aesthetics</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Medical aesthetics/injectable training academy</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>Westminster Bridge Road, London SE1</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interfaceaesthetics.co.uk</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>contact@interfaceaesthetics.co.uk</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>07944 543113</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Dr James Olding (Founder/Lead Trainer; Senior Specialist Registrar in Oral &amp; Maxillofacial Surgery, GetHarley Medical Aesthetic Practitioner of the Year 2025)</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr"/>
+      <c r="I412" s="2" t="inlineStr"/>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning consultant-led injectables training academy for medical professionals; course fees run into thousands per delegate, repeat cohorts</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>Award win (GetHarley 2025) = active PR/marketing investment</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning credentials not yet the AI-cited answer for 'medical aesthetics training London'</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>'2025 Practitioner of the Year - own that exact AEO trust signal in AI-search answers'</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>Strong credentialed-founder story, high-value course fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>Bristol School of Yoga</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>Yoga teacher training school</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>Backfields Lane, Bristol BS2</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bristolschoolofyoga.co.uk</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F413" s="4" t="inlineStr"/>
+      <c r="G413" s="4" t="inlineStr">
+        <is>
+          <t>Laura Gilmore (Founder/Director)</t>
+        </is>
+      </c>
+      <c r="H413" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/lauragilmoreyoga</t>
+        </is>
+      </c>
+      <c r="I413" s="4" t="inlineStr"/>
+      <c r="J413" s="4" t="inlineStr">
+        <is>
+          <t>Independent 200hr/300hr yoga teacher-training provider; trainee fees run into thousands per cohort, repeat intakes</t>
+        </is>
+      </c>
+      <c r="K413" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L413" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M413" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N413" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O413" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P413" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'yoga teacher training Bristol' searches not yet AI-answer dominated by this school</t>
+        </is>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>'Own the AI-cited answer for yoga teacher training in Bristol - not just another studio timetable'</t>
+        </is>
+      </c>
+      <c r="R413" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S413" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T413" s="4" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>Creative Crowd</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>Creative &amp; marketing recruitment agency</t>
+        </is>
+      </c>
+      <c r="C414" s="3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>https://www.creativecrowd.london</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F414" s="3" t="inlineStr"/>
+      <c r="G414" s="3" t="inlineStr">
+        <is>
+          <t>Surfraz Alam &amp; Daniel Levy (Co-founders)</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/creative-crowd-recruitment</t>
+        </is>
+      </c>
+      <c r="I414" s="3" t="inlineStr"/>
+      <c r="J414" s="3" t="inlineStr">
+        <is>
+          <t>Independent specialist recruiter placing creative/marketing/digital talent into agencies and brands; placement fees on mid-senior creative roles are substantial</t>
+        </is>
+      </c>
+      <c r="K414" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L414" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M414" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N414" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O414" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated department landing pages = active SEO investment</t>
+        </is>
+      </c>
+      <c r="P414" s="3" t="inlineStr">
+        <is>
+          <t>Crowded London creative-recruitment market with many similarly-positioned boutiques</t>
+        </is>
+      </c>
+      <c r="Q414" s="3" t="inlineStr">
+        <is>
+          <t>'You built pages for every creative discipline - let's make AI cite them, not just index them'</t>
+        </is>
+      </c>
+      <c r="R414" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S414" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T414" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T411"/>
+  <autoFilter ref="A1:T414"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36068,7 +36336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B164"/>
+  <dimension ref="A1:B167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -36088,7 +36356,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
@@ -37685,6 +37953,36 @@
         </is>
       </c>
       <c r="B164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Medical aesthetics/injectable training academy</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Yoga teacher training school</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Creative &amp; marketing recruitment agency</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$431</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T414"/>
+  <dimension ref="A1:T431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -36324,8 +36324,1588 @@
       </c>
       <c r="T414" s="3" t="inlineStr"/>
     </row>
+    <row r="415">
+      <c r="A415" s="3" t="inlineStr">
+        <is>
+          <t>Blake Architects</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>Architecture practice</t>
+        </is>
+      </c>
+      <c r="C415" s="3" t="inlineStr">
+        <is>
+          <t>Winstone, Cirencester, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>https://www.blakearchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F415" s="3" t="inlineStr">
+        <is>
+          <t>01285 841407</t>
+        </is>
+      </c>
+      <c r="G415" s="3" t="inlineStr">
+        <is>
+          <t>Jonathan Nettleton (Founder, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H415" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/blake-architects-limited</t>
+        </is>
+      </c>
+      <c r="I415" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/blakearchitects; facebook.com/BlakeArchitectsLimited</t>
+        </is>
+      </c>
+      <c r="J415" s="3" t="inlineStr">
+        <is>
+          <t>RIBA Chartered practice specialising in barn conversions to listed manors; single-site independent studio in a converted Cotswold barn, project fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K415" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L415" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M415" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N415" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O415" s="3" t="inlineStr">
+        <is>
+          <t>Instagram (3.9k followers) + Green Register membership = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P415" s="3" t="inlineStr">
+        <is>
+          <t>Niche listed-building/barn-conversion expertise not yet the AI-cited answer for Cotswolds architects</t>
+        </is>
+      </c>
+      <c r="Q415" s="3" t="inlineStr">
+        <is>
+          <t>'RIBA-chartered barn-conversion specialists - own that exact AEO niche in the Cotswolds'</t>
+        </is>
+      </c>
+      <c r="R415" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S415" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T415" s="3" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>Studio Bellord (Camilla Bellord Interiors)</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>Interior design studio</t>
+        </is>
+      </c>
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t>Great Rissington, nr Bourton-on-the-Water, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>https://www.studiobellord.com</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F416" s="3" t="inlineStr">
+        <is>
+          <t>07584 044052</t>
+        </is>
+      </c>
+      <c r="G416" s="3" t="inlineStr">
+        <is>
+          <t>Camilla Bellord &amp; Tom Bellord (Husband-and-wife owners)</t>
+        </is>
+      </c>
+      <c r="H416" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/camilla-bellord-b40b9563</t>
+        </is>
+      </c>
+      <c r="I416" s="3" t="inlineStr"/>
+      <c r="J416" s="3" t="inlineStr">
+        <is>
+          <t>Bespoke private residential interior design across the Cotswolds; KLC-trained founder with 20+ years experience, project fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K416" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L416" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M416" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N416" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O416" s="3" t="inlineStr">
+        <is>
+          <t>Featured on Houzz and industry blogs = active PR/marketing</t>
+        </is>
+      </c>
+      <c r="P416" s="3" t="inlineStr">
+        <is>
+          <t>Houzz features not yet converted into AI-cited answers for 'interior designer Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q416" s="3" t="inlineStr">
+        <is>
+          <t>'Featured on Houzz - let's make AI cite you the same way for search'</t>
+        </is>
+      </c>
+      <c r="R416" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S416" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T416" s="3" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="3" t="inlineStr">
+        <is>
+          <t>Studio Hudson Architects</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="inlineStr">
+        <is>
+          <t>Architecture practice</t>
+        </is>
+      </c>
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t>Royal Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>https://www.studio-hudson.co.uk</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F417" s="3" t="inlineStr"/>
+      <c r="G417" s="3" t="inlineStr">
+        <is>
+          <t>Ian Hudson (Founder/Principal Architect, est. 2012)</t>
+        </is>
+      </c>
+      <c r="H417" s="3" t="inlineStr"/>
+      <c r="I417" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/studiohudson1</t>
+        </is>
+      </c>
+      <c r="J417" s="3" t="inlineStr">
+        <is>
+          <t>RIBA Chartered residential practice covering Sevenoaks/Tonbridge/Maidstone; award-winning one-founder studio, project fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K417" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L417" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M417" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N417" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O417" s="3" t="inlineStr">
+        <is>
+          <t>Two industry awards (2017, 2021) = active reputation-building</t>
+        </is>
+      </c>
+      <c r="P417" s="3" t="inlineStr">
+        <is>
+          <t>Award wins not yet the AI-cited trust signal for 'architect Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q417" s="3" t="inlineStr">
+        <is>
+          <t>'Award-winning since 2017 - own that AEO trust signal against bigger multi-office practices'</t>
+        </is>
+      </c>
+      <c r="R417" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S417" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T417" s="3" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="inlineStr">
+        <is>
+          <t>Barkerdesign</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>Interior design studio</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>https://www.barker-design.com</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F418" s="3" t="inlineStr">
+        <is>
+          <t>07788 581928</t>
+        </is>
+      </c>
+      <c r="G418" s="3" t="inlineStr">
+        <is>
+          <t>Justine Hodgson-Barker (Founder, BIID-accredited)</t>
+        </is>
+      </c>
+      <c r="H418" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/justine-hodgson-barker-8626a4107</t>
+        </is>
+      </c>
+      <c r="I418" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/barker_design</t>
+        </is>
+      </c>
+      <c r="J418" s="3" t="inlineStr">
+        <is>
+          <t>High-end interior design for period/character homes across Kent and East Sussex; BIID accreditation and House &amp; Garden Directory membership signal premium positioning, project fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K418" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L418" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M418" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N418" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O418" s="3" t="inlineStr">
+        <is>
+          <t>House &amp; Garden Directory + press features (Great British Life, Priceless) = active PR</t>
+        </is>
+      </c>
+      <c r="P418" s="3" t="inlineStr">
+        <is>
+          <t>Press features not yet the AI-cited answer for 'interior designer Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q418" s="3" t="inlineStr">
+        <is>
+          <t>'House &amp; Garden Directory listed - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R418" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S418" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T418" s="3" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt Glass Chartered Architects</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>Architecture practice</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wyattglass.co.uk</t>
+        </is>
+      </c>
+      <c r="E419" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F419" s="3" t="inlineStr">
+        <is>
+          <t>01732 746600</t>
+        </is>
+      </c>
+      <c r="G419" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt Glass (Founder, est. 1992)</t>
+        </is>
+      </c>
+      <c r="H419" s="3" t="inlineStr"/>
+      <c r="I419" s="3" t="inlineStr"/>
+      <c r="J419" s="3" t="inlineStr">
+        <is>
+          <t>33-year RIBA Chartered practice for extensions, conversions, new builds and listed buildings; one of the longest-running independents in the area, project fees run into tens of thousands</t>
+        </is>
+      </c>
+      <c r="K419" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L419" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M419" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N419" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O419" s="3" t="inlineStr">
+        <is>
+          <t>33-year trading history = established local reputation</t>
+        </is>
+      </c>
+      <c r="P419" s="3" t="inlineStr">
+        <is>
+          <t>Long heritage not yet leveraged as an AEO trust signal against newer competitors</t>
+        </is>
+      </c>
+      <c r="Q419" s="3" t="inlineStr">
+        <is>
+          <t>'33 years designing Sevenoaks homes - own that AEO trust signal in AI-search answers'</t>
+        </is>
+      </c>
+      <c r="R419" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S419" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T419" s="3" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="4" t="inlineStr">
+        <is>
+          <t>Catherine Westoby Interior Design</t>
+        </is>
+      </c>
+      <c r="B420" s="4" t="inlineStr">
+        <is>
+          <t>Interior design studio</t>
+        </is>
+      </c>
+      <c r="C420" s="4" t="inlineStr">
+        <is>
+          <t>Tonbridge, Kent</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>https://www.catherinewestobyinteriordesign.co.uk</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>catherinewestoby.interiordesign@gmail.com</t>
+        </is>
+      </c>
+      <c r="F420" s="4" t="inlineStr"/>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>Catherine Westoby (Founder)</t>
+        </is>
+      </c>
+      <c r="H420" s="4" t="inlineStr"/>
+      <c r="I420" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/catherinewestobyinteriordesign</t>
+        </is>
+      </c>
+      <c r="J420" s="4" t="inlineStr">
+        <is>
+          <t>Solo-practitioner residential interior designer across Sevenoaks/Tunbridge Wells/Tonbridge; Houzz-listed, project fees run into thousands per client</t>
+        </is>
+      </c>
+      <c r="K420" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L420" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M420" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N420" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O420" s="4" t="inlineStr">
+        <is>
+          <t>Houzz listing</t>
+        </is>
+      </c>
+      <c r="P420" s="4" t="inlineStr">
+        <is>
+          <t>Solo practitioner needs to compete with larger studios for AI-search visibility</t>
+        </is>
+      </c>
+      <c r="Q420" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific Kent-market AEO niche (e.g. period-home interiors) vs bigger studios</t>
+        </is>
+      </c>
+      <c r="R420" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S420" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T420" s="4" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="inlineStr">
+        <is>
+          <t>Montpellier Medical</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>Private GP practice</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>Montpellier Parade, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>https://www.montpelliermedical.co.uk</t>
+        </is>
+      </c>
+      <c r="E421" s="3" t="inlineStr">
+        <is>
+          <t>admin@montpelliermedical.co.uk</t>
+        </is>
+      </c>
+      <c r="F421" s="3" t="inlineStr">
+        <is>
+          <t>01242 379 138</t>
+        </is>
+      </c>
+      <c r="G421" s="3" t="inlineStr">
+        <is>
+          <t>Dr Laura O'Loghlen &amp; Dr Justin Forbes (Co-founders, opened 2025)</t>
+        </is>
+      </c>
+      <c r="H421" s="3" t="inlineStr"/>
+      <c r="I421" s="3" t="inlineStr"/>
+      <c r="J421" s="3" t="inlineStr">
+        <is>
+          <t>New two-doctor private GP practice offering 30-min appointments/health checks/blood tests; private consultation fees run into hundreds per visit, repeat annual health-check clients</t>
+        </is>
+      </c>
+      <c r="K421" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L421" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M421" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N421" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O421" s="3" t="inlineStr">
+        <is>
+          <t>None visible - newly opened 2025</t>
+        </is>
+      </c>
+      <c r="P421" s="3" t="inlineStr">
+        <is>
+          <t>Brand-new practice with no AI-search presence yet - ground-floor opportunity</t>
+        </is>
+      </c>
+      <c r="Q421" s="3" t="inlineStr">
+        <is>
+          <t>'You're brand new in Cheltenham - be the AI-cited answer before competitors are'</t>
+        </is>
+      </c>
+      <c r="R421" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S421" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T421" s="3" t="inlineStr">
+        <is>
+          <t>Opened March 2025, CQC-registered - very new, high AEO upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="inlineStr">
+        <is>
+          <t>Cotswold Private GP Service</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>Private GP practice</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>Hatherley Lane, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cotswoldprivategp.co.uk</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F422" s="3" t="inlineStr">
+        <is>
+          <t>01242 700350</t>
+        </is>
+      </c>
+      <c r="G422" s="3" t="inlineStr">
+        <is>
+          <t>Dr Hosur, Dr Meenakshi Raina, Dr Junemani (Clinical team, 20+ yrs NHS experience each)</t>
+        </is>
+      </c>
+      <c r="H422" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/cotswold-private-gp</t>
+        </is>
+      </c>
+      <c r="I422" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/cotswoldprivategp; facebook.com/p/Cotswold-Private-GP-Service</t>
+        </is>
+      </c>
+      <c r="J422" s="3" t="inlineStr">
+        <is>
+          <t>Same-day private GP consultations across Cheltenham/Cotswolds; private consultation fees run into hundreds per visit with repeat patients</t>
+        </is>
+      </c>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L422" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M422" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N422" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O422" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook/LinkedIn presence = active marketing</t>
+        </is>
+      </c>
+      <c r="P422" s="3" t="inlineStr">
+        <is>
+          <t>Multi-channel social presence not yet converted into AI-cited answers for 'private GP Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q422" s="3" t="inlineStr">
+        <is>
+          <t>'You're already posting on 3 platforms - let's make AI cite you too'</t>
+        </is>
+      </c>
+      <c r="R422" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S422" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T422" s="3" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Ruth Jackson Aesthetics</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (non-surgical)</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>St George's Road, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ruthjacksonaesthetics.co.uk</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>07804 432426</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Ruth Jackson (Founder, nurse prescriber)</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr"/>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Ruth-Jackson-Aesthetics-100093995566592</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning nurse-led non-surgical aesthetics clinic (fillers, HIFU, facials) plus mobile service; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr">
+        <is>
+          <t>2025 National Winner, Best Aesthetics Business in England award</t>
+        </is>
+      </c>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>National award win not yet the AI-cited trust signal for 'aesthetics clinic Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>'National award winner 2025 - own that exact AEO trust signal in AI-search answers'</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S423" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T423" s="2" t="inlineStr">
+        <is>
+          <t>National award win = strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="inlineStr">
+        <is>
+          <t>Oxona Healthcare</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>Private dermatology &amp; women's health clinics</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="inlineStr">
+        <is>
+          <t>Headington, Oxford (+ Chipping Norton, Didcot, Henley, St Albans)</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oxonahealth.co.uk</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="inlineStr">
+        <is>
+          <t>reception@oxonahealth.co.uk</t>
+        </is>
+      </c>
+      <c r="F424" s="3" t="inlineStr">
+        <is>
+          <t>01865 965 027</t>
+        </is>
+      </c>
+      <c r="G424" s="3" t="inlineStr">
+        <is>
+          <t>Megan (Co-founder, Business Development)</t>
+        </is>
+      </c>
+      <c r="H424" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/oxonahealthcare</t>
+        </is>
+      </c>
+      <c r="I424" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/oxona_health; facebook.com/Oxonahealthcare</t>
+        </is>
+      </c>
+      <c r="J424" s="3" t="inlineStr">
+        <is>
+          <t>Independent multi-site dermatology/women's health group across 5 Home Counties towns; consultant-led private appointments run into hundreds per visit, repeat patients</t>
+        </is>
+      </c>
+      <c r="K424" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L424" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M424" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N424" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O424" s="3" t="inlineStr">
+        <is>
+          <t>Multi-channel social presence + multi-site expansion = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P424" s="3" t="inlineStr">
+        <is>
+          <t>5-site footprint not matched by 5-location AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q424" s="3" t="inlineStr">
+        <is>
+          <t>Per-location AEO content to own each town's 'private dermatologist near me' AI answer separately</t>
+        </is>
+      </c>
+      <c r="R424" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S424" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T424" s="3" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>My Dermatologist (Dr Jonathan Bowling)</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>Private dermatology practice</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>Headington, Oxford</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mydermatologist.co.uk</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>info@mydermatologist.co.uk</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>01865 861577</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Dr Jonathan Bowling (Consultant Dermatologist, FRCP, ex-Oxford Univ. Hospitals lecturer)</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr"/>
+      <c r="I425" s="2" t="inlineStr"/>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consultant skin cancer/mole screening practice; author of an award-winning dermoscopy textbook, trained 4,000+ clinicians - premium per-consultation fees</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr">
+        <is>
+          <t>Published award-winning textbook = strong authority/credibility asset</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional published-authority credential not yet the AI-cited answer for 'private dermatologist Oxford'</t>
+        </is>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>'You wrote the textbook other dermatologists train from - own that AEO authority signal'</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S425" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T425" s="2" t="inlineStr">
+        <is>
+          <t>Textbook author + 4,000 clinicians trained - exceptional authority story</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="4" t="inlineStr">
+        <is>
+          <t>Town House Face &amp; Body Clinic</t>
+        </is>
+      </c>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (non-surgical)</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="inlineStr">
+        <is>
+          <t>Albany Road, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>https://www.townhousefaceandbodyclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>enquiries@townhousefaceandbodyclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>01242 303785</t>
+        </is>
+      </c>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>Eliza (Founder, 30+ yrs NHS nursing background, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H426" s="4" t="inlineStr"/>
+      <c r="I426" s="4" t="inlineStr"/>
+      <c r="J426" s="4" t="inlineStr">
+        <is>
+          <t>14-year independent non-surgical aesthetics clinic with natural-results focus; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K426" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L426" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M426" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N426" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O426" s="4" t="inlineStr">
+        <is>
+          <t>14-year trading history</t>
+        </is>
+      </c>
+      <c r="P426" s="4" t="inlineStr">
+        <is>
+          <t>Long heritage not yet leveraged as an AEO trust signal against newer Cheltenham aesthetics clinics</t>
+        </is>
+      </c>
+      <c r="Q426" s="4" t="inlineStr">
+        <is>
+          <t>'14 years of natural-results aesthetics in Cheltenham - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R426" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S426" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T426" s="4" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Charles Lear &amp; Co</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>The Promenade, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.charleslear.co.uk</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>01242 222722</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Tom Hatcher (Director/Owner); founded 1992 by Charles Lear, trading roots to 1947</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/tom-hatcher-b045aa30</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/CharlesLearCo; instagram.com/charleslearco</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>Cheltenham's longest-established estate agent (roots to 1947), International Property Award winner; sales commissions on premium property are substantial</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence; International Property Award win</t>
+        </is>
+      </c>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning heritage brand not yet the AI-cited answer for 'estate agent Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>'International Property Award winner, trading since 1947 - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S427" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="inlineStr">
+        <is>
+          <t>Strong heritage + award story, high-value AEO target</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="3" t="inlineStr">
+        <is>
+          <t>Osborne Heath</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>Sunninghill, Ascot &amp; Windsor</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>https://www.osborneheath.co.uk</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F428" s="3" t="inlineStr">
+        <is>
+          <t>01344 627777</t>
+        </is>
+      </c>
+      <c r="G428" s="3" t="inlineStr">
+        <is>
+          <t>James Niknejad (Founding Director, est. 2016)</t>
+        </is>
+      </c>
+      <c r="H428" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/james-niknejad-mnaea-038109117</t>
+        </is>
+      </c>
+      <c r="I428" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/osborneheathltd; instagram.com/osborneheath</t>
+        </is>
+      </c>
+      <c r="J428" s="3" t="inlineStr">
+        <is>
+          <t>Multi-award-winning independent luxury-homes agent in Ascot/Windsor; commissions on high-value property sales are substantial</t>
+        </is>
+      </c>
+      <c r="K428" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L428" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M428" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N428" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O428" s="3" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence; multiple industry awards</t>
+        </is>
+      </c>
+      <c r="P428" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning credentials not yet the AI-cited answer for 'estate agent Ascot'</t>
+        </is>
+      </c>
+      <c r="Q428" s="3" t="inlineStr">
+        <is>
+          <t>'Multi-award-winning luxury agent - own that AEO trust signal in Ascot/Windsor'</t>
+        </is>
+      </c>
+      <c r="R428" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S428" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T428" s="3" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="inlineStr">
+        <is>
+          <t>Duncan Yeardley</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; lettings agent</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="inlineStr">
+        <is>
+          <t>Sunninghill, Ascot (Ascot/Bracknell)</t>
+        </is>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>https://www.duncanyeardley.co.uk</t>
+        </is>
+      </c>
+      <c r="E429" s="3" t="inlineStr">
+        <is>
+          <t>nick@duncanyeardley.co.uk</t>
+        </is>
+      </c>
+      <c r="F429" s="3" t="inlineStr">
+        <is>
+          <t>01344 874300</t>
+        </is>
+      </c>
+      <c r="G429" s="3" t="inlineStr">
+        <is>
+          <t>Nick Thring (Owner, took over 2012; family affair with sister Helen &amp; wife Charlotte)</t>
+        </is>
+      </c>
+      <c r="H429" s="3" t="inlineStr"/>
+      <c r="I429" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/duncan.yeardley.estate.agent</t>
+        </is>
+      </c>
+      <c r="J429" s="3" t="inlineStr">
+        <is>
+          <t>38-year family-run estate agent trading since 1987 in Ascot/Bracknell; commissions on premium property sales recur</t>
+        </is>
+      </c>
+      <c r="K429" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L429" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M429" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N429" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O429" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; long family-run history</t>
+        </is>
+      </c>
+      <c r="P429" s="3" t="inlineStr">
+        <is>
+          <t>'Real family affair' story not yet leveraged as an AEO trust signal</t>
+        </is>
+      </c>
+      <c r="Q429" s="3" t="inlineStr">
+        <is>
+          <t>'A real family affair since 1987 - own that AEO trust signal against corporate agents'</t>
+        </is>
+      </c>
+      <c r="R429" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S429" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T429" s="3" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="4" t="inlineStr">
+        <is>
+          <t>The Bristol Driving School</t>
+        </is>
+      </c>
+      <c r="B430" s="4" t="inlineStr">
+        <is>
+          <t>Driving school &amp; ADI instructor training</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>Coombe Dingle, Bristol</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thebristoldrivingschool.com</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>0117 968 3344</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>Long-established, ORDIT founder member</t>
+        </is>
+      </c>
+      <c r="H430" s="4" t="inlineStr"/>
+      <c r="I430" s="4" t="inlineStr"/>
+      <c r="J430" s="4" t="inlineStr">
+        <is>
+          <t>~30-year Bristol driving school with a dedicated ADI (instructor) training arm; ORDIT/MSA-accredited, trainee-instructor course fees run into thousands per cohort</t>
+        </is>
+      </c>
+      <c r="K430" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L430" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M430" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N430" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O430" s="4" t="inlineStr">
+        <is>
+          <t>ORDIT founder-member status = established industry credibility</t>
+        </is>
+      </c>
+      <c r="P430" s="4" t="inlineStr">
+        <is>
+          <t>30-year heritage and ORDIT pedigree not yet the AI-cited answer for 'become a driving instructor Bristol'</t>
+        </is>
+      </c>
+      <c r="Q430" s="4" t="inlineStr">
+        <is>
+          <t>'A founder member of ORDIT - own that exact AEO trust signal for ADI training in Bristol'</t>
+        </is>
+      </c>
+      <c r="R430" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S430" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T430" s="4" t="inlineStr">
+        <is>
+          <t>Founder name unconfirmed via public search - verify before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="inlineStr">
+        <is>
+          <t>Sapphire Driving Academy</t>
+        </is>
+      </c>
+      <c r="B431" s="4" t="inlineStr">
+        <is>
+          <t>Driving school &amp; ADI instructor training</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="inlineStr">
+        <is>
+          <t>Harlington, Hayes, West London</t>
+        </is>
+      </c>
+      <c r="D431" s="4" t="inlineStr">
+        <is>
+          <t>https://sapphiredrivingacademy.co.uk</t>
+        </is>
+      </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>sapphiredrivingacademy@gmail.com</t>
+        </is>
+      </c>
+      <c r="F431" s="4" t="inlineStr">
+        <is>
+          <t>07596 786786</t>
+        </is>
+      </c>
+      <c r="G431" s="4" t="inlineStr">
+        <is>
+          <t>Nadia (Founder/Lead Trainer, ex-DVSA driving examiner)</t>
+        </is>
+      </c>
+      <c r="H431" s="4" t="inlineStr"/>
+      <c r="I431" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Sapphire-Driving-Academy-100089952324304; instagram.com/sapphiredrivingacademy_</t>
+        </is>
+      </c>
+      <c r="J431" s="4" t="inlineStr">
+        <is>
+          <t>West London driving school with an ADI instructor-training arm led by an ex-DVSA examiner; ~100 instructors qualified to date, trainee course fees run into thousands per cohort</t>
+        </is>
+      </c>
+      <c r="K431" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L431" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M431" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N431" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O431" s="4" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence</t>
+        </is>
+      </c>
+      <c r="P431" s="4" t="inlineStr">
+        <is>
+          <t>Ex-DVSA-examiner credential not yet the AI-cited trust signal for 'ADI training West London'</t>
+        </is>
+      </c>
+      <c r="Q431" s="4" t="inlineStr">
+        <is>
+          <t>'Trained by an ex-DVSA examiner - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R431" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S431" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T431" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T414"/>
+  <autoFilter ref="A1:T431"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36336,7 +37916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B167"/>
+  <dimension ref="A1:B174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -36356,7 +37936,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5">
@@ -36373,7 +37953,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -36519,17 +38099,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -36539,7 +38119,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -36549,7 +38129,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -36559,7 +38139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -36569,7 +38149,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -36579,7 +38159,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -36589,7 +38169,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -36599,7 +38179,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -36609,7 +38189,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -36619,7 +38199,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -36629,7 +38209,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kitchen &amp; bathroom design</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -36639,27 +38219,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Kitchen &amp; bathroom design</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Architecture practice</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -36669,7 +38249,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -36679,7 +38259,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -36689,7 +38269,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -36699,7 +38279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -36709,7 +38289,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -36719,7 +38299,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -36729,7 +38309,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -36739,7 +38319,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -36749,7 +38329,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -36759,7 +38339,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -36769,7 +38349,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -36779,7 +38359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -36789,7 +38369,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -36799,7 +38379,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -36809,7 +38389,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -36819,7 +38399,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -36829,7 +38409,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -36839,57 +38419,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -36899,7 +38479,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -36909,7 +38489,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -36919,7 +38499,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -36929,7 +38509,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -36939,7 +38519,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -36949,7 +38529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -36959,7 +38539,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -36969,7 +38549,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -36979,7 +38559,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -36989,7 +38569,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -36999,7 +38579,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -37009,7 +38589,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -37019,7 +38599,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -37029,7 +38609,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -37039,7 +38619,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -37049,7 +38629,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -37059,7 +38639,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -37069,7 +38649,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -37079,7 +38659,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -37089,7 +38669,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -37099,7 +38679,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -37109,7 +38689,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -37119,7 +38699,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -37129,7 +38709,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -37139,7 +38719,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -37149,7 +38729,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -37159,7 +38739,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -37169,7 +38749,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -37179,7 +38759,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -37189,7 +38769,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -37199,7 +38779,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -37209,7 +38789,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -37219,7 +38799,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -37229,7 +38809,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -37239,7 +38819,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -37249,7 +38829,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -37259,7 +38839,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -37269,7 +38849,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -37279,7 +38859,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -37289,7 +38869,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -37299,7 +38879,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -37309,7 +38889,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -37319,7 +38899,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -37329,7 +38909,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -37339,7 +38919,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -37349,7 +38929,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -37359,7 +38939,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -37369,7 +38949,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -37379,7 +38959,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -37389,7 +38969,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -37399,7 +38979,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -37409,7 +38989,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -37419,7 +38999,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -37429,7 +39009,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -37439,7 +39019,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -37449,7 +39029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -37459,7 +39039,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -37469,7 +39049,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -37479,7 +39059,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -37489,7 +39069,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -37499,7 +39079,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -37509,7 +39089,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -37519,7 +39099,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -37529,7 +39109,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -37539,7 +39119,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -37549,7 +39129,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -37559,7 +39139,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -37569,7 +39149,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -37579,7 +39159,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -37589,7 +39169,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -37599,7 +39179,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -37609,7 +39189,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -37619,7 +39199,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -37629,7 +39209,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -37639,7 +39219,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -37649,7 +39229,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -37659,7 +39239,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -37669,7 +39249,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -37679,7 +39259,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -37689,7 +39269,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -37699,7 +39279,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -37709,7 +39289,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -37719,7 +39299,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -37729,7 +39309,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -37739,7 +39319,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -37749,7 +39329,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -37759,7 +39339,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -37769,7 +39349,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -37779,7 +39359,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -37789,7 +39369,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -37799,7 +39379,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -37809,7 +39389,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -37819,7 +39399,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -37829,7 +39409,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -37839,7 +39419,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -37849,7 +39429,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -37859,7 +39439,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -37869,7 +39449,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -37879,7 +39459,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -37889,7 +39469,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -37899,7 +39479,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -37909,7 +39489,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -37919,7 +39499,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -37929,7 +39509,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -37939,7 +39519,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -37949,7 +39529,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -37959,7 +39539,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -37969,7 +39549,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -37979,10 +39559,80 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>Beauty/aesthetics training academy</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Beauty/hair training academy</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Medical aesthetics/injectable training academy</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Yoga teacher training school</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Private dermatology &amp; women's health clinics</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Private dermatology practice</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Estate &amp; lettings agent</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$448</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T431"/>
+  <dimension ref="A1:T448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -37904,8 +37904,1600 @@
       </c>
       <c r="T431" s="4" t="inlineStr"/>
     </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>Jack's Barn</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (converted barn)</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>Aldington, Ashford, Kent</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jacksbarnkent.co.uk</t>
+        </is>
+      </c>
+      <c r="E432" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F432" s="3" t="inlineStr">
+        <is>
+          <t>07966 525067</t>
+        </is>
+      </c>
+      <c r="G432" s="3" t="inlineStr">
+        <is>
+          <t>Wanstall family (100+ years farming the land)</t>
+        </is>
+      </c>
+      <c r="H432" s="3" t="inlineStr"/>
+      <c r="I432" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/jacksbarnkent; facebook.com/jacksbarnkent</t>
+        </is>
+      </c>
+      <c r="J432" s="3" t="inlineStr">
+        <is>
+          <t>14th-century converted barn on a century-old family farm; wedding bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L432" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M432" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N432" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O432" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence = active marketing</t>
+        </is>
+      </c>
+      <c r="P432" s="3" t="inlineStr">
+        <is>
+          <t>Century-old family farm story not yet the AI-cited answer for 'barn wedding venue Kent'</t>
+        </is>
+      </c>
+      <c r="Q432" s="3" t="inlineStr">
+        <is>
+          <t>'A family farm for 100+ years, now Kent's most characterful barn wedding venue - own that AEO story'</t>
+        </is>
+      </c>
+      <c r="R432" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S432" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T432" s="3" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>The Harty Estate</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Sheppey, nr Faversham, Kent</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thehartyestate.co.uk</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Alex &amp; Victoria Burden (Third-generation family farm since 1960s)</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr"/>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/thehartyestate; facebook.com/thehartyestate</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>Award-winning waterside estuary wedding venue on a third-generation family farm; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K433" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr">
+        <is>
+          <t>2025 Kent Wedding Awards winner ('Wedding Venue of the Year') = active PR/marketing</t>
+        </is>
+      </c>
+      <c r="P433" s="2" t="inlineStr">
+        <is>
+          <t>Award win not yet the AI-cited trust signal for 'wedding venue Kent'</t>
+        </is>
+      </c>
+      <c r="Q433" s="2" t="inlineStr">
+        <is>
+          <t>'2025 Kent Wedding Venue of the Year - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S433" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T433" s="2" t="inlineStr">
+        <is>
+          <t>Recent award win = strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>Clock Barn</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (thatched barn on working farm)</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>Whitchurch, Hampshire</t>
+        </is>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>https://www.clockbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F434" s="3" t="inlineStr">
+        <is>
+          <t>01256 630199</t>
+        </is>
+      </c>
+      <c r="G434" s="3" t="inlineStr">
+        <is>
+          <t>Family-run since 1997</t>
+        </is>
+      </c>
+      <c r="H434" s="3" t="inlineStr"/>
+      <c r="I434" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/ClockBarn</t>
+        </is>
+      </c>
+      <c r="J434" s="3" t="inlineStr">
+        <is>
+          <t>19th-century thatched barn venue on a working farm, hosting weddings since 2004; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K434" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L434" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M434" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N434" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O434" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 20+ year trading history</t>
+        </is>
+      </c>
+      <c r="P434" s="3" t="inlineStr">
+        <is>
+          <t>20-year heritage not yet the AI-cited answer for 'barn wedding venue Hampshire'</t>
+        </is>
+      </c>
+      <c r="Q434" s="3" t="inlineStr">
+        <is>
+          <t>'Hosting weddings since 2004 in our iconic thatched barn - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R434" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S434" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T434" s="3" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="inlineStr">
+        <is>
+          <t>Hollands Farm Weddings &amp; Events</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (working farm)</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>Great Milton, Oxford</t>
+        </is>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollandsfarmevents.com</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="inlineStr">
+        <is>
+          <t>laura@hollandsfarmevents.com</t>
+        </is>
+      </c>
+      <c r="F435" s="3" t="inlineStr">
+        <is>
+          <t>07889 703791</t>
+        </is>
+      </c>
+      <c r="G435" s="3" t="inlineStr">
+        <is>
+          <t>Family-run (Laura, contact)</t>
+        </is>
+      </c>
+      <c r="H435" s="3" t="inlineStr"/>
+      <c r="I435" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/hollandsfarmevents</t>
+        </is>
+      </c>
+      <c r="J435" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned rural wedding venue on a 500-acre working farm near the M40; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L435" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M435" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N435" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O435" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence</t>
+        </is>
+      </c>
+      <c r="P435" s="3" t="inlineStr">
+        <is>
+          <t>Working-farm setting not yet the AI-cited answer for 'wedding venue Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="Q435" s="3" t="inlineStr">
+        <is>
+          <t>'A 500-acre working farm wedding venue - own that AEO story in Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="R435" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S435" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T435" s="3" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>Lains Barn</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (restored historic barn)</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>Ardington, Wantage, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lainsbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>events@lainsbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>01235 832745</t>
+        </is>
+      </c>
+      <c r="G436" s="3" t="inlineStr">
+        <is>
+          <t>Sherry family (Tom Sherry, Michelin-trained executive chef; 50+ yrs combined catering experience)</t>
+        </is>
+      </c>
+      <c r="H436" s="3" t="inlineStr"/>
+      <c r="I436" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/lainsbarn; facebook.com/lainsbarnoxfordshire</t>
+        </is>
+      </c>
+      <c r="J436" s="3" t="inlineStr">
+        <is>
+          <t>Award-winning restored barn venue with in-house Michelin-trained catering; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K436" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L436" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M436" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N436" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O436" s="3" t="inlineStr">
+        <is>
+          <t>Instagram (5.4k followers); Michelin-trained chef credential = strong PR asset</t>
+        </is>
+      </c>
+      <c r="P436" s="3" t="inlineStr">
+        <is>
+          <t>Michelin-trained chef story not yet the AI-cited answer for 'wedding venue Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="Q436" s="3" t="inlineStr">
+        <is>
+          <t>'Michelin-trained catering at an award-winning barn venue - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R436" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S436" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T436" s="3" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Partridge Muir &amp; Warren (PMW)</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>Chartered IFA / wealth management</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>Esher, Surrey</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pmw.co.uk</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>01372 471550</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Simon Lewis (CEO)</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/partridge-muir-&amp;-warren-ltd</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/pmwesher; instagram.com/pmwesher</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>Chartered financial planning firm trading since 1969 with generational family-client relationships; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L437" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N437" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O437" s="2" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence; Chartered status; 55+ year heritage</t>
+        </is>
+      </c>
+      <c r="P437" s="2" t="inlineStr">
+        <is>
+          <t>55-year heritage not yet the AI-cited answer for 'financial planner Esher'</t>
+        </is>
+      </c>
+      <c r="Q437" s="2" t="inlineStr">
+        <is>
+          <t>'Advising Esher families since 1969, now into the second generation - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S437" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T437" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional heritage (56 yrs) - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>Heritage Independent Mortgage Advisers</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>Independent mortgage broker</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>https://www.heritageima.com</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>info@heritageima.com</t>
+        </is>
+      </c>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>01483 531025</t>
+        </is>
+      </c>
+      <c r="G438" s="3" t="inlineStr">
+        <is>
+          <t>Paul Glover (Director)</t>
+        </is>
+      </c>
+      <c r="H438" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/heritage-independent-mortgage-advisers</t>
+        </is>
+      </c>
+      <c r="I438" s="3" t="inlineStr"/>
+      <c r="J438" s="3" t="inlineStr">
+        <is>
+          <t>Whole-of-market independent mortgage broker (residential/BTL/equity release/specialist lending) since 2000; commission per completed mortgage recurs with remortgage clients</t>
+        </is>
+      </c>
+      <c r="K438" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L438" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M438" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N438" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O438" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 25-year trading history</t>
+        </is>
+      </c>
+      <c r="P438" s="3" t="inlineStr">
+        <is>
+          <t>25-year heritage not yet the AI-cited answer for 'mortgage broker Guildford'</t>
+        </is>
+      </c>
+      <c r="Q438" s="3" t="inlineStr">
+        <is>
+          <t>'25 years of whole-of-market mortgage advice in Guildford - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R438" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S438" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T438" s="3" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="4" t="inlineStr">
+        <is>
+          <t>C A Financial Services</t>
+        </is>
+      </c>
+      <c r="B439" s="4" t="inlineStr">
+        <is>
+          <t>Independent financial planning</t>
+        </is>
+      </c>
+      <c r="C439" s="4" t="inlineStr">
+        <is>
+          <t>Kemsing, Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D439" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cafinancialservices.co.uk</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>craig.atkins@cafinancialservices.co.uk</t>
+        </is>
+      </c>
+      <c r="F439" s="4" t="inlineStr">
+        <is>
+          <t>01732 617950</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>Craig Atkins (Founder/Owner, est. 2007)</t>
+        </is>
+      </c>
+      <c r="H439" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/c-a-financial-services</t>
+        </is>
+      </c>
+      <c r="I439" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/cafsuk</t>
+        </is>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>Sole-owned independent financial planning practice (pensions/investments/tax/protection/estate planning); ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K439" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L439" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M439" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N439" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O439" s="4" t="inlineStr">
+        <is>
+          <t>Facebook/LinkedIn presence; 18-year trading history</t>
+        </is>
+      </c>
+      <c r="P439" s="4" t="inlineStr">
+        <is>
+          <t>18-year sole-practitioner heritage not yet the AI-cited answer for 'financial adviser Sevenoaks'</t>
+        </is>
+      </c>
+      <c r="Q439" s="4" t="inlineStr">
+        <is>
+          <t>'18 years of independent financial planning in Sevenoaks - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R439" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S439" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T439" s="4" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="inlineStr">
+        <is>
+          <t>Isis Financial Planners</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>Chartered independent financial planners</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>Farmoor, Oxford</t>
+        </is>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>https://www.isisfp.co.uk</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="inlineStr">
+        <is>
+          <t>postbox@isisfp.co.uk</t>
+        </is>
+      </c>
+      <c r="F440" s="3" t="inlineStr">
+        <is>
+          <t>01865 655980</t>
+        </is>
+      </c>
+      <c r="G440" s="3" t="inlineStr">
+        <is>
+          <t>Louis Letourneau (Founder, Chartered Financial Planner, est. 2002)</t>
+        </is>
+      </c>
+      <c r="H440" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/isis-financial-planners-limited</t>
+        </is>
+      </c>
+      <c r="I440" s="3" t="inlineStr"/>
+      <c r="J440" s="3" t="inlineStr">
+        <is>
+          <t>Chartered wealth-management/retirement-planning firm trading since 2002; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K440" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L440" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M440" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N440" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O440" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; Chartered status; 23-year heritage</t>
+        </is>
+      </c>
+      <c r="P440" s="3" t="inlineStr">
+        <is>
+          <t>23-year heritage not yet the AI-cited answer for 'financial planner Oxford'</t>
+        </is>
+      </c>
+      <c r="Q440" s="3" t="inlineStr">
+        <is>
+          <t>'23 years of Chartered financial planning in Oxford - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R440" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S440" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T440" s="3" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="inlineStr">
+        <is>
+          <t>Pattenden Vets</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>Veterinary practice</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>Marden, Kent</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pattendenvets.com</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>info@pattendenvets.com</t>
+        </is>
+      </c>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>01622 397900</t>
+        </is>
+      </c>
+      <c r="G441" s="3" t="inlineStr">
+        <is>
+          <t>Dr Lara Hummel, Robert Everitt, Dr Laura Heasman &amp; Dr Vanessa Martin MRCVS (Directors, est. 2018)</t>
+        </is>
+      </c>
+      <c r="H441" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/pattenden-vets</t>
+        </is>
+      </c>
+      <c r="I441" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/pattendenvets; facebook.com/pattendenvets</t>
+        </is>
+      </c>
+      <c r="J441" s="3" t="inlineStr">
+        <is>
+          <t>Independent small-animal/exotic practice recently celebrating its 7th anniversary; consultation/treatment fees plus repeat annual health-plan clients</t>
+        </is>
+      </c>
+      <c r="K441" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L441" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M441" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N441" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O441" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram/Facebook presence = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P441" s="3" t="inlineStr">
+        <is>
+          <t>Multi-channel social presence not yet converted into AI-cited answers for 'vet Marden'</t>
+        </is>
+      </c>
+      <c r="Q441" s="3" t="inlineStr">
+        <is>
+          <t>'You're already active on 3 platforms - let's make AI cite you for local vet searches too'</t>
+        </is>
+      </c>
+      <c r="R441" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S441" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T441" s="3" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Family Vets</t>
+        </is>
+      </c>
+      <c r="B442" s="4" t="inlineStr">
+        <is>
+          <t>Veterinary practice</t>
+        </is>
+      </c>
+      <c r="C442" s="4" t="inlineStr">
+        <is>
+          <t>Jacobs Well, Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>https://www.surreyfamilyvets.co.uk</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>hello@surreyfamilyvets.co.uk</t>
+        </is>
+      </c>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>01483 322023</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>Natalia &amp; Marcos (Husband-and-wife founders)</t>
+        </is>
+      </c>
+      <c r="H442" s="4" t="inlineStr"/>
+      <c r="I442" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/surreyfamilyvets; facebook.com/SurreyFamilyVets</t>
+        </is>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>Husband-and-wife independent practice with on-site diagnostics and keyhole surgery; consultation/treatment fees plus repeat annual health-plan clients</t>
+        </is>
+      </c>
+      <c r="K442" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L442" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M442" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N442" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O442" s="4" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P442" s="4" t="inlineStr">
+        <is>
+          <t>Husband-and-wife story not yet the AI-cited trust signal for 'vet Guildford'</t>
+        </is>
+      </c>
+      <c r="Q442" s="4" t="inlineStr">
+        <is>
+          <t>'A husband-and-wife vet team you can trust - own that AEO story in Guildford'</t>
+        </is>
+      </c>
+      <c r="R442" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S442" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T442" s="4" t="inlineStr">
+        <is>
+          <t>Confirm Companies House entry before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="3" t="inlineStr">
+        <is>
+          <t>Iffley Vets</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>Veterinary practice (small independent group)</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>Oxford &amp; Wheatley, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>https://www.iffleyvets.com</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="inlineStr">
+        <is>
+          <t>info@iffleyvets.com</t>
+        </is>
+      </c>
+      <c r="F443" s="3" t="inlineStr">
+        <is>
+          <t>01865 242600</t>
+        </is>
+      </c>
+      <c r="G443" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Bartholomew, Katharine Morrison &amp; Cameron Forbes MRCVS (Vet-owner directors, part of DNA Vetcare)</t>
+        </is>
+      </c>
+      <c r="H443" s="3" t="inlineStr"/>
+      <c r="I443" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Iffley-Vets-Oxford-Wheatley</t>
+        </is>
+      </c>
+      <c r="J443" s="3" t="inlineStr">
+        <is>
+          <t>Vet-owned two-site independent group (not PE/corporate-backed) named 'Best Vets in Oxfordshire 2026'; consultation/treatment fees plus repeat annual health-plan clients</t>
+        </is>
+      </c>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L443" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M443" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N443" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O443" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; recent 'Best Vets in Oxfordshire 2026' award</t>
+        </is>
+      </c>
+      <c r="P443" s="3" t="inlineStr">
+        <is>
+          <t>Award win not yet the AI-cited trust signal for 'vet Oxford'</t>
+        </is>
+      </c>
+      <c r="Q443" s="3" t="inlineStr">
+        <is>
+          <t>'Best Vets in Oxfordshire 2026 - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R443" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S443" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T443" s="3" t="inlineStr">
+        <is>
+          <t>Small owner-vet group (DNA Vetcare), not corporate-chain owned</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="inlineStr">
+        <is>
+          <t>Capstone Solicitors</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, family, private client)</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>Bishopston, Bristol</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>https://www.capstonelaw.co.uk</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@capstonelaw.co.uk</t>
+        </is>
+      </c>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>0117 942 8214</t>
+        </is>
+      </c>
+      <c r="G444" s="3" t="inlineStr">
+        <is>
+          <t>Richard Vooght &amp; Rob Wilson (Partners; office trading continuously since 1973)</t>
+        </is>
+      </c>
+      <c r="H444" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/capstone-solicitors</t>
+        </is>
+      </c>
+      <c r="I444" s="3" t="inlineStr"/>
+      <c r="J444" s="3" t="inlineStr">
+        <is>
+          <t>Independent Bristol firm with roots to 1973 (rebranded 2013), grows entirely by referral with no third-party lead-buying; conveyancing fees plus private-client work recur</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L444" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M444" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N444" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O444" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 50+ year trading roots</t>
+        </is>
+      </c>
+      <c r="P444" s="3" t="inlineStr">
+        <is>
+          <t>50-year heritage not yet the AI-cited answer for 'solicitor Bristol'</t>
+        </is>
+      </c>
+      <c r="Q444" s="3" t="inlineStr">
+        <is>
+          <t>'Trading since 1973, no lead-buying, pure reputation - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R444" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S444" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T444" s="3" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="4" t="inlineStr">
+        <is>
+          <t>Beaufort Montague Harris (BMH Solicitors)</t>
+        </is>
+      </c>
+      <c r="B445" s="4" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, private client)</t>
+        </is>
+      </c>
+      <c r="C445" s="4" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D445" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bmhsolicitors.co.uk</t>
+        </is>
+      </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F445" s="4" t="inlineStr">
+        <is>
+          <t>01225 667648</t>
+        </is>
+      </c>
+      <c r="G445" s="4" t="inlineStr">
+        <is>
+          <t>Geraint James (Owner)</t>
+        </is>
+      </c>
+      <c r="H445" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/geraint-james-8b9b6414</t>
+        </is>
+      </c>
+      <c r="I445" s="4" t="inlineStr"/>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>Single-office Bath firm formed via 2019 merger of two established local practices; conveyancing fees plus private-client work recur</t>
+        </is>
+      </c>
+      <c r="K445" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L445" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M445" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N445" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O445" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P445" s="4" t="inlineStr">
+        <is>
+          <t>Merger of two established firms not yet leveraged as an AEO trust signal</t>
+        </is>
+      </c>
+      <c r="Q445" s="4" t="inlineStr">
+        <is>
+          <t>'Two established Bath firms, now one - own that combined-heritage AEO story'</t>
+        </is>
+      </c>
+      <c r="R445" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S445" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T445" s="4" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="4" t="inlineStr">
+        <is>
+          <t>Surrey Property Lawyers</t>
+        </is>
+      </c>
+      <c r="B446" s="4" t="inlineStr">
+        <is>
+          <t>Conveyancing solicitors</t>
+        </is>
+      </c>
+      <c r="C446" s="4" t="inlineStr">
+        <is>
+          <t>Onslow Village, Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>https://www.surreypropertylawyers.co.uk</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>info@surreypropertylawyers.co.uk</t>
+        </is>
+      </c>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>01483 485800</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>Catherine Fewings &amp; Amanda (Team)</t>
+        </is>
+      </c>
+      <c r="H446" s="4" t="inlineStr"/>
+      <c r="I446" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/SurreyPropertyLawyers</t>
+        </is>
+      </c>
+      <c r="J446" s="4" t="inlineStr">
+        <is>
+          <t>Boutique conveyancing-only specialist built on client reviews/local reputation rather than volume; conveyancing fees per transaction, repeat referral clients</t>
+        </is>
+      </c>
+      <c r="K446" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L446" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M446" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N446" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O446" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P446" s="4" t="inlineStr">
+        <is>
+          <t>Review-driven growth not yet converted into AI-cited answers for 'conveyancing solicitor Guildford'</t>
+        </is>
+      </c>
+      <c r="Q446" s="4" t="inlineStr">
+        <is>
+          <t>'Built on 5-star reviews, not volume - let's make AI cite those reviews too'</t>
+        </is>
+      </c>
+      <c r="R446" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S446" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T446" s="4" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="4" t="inlineStr">
+        <is>
+          <t>Hunter Peddell Property Law</t>
+        </is>
+      </c>
+      <c r="B447" s="4" t="inlineStr">
+        <is>
+          <t>Law firm (residential &amp; commercial property)</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="inlineStr">
+        <is>
+          <t>Claygate, Esher, Surrey</t>
+        </is>
+      </c>
+      <c r="D447" s="4" t="inlineStr">
+        <is>
+          <t>via directory listing</t>
+        </is>
+      </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>ihunter@hpplaw.co.uk</t>
+        </is>
+      </c>
+      <c r="F447" s="4" t="inlineStr">
+        <is>
+          <t>01372 477900</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>Ian Hunter (Partner, solicitor since 1980) &amp; Loretta Peddell (Partner, 35+ yrs experience)</t>
+        </is>
+      </c>
+      <c r="H447" s="4" t="inlineStr"/>
+      <c r="I447" s="4" t="inlineStr"/>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>Long-standing two-partner practice with 40+ years combined local experience serving Esher/Claygate/Cobham; conveyancing fees per transaction, repeat local-client referrals</t>
+        </is>
+      </c>
+      <c r="K447" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L447" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M447" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N447" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O447" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P447" s="4" t="inlineStr">
+        <is>
+          <t>40+ years combined experience not yet leveraged as an AEO trust signal in a no-website/no-social firm</t>
+        </is>
+      </c>
+      <c r="Q447" s="4" t="inlineStr">
+        <is>
+          <t>'40+ years of combined Esher property law experience - own that AEO trust signal, starting with a stronger web presence'</t>
+        </is>
+      </c>
+      <c r="R447" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S447" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T447" s="4" t="inlineStr">
+        <is>
+          <t>No website/social presence found - verify a live site exists before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3" t="inlineStr">
+        <is>
+          <t>Cunningham Eves Solicitors</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, private client, family)</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="inlineStr">
+        <is>
+          <t>Leatherhead &amp; Dorking, Surrey</t>
+        </is>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cunninghameves.com</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="inlineStr">
+        <is>
+          <t>info@cunninghameves.com</t>
+        </is>
+      </c>
+      <c r="F448" s="3" t="inlineStr">
+        <is>
+          <t>01372 897857</t>
+        </is>
+      </c>
+      <c r="G448" s="3" t="inlineStr">
+        <is>
+          <t>Richard Cunningham (Managing Partner) &amp; Christine Eves (Senior Partner); founded 2020/21 by 4 partners</t>
+        </is>
+      </c>
+      <c r="H448" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/cunningham-eves-solicitors</t>
+        </is>
+      </c>
+      <c r="I448" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/cunninghamevessolicitors; facebook.com/CunninghamEvesSolicitors</t>
+        </is>
+      </c>
+      <c r="J448" s="3" t="inlineStr">
+        <is>
+          <t>Fast-growing two-office firm founded by 4 partners with a decade+ working together previously; conveyancing/private-client/family fees recur across the Cobham/Leatherhead/Dorking corridor</t>
+        </is>
+      </c>
+      <c r="K448" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L448" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M448" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N448" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O448" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram/Facebook presence = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P448" s="3" t="inlineStr">
+        <is>
+          <t>Rapid organic growth not yet matched by AI-search dominance across 2 offices</t>
+        </is>
+      </c>
+      <c r="Q448" s="3" t="inlineStr">
+        <is>
+          <t>'You grew from 4 partners to 2 offices by reputation - let's make AI cite you the same way'</t>
+        </is>
+      </c>
+      <c r="R448" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S448" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T448" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T431"/>
+  <autoFilter ref="A1:T448"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37916,7 +39508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B174"/>
+  <dimension ref="A1:B190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -37936,7 +39528,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>430</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5">
@@ -38469,17 +40061,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -38489,7 +40081,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -38499,7 +40091,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -38509,7 +40101,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -38519,7 +40111,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -38529,7 +40121,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -38539,7 +40131,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -38549,7 +40141,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -38559,7 +40151,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -38569,7 +40161,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -38579,7 +40171,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -38589,7 +40181,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -38599,7 +40191,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -38609,7 +40201,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -38619,7 +40211,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -38629,7 +40221,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -38639,7 +40231,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -38649,7 +40241,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -38659,7 +40251,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -38669,7 +40261,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -38679,7 +40271,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -38689,7 +40281,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -38699,7 +40291,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -38709,7 +40301,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -38719,7 +40311,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -38729,7 +40321,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -38739,7 +40331,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -38749,7 +40341,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -38759,7 +40351,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -38769,7 +40361,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -38779,7 +40371,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -38789,7 +40381,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -38799,7 +40391,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -38809,7 +40401,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -38819,7 +40411,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -38829,7 +40421,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -38839,7 +40431,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -38849,7 +40441,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -38859,7 +40451,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -38869,7 +40461,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -38879,7 +40471,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -38889,7 +40481,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -38899,7 +40491,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -38909,7 +40501,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -38919,7 +40511,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -38929,7 +40521,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -38939,7 +40531,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -38949,7 +40541,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -38959,7 +40551,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -38969,7 +40561,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -38979,7 +40571,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -38989,7 +40581,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -38999,7 +40591,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -39009,7 +40601,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -39019,7 +40611,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -39029,7 +40621,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -39039,7 +40631,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -39049,7 +40641,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -39059,7 +40651,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -39069,7 +40661,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -39079,7 +40671,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -39089,7 +40681,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -39099,7 +40691,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -39109,7 +40701,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -39119,7 +40711,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -39129,7 +40721,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -39139,7 +40731,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -39149,7 +40741,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -39159,7 +40751,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -39169,7 +40761,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -39179,7 +40771,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -39189,7 +40781,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -39199,7 +40791,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -39209,7 +40801,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -39219,7 +40811,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -39229,7 +40821,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -39239,7 +40831,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -39249,7 +40841,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -39259,7 +40851,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -39269,7 +40861,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -39279,7 +40871,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -39289,7 +40881,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -39299,7 +40891,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -39309,7 +40901,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -39319,7 +40911,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -39329,7 +40921,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -39339,7 +40931,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -39349,7 +40941,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -39359,7 +40951,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -39369,7 +40961,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -39379,7 +40971,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -39389,7 +40981,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -39399,7 +40991,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -39409,7 +41001,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -39419,7 +41011,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -39429,7 +41021,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -39439,7 +41031,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -39449,7 +41041,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -39459,7 +41051,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -39469,7 +41061,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -39479,7 +41071,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -39489,7 +41081,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -39499,7 +41091,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -39509,7 +41101,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -39519,7 +41111,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -39529,7 +41121,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -39539,7 +41131,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -39549,7 +41141,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -39559,7 +41151,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -39569,7 +41161,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Beauty/aesthetics training academy</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -39579,7 +41171,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Beauty/hair training academy</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -39589,7 +41181,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Medical aesthetics/injectable training academy</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -39599,7 +41191,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Creative &amp; marketing recruitment agency</t>
+          <t>Yoga teacher training school</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -39609,7 +41201,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Private dermatology &amp; women's health clinics</t>
+          <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -39619,7 +41211,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Private dermatology practice</t>
+          <t>Private dermatology &amp; women's health clinics</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -39629,10 +41221,170 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>Private dermatology practice</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>Estate &amp; lettings agent</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Wedding venue (converted barn)</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Wedding venue (thatched barn on working farm)</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Wedding venue (working farm)</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Wedding venue (restored historic barn)</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Chartered IFA / wealth management</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Independent mortgage broker</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Independent financial planning</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Chartered independent financial planners</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Veterinary practice (small independent group)</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, family, private client)</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, private client)</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Conveyancing solicitors</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Law firm (residential &amp; commercial property)</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Law firm (conveyancing, private client, family)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$448</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$471</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T448"/>
+  <dimension ref="A1:T471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -39496,8 +39496,2156 @@
       </c>
       <c r="T448" s="3" t="inlineStr"/>
     </row>
+    <row r="449">
+      <c r="A449" s="3" t="inlineStr">
+        <is>
+          <t>Solar Age UK</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>Solar &amp; heat pump installer</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>Barham, Canterbury, Kent</t>
+        </is>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>https://www.solarage.co.uk</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="inlineStr">
+        <is>
+          <t>info@solarage.co.uk</t>
+        </is>
+      </c>
+      <c r="F449" s="3" t="inlineStr">
+        <is>
+          <t>01227 832299</t>
+        </is>
+      </c>
+      <c r="G449" s="3" t="inlineStr">
+        <is>
+          <t>Piotr Bojda (Director)</t>
+        </is>
+      </c>
+      <c r="H449" s="3" t="inlineStr"/>
+      <c r="I449" s="3" t="inlineStr"/>
+      <c r="J449" s="3" t="inlineStr">
+        <is>
+          <t>Family-run MCS-accredited installer since October 2009 (16-year track record) covering solar PV/thermal and ground/air/water-source heat pumps; installation jobs worth thousands to tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K449" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L449" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M449" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N449" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O449" s="3" t="inlineStr">
+        <is>
+          <t>16-year MCS accreditation + RECC membership = established credibility</t>
+        </is>
+      </c>
+      <c r="P449" s="3" t="inlineStr">
+        <is>
+          <t>16-year heritage not yet the AI-cited answer for 'solar installer Kent'</t>
+        </is>
+      </c>
+      <c r="Q449" s="3" t="inlineStr">
+        <is>
+          <t>'MCS-accredited since 2009 - own that exact AEO trust signal in AI-search answers'</t>
+        </is>
+      </c>
+      <c r="R449" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S449" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T449" s="3" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="4" t="inlineStr">
+        <is>
+          <t>South East Solar &amp; Electrical</t>
+        </is>
+      </c>
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t>Solar PV &amp; electrical installer</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="inlineStr">
+        <is>
+          <t>Rochester, Kent (also Sevenoaks)</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>https://www.southeastsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>office@southeastsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>01634 553422</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>Director details not public - verify via Companies House #09345242</t>
+        </is>
+      </c>
+      <c r="H450" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/south-east-solar-and-electrical-limited</t>
+        </is>
+      </c>
+      <c r="I450" s="4" t="inlineStr"/>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>11-year residential/commercial solar &amp; electrical installer; installation jobs worth thousands to tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K450" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L450" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M450" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N450" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O450" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 11-year trading history</t>
+        </is>
+      </c>
+      <c r="P450" s="4" t="inlineStr">
+        <is>
+          <t>11-year heritage not yet the AI-cited answer for 'solar installer Kent'</t>
+        </is>
+      </c>
+      <c r="Q450" s="4" t="inlineStr">
+        <is>
+          <t>'11 years installing solar across Kent - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R450" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S450" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T450" s="4" t="inlineStr">
+        <is>
+          <t>Confirm director name via Companies House before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Cinergi</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Heat pump &amp; EV charger installer</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>Romsey, Hampshire (covers Hants/Dorset/Wilts/Oxon/Surrey)</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cinergi.co.uk</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>info@cinergi.co.uk</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>0800 321 3142</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Dan Loveridge (Founder/Managing Director)</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/cinergi-ltd</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/CinergiUK; instagram.com/cinergi_</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>Ranked in Ofgem's top 1% of heat pump installers nationally, uses only in-house engineers (no subcontracting); installation jobs worth thousands to tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K451" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L451" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N451" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence; Ofgem top 1% ranking = exceptional credibility asset</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem top 1% ranking not yet the AI-cited trust signal for 'heat pump installer Hampshire'</t>
+        </is>
+      </c>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>'Ranked in Ofgem's top 1% of heat pump installers - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R451" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S451" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T451" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem top 1% credential is an exceptional AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="4" t="inlineStr">
+        <is>
+          <t>Volts Waggon</t>
+        </is>
+      </c>
+      <c r="B452" s="4" t="inlineStr">
+        <is>
+          <t>Solar PV &amp; EV charger installer</t>
+        </is>
+      </c>
+      <c r="C452" s="4" t="inlineStr">
+        <is>
+          <t>Hedge End, Southampton, Hampshire</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="inlineStr">
+        <is>
+          <t>https://www.voltswaggon.co.uk</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>john@voltswaggon.co.uk</t>
+        </is>
+      </c>
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>07585 306346</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>John Wood (Founder, certified electrician, est. 2022)</t>
+        </is>
+      </c>
+      <c r="H452" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/woodster; linkedin.com/company/volts-waggon</t>
+        </is>
+      </c>
+      <c r="I452" s="4" t="inlineStr"/>
+      <c r="J452" s="4" t="inlineStr">
+        <is>
+          <t>Growing bespoke residential solar/battery/EV-charger installer with 50+ installations across Hampshire/East Dorset; installation jobs worth thousands to tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K452" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L452" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M452" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N452" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O452" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P452" s="4" t="inlineStr">
+        <is>
+          <t>Early-stage growth business - ground-floor opportunity to own local AEO search before bigger installers do</t>
+        </is>
+      </c>
+      <c r="Q452" s="4" t="inlineStr">
+        <is>
+          <t>'50+ installations and growing - be the AI-cited answer before the bigger installers catch on'</t>
+        </is>
+      </c>
+      <c r="R452" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S452" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T452" s="4" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="4" t="inlineStr">
+        <is>
+          <t>Justin Bucknell Electrical</t>
+        </is>
+      </c>
+      <c r="B453" s="4" t="inlineStr">
+        <is>
+          <t>Electrical contractor &amp; solar installer</t>
+        </is>
+      </c>
+      <c r="C453" s="4" t="inlineStr">
+        <is>
+          <t>Bicester, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D453" s="4" t="inlineStr">
+        <is>
+          <t>https://www.justinbucknellelectrical.co.uk</t>
+        </is>
+      </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F453" s="4" t="inlineStr"/>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>Justin Bucknell (Founder, ~20 years trading)</t>
+        </is>
+      </c>
+      <c r="H453" s="4" t="inlineStr"/>
+      <c r="I453" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/justinbucknellelectrical</t>
+        </is>
+      </c>
+      <c r="J453" s="4" t="inlineStr">
+        <is>
+          <t>20-year local electrical contractor with MCS-accredited solar installation arm; Which? Trusted Trader listed, installation jobs worth thousands each</t>
+        </is>
+      </c>
+      <c r="K453" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L453" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M453" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N453" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O453" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence; Which? Trusted Trader listing; 20-year trading history</t>
+        </is>
+      </c>
+      <c r="P453" s="4" t="inlineStr">
+        <is>
+          <t>20-year heritage and trusted-trader status not yet the AI-cited answer for 'solar installer Bicester'</t>
+        </is>
+      </c>
+      <c r="Q453" s="4" t="inlineStr">
+        <is>
+          <t>'Which? Trusted Trader for 20 years - own that AEO trust signal in Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="R453" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S453" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T453" s="4" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="4" t="inlineStr">
+        <is>
+          <t>Capital Solar</t>
+        </is>
+      </c>
+      <c r="B454" s="4" t="inlineStr">
+        <is>
+          <t>Solar PV installer</t>
+        </is>
+      </c>
+      <c r="C454" s="4" t="inlineStr">
+        <is>
+          <t>Abingdon, Oxfordshire (Oxfordshire-wide)</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>https://www.capitalsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>dan@capitalsolar.co.uk</t>
+        </is>
+      </c>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>07931 957447</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>Dan (Director) - surname unconfirmed, verify via Companies House #11850466</t>
+        </is>
+      </c>
+      <c r="H454" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/capital-electrical-and-solar</t>
+        </is>
+      </c>
+      <c r="I454" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/capitalelectricalandsolar</t>
+        </is>
+      </c>
+      <c r="J454" s="4" t="inlineStr">
+        <is>
+          <t>Oxfordshire-wide solar PV installer; installation jobs worth thousands to tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K454" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L454" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M454" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N454" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O454" s="4" t="inlineStr">
+        <is>
+          <t>Facebook/LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P454" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'solar installer Oxfordshire' searches not yet AI-answer dominated by this installer</t>
+        </is>
+      </c>
+      <c r="Q454" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific Oxfordshire-town AEO niche vs bigger regional installers</t>
+        </is>
+      </c>
+      <c r="R454" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S454" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T454" s="4" t="inlineStr">
+        <is>
+          <t>Confirm director surname via Companies House before outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="4" t="inlineStr">
+        <is>
+          <t>The Pilates Sphere</t>
+        </is>
+      </c>
+      <c r="B455" s="4" t="inlineStr">
+        <is>
+          <t>Reformer Pilates studio</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="inlineStr">
+        <is>
+          <t>Richmond, London TW9</t>
+        </is>
+      </c>
+      <c r="D455" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thepilatessphere.co.uk</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F455" s="4" t="inlineStr"/>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>Charlotte Faul (Owner, rebranded/relaunched summer 2024)</t>
+        </is>
+      </c>
+      <c r="H455" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/charlotte-faul</t>
+        </is>
+      </c>
+      <c r="I455" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/thepilatessphere.richmond; facebook.com/61573085375104</t>
+        </is>
+      </c>
+      <c r="J455" s="4" t="inlineStr">
+        <is>
+          <t>Independent boutique reformer Pilates studio serving Richmond/Kew/Twickenham/Kingston; class packages and memberships worth hundreds to thousands per client per year</t>
+        </is>
+      </c>
+      <c r="K455" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L455" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M455" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N455" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O455" s="4" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence = active marketing</t>
+        </is>
+      </c>
+      <c r="P455" s="4" t="inlineStr">
+        <is>
+          <t>Recent rebrand not yet the AI-cited answer for 'reformer Pilates Richmond'</t>
+        </is>
+      </c>
+      <c r="Q455" s="4" t="inlineStr">
+        <is>
+          <t>'Just relaunched - be the AI-cited answer before the old brand's search history fades'</t>
+        </is>
+      </c>
+      <c r="R455" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S455" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T455" s="4" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="4" t="inlineStr">
+        <is>
+          <t>Victoria Hinds Pilates</t>
+        </is>
+      </c>
+      <c r="B456" s="4" t="inlineStr">
+        <is>
+          <t>Classical Pilates studio</t>
+        </is>
+      </c>
+      <c r="C456" s="4" t="inlineStr">
+        <is>
+          <t>St Margarets/East Twickenham (serving Richmond)</t>
+        </is>
+      </c>
+      <c r="D456" s="4" t="inlineStr">
+        <is>
+          <t>https://www.victoriahindspilates.co.uk</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F456" s="4" t="inlineStr">
+        <is>
+          <t>07853 902032</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>Victoria Hinds (Founder, Body Control Pilates-certified, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H456" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/victoria-hinds-99938648</t>
+        </is>
+      </c>
+      <c r="I456" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/victoria_hindspilates</t>
+        </is>
+      </c>
+      <c r="J456" s="4" t="inlineStr">
+        <is>
+          <t>14-year solo-owner classical Pilates studio (mat &amp; reformer, private and small-group); class packages worth hundreds to thousands per client per year</t>
+        </is>
+      </c>
+      <c r="K456" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L456" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M456" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N456" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O456" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram presence; 14-year trading history</t>
+        </is>
+      </c>
+      <c r="P456" s="4" t="inlineStr">
+        <is>
+          <t>14-year heritage not yet the AI-cited answer for 'Pilates Richmond'</t>
+        </is>
+      </c>
+      <c r="Q456" s="4" t="inlineStr">
+        <is>
+          <t>'14 years teaching classical Pilates in Richmond - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R456" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S456" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T456" s="4" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham Pilates &amp; Yoga Studios</t>
+        </is>
+      </c>
+      <c r="B457" s="4" t="inlineStr">
+        <is>
+          <t>Pilates &amp; yoga studio (+ teacher training)</t>
+        </is>
+      </c>
+      <c r="C457" s="4" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D457" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cheltenhampilatesandyoga.co.uk</t>
+        </is>
+      </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>nicky@cheltenhampilatesandyoga.co.uk</t>
+        </is>
+      </c>
+      <c r="F457" s="4" t="inlineStr"/>
+      <c r="G457" s="4" t="inlineStr">
+        <is>
+          <t>Nicky Gladman (Founder, 20 years teaching Pilates, studio est. 2009)</t>
+        </is>
+      </c>
+      <c r="H457" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/nicky-gladman-7683b9153</t>
+        </is>
+      </c>
+      <c r="I457" s="4" t="inlineStr"/>
+      <c r="J457" s="4" t="inlineStr">
+        <is>
+          <t>One of Cheltenham's most established independent studios (15+ years at current site) offering classes and teacher training; class packages and trainee course fees recur</t>
+        </is>
+      </c>
+      <c r="K457" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L457" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M457" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N457" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O457" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 15+ year trading history</t>
+        </is>
+      </c>
+      <c r="P457" s="4" t="inlineStr">
+        <is>
+          <t>15-year heritage not yet the AI-cited answer for 'Pilates Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q457" s="4" t="inlineStr">
+        <is>
+          <t>'15 years at the same Cheltenham studio - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R457" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S457" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T457" s="4" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="3" t="inlineStr">
+        <is>
+          <t>The Studio Cheltenham</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>Reformer Pilates studio</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>The Brewery Quarter, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D458" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thestudiocheltenham.com</t>
+        </is>
+      </c>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>hello@thestudiocheltenham.com</t>
+        </is>
+      </c>
+      <c r="F458" s="3" t="inlineStr"/>
+      <c r="G458" s="3" t="inlineStr">
+        <is>
+          <t>Fontaine Wright (Co-founder, former Team GB badminton player) &amp; Harry (Co-founder, launched Oct 2024)</t>
+        </is>
+      </c>
+      <c r="H458" s="3" t="inlineStr"/>
+      <c r="I458" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/thestudiocheltenham; facebook.com/p/The-Studio-Cheltenham-61561700947780</t>
+        </is>
+      </c>
+      <c r="J458" s="3" t="inlineStr">
+        <is>
+          <t>New strength-focused dynamic reformer Pilates studio from a former Team GB athlete, with press coverage in SoGlos; class packages and memberships worth hundreds to thousands per client per year</t>
+        </is>
+      </c>
+      <c r="K458" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L458" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M458" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N458" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O458" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence; press coverage (SoGlos) = active PR</t>
+        </is>
+      </c>
+      <c r="P458" s="3" t="inlineStr">
+        <is>
+          <t>Team GB founder story and press coverage not yet the AI-cited answer for 'Pilates Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q458" s="3" t="inlineStr">
+        <is>
+          <t>'Founded by a former Team GB athlete - own that exact AEO story before competitors catch on'</t>
+        </is>
+      </c>
+      <c r="R458" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S458" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T458" s="3" t="inlineStr">
+        <is>
+          <t>New studio (Oct 2024), explicitly markets as 'proudly independent'</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>Every Body Studio</t>
+        </is>
+      </c>
+      <c r="B459" s="4" t="inlineStr">
+        <is>
+          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
+        </is>
+      </c>
+      <c r="C459" s="4" t="inlineStr">
+        <is>
+          <t>St Clements/Magdalen Road, Oxford</t>
+        </is>
+      </c>
+      <c r="D459" s="4" t="inlineStr">
+        <is>
+          <t>https://www.everybodystudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>hello@everybodystudio.co.uk</t>
+        </is>
+      </c>
+      <c r="F459" s="4" t="inlineStr">
+        <is>
+          <t>07813 691906</t>
+        </is>
+      </c>
+      <c r="G459" s="4" t="inlineStr">
+        <is>
+          <t>Katie Gordon (Founder)</t>
+        </is>
+      </c>
+      <c r="H459" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/katie-gordon-73702253</t>
+        </is>
+      </c>
+      <c r="I459" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/EverybodyStudioOxford</t>
+        </is>
+      </c>
+      <c r="J459" s="4" t="inlineStr">
+        <is>
+          <t>Inclusive independent movement studio running its own yoga teacher-training programme, listed on the Independent Oxford directory; class packages and trainee course fees recur</t>
+        </is>
+      </c>
+      <c r="K459" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L459" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M459" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N459" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O459" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; Independent Oxford directory listing</t>
+        </is>
+      </c>
+      <c r="P459" s="4" t="inlineStr">
+        <is>
+          <t>Independent Oxford listing not yet converted into AI-cited answers for 'yoga studio Oxford'</t>
+        </is>
+      </c>
+      <c r="Q459" s="4" t="inlineStr">
+        <is>
+          <t>'Listed on Independent Oxford - let's make AI cite you too'</t>
+        </is>
+      </c>
+      <c r="R459" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S459" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T459" s="4" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="3" t="inlineStr">
+        <is>
+          <t>TUFFCORE</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>Women-only strength &amp; personal training studio</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>Cowley, Oxford</t>
+        </is>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>https://www.teamtuffcore.com</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F460" s="3" t="inlineStr">
+        <is>
+          <t>07904 122815</t>
+        </is>
+      </c>
+      <c r="G460" s="3" t="inlineStr">
+        <is>
+          <t>Igor (Founder, martial arts/combat sports background) &amp; Agata (Coach)</t>
+        </is>
+      </c>
+      <c r="H460" s="3" t="inlineStr"/>
+      <c r="I460" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/tuffcorefitness_ox</t>
+        </is>
+      </c>
+      <c r="J460" s="3" t="inlineStr">
+        <is>
+          <t>Largest women-only small-group strength/PT studio in Oxford, niche-focused on women 30+; membership and PT packages worth thousands per client per year</t>
+        </is>
+      </c>
+      <c r="K460" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L460" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M460" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N460" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O460" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence; strong niche positioning</t>
+        </is>
+      </c>
+      <c r="P460" s="3" t="inlineStr">
+        <is>
+          <t>Niche positioning not yet the AI-cited answer for 'women's strength training Oxford'</t>
+        </is>
+      </c>
+      <c r="Q460" s="3" t="inlineStr">
+        <is>
+          <t>'The largest women-only strength studio in Oxford - own that exact AEO niche'</t>
+        </is>
+      </c>
+      <c r="R460" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S460" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T460" s="3" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="3" t="inlineStr">
+        <is>
+          <t>Edmans &amp; Co</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>Immigration &amp; commercial law firm</t>
+        </is>
+      </c>
+      <c r="C461" s="3" t="inlineStr">
+        <is>
+          <t>Chancery Lane, London</t>
+        </is>
+      </c>
+      <c r="D461" s="3" t="inlineStr">
+        <is>
+          <t>https://www.edmansco.com</t>
+        </is>
+      </c>
+      <c r="E461" s="3" t="inlineStr">
+        <is>
+          <t>info@edmansco.com</t>
+        </is>
+      </c>
+      <c r="F461" s="3" t="inlineStr">
+        <is>
+          <t>020 8935 5205</t>
+        </is>
+      </c>
+      <c r="G461" s="3" t="inlineStr">
+        <is>
+          <t>David Manasyan &amp; Emil Manasyan (Founding brothers)</t>
+        </is>
+      </c>
+      <c r="H461" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/edmans; linkedin.com/in/emilmanasyan</t>
+        </is>
+      </c>
+      <c r="I461" s="3" t="inlineStr"/>
+      <c r="J461" s="3" t="inlineStr">
+        <is>
+          <t>Boutique OISC Level 3 immigration/commercial firm founded by immigrants who experienced the visa process firsthand; single-case fees run into thousands</t>
+        </is>
+      </c>
+      <c r="K461" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L461" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M461" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N461" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O461" s="3" t="inlineStr">
+        <is>
+          <t>Tech-forward 'modern law firm' positioning = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P461" s="3" t="inlineStr">
+        <is>
+          <t>Founder-story angle not yet the AI-cited trust signal for 'immigration solicitor London'</t>
+        </is>
+      </c>
+      <c r="Q461" s="3" t="inlineStr">
+        <is>
+          <t>'Founded by immigrants who lived the visa process - own that authentic AEO story'</t>
+        </is>
+      </c>
+      <c r="R461" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S461" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T461" s="3" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Laura Devine Immigration</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Immigration law firm (UK/US)</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>Cannon Street, London (+ New York)</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lauradevine.com</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@lauradevine.com</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>020 7469 6460</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Laura Devine (Founder, est. 2003) &amp; Sophie Barrett-Brown (Senior Partner)</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/laura-devine-immigration; linkedin.com/in/lauradevineimmigration</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr"/>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>Top-tier boutique transatlantic immigration firm, Legal 500 Hall of Fame and Chambers 'Eminent Practitioner' ranked; single-case fees run into thousands to tens of thousands</t>
+        </is>
+      </c>
+      <c r="K462" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N462" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>2,400+ LinkedIn followers; top-tier legal directory rankings</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr">
+        <is>
+          <t>Elite rankings not yet the AI-cited answer for 'immigration lawyer London'</t>
+        </is>
+      </c>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>'Legal 500 Hall of Fame - own that exact AEO trust signal against bigger immigration firms'</t>
+        </is>
+      </c>
+      <c r="R462" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>Elite rankings + transatlantic reach - high-value AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Currey &amp; Co</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Private client law firm (wills, trusts, estates)</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>Marylebone, London</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.curreyandco.co.uk</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@curreyandco.co.uk</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>020 7802 2700</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Robert Currey (Chairman); founded 1812 by Benjamin Currey</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/currey-&amp;-co-llp</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr"/>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>213-year boutique private-client firm for landed-estate and HNW families, deliberately kept small and partner-led; estate-planning fees run into tens of thousands per family</t>
+        </is>
+      </c>
+      <c r="K463" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L463" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M463" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N463" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O463" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; Chambers High Net Worth ranking; 200+ year heritage</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional 213-year heritage not yet the AI-cited answer for 'private client solicitor London'</t>
+        </is>
+      </c>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>'Advising families since 1812 - own that exact AEO trust signal, unmatched by any competitor'</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S463" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional 213-year heritage - among the strongest AEO trust stories in the whole database</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="3" t="inlineStr">
+        <is>
+          <t>Maurice Turnor Gardner</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>Private wealth &amp; estate planning law firm</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>City of London</t>
+        </is>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mauriceturnorgardner.com</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@mauriceturnorgardner.com</t>
+        </is>
+      </c>
+      <c r="F464" s="3" t="inlineStr">
+        <is>
+          <t>020 7786 8710</t>
+        </is>
+      </c>
+      <c r="G464" s="3" t="inlineStr">
+        <is>
+          <t>Clare Maurice (Senior Partner, first female partner at Allen &amp; Overy 1985); founded 2009</t>
+        </is>
+      </c>
+      <c r="H464" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/maurice-turnor-gardner-llp</t>
+        </is>
+      </c>
+      <c r="I464" s="3" t="inlineStr"/>
+      <c r="J464" s="3" t="inlineStr">
+        <is>
+          <t>Boutique private wealth firm for complex HNW estates, demerged from Allen &amp; Overy in 2009; estate-planning fees run into tens of thousands per family</t>
+        </is>
+      </c>
+      <c r="K464" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L464" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M464" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N464" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O464" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; Lifetime Achievement award (British Legal Awards 2023)</t>
+        </is>
+      </c>
+      <c r="P464" s="3" t="inlineStr">
+        <is>
+          <t>Senior partner's award and A&amp;O pedigree not yet the AI-cited trust signal</t>
+        </is>
+      </c>
+      <c r="Q464" s="3" t="inlineStr">
+        <is>
+          <t>'Founded by A&amp;O's first female partner - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R464" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S464" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T464" s="3" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="3" t="inlineStr">
+        <is>
+          <t>RMW Law</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>Private wealth law firm (UHNW)</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="inlineStr">
+        <is>
+          <t>Old Bailey, London</t>
+        </is>
+      </c>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rmwlaw.co.uk</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="inlineStr">
+        <is>
+          <t>mail@rmwlaw.co.uk</t>
+        </is>
+      </c>
+      <c r="F465" s="3" t="inlineStr">
+        <is>
+          <t>020 7597 6416</t>
+        </is>
+      </c>
+      <c r="G465" s="3" t="inlineStr">
+        <is>
+          <t>John Riches &amp; Samantha Morgan (Founders, ex-Withers, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H465" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/rmw-law-llp; linkedin.com/in/john-riches-93014415</t>
+        </is>
+      </c>
+      <c r="I465" s="3" t="inlineStr"/>
+      <c r="J465" s="3" t="inlineStr">
+        <is>
+          <t>Boutique UHNW private wealth firm (trusts, foundations, succession); estate-planning fees run into tens of thousands per family</t>
+        </is>
+      </c>
+      <c r="K465" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L465" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M465" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N465" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O465" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; Chambers HNW ranking, top-tier global recognition for founder</t>
+        </is>
+      </c>
+      <c r="P465" s="3" t="inlineStr">
+        <is>
+          <t>Founder's global top-tier ranking not yet the AI-cited answer for 'private wealth lawyer London'</t>
+        </is>
+      </c>
+      <c r="Q465" s="3" t="inlineStr">
+        <is>
+          <t>'Globally top-ranked for private wealth work - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R465" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S465" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T465" s="3" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Home Counties Carers</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Home care &amp; live-in care agency</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>Ripley, Surrey</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.homecountiescarers.co.uk</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>mkalupka@homecountiescarers.co.uk</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>01483 224985</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Family-run (verify via Companies House #07647044)</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/home-counties-carers</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/HomeCountiesCarers</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>CQC Outstanding-rated home/live-in/dementia care agency and Surrey Care Provider of the Year winner; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K466" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N466" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O466" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; CQC Outstanding + regional award</t>
+        </is>
+      </c>
+      <c r="P466" s="2" t="inlineStr">
+        <is>
+          <t>CQC Outstanding rating and award win not yet the AI-cited trust signal for 'home care Surrey'</t>
+        </is>
+      </c>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>'CQC Outstanding and Surrey Care Provider of the Year - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>CQC Outstanding + award win - strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>All About Home Care</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Home care agency</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells/Tonbridge/Sevenoaks/Maidstone, Kent</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allabouthomecare.co.uk</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>01732 447 055</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Kieron Brennan &amp; David Barrett (Co-founders, est. 2014)</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/davidrlbarrett</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/allabouthomecareHQ; instagram.com/allabouthomecarehq</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>CQC Outstanding-rated community home care provider, 'Top 20 Recommended Home Care Provider (South East)' three years running; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K467" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O467" s="2" t="inlineStr">
+        <is>
+          <t>Multi-channel social presence; CQC Outstanding + 3-year 'Top 20' recognition</t>
+        </is>
+      </c>
+      <c r="P467" s="2" t="inlineStr">
+        <is>
+          <t>3 years of 'Top 20' recognition not yet the AI-cited answer for 'home care Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>'Top 20 Recommended Home Care Provider, 3 years running - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>CQC Outstanding + repeat regional recognition - strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="3" t="inlineStr">
+        <is>
+          <t>Gardiner's Homecare</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>Home care agency</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>Caversham, Reading (Berkshire/South Oxfordshire)</t>
+        </is>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gardinershomecare.co.uk</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>simon@gardinershomecare.co.uk</t>
+        </is>
+      </c>
+      <c r="F468" s="3" t="inlineStr">
+        <is>
+          <t>0118 334 7474</t>
+        </is>
+      </c>
+      <c r="G468" s="3" t="inlineStr">
+        <is>
+          <t>Simon Mahony (Director, third-generation family ownership, est. 1968)</t>
+        </is>
+      </c>
+      <c r="H468" s="3" t="inlineStr"/>
+      <c r="I468" s="3" t="inlineStr"/>
+      <c r="J468" s="3" t="inlineStr">
+        <is>
+          <t>57-year, third-generation family home care agency; CQC rated Good overall, Outstanding for Responsiveness; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K468" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L468" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M468" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N468" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O468" s="3" t="inlineStr">
+        <is>
+          <t>CQC Outstanding-for-Responsiveness rating; 57-year heritage</t>
+        </is>
+      </c>
+      <c r="P468" s="3" t="inlineStr">
+        <is>
+          <t>57 years of family heritage not yet the AI-cited answer for 'home care Reading'</t>
+        </is>
+      </c>
+      <c r="Q468" s="3" t="inlineStr">
+        <is>
+          <t>'Three generations of family care since 1968 - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R468" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S468" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T468" s="3" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="4" t="inlineStr">
+        <is>
+          <t>1 to 1 Care</t>
+        </is>
+      </c>
+      <c r="B469" s="4" t="inlineStr">
+        <is>
+          <t>Home care agency</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="inlineStr">
+        <is>
+          <t>Chalgrove, South Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="inlineStr">
+        <is>
+          <t>https://www.1to1care.co.uk</t>
+        </is>
+      </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>care@1to1care.co.uk</t>
+        </is>
+      </c>
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>01865 343134</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>Family-owned, est. 2004; Sheena (Care Manager, 15 years)</t>
+        </is>
+      </c>
+      <c r="H469" s="4" t="inlineStr"/>
+      <c r="I469" s="4" t="inlineStr"/>
+      <c r="J469" s="4" t="inlineStr">
+        <is>
+          <t>21-year family-owned home care agency, CQC Good across all five categories; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K469" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L469" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M469" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N469" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O469" s="4" t="inlineStr">
+        <is>
+          <t>CQC Good across all categories; 21-year trading history</t>
+        </is>
+      </c>
+      <c r="P469" s="4" t="inlineStr">
+        <is>
+          <t>21-year heritage and consistent CQC ratings not yet the AI-cited answer for 'home care Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="Q469" s="4" t="inlineStr">
+        <is>
+          <t>'21 years of consistent 5-star CQC ratings - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R469" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S469" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T469" s="4" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="4" t="inlineStr">
+        <is>
+          <t>Amily Homecare</t>
+        </is>
+      </c>
+      <c r="B470" s="4" t="inlineStr">
+        <is>
+          <t>Home care &amp; live-in care agency</t>
+        </is>
+      </c>
+      <c r="C470" s="4" t="inlineStr">
+        <is>
+          <t>Walton-on-Thames, Surrey</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amily.co.uk</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>admin@amily.co.uk</t>
+        </is>
+      </c>
+      <c r="F470" s="4" t="inlineStr">
+        <is>
+          <t>01932 259613</t>
+        </is>
+      </c>
+      <c r="G470" s="4" t="inlineStr">
+        <is>
+          <t>Suvendu 'Butch' Seal (Owner/CEO)</t>
+        </is>
+      </c>
+      <c r="H470" s="4" t="inlineStr"/>
+      <c r="I470" s="4" t="inlineStr"/>
+      <c r="J470" s="4" t="inlineStr">
+        <is>
+          <t>CQC Good-rated family-run home and live-in care agency in Walton-on-Thames; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K470" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L470" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M470" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N470" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O470" s="4" t="inlineStr">
+        <is>
+          <t>CQC Good rating</t>
+        </is>
+      </c>
+      <c r="P470" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'home care Walton-on-Thames' searches not yet AI-answer dominated by this agency</t>
+        </is>
+      </c>
+      <c r="Q470" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific Surrey-town AEO niche vs bigger regional care agencies</t>
+        </is>
+      </c>
+      <c r="R470" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S470" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T470" s="4" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="inlineStr">
+        <is>
+          <t>County Carers</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>Residential &amp; domiciliary care provider</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>Crowthorne, Berkshire (Wokingham/Bracknell area)</t>
+        </is>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>https://www.countycarers.com</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>0118 973 3302</t>
+        </is>
+      </c>
+      <c r="G471" s="3" t="inlineStr">
+        <is>
+          <t>Eloise Wakeford (Founder &amp; Proprietor/CEO, CQC-registered since age 19, est. 2014)</t>
+        </is>
+      </c>
+      <c r="H471" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/eloise-wakeford-981460138; linkedin.com/company/county-carers-ltd</t>
+        </is>
+      </c>
+      <c r="I471" s="3" t="inlineStr"/>
+      <c r="J471" s="3" t="inlineStr">
+        <is>
+          <t>11-year care provider serving 100+ clients, founded by a CQC-registered manager since age 19; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L471" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M471" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N471" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O471" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; young-founder credibility story</t>
+        </is>
+      </c>
+      <c r="P471" s="3" t="inlineStr">
+        <is>
+          <t>Founder's early-CQC-registration story not yet the AI-cited trust signal for 'care provider Berkshire'</t>
+        </is>
+      </c>
+      <c r="Q471" s="3" t="inlineStr">
+        <is>
+          <t>'CQC-registered at 19, now serving 100+ families - own that exact AEO founder story'</t>
+        </is>
+      </c>
+      <c r="R471" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S471" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T471" s="3" t="inlineStr">
+        <is>
+          <t>Distinct from similarly-named 'County Care Berkshire Ltd' - do not conflate</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T448"/>
+  <autoFilter ref="A1:T471"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39508,7 +41656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -39528,7 +41676,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>447</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5">
@@ -39831,17 +41979,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Home care agency</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -39851,7 +41999,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -39861,7 +42009,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -39871,7 +42019,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -39881,7 +42029,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -39891,7 +42039,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -39901,7 +42049,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -39911,7 +42059,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -39921,7 +42069,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -39931,7 +42079,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -39941,7 +42089,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -39951,7 +42099,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -39961,7 +42109,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -39971,7 +42119,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -39981,7 +42129,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -39991,7 +42139,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -40001,7 +42149,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -40011,7 +42159,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -40021,7 +42169,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -40031,7 +42179,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Private GP practice</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -40041,7 +42189,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Aesthetics clinic (non-surgical)</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -40051,7 +42199,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Driving school &amp; ADI instructor training</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -40061,7 +42209,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Veterinary practice</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -40071,37 +42219,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Reformer Pilates studio</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Home care &amp; live-in care agency</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -40111,7 +42259,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -40121,7 +42269,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -40131,7 +42279,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -40141,7 +42289,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -40151,7 +42299,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -40161,7 +42309,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -40171,7 +42319,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -40181,7 +42329,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -40191,7 +42339,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -40201,7 +42349,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -40211,7 +42359,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -40221,7 +42369,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -40231,7 +42379,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -40241,7 +42389,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -40251,7 +42399,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -40261,7 +42409,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -40271,7 +42419,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -40281,7 +42429,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -40291,7 +42439,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -40301,7 +42449,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -40311,7 +42459,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -40321,7 +42469,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -40331,7 +42479,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -40341,7 +42489,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -40351,7 +42499,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -40361,7 +42509,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -40371,7 +42519,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -40381,7 +42529,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -40391,7 +42539,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -40401,7 +42549,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -40411,7 +42559,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -40421,7 +42569,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -40431,7 +42579,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -40441,7 +42589,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -40451,7 +42599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -40461,7 +42609,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -40471,7 +42619,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -40481,7 +42629,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -40491,7 +42639,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -40501,7 +42649,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -40511,7 +42659,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -40521,7 +42669,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -40531,7 +42679,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -40541,7 +42689,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -40551,7 +42699,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -40561,7 +42709,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -40571,7 +42719,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -40581,7 +42729,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -40591,7 +42739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -40601,7 +42749,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -40611,7 +42759,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -40621,7 +42769,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -40631,7 +42779,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -40641,7 +42789,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -40651,7 +42799,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -40661,7 +42809,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -40671,7 +42819,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -40681,7 +42829,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -40691,7 +42839,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -40701,7 +42849,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -40711,7 +42859,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -40721,7 +42869,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -40731,7 +42879,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -40741,7 +42889,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -40751,7 +42899,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -40761,7 +42909,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -40771,7 +42919,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -40781,7 +42929,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -40791,7 +42939,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -40801,7 +42949,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -40811,7 +42959,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -40821,7 +42969,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -40831,7 +42979,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -40841,7 +42989,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -40851,7 +42999,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -40861,7 +43009,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -40871,7 +43019,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -40881,7 +43029,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -40891,7 +43039,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -40901,7 +43049,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -40911,7 +43059,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -40921,7 +43069,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -40931,7 +43079,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -40941,7 +43089,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -40951,7 +43099,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -40961,7 +43109,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -40971,7 +43119,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -40981,7 +43129,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -40991,7 +43139,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -41001,7 +43149,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -41011,7 +43159,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -41021,7 +43169,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -41031,7 +43179,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -41041,7 +43189,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -41051,7 +43199,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -41061,7 +43209,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -41071,7 +43219,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -41081,7 +43229,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -41091,7 +43239,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -41101,7 +43249,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -41111,7 +43259,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -41121,7 +43269,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -41131,7 +43279,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -41141,7 +43289,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -41151,7 +43299,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -41161,7 +43309,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -41171,7 +43319,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -41181,7 +43329,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -41191,7 +43339,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Beauty/aesthetics training academy</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -41201,7 +43349,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Creative &amp; marketing recruitment agency</t>
+          <t>Beauty/hair training academy</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -41211,7 +43359,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Private dermatology &amp; women's health clinics</t>
+          <t>Medical aesthetics/injectable training academy</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -41221,7 +43369,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Private dermatology practice</t>
+          <t>Yoga teacher training school</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -41231,7 +43379,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Estate &amp; lettings agent</t>
+          <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -41241,7 +43389,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Wedding venue (converted barn)</t>
+          <t>Private dermatology &amp; women's health clinics</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -41251,7 +43399,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Wedding venue (waterside barn &amp; estate)</t>
+          <t>Private dermatology practice</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -41261,7 +43409,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Wedding venue (thatched barn on working farm)</t>
+          <t>Estate &amp; lettings agent</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -41271,7 +43419,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Wedding venue (working farm)</t>
+          <t>Wedding venue (converted barn)</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -41281,7 +43429,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Wedding venue (restored historic barn)</t>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -41291,7 +43439,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Chartered IFA / wealth management</t>
+          <t>Wedding venue (thatched barn on working farm)</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -41301,7 +43449,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Independent mortgage broker</t>
+          <t>Wedding venue (working farm)</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -41311,7 +43459,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Independent financial planning</t>
+          <t>Wedding venue (restored historic barn)</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -41321,7 +43469,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Chartered independent financial planners</t>
+          <t>Chartered IFA / wealth management</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -41331,7 +43479,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Veterinary practice (small independent group)</t>
+          <t>Independent mortgage broker</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -41341,7 +43489,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, family, private client)</t>
+          <t>Independent financial planning</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -41351,7 +43499,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, private client)</t>
+          <t>Chartered independent financial planners</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -41361,7 +43509,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Conveyancing solicitors</t>
+          <t>Veterinary practice (small independent group)</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -41371,7 +43519,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Law firm (residential &amp; commercial property)</t>
+          <t>Law firm (conveyancing, family, private client)</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -41381,10 +43529,200 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>Law firm (conveyancing, private client)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Conveyancing solicitors</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Law firm (residential &amp; commercial property)</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>Law firm (conveyancing, private client, family)</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Solar &amp; heat pump installer</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Solar PV &amp; electrical installer</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Heat pump &amp; EV charger installer</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Solar PV &amp; EV charger installer</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Electrical contractor &amp; solar installer</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Solar PV installer</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Classical Pilates studio</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Pilates &amp; yoga studio (+ teacher training)</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Women-only strength &amp; personal training studio</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Immigration &amp; commercial law firm</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Immigration law firm (UK/US)</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Private client law firm (wills, trusts, estates)</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Private wealth &amp; estate planning law firm</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Private wealth law firm (UHNW)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Residential &amp; domiciliary care provider</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$492</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T471"/>
+  <dimension ref="A1:T492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -41644,8 +41644,1984 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="4" t="inlineStr">
+        <is>
+          <t>Byrne's Tuition (Islington Maths &amp; English)</t>
+        </is>
+      </c>
+      <c r="B472" s="4" t="inlineStr">
+        <is>
+          <t>Private tuition (primary/11+)</t>
+        </is>
+      </c>
+      <c r="C472" s="4" t="inlineStr">
+        <is>
+          <t>Islington, North London</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>https://www.islingtonmathsandenglish.co.uk</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>denisegbyrne@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>07949 669275</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>Denise Byrne (Founder, PGCE Primary &amp; English, est. 2008)</t>
+        </is>
+      </c>
+      <c r="H472" s="4" t="inlineStr"/>
+      <c r="I472" s="4" t="inlineStr"/>
+      <c r="J472" s="4" t="inlineStr">
+        <is>
+          <t>17-year sole-practitioner tutor with 26+ years' teaching experience; per-session tuition fees recur weekly across a family's school years</t>
+        </is>
+      </c>
+      <c r="K472" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L472" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M472" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N472" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O472" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P472" s="4" t="inlineStr">
+        <is>
+          <t>No website polish/social presence - relies entirely on word-of-mouth and testimonials</t>
+        </is>
+      </c>
+      <c r="Q472" s="4" t="inlineStr">
+        <is>
+          <t>'26 years of trusted local tutoring - let's build the AEO presence to match your reputation'</t>
+        </is>
+      </c>
+      <c r="R472" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S472" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T472" s="4" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Into The Woods Outdoor Nursery</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 'Forest School' nursery</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>Highgate &amp; Hampstead Heath, North London</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intothewoodsnursery.co.uk</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr"/>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Emma Shaw (Founder, ex-primary teacher)</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/into-the-woods-outdoor-nursery-ltd</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/intothewoodsnursery; instagram.com/intothewoodsnursery</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>North London's first full-time outdoor 'Forest School' nursery concept, Ofsted-registered; nursery fees run into thousands per year per child</t>
+        </is>
+      </c>
+      <c r="K473" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N473" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook/Instagram presence = active marketing</t>
+        </is>
+      </c>
+      <c r="P473" s="2" t="inlineStr">
+        <is>
+          <t>Genuinely unique 'first outdoor nursery' positioning not yet the AI-cited answer for 'outdoor nursery North London'</t>
+        </is>
+      </c>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>'North London's first outdoor nursery - own that exact AEO category-creator positioning'</t>
+        </is>
+      </c>
+      <c r="R473" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S473" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>Genuine category-first positioning - strong AEO differentiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="3" t="inlineStr">
+        <is>
+          <t>Shapes Day Nurseries</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>Day nursery group (3 sites)</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>Reigate, Epsom &amp; Banstead, Surrey</t>
+        </is>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shapesdaynursery.co.uk</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F474" s="3" t="inlineStr">
+        <is>
+          <t>01737 221441</t>
+        </is>
+      </c>
+      <c r="G474" s="3" t="inlineStr">
+        <is>
+          <t>Owner-operated (started in childcare aged 16); verify name via Companies House #07450220</t>
+        </is>
+      </c>
+      <c r="H474" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/shapes-day-nurseries-ltd</t>
+        </is>
+      </c>
+      <c r="I474" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/shapesdaynurseriesltd; instagram.com/shapesdaynurseriesltd</t>
+        </is>
+      </c>
+      <c r="J474" s="3" t="inlineStr">
+        <is>
+          <t>Independently owned 3-site nursery group personally run by its founder; nursery fees run into thousands per year per child across 3 locations</t>
+        </is>
+      </c>
+      <c r="K474" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L474" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M474" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N474" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O474" s="3" t="inlineStr">
+        <is>
+          <t>Multi-channel social presence = active marketing investment</t>
+        </is>
+      </c>
+      <c r="P474" s="3" t="inlineStr">
+        <is>
+          <t>3-site footprint not matched by 3-location AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q474" s="3" t="inlineStr">
+        <is>
+          <t>Per-site AEO content to own Reigate/Epsom/Banstead 'nursery near me' searches separately</t>
+        </is>
+      </c>
+      <c r="R474" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S474" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T474" s="3" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="4" t="inlineStr">
+        <is>
+          <t>Eden Tutors</t>
+        </is>
+      </c>
+      <c r="B475" s="4" t="inlineStr">
+        <is>
+          <t>Private tuition (primary/11+)</t>
+        </is>
+      </c>
+      <c r="C475" s="4" t="inlineStr">
+        <is>
+          <t>Virginia Water, Surrey (Ascot/Windsor border)</t>
+        </is>
+      </c>
+      <c r="D475" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eden-tutors.co.uk</t>
+        </is>
+      </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F475" s="4" t="inlineStr">
+        <is>
+          <t>01344 508077</t>
+        </is>
+      </c>
+      <c r="G475" s="4" t="inlineStr">
+        <is>
+          <t>Hannah Nuthall &amp; Rebecca Nuthall (Sister co-founders, both PGCE/QTS)</t>
+        </is>
+      </c>
+      <c r="H475" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/eden-tutors</t>
+        </is>
+      </c>
+      <c r="I475" s="4" t="inlineStr"/>
+      <c r="J475" s="4" t="inlineStr">
+        <is>
+          <t>Sister-founded tutoring practice covering the Virginia Water/Ascot/Windsor corridor; per-session tuition fees recur weekly across a family's school years, especially around 11+ exams</t>
+        </is>
+      </c>
+      <c r="K475" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L475" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M475" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N475" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O475" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P475" s="4" t="inlineStr">
+        <is>
+          <t>11+ exam-prep demand in a wealthy catchment not yet the AI-cited answer for this practice</t>
+        </is>
+      </c>
+      <c r="Q475" s="4" t="inlineStr">
+        <is>
+          <t>'Own the AI-cited answer for 11+ tutoring in the Ascot/Virginia Water corridor'</t>
+        </is>
+      </c>
+      <c r="R475" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S475" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T475" s="4" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Archfield House Nursery</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>Day nursery &amp; pre-school</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>Cotham, Bristol</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.archfieldhousenursery.co.uk</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>accounts@archfieldhousenursery.co.uk</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>0117 942 2120</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Rebecca Clevett (Nursery Head); privately owned since 1986</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr"/>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/archfieldhousenursery; instagram.com/archfieldhousenursery</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>Nearly 40-year Ofsted Outstanding-rated independent Bristol nursery; nursery fees run into thousands per year per child</t>
+        </is>
+      </c>
+      <c r="K476" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram presence; Ofsted Outstanding rating; 39-year heritage</t>
+        </is>
+      </c>
+      <c r="P476" s="2" t="inlineStr">
+        <is>
+          <t>39-year heritage and Outstanding Ofsted rating not yet the AI-cited answer for 'nursery Bristol'</t>
+        </is>
+      </c>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>'Ofsted Outstanding for nearly 40 years - own that exact AEO trust signal in Bristol'</t>
+        </is>
+      </c>
+      <c r="R476" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr">
+        <is>
+          <t>Ofsted Outstanding + 39-year heritage - strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>MLP Wealth</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>IFA / wealth management</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>Banstead, Surrey</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mlpwealth.co.uk</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>info@mlpwealth.co.uk</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>020 8296 1799</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Paul Standerwick &amp; Seán Standerwick (2nd-generation, father Paolo founded 1983)</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/seanstanderwick</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/MLPWealth</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>42-year family-run Chartered IFA, featured in FT Adviser Top 50 Boutique Advisers and VouchedFor Top Rated Guide every year since inception; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K477" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N477" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O477" s="2" t="inlineStr">
+        <is>
+          <t>Facebook presence; FT Adviser Top 50 + VouchedFor recognition every year since 1983</t>
+        </is>
+      </c>
+      <c r="P477" s="2" t="inlineStr">
+        <is>
+          <t>Consistent multi-decade press recognition not yet the AI-cited answer for 'IFA Banstead'</t>
+        </is>
+      </c>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>'FT Adviser Top 50 every year since 1983 - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R477" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional consistent-recognition heritage - strong AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>GPFM (Gerald Pepper Financial Management)</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Chartered lifestyle financial planning</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>Hertford, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gpfm.co.uk</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@gpfm.co.uk</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>01992 500 261</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Simon Frost &amp; Scott Atkinson (Co-Managing Directors)</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/gp-financial-management</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/gpfmfinancial</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>Chartered 'lifestyle financial planning' firm voted #1 Boutique Adviser in FT Adviser Top 50, won VouchedFor Client Trust Award 2025; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr">
+        <is>
+          <t>Facebook presence; #1 Boutique Adviser ranking + 2025 award win</t>
+        </is>
+      </c>
+      <c r="P478" s="2" t="inlineStr">
+        <is>
+          <t>#1 ranking and recent award not yet the AI-cited trust signal for 'financial planner Hertford'</t>
+        </is>
+      </c>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>'Voted #1 Boutique Adviser in the UK - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr">
+        <is>
+          <t>#1 national ranking + 2025 award - exceptional AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="3" t="inlineStr">
+        <is>
+          <t>Jane Smith Financial Planning</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>Chartered independent financial planning</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>Olney, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>https://www.janesmithfinancial.com</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="inlineStr">
+        <is>
+          <t>info@janesmithfinancial.com</t>
+        </is>
+      </c>
+      <c r="F479" s="3" t="inlineStr">
+        <is>
+          <t>01234 713131</t>
+        </is>
+      </c>
+      <c r="G479" s="3" t="inlineStr">
+        <is>
+          <t>Nicola Watts (Director, 2nd-generation; founded 1994 by mother Jane Smith)</t>
+        </is>
+      </c>
+      <c r="H479" s="3" t="inlineStr"/>
+      <c r="I479" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/IFAinOlney</t>
+        </is>
+      </c>
+      <c r="J479" s="3" t="inlineStr">
+        <is>
+          <t>31-year two-generation family Chartered IFA practice; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K479" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L479" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M479" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N479" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O479" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; Chartered/Accredited status</t>
+        </is>
+      </c>
+      <c r="P479" s="3" t="inlineStr">
+        <is>
+          <t>31-year family heritage not yet the AI-cited answer for 'financial planner Olney'</t>
+        </is>
+      </c>
+      <c r="Q479" s="3" t="inlineStr">
+        <is>
+          <t>'Two generations of Chartered financial planning in Olney - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R479" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S479" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T479" s="3" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>Financial Planning Partners (FPP)</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>Independent Chartered financial planning</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>Crowthorne, Berkshire</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fpp-ifa.co.uk</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>info@fpp-ifa.co.uk</t>
+        </is>
+      </c>
+      <c r="F480" s="3" t="inlineStr">
+        <is>
+          <t>01344 778990</t>
+        </is>
+      </c>
+      <c r="G480" s="3" t="inlineStr">
+        <is>
+          <t>David Hearne (CISI 'CFP Professional of the Year' 2022) &amp; Andrew Hearne (Chartered Financial Planner)</t>
+        </is>
+      </c>
+      <c r="H480" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/davidjhearne; linkedin.com/company/financial-planning-partners-ltd</t>
+        </is>
+      </c>
+      <c r="I480" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/fppifa</t>
+        </is>
+      </c>
+      <c r="J480" s="3" t="inlineStr">
+        <is>
+          <t>Chartered wealth-management firm led by a national award-winning adviser; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L480" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M480" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N480" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O480" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; CISI national award win (2022)</t>
+        </is>
+      </c>
+      <c r="P480" s="3" t="inlineStr">
+        <is>
+          <t>National award win not yet the AI-cited trust signal for 'financial planner Berkshire'</t>
+        </is>
+      </c>
+      <c r="Q480" s="3" t="inlineStr">
+        <is>
+          <t>'CFP Professional of the Year 2022 - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R480" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S480" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T480" s="3" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="inlineStr">
+        <is>
+          <t>Chapters Financial</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>Independent Chartered financial planning</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chaptersfinancial.com</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
+          <t>info@chaptersfinancial.com</t>
+        </is>
+      </c>
+      <c r="F481" s="3" t="inlineStr">
+        <is>
+          <t>01483 578 800</t>
+        </is>
+      </c>
+      <c r="G481" s="3" t="inlineStr">
+        <is>
+          <t>Keith Churchouse (Director, CFP) with Esther Dadswell &amp; Vicky Fulcher</t>
+        </is>
+      </c>
+      <c r="H481" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/chapters-financial-limited</t>
+        </is>
+      </c>
+      <c r="I481" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/chaptersfinancial</t>
+        </is>
+      </c>
+      <c r="J481" s="3" t="inlineStr">
+        <is>
+          <t>20-year Chartered financial planning firm serving Surrey/South East individuals; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L481" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M481" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N481" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O481" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; 20-year client-service milestone (2024)</t>
+        </is>
+      </c>
+      <c r="P481" s="3" t="inlineStr">
+        <is>
+          <t>20-year milestone not yet the AI-cited answer for 'financial planner Guildford'</t>
+        </is>
+      </c>
+      <c r="Q481" s="3" t="inlineStr">
+        <is>
+          <t>'20 years of client service in Guildford - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R481" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S481" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T481" s="3" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>Dial A Geek</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>IT support &amp; managed services (MSP)</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dialageek.co.uk</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>dialageek2018@gmail.com</t>
+        </is>
+      </c>
+      <c r="F482" s="3" t="inlineStr">
+        <is>
+          <t>0117 369 4335</t>
+        </is>
+      </c>
+      <c r="G482" s="3" t="inlineStr">
+        <is>
+          <t>Gildas Jones ('Chief Geek', Founder, est. 2006)</t>
+        </is>
+      </c>
+      <c r="H482" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/dialageek</t>
+        </is>
+      </c>
+      <c r="I482" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/dialageek</t>
+        </is>
+      </c>
+      <c r="J482" s="3" t="inlineStr">
+        <is>
+          <t>18-year founder-led Bristol MSP serving 1,000+ businesses with IT support/cyber security/managed AI services; monthly support contracts recur across all clients</t>
+        </is>
+      </c>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L482" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M482" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N482" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O482" s="3" t="inlineStr">
+        <is>
+          <t>Facebook/LinkedIn presence; press coverage (Bristol247 18th-anniversary feature)</t>
+        </is>
+      </c>
+      <c r="P482" s="3" t="inlineStr">
+        <is>
+          <t>18-year milestone and press coverage not yet the AI-cited answer for 'IT support Bristol'</t>
+        </is>
+      </c>
+      <c r="Q482" s="3" t="inlineStr">
+        <is>
+          <t>'18 years, 1,000+ businesses helped - own that exact AEO trust signal in Bristol IT support'</t>
+        </is>
+      </c>
+      <c r="R482" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S482" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T482" s="3" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr">
+        <is>
+          <t>Business Control</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>Outsourced finance &amp; business consultancy</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>Odd Down, Bath</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>https://www.businesscontrol.co.uk</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>hello@businesscontrol.co.uk</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>01225 840538</t>
+        </is>
+      </c>
+      <c r="G483" s="3" t="inlineStr">
+        <is>
+          <t>Richard Starkey ACMA (Founder/Managing Director, est. 1990)</t>
+        </is>
+      </c>
+      <c r="H483" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/businesscontrol</t>
+        </is>
+      </c>
+      <c r="I483" s="3" t="inlineStr"/>
+      <c r="J483" s="3" t="inlineStr">
+        <is>
+          <t>36-year Bath outsourced-finance consultancy for SMEs and start-ups; monthly retained finance/consultancy fees recur across a client's growth</t>
+        </is>
+      </c>
+      <c r="K483" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L483" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M483" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N483" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O483" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 36-year trading history; strong client testimonials</t>
+        </is>
+      </c>
+      <c r="P483" s="3" t="inlineStr">
+        <is>
+          <t>36-year heritage not yet the AI-cited answer for 'outsourced finance Bath'</t>
+        </is>
+      </c>
+      <c r="Q483" s="3" t="inlineStr">
+        <is>
+          <t>'36 years as Bath's outsourced finance team - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R483" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S483" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T483" s="3" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>Oscura</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>IT support, hosting &amp; web development (MSP)</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oscura.co.uk</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>support@oscura.co.uk</t>
+        </is>
+      </c>
+      <c r="F484" s="3" t="inlineStr">
+        <is>
+          <t>0118 959 7600</t>
+        </is>
+      </c>
+      <c r="G484" s="3" t="inlineStr">
+        <is>
+          <t>Stephen John Leitch &amp; Graham Andrew Loader (Directors, ISP roots to 1997)</t>
+        </is>
+      </c>
+      <c r="H484" s="3" t="inlineStr"/>
+      <c r="I484" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/oscuraltd</t>
+        </is>
+      </c>
+      <c r="J484" s="3" t="inlineStr">
+        <is>
+          <t>28-year Reading IT/hosting/web MSP with a low digital footprint (29 LinkedIn followers) despite deep trading history - strong SEO/AEO upside; monthly support/hosting contracts recur</t>
+        </is>
+      </c>
+      <c r="K484" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L484" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M484" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N484" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O484" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; long trading history but thin digital marketing</t>
+        </is>
+      </c>
+      <c r="P484" s="3" t="inlineStr">
+        <is>
+          <t>Low digital footprint despite 28 years trading = clear AEO upside opportunity</t>
+        </is>
+      </c>
+      <c r="Q484" s="3" t="inlineStr">
+        <is>
+          <t>'28 years trading but almost invisible online - massive AEO upside waiting to be unlocked'</t>
+        </is>
+      </c>
+      <c r="R484" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S484" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T484" s="3" t="inlineStr">
+        <is>
+          <t>Low online footprint despite long heritage = strong AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="inlineStr">
+        <is>
+          <t>Oxford IT Solutions</t>
+        </is>
+      </c>
+      <c r="B485" s="4" t="inlineStr">
+        <is>
+          <t>IT support (MSP)</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
+        <is>
+          <t>Kidlington, Oxford</t>
+        </is>
+      </c>
+      <c r="D485" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oxforditsolutions.com</t>
+        </is>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>hello@oxforditsolutions.com</t>
+        </is>
+      </c>
+      <c r="F485" s="4" t="inlineStr">
+        <is>
+          <t>01865 364995</t>
+        </is>
+      </c>
+      <c r="G485" s="4" t="inlineStr">
+        <is>
+          <t>Rob Williams (Founder, running with wife Jenny since 2010)</t>
+        </is>
+      </c>
+      <c r="H485" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/rob-williams-873b2412; linkedin.com/company/oxford-it-solutions</t>
+        </is>
+      </c>
+      <c r="I485" s="4" t="inlineStr"/>
+      <c r="J485" s="4" t="inlineStr">
+        <is>
+          <t>15-year husband-and-wife-run MSP serving 450+ clients (SMEs, schools, home users) with a Cyber Essentials focus; monthly support contracts recur</t>
+        </is>
+      </c>
+      <c r="K485" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L485" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M485" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N485" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O485" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 450+ clients served</t>
+        </is>
+      </c>
+      <c r="P485" s="4" t="inlineStr">
+        <is>
+          <t>450+ clients served not yet the AI-cited trust signal for 'IT support Oxford'</t>
+        </is>
+      </c>
+      <c r="Q485" s="4" t="inlineStr">
+        <is>
+          <t>'450+ clients trust us with their IT - own that exact AEO trust signal in Oxford'</t>
+        </is>
+      </c>
+      <c r="R485" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S485" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T485" s="4" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="inlineStr">
+        <is>
+          <t>Jo Richings Business &amp; Executive Coaching</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>Executive coaching &amp; leadership training</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jorichings.com</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>jo@jorichings.co.uk</t>
+        </is>
+      </c>
+      <c r="F486" s="3" t="inlineStr">
+        <is>
+          <t>07813 963523</t>
+        </is>
+      </c>
+      <c r="G486" s="3" t="inlineStr">
+        <is>
+          <t>Jo Richings (Founder)</t>
+        </is>
+      </c>
+      <c r="H486" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jorichingsbusinesscoach</t>
+        </is>
+      </c>
+      <c r="I486" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/jorichings2018</t>
+        </is>
+      </c>
+      <c r="J486" s="3" t="inlineStr">
+        <is>
+          <t>Solo executive/leadership coach who also runs a training arm with ~18 associate trainers and founded the 3,000+ member Bristol Small Business Network; corporate coaching/training retainers recur</t>
+        </is>
+      </c>
+      <c r="K486" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L486" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M486" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N486" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O486" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; founded a 3,000+ member local business network</t>
+        </is>
+      </c>
+      <c r="P486" s="3" t="inlineStr">
+        <is>
+          <t>Community-builder reputation (3,000+ member network) not yet the AI-cited trust signal for 'business coach Bristol'</t>
+        </is>
+      </c>
+      <c r="Q486" s="3" t="inlineStr">
+        <is>
+          <t>'Founded Bristol's 3,000+ member Small Business Network - own that exact AEO community-trust signal'</t>
+        </is>
+      </c>
+      <c r="R486" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S486" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T486" s="3" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="3" t="inlineStr">
+        <is>
+          <t>Cotswold Lime Works</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>Lime plastering/render conservation specialist</t>
+        </is>
+      </c>
+      <c r="C487" s="3" t="inlineStr">
+        <is>
+          <t>Coln St Aldwyns/Aldsworth, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cotswoldlimeworks.co.uk</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F487" s="3" t="inlineStr">
+        <is>
+          <t>07944 746947</t>
+        </is>
+      </c>
+      <c r="G487" s="3" t="inlineStr">
+        <is>
+          <t>Callum David (Owner)</t>
+        </is>
+      </c>
+      <c r="H487" s="3" t="inlineStr"/>
+      <c r="I487" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/cotswoldlimework; facebook.com/cotswoldlime</t>
+        </is>
+      </c>
+      <c r="J487" s="3" t="inlineStr">
+        <is>
+          <t>12-year sole-trader conservation lime plasterer with Grade I/II listed-building project experience (churches, manor houses, schools); project fees run into thousands each</t>
+        </is>
+      </c>
+      <c r="K487" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L487" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M487" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N487" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O487" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P487" s="3" t="inlineStr">
+        <is>
+          <t>Grade I/II listed-building project portfolio not yet the AI-cited answer for 'lime plasterer Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q487" s="3" t="inlineStr">
+        <is>
+          <t>'Trusted on Grade I listed churches and manor houses - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R487" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S487" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T487" s="3" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>Lime Plasterers</t>
+        </is>
+      </c>
+      <c r="B488" s="4" t="inlineStr">
+        <is>
+          <t>Lime plastering &amp; traditional render specialist</t>
+        </is>
+      </c>
+      <c r="C488" s="4" t="inlineStr">
+        <is>
+          <t>Benhall, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lime-plasterers.co.uk</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F488" s="4" t="inlineStr">
+        <is>
+          <t>01242 701237</t>
+        </is>
+      </c>
+      <c r="G488" s="4" t="inlineStr">
+        <is>
+          <t>Thomas Campbell (Contact); team with 50+ years combined experience</t>
+        </is>
+      </c>
+      <c r="H488" s="4" t="inlineStr"/>
+      <c r="I488" s="4" t="inlineStr"/>
+      <c r="J488" s="4" t="inlineStr">
+        <is>
+          <t>Small skilled team focused on Cheltenham/Cotswolds heritage-property lime plastering and pointing; project fees run into thousands each</t>
+        </is>
+      </c>
+      <c r="K488" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L488" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M488" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N488" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O488" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P488" s="4" t="inlineStr">
+        <is>
+          <t>50+ years combined experience not yet the AI-cited answer for 'lime plasterer Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q488" s="4" t="inlineStr">
+        <is>
+          <t>'50+ years of combined heritage-plastering experience - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R488" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S488" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T488" s="4" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Bath Bespoke</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>Sash window manufacture &amp; restoration</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>Winsley, nr Bath</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bathbespoke.co.uk</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>01225 920900</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>James Etheridge &amp; Tom Jones-Marquez (Founders, est. 2009)</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/bath-bespoke-limited</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr"/>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>15-year bespoke sash-window joinery firm with Royal Crescent project experience and up to 50-year timber guarantees; project fees run into thousands per property</t>
+        </is>
+      </c>
+      <c r="K489" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M489" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N489" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O489" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; Royal Crescent project credential; 50-year guarantee marketing</t>
+        </is>
+      </c>
+      <c r="P489" s="2" t="inlineStr">
+        <is>
+          <t>Royal Crescent project credential not yet the AI-cited answer for 'sash window restoration Bath'</t>
+        </is>
+      </c>
+      <c r="Q489" s="2" t="inlineStr">
+        <is>
+          <t>'Restored windows on the Royal Crescent - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R489" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S489" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T489" s="2" t="inlineStr">
+        <is>
+          <t>Royal Crescent project credential - exceptional AEO hook for Bath heritage market</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="inlineStr">
+        <is>
+          <t>K Pitman Joinery</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>Bespoke joinery (sash windows, doors, cabinetry)</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>Norton St Philip, nr Bath</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kpitmanjoinery.co.uk</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@kpitmanjoinery.co.uk</t>
+        </is>
+      </c>
+      <c r="F490" s="3" t="inlineStr">
+        <is>
+          <t>01373 384742</t>
+        </is>
+      </c>
+      <c r="G490" s="3" t="inlineStr">
+        <is>
+          <t>Ken Pitman (Founder, est. 1968) &amp; Andrew Pitman (2nd generation)</t>
+        </is>
+      </c>
+      <c r="H490" s="3" t="inlineStr"/>
+      <c r="I490" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/kpitmanjoinery</t>
+        </is>
+      </c>
+      <c r="J490" s="3" t="inlineStr">
+        <is>
+          <t>57-year two-generation family joinery workshop serving Bath/Frome/South West; project fees run into thousands per property</t>
+        </is>
+      </c>
+      <c r="K490" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L490" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M490" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N490" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O490" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 57-year trading history</t>
+        </is>
+      </c>
+      <c r="P490" s="3" t="inlineStr">
+        <is>
+          <t>57-year family heritage not yet the AI-cited answer for 'bespoke joinery Bath'</t>
+        </is>
+      </c>
+      <c r="Q490" s="3" t="inlineStr">
+        <is>
+          <t>'57 years of family joinery craftsmanship - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R490" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S490" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T490" s="3" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="inlineStr">
+        <is>
+          <t>Simon Watts Joinery</t>
+        </is>
+      </c>
+      <c r="B491" s="4" t="inlineStr">
+        <is>
+          <t>Bespoke joinery for listed/conservation buildings</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>Evesham, Vale of Evesham (edge of Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D491" s="4" t="inlineStr">
+        <is>
+          <t>https://www.simonwattsjoinery.com</t>
+        </is>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>info@simonwattsjoinery.com</t>
+        </is>
+      </c>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>01386 765429</t>
+        </is>
+      </c>
+      <c r="G491" s="4" t="inlineStr">
+        <is>
+          <t>Dan &amp; Lyndsey Gregory (Successors, continuing founder Simon Watts's legacy since his 2021 passing)</t>
+        </is>
+      </c>
+      <c r="H491" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/simon-watts-joinery-limited</t>
+        </is>
+      </c>
+      <c r="I491" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/simonwattsjoinery</t>
+        </is>
+      </c>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>Listed-building/conservation-area joinery specialist with a strong continuity story across the Cotswolds; project fees run into thousands per property</t>
+        </is>
+      </c>
+      <c r="K491" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L491" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M491" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N491" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O491" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P491" s="4" t="inlineStr">
+        <is>
+          <t>Founder-legacy continuity story not yet the AI-cited trust signal for 'conservation joinery Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q491" s="4" t="inlineStr">
+        <is>
+          <t>'Carrying forward a founder's legacy of listed-building craftsmanship - own that AEO story'</t>
+        </is>
+      </c>
+      <c r="R491" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S491" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T491" s="4" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="inlineStr">
+        <is>
+          <t>J E Righton Builders</t>
+        </is>
+      </c>
+      <c r="B492" s="4" t="inlineStr">
+        <is>
+          <t>Conservation/heritage builder</t>
+        </is>
+      </c>
+      <c r="C492" s="4" t="inlineStr">
+        <is>
+          <t>Mickleton, Chipping Campden, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jebuildright.co.uk</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>01789 430240</t>
+        </is>
+      </c>
+      <c r="G492" s="4" t="inlineStr">
+        <is>
+          <t>James Righton (Founder, 20+ years hands-on experience, 30+ years firm history)</t>
+        </is>
+      </c>
+      <c r="H492" s="4" t="inlineStr"/>
+      <c r="I492" s="4" t="inlineStr"/>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>FMB member since 2012, NHBC-registered heritage builder specialising in sympathetic period/listed-property restoration across Chipping Campden/Broadway/Stow-on-the-Wold/Stratford; project fees run into tens of thousands each</t>
+        </is>
+      </c>
+      <c r="K492" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L492" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M492" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N492" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O492" s="4" t="inlineStr">
+        <is>
+          <t>FMB membership; NHBC registration</t>
+        </is>
+      </c>
+      <c r="P492" s="4" t="inlineStr">
+        <is>
+          <t>FMB/NHBC credentials not yet the AI-cited answer for 'heritage builder Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q492" s="4" t="inlineStr">
+        <is>
+          <t>'FMB member since 2012, NHBC-registered - own that exact AEO trust signal in the Cotswolds'</t>
+        </is>
+      </c>
+      <c r="R492" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S492" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T492" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T471"/>
+  <autoFilter ref="A1:T492"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41656,7 +43632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -41676,7 +43652,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>470</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5">
@@ -42079,7 +44055,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -42089,7 +44065,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -42099,7 +44075,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -42109,7 +44085,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -42119,7 +44095,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -42129,7 +44105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -42139,7 +44115,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -42149,7 +44125,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -42159,7 +44135,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -42169,7 +44145,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -42179,7 +44155,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -42189,7 +44165,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Private GP practice</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -42199,7 +44175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Aesthetics clinic (non-surgical)</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -42209,7 +44185,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Driving school &amp; ADI instructor training</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -42219,7 +44195,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Veterinary practice</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -42229,7 +44205,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Reformer Pilates studio</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -42239,7 +44215,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Home care &amp; live-in care agency</t>
+          <t>Reformer Pilates studio</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -42249,37 +44225,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Home care &amp; live-in care agency</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Private tuition (primary/11+)</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Independent Chartered financial planning</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -42289,7 +44265,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -42299,7 +44275,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -42309,7 +44285,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -42319,7 +44295,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -42329,7 +44305,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -42339,7 +44315,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -42349,7 +44325,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -42359,7 +44335,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -42369,7 +44345,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -42379,7 +44355,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -42389,7 +44365,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -42399,7 +44375,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -42409,7 +44385,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -42419,7 +44395,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -42429,7 +44405,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -42439,7 +44415,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -42449,7 +44425,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -42459,7 +44435,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -42469,7 +44445,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -42479,7 +44455,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -42489,7 +44465,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -42499,7 +44475,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -42509,7 +44485,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -42519,7 +44495,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -42529,7 +44505,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -42539,7 +44515,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -42549,7 +44525,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -42559,7 +44535,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -42569,7 +44545,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -42579,7 +44555,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -42589,7 +44565,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -42599,7 +44575,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -42609,7 +44585,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -42619,7 +44595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -42629,7 +44605,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -42639,7 +44615,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -42649,7 +44625,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -42659,7 +44635,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -42669,7 +44645,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -42679,7 +44655,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -42689,7 +44665,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -42699,7 +44675,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -42709,7 +44685,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -42719,7 +44695,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -42729,7 +44705,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -42739,7 +44715,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -42749,7 +44725,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -42759,7 +44735,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -42769,7 +44745,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -42779,7 +44755,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -42789,7 +44765,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -42799,7 +44775,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -42809,7 +44785,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -42819,7 +44795,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -42829,7 +44805,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -42839,7 +44815,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -42849,7 +44825,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -42859,7 +44835,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -42869,7 +44845,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -42879,7 +44855,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -42889,7 +44865,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -42899,7 +44875,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -42909,7 +44885,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -42919,7 +44895,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -42929,7 +44905,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -42939,7 +44915,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -42949,7 +44925,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -42959,7 +44935,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -42969,7 +44945,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -42979,7 +44955,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -42989,7 +44965,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -42999,7 +44975,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -43009,7 +44985,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -43019,7 +44995,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -43029,7 +45005,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -43039,7 +45015,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -43049,7 +45025,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -43059,7 +45035,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -43069,7 +45045,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -43079,7 +45055,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -43089,7 +45065,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -43099,7 +45075,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -43109,7 +45085,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -43119,7 +45095,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -43129,7 +45105,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -43139,7 +45115,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -43149,7 +45125,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -43159,7 +45135,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -43169,7 +45145,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -43179,7 +45155,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -43189,7 +45165,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -43199,7 +45175,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -43209,7 +45185,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -43219,7 +45195,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -43229,7 +45205,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -43239,7 +45215,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -43249,7 +45225,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -43259,7 +45235,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -43269,7 +45245,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -43279,7 +45255,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -43289,7 +45265,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -43299,7 +45275,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -43309,7 +45285,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -43319,7 +45295,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -43329,7 +45305,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -43339,7 +45315,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -43349,7 +45325,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -43359,7 +45335,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Beauty/aesthetics training academy</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -43369,7 +45345,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Beauty/hair training academy</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -43379,7 +45355,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Creative &amp; marketing recruitment agency</t>
+          <t>Medical aesthetics/injectable training academy</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -43389,7 +45365,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Private dermatology &amp; women's health clinics</t>
+          <t>Yoga teacher training school</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -43399,7 +45375,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Private dermatology practice</t>
+          <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -43409,7 +45385,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Estate &amp; lettings agent</t>
+          <t>Private dermatology &amp; women's health clinics</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -43419,7 +45395,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Wedding venue (converted barn)</t>
+          <t>Private dermatology practice</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -43429,7 +45405,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Wedding venue (waterside barn &amp; estate)</t>
+          <t>Estate &amp; lettings agent</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -43439,7 +45415,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Wedding venue (thatched barn on working farm)</t>
+          <t>Wedding venue (converted barn)</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -43449,7 +45425,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Wedding venue (working farm)</t>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -43459,7 +45435,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Wedding venue (restored historic barn)</t>
+          <t>Wedding venue (thatched barn on working farm)</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -43469,7 +45445,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Chartered IFA / wealth management</t>
+          <t>Wedding venue (working farm)</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -43479,7 +45455,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Independent mortgage broker</t>
+          <t>Wedding venue (restored historic barn)</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -43489,7 +45465,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Independent financial planning</t>
+          <t>Chartered IFA / wealth management</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -43499,7 +45475,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Chartered independent financial planners</t>
+          <t>Independent mortgage broker</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -43509,7 +45485,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Veterinary practice (small independent group)</t>
+          <t>Independent financial planning</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -43519,7 +45495,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, family, private client)</t>
+          <t>Chartered independent financial planners</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -43529,7 +45505,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, private client)</t>
+          <t>Veterinary practice (small independent group)</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -43539,7 +45515,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Conveyancing solicitors</t>
+          <t>Law firm (conveyancing, family, private client)</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -43549,7 +45525,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Law firm (residential &amp; commercial property)</t>
+          <t>Law firm (conveyancing, private client)</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -43559,7 +45535,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, private client, family)</t>
+          <t>Conveyancing solicitors</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -43569,7 +45545,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Solar &amp; heat pump installer</t>
+          <t>Law firm (residential &amp; commercial property)</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -43579,7 +45555,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Solar PV &amp; electrical installer</t>
+          <t>Law firm (conveyancing, private client, family)</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -43589,7 +45565,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Heat pump &amp; EV charger installer</t>
+          <t>Solar &amp; heat pump installer</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -43599,7 +45575,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Solar PV &amp; EV charger installer</t>
+          <t>Solar PV &amp; electrical installer</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -43609,7 +45585,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Electrical contractor &amp; solar installer</t>
+          <t>Heat pump &amp; EV charger installer</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -43619,7 +45595,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Solar PV installer</t>
+          <t>Solar PV &amp; EV charger installer</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -43629,7 +45605,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Classical Pilates studio</t>
+          <t>Electrical contractor &amp; solar installer</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -43639,7 +45615,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Pilates &amp; yoga studio (+ teacher training)</t>
+          <t>Solar PV installer</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -43649,7 +45625,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
+          <t>Classical Pilates studio</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -43659,7 +45635,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Women-only strength &amp; personal training studio</t>
+          <t>Pilates &amp; yoga studio (+ teacher training)</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -43669,7 +45645,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Immigration &amp; commercial law firm</t>
+          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -43679,7 +45655,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Immigration law firm (UK/US)</t>
+          <t>Women-only strength &amp; personal training studio</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -43689,7 +45665,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Private client law firm (wills, trusts, estates)</t>
+          <t>Immigration &amp; commercial law firm</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -43699,7 +45675,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Private wealth &amp; estate planning law firm</t>
+          <t>Immigration law firm (UK/US)</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -43709,7 +45685,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Private wealth law firm (UHNW)</t>
+          <t>Private client law firm (wills, trusts, estates)</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -43719,10 +45695,190 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Private wealth &amp; estate planning law firm</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Private wealth law firm (UHNW)</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>Residential &amp; domiciliary care provider</t>
         </is>
       </c>
-      <c r="B209" t="n">
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Outdoor 'Forest School' nursery</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Day nursery group (3 sites)</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Day nursery &amp; pre-school</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Chartered lifestyle financial planning</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Chartered independent financial planning</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>IT support &amp; managed services (MSP)</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Outsourced finance &amp; business consultancy</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>IT support, hosting &amp; web development (MSP)</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>IT support (MSP)</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Executive coaching &amp; leadership training</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Lime plastering/render conservation specialist</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Lime plastering &amp; traditional render specialist</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sash window manufacture &amp; restoration</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Bespoke joinery (sash windows, doors, cabinetry)</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Bespoke joinery for listed/conservation buildings</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Conservation/heritage builder</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$492</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$508</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T492"/>
+  <dimension ref="A1:T508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -43620,8 +43620,1460 @@
       </c>
       <c r="T492" s="4" t="inlineStr"/>
     </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>The Guildford Spine Centre</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>Chiropractic clinic</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>https://www.spinecentreguildford.co.uk</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>01483 808868</t>
+        </is>
+      </c>
+      <c r="G493" s="3" t="inlineStr">
+        <is>
+          <t>Alex Symington (Founder, est. 2014)</t>
+        </is>
+      </c>
+      <c r="H493" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/alex-spinecentreguildford-3192a5290</t>
+        </is>
+      </c>
+      <c r="I493" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/guildfordspinecentre</t>
+        </is>
+      </c>
+      <c r="J493" s="3" t="inlineStr">
+        <is>
+          <t>11-year independent chiropractic clinic founded by a former busy London practitioner; private treatment packages worth hundreds to thousands per patient</t>
+        </is>
+      </c>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L493" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M493" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N493" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O493" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram presence; 11-year trading history</t>
+        </is>
+      </c>
+      <c r="P493" s="3" t="inlineStr">
+        <is>
+          <t>11-year heritage not yet the AI-cited answer for 'chiropractor Guildford'</t>
+        </is>
+      </c>
+      <c r="Q493" s="3" t="inlineStr">
+        <is>
+          <t>'From a busy London practice to Guildford's trusted chiropractor - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R493" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S493" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T493" s="3" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="3" t="inlineStr">
+        <is>
+          <t>The Atman Clinic</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>Southborough, Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D494" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atmanclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E494" s="3" t="inlineStr">
+        <is>
+          <t>info@atmanclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="F494" s="3" t="inlineStr">
+        <is>
+          <t>01892 544 783</t>
+        </is>
+      </c>
+      <c r="G494" s="3" t="inlineStr">
+        <is>
+          <t>Geoffrey Montague-Smith D.O. (Founder, est. 1994)</t>
+        </is>
+      </c>
+      <c r="H494" s="3" t="inlineStr"/>
+      <c r="I494" s="3" t="inlineStr"/>
+      <c r="J494" s="3" t="inlineStr">
+        <is>
+          <t>31-year established osteopathy clinic offering structural/cranial osteopathy and sports injury treatment; private treatment packages worth hundreds to thousands per patient</t>
+        </is>
+      </c>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L494" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M494" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N494" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O494" s="3" t="inlineStr">
+        <is>
+          <t>31-year trading history</t>
+        </is>
+      </c>
+      <c r="P494" s="3" t="inlineStr">
+        <is>
+          <t>31-year heritage not yet the AI-cited answer for 'osteopath Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q494" s="3" t="inlineStr">
+        <is>
+          <t>'31 years of osteopathic care in Tunbridge Wells - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R494" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S494" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T494" s="3" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="inlineStr">
+        <is>
+          <t>CJ Osteopathy</t>
+        </is>
+      </c>
+      <c r="B495" s="4" t="inlineStr">
+        <is>
+          <t>Osteopathy clinic</t>
+        </is>
+      </c>
+      <c r="C495" s="4" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D495" s="4" t="inlineStr">
+        <is>
+          <t>https://cjosteopathy.co.uk</t>
+        </is>
+      </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F495" s="4" t="inlineStr"/>
+      <c r="G495" s="4" t="inlineStr">
+        <is>
+          <t>Caroline Jack (Founder/Principal Osteopath, est. 2009)</t>
+        </is>
+      </c>
+      <c r="H495" s="4" t="inlineStr"/>
+      <c r="I495" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/osteopathyCJ</t>
+        </is>
+      </c>
+      <c r="J495" s="4" t="inlineStr">
+        <is>
+          <t>16-year solo-practitioner osteopathy clinic in central Tunbridge Wells with 50+ patient reviews; private treatment packages worth hundreds to thousands per patient</t>
+        </is>
+      </c>
+      <c r="K495" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L495" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M495" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N495" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O495" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence; 52 reviews on Birdeye</t>
+        </is>
+      </c>
+      <c r="P495" s="4" t="inlineStr">
+        <is>
+          <t>Strong review base not yet converted into AI-cited answers for 'osteopath Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q495" s="4" t="inlineStr">
+        <is>
+          <t>'52+ patient reviews - let's make AI cite those, not just Google'</t>
+        </is>
+      </c>
+      <c r="R495" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S495" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T495" s="4" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge &amp; Walton Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic (3 locations)</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>Weybridge, Walton-on-Thames &amp; Brooklands, Surrey</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>https://www.weybridgephysio.co.uk</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>info@weybridgephysio.co.uk</t>
+        </is>
+      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>01932 847 900</t>
+        </is>
+      </c>
+      <c r="G496" s="3" t="inlineStr">
+        <is>
+          <t>Michael O'Reilly (Founder, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H496" s="3" t="inlineStr"/>
+      <c r="I496" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/WeybridgeWaltonPhysiotherapy</t>
+        </is>
+      </c>
+      <c r="J496" s="3" t="inlineStr">
+        <is>
+          <t>20-year independent physiotherapy practice across 3 Surrey locations; private treatment packages worth hundreds to thousands per patient</t>
+        </is>
+      </c>
+      <c r="K496" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L496" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M496" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N496" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O496" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 3-location expansion; 20-year trading history</t>
+        </is>
+      </c>
+      <c r="P496" s="3" t="inlineStr">
+        <is>
+          <t>3-location footprint not matched by 3-location AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q496" s="3" t="inlineStr">
+        <is>
+          <t>Per-location AEO content to own Weybridge/Walton/Brooklands 'physio near me' searches separately</t>
+        </is>
+      </c>
+      <c r="R496" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S496" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T496" s="3" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="inlineStr">
+        <is>
+          <t>Vitality Physiotherapy</t>
+        </is>
+      </c>
+      <c r="B497" s="4" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic</t>
+        </is>
+      </c>
+      <c r="C497" s="4" t="inlineStr">
+        <is>
+          <t>Esher, Surrey (+ Southwark, London)</t>
+        </is>
+      </c>
+      <c r="D497" s="4" t="inlineStr">
+        <is>
+          <t>https://www.vitality-physio.co.uk</t>
+        </is>
+      </c>
+      <c r="E497" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F497" s="4" t="inlineStr">
+        <is>
+          <t>020 7193 9928</t>
+        </is>
+      </c>
+      <c r="G497" s="4" t="inlineStr">
+        <is>
+          <t>Janine Enoch (Founder/Clinical Director)</t>
+        </is>
+      </c>
+      <c r="H497" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/vitalityphysio</t>
+        </is>
+      </c>
+      <c r="I497" s="4" t="inlineStr"/>
+      <c r="J497" s="4" t="inlineStr">
+        <is>
+          <t>Two-location physiotherapy practice with a shoulder/respiratory/running specialist founder; private treatment packages worth hundreds to thousands per patient</t>
+        </is>
+      </c>
+      <c r="K497" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L497" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M497" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N497" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O497" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P497" s="4" t="inlineStr">
+        <is>
+          <t>New Esher location not yet the AI-cited answer for 'physiotherapist Esher'</t>
+        </is>
+      </c>
+      <c r="Q497" s="4" t="inlineStr">
+        <is>
+          <t>'New to Esher - be the AI-cited answer before competitors are'</t>
+        </is>
+      </c>
+      <c r="R497" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S497" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T497" s="4" t="inlineStr">
+        <is>
+          <t>Recently opened Esher location per LinkedIn post</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>EAB Homes</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>Luxury home builder &amp; developer</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>Beaconsfield, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eabhomes.co.uk</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr"/>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>Paul (Founder, started 1986) &amp; Julia (Partner)</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/eab-homes</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/eabhomes</t>
+        </is>
+      </c>
+      <c r="J498" s="2" t="inlineStr">
+        <is>
+          <t>39-year bespoke luxury new-build and extension specialist serving Beaconsfield/Marlow; project fees run into hundreds of thousands per build</t>
+        </is>
+      </c>
+      <c r="K498" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L498" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N498" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O498" s="2" t="inlineStr">
+        <is>
+          <t>Facebook/LinkedIn presence; 39-year trading history</t>
+        </is>
+      </c>
+      <c r="P498" s="2" t="inlineStr">
+        <is>
+          <t>39-year heritage not yet the AI-cited answer for 'luxury home builder Beaconsfield'</t>
+        </is>
+      </c>
+      <c r="Q498" s="2" t="inlineStr">
+        <is>
+          <t>'39 years building Beaconsfield's finest homes - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R498" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S498" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T498" s="2" t="inlineStr">
+        <is>
+          <t>39-year heritage + very high-value builds - strong AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="inlineStr">
+        <is>
+          <t>G R Regan &amp; Son</t>
+        </is>
+      </c>
+      <c r="B499" s="4" t="inlineStr">
+        <is>
+          <t>Roofing contractor</t>
+        </is>
+      </c>
+      <c r="C499" s="4" t="inlineStr">
+        <is>
+          <t>Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D499" s="4" t="inlineStr">
+        <is>
+          <t>https://www.grreganroofing.com</t>
+        </is>
+      </c>
+      <c r="E499" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F499" s="4" t="inlineStr">
+        <is>
+          <t>01732 463 156</t>
+        </is>
+      </c>
+      <c r="G499" s="4" t="inlineStr">
+        <is>
+          <t>Family-owned, est. ~1994 (30 years trading)</t>
+        </is>
+      </c>
+      <c r="H499" s="4" t="inlineStr"/>
+      <c r="I499" s="4" t="inlineStr"/>
+      <c r="J499" s="4" t="inlineStr">
+        <is>
+          <t>30-year family-owned roofing business serving Sevenoaks and the South East; project fees run into thousands per roof</t>
+        </is>
+      </c>
+      <c r="K499" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L499" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M499" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N499" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O499" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P499" s="4" t="inlineStr">
+        <is>
+          <t>30-year heritage not yet the AI-cited answer for 'roofer Sevenoaks'</t>
+        </is>
+      </c>
+      <c r="Q499" s="4" t="inlineStr">
+        <is>
+          <t>'30 years of family roofing in Sevenoaks - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R499" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S499" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T499" s="4" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>Weatherall Roofing</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>Roofing contractor</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>Southborough, Tunbridge Wells, Kent</t>
+        </is>
+      </c>
+      <c r="D500" s="3" t="inlineStr">
+        <is>
+          <t>https://www.weatherallroofing.co.uk</t>
+        </is>
+      </c>
+      <c r="E500" s="3" t="inlineStr">
+        <is>
+          <t>enquiry@weatherallroofing.co.uk</t>
+        </is>
+      </c>
+      <c r="F500" s="3" t="inlineStr">
+        <is>
+          <t>01892 535478</t>
+        </is>
+      </c>
+      <c r="G500" s="3" t="inlineStr">
+        <is>
+          <t>Clive Berry (Founder)</t>
+        </is>
+      </c>
+      <c r="H500" s="3" t="inlineStr"/>
+      <c r="I500" s="3" t="inlineStr"/>
+      <c r="J500" s="3" t="inlineStr">
+        <is>
+          <t>40+ year family-run roofing firm covering all aspects of roofing (incl. EPDM/green/slate) across Tunbridge Wells/Tonbridge/Sevenoaks; project fees run into thousands per roof</t>
+        </is>
+      </c>
+      <c r="K500" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L500" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M500" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N500" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O500" s="3" t="inlineStr">
+        <is>
+          <t>TrustMark accreditation; 40+ year trading history</t>
+        </is>
+      </c>
+      <c r="P500" s="3" t="inlineStr">
+        <is>
+          <t>40-year heritage not yet the AI-cited answer for 'roofer Tunbridge Wells'</t>
+        </is>
+      </c>
+      <c r="Q500" s="3" t="inlineStr">
+        <is>
+          <t>'40+ years of family roofing expertise - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R500" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S500" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T500" s="3" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>Nixon Electrical Contractors</t>
+        </is>
+      </c>
+      <c r="B501" s="4" t="inlineStr">
+        <is>
+          <t>Electrical contractor</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="inlineStr">
+        <is>
+          <t>Chesham, Buckinghamshire (Amersham/Beaconsfield/Chalfonts)</t>
+        </is>
+      </c>
+      <c r="D501" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cheshamelectrician.co.uk</t>
+        </is>
+      </c>
+      <c r="E501" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F501" s="4" t="inlineStr">
+        <is>
+          <t>07973 660552</t>
+        </is>
+      </c>
+      <c r="G501" s="4" t="inlineStr">
+        <is>
+          <t>Martin Nixon (Founder, est. 1996)</t>
+        </is>
+      </c>
+      <c r="H501" s="4" t="inlineStr"/>
+      <c r="I501" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/nixonelectricalcontractors</t>
+        </is>
+      </c>
+      <c r="J501" s="4" t="inlineStr">
+        <is>
+          <t>29-year NICEIC-approved, City &amp; Guilds-qualified electrical contractor serving Chesham/Amersham/Beaconsfield/Chalfont St Giles; project fees run into thousands per job with repeat commercial clients</t>
+        </is>
+      </c>
+      <c r="K501" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L501" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M501" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N501" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O501" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence; NICEIC accreditation; 29-year trading history</t>
+        </is>
+      </c>
+      <c r="P501" s="4" t="inlineStr">
+        <is>
+          <t>29-year NICEIC-approved heritage not yet the AI-cited answer for 'electrician Chesham'</t>
+        </is>
+      </c>
+      <c r="Q501" s="4" t="inlineStr">
+        <is>
+          <t>'29 years NICEIC-approved in Chesham and Amersham - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R501" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S501" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T501" s="4" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>Lovat House Dental Practice</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>Dental practice (specialist, implants, aesthetics)</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="D502" s="3" t="inlineStr">
+        <is>
+          <t>https://lovathousedental.co.uk</t>
+        </is>
+      </c>
+      <c r="E502" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F502" s="3" t="inlineStr">
+        <is>
+          <t>01242 522841</t>
+        </is>
+      </c>
+      <c r="G502" s="3" t="inlineStr">
+        <is>
+          <t>James Barber &amp; Andrew Barber (Brothers, Principal Dental Surgeons)</t>
+        </is>
+      </c>
+      <c r="H502" s="3" t="inlineStr"/>
+      <c r="I502" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/lovathousedentalcheltenham</t>
+        </is>
+      </c>
+      <c r="J502" s="3" t="inlineStr">
+        <is>
+          <t>Independent brother-owned specialist dental practice offering implants and aesthetic dentistry; private treatment fees run into thousands per patient</t>
+        </is>
+      </c>
+      <c r="K502" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L502" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M502" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N502" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O502" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P502" s="3" t="inlineStr">
+        <is>
+          <t>Brother-owned specialist practice not yet the AI-cited answer for 'dental implants Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q502" s="3" t="inlineStr">
+        <is>
+          <t>'Two brothers, one specialist dental practice - own that AEO trust story'</t>
+        </is>
+      </c>
+      <c r="R502" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S502" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T502" s="3" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr">
+        <is>
+          <t>17 Dental</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>Dental practice (general, cosmetic, surgical)</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>https://www.17dental.com</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>17dental@gmail.com</t>
+        </is>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>01483 575908</t>
+        </is>
+      </c>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>Dr Waseem Akhtar &amp; Associates</t>
+        </is>
+      </c>
+      <c r="H503" s="3" t="inlineStr"/>
+      <c r="I503" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/17.dental</t>
+        </is>
+      </c>
+      <c r="J503" s="3" t="inlineStr">
+        <is>
+          <t>Long-established independent Guildford practice offering minor oral surgery and dental implants; private treatment fees run into thousands per patient</t>
+        </is>
+      </c>
+      <c r="K503" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L503" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M503" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N503" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O503" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence</t>
+        </is>
+      </c>
+      <c r="P503" s="3" t="inlineStr">
+        <is>
+          <t>Long-established local reputation not yet the AI-cited answer for 'dentist Guildford'</t>
+        </is>
+      </c>
+      <c r="Q503" s="3" t="inlineStr">
+        <is>
+          <t>'Long-established and independent - own that exact AEO trust signal in Guildford'</t>
+        </is>
+      </c>
+      <c r="R503" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S503" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T503" s="3" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>The Neem Tree Dental Practice (Esher)</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>Dental practice (holistic, implants, orthodontics)</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>Esher High Street, Surrey</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>https://theneemtree.co.uk</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>01372 464 000</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>Dr Smita (Founder, opened first practice 2004; Esher site since 2006)</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr"/>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/the.neem.tree.dental.group</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>One of Surrey's most established dental practices (19 years on Esher High Street), handling complex cases other practices refer out; private treatment fees run into thousands per patient</t>
+        </is>
+      </c>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L504" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N504" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O504" s="2" t="inlineStr">
+        <is>
+          <t>Facebook presence; 19-year trading history; complex-referral reputation</t>
+        </is>
+      </c>
+      <c r="P504" s="2" t="inlineStr">
+        <is>
+          <t>19-year heritage and complex-case reputation not yet the AI-cited answer for 'dentist Esher'</t>
+        </is>
+      </c>
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>'The practice other dentists refer complex cases to - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R504" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S504" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T504" s="2" t="inlineStr">
+        <is>
+          <t>19-year heritage + referral-of-choice reputation - strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="3" t="inlineStr">
+        <is>
+          <t>Belgarum</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; lettings agent</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>Winchester, Hampshire</t>
+        </is>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>https://www.belgarum.com</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>01962 844 460</t>
+        </is>
+      </c>
+      <c r="G505" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned (est. 1989 as a letting agent, sales dept. added 2003)</t>
+        </is>
+      </c>
+      <c r="H505" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/belgarum-estate-agents-limited</t>
+        </is>
+      </c>
+      <c r="I505" s="3" t="inlineStr"/>
+      <c r="J505" s="3" t="inlineStr">
+        <is>
+          <t>36-year family-owned independent Winchester agent with an explicit 'anti-corporate ethos'; sales commissions on premium Winchester property are substantial</t>
+        </is>
+      </c>
+      <c r="K505" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L505" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M505" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N505" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O505" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; explicit 'independent, anti-corporate' marketing message; 36-year heritage</t>
+        </is>
+      </c>
+      <c r="P505" s="3" t="inlineStr">
+        <is>
+          <t>'Anti-corporate' positioning not yet the AI-cited answer for 'estate agent Winchester'</t>
+        </is>
+      </c>
+      <c r="Q505" s="3" t="inlineStr">
+        <is>
+          <t>'36 years of anti-corporate, independent service - own that exact AEO positioning'</t>
+        </is>
+      </c>
+      <c r="R505" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S505" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T505" s="3" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="3" t="inlineStr">
+        <is>
+          <t>HÁM Interiors</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>Architecture, interior design &amp; build practice</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>Hambleden Valley, nr Henley-on-Thames</t>
+        </is>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>https://www.haminteriors.com</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F506" s="3" t="inlineStr"/>
+      <c r="G506" s="3" t="inlineStr">
+        <is>
+          <t>Nick, Pamela, Kate &amp; Tom Cox (Family founders, est. 2011)</t>
+        </is>
+      </c>
+      <c r="H506" s="3" t="inlineStr"/>
+      <c r="I506" s="3" t="inlineStr"/>
+      <c r="J506" s="3" t="inlineStr">
+        <is>
+          <t>14-year family-run architecture/interiors/build practice in the Hambleden Valley; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K506" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L506" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M506" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N506" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O506" s="3" t="inlineStr">
+        <is>
+          <t>14-year family-run trading history</t>
+        </is>
+      </c>
+      <c r="P506" s="3" t="inlineStr">
+        <is>
+          <t>Family-run, full-service (design + build) positioning not yet the AI-cited answer for 'interior design Henley'</t>
+        </is>
+      </c>
+      <c r="Q506" s="3" t="inlineStr">
+        <is>
+          <t>'One family, design through to build - own that exact AEO full-service positioning'</t>
+        </is>
+      </c>
+      <c r="R506" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S506" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T506" s="3" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="inlineStr">
+        <is>
+          <t>Marlow Face &amp; Body</t>
+        </is>
+      </c>
+      <c r="B507" s="4" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (face, body, skin)</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="inlineStr">
+        <is>
+          <t>Marlow, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D507" s="4" t="inlineStr">
+        <is>
+          <t>https://marlowfaceandbody.com</t>
+        </is>
+      </c>
+      <c r="E507" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F507" s="4" t="inlineStr"/>
+      <c r="G507" s="4" t="inlineStr">
+        <is>
+          <t>Elisabeth Bester (Founder, est. 2014)</t>
+        </is>
+      </c>
+      <c r="H507" s="4" t="inlineStr"/>
+      <c r="I507" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/marlowfaceandbody (handle per site posts)</t>
+        </is>
+      </c>
+      <c r="J507" s="4" t="inlineStr">
+        <is>
+          <t>11-year independent aesthetics clinic (cryolipolysis, radiofrequency, LED photon therapy); repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K507" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L507" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M507" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N507" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O507" s="4" t="inlineStr">
+        <is>
+          <t>Instagram presence; 11-year trading history</t>
+        </is>
+      </c>
+      <c r="P507" s="4" t="inlineStr">
+        <is>
+          <t>11-year heritage not yet the AI-cited answer for 'aesthetics clinic Marlow'</t>
+        </is>
+      </c>
+      <c r="Q507" s="4" t="inlineStr">
+        <is>
+          <t>'11 years of trusted aesthetics treatments in Marlow - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R507" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S507" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T507" s="4" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>Appearance Based Medicine (AB Med)</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>Medical aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>Marlow, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ab-med.co.uk</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F508" s="3" t="inlineStr"/>
+      <c r="G508" s="3" t="inlineStr">
+        <is>
+          <t>Clare McLoughlin RGN INP (Founder, pioneering medical aesthetics since 1999)</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="inlineStr"/>
+      <c r="I508" s="3" t="inlineStr"/>
+      <c r="J508" s="3" t="inlineStr">
+        <is>
+          <t>Founded by a pioneering nurse prescriber with 25+ years in medical aesthetics; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K508" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L508" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M508" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N508" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O508" s="3" t="inlineStr">
+        <is>
+          <t>25+ year pioneer credential = strong authority asset</t>
+        </is>
+      </c>
+      <c r="P508" s="3" t="inlineStr">
+        <is>
+          <t>Pioneer-since-1999 story not yet the AI-cited trust signal for 'medical aesthetics Marlow'</t>
+        </is>
+      </c>
+      <c r="Q508" s="3" t="inlineStr">
+        <is>
+          <t>'A pioneer in medical aesthetics since 1999 - own that exact AEO authority signal'</t>
+        </is>
+      </c>
+      <c r="R508" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S508" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T508" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T492"/>
+  <autoFilter ref="A1:T508"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43632,7 +45084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -43652,7 +45104,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5">
@@ -43755,7 +45207,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aesthetics clinic</t>
+          <t>Physiotherapy clinic</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -43765,11 +45217,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physiotherapy clinic</t>
+          <t>Aesthetics clinic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -43795,7 +45247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -43805,7 +45257,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -43815,27 +45267,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -43845,7 +45297,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -43855,7 +45307,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -44195,7 +45647,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Driving school &amp; ADI instructor training</t>
+          <t>Estate &amp; lettings agent</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -44205,7 +45657,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Veterinary practice</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -44215,7 +45667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Reformer Pilates studio</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -44225,7 +45677,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Home care &amp; live-in care agency</t>
+          <t>Reformer Pilates studio</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -44235,7 +45687,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Private tuition (primary/11+)</t>
+          <t>Home care &amp; live-in care agency</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -44245,7 +45697,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Independent Chartered financial planning</t>
+          <t>Private tuition (primary/11+)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -44255,27 +45707,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Independent Chartered financial planning</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Roofing contractor</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -44285,7 +45737,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -44295,7 +45747,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -44305,7 +45757,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -44315,7 +45767,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -44325,7 +45777,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -44335,7 +45787,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -44345,7 +45797,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -44355,7 +45807,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -44365,7 +45817,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -44375,7 +45827,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -44385,7 +45837,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -44395,7 +45847,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -44405,7 +45857,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -44415,7 +45867,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -44425,7 +45877,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -44435,7 +45887,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -44445,7 +45897,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -44455,7 +45907,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -44465,7 +45917,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -44475,7 +45927,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -44485,7 +45937,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -44495,7 +45947,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -44505,7 +45957,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -44515,7 +45967,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -44525,7 +45977,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -44535,7 +45987,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -44545,7 +45997,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -44555,7 +46007,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -44565,7 +46017,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -44575,7 +46027,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -44585,7 +46037,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -44595,7 +46047,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -44605,7 +46057,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -44615,7 +46067,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -44625,7 +46077,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -44635,7 +46087,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -44645,7 +46097,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -44655,7 +46107,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -44665,7 +46117,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -44675,7 +46127,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -44685,7 +46137,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -44695,7 +46147,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -44705,7 +46157,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -44715,7 +46167,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -44725,7 +46177,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -44735,7 +46187,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -44745,7 +46197,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -44755,7 +46207,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -44765,7 +46217,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -44775,7 +46227,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -44785,7 +46237,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -44795,7 +46247,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -44805,7 +46257,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -44815,7 +46267,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -44825,7 +46277,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -44835,7 +46287,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -44845,7 +46297,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -44855,7 +46307,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -44865,7 +46317,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -44875,7 +46327,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -44885,7 +46337,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -44895,7 +46347,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -44905,7 +46357,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -44915,7 +46367,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -44925,7 +46377,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -44935,7 +46387,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -44945,7 +46397,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -44955,7 +46407,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -44965,7 +46417,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -44975,7 +46427,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -44985,7 +46437,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -44995,7 +46447,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -45005,7 +46457,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -45015,7 +46467,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -45025,7 +46477,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -45035,7 +46487,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -45045,7 +46497,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -45055,7 +46507,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -45065,7 +46517,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -45075,7 +46527,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -45085,7 +46537,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -45095,7 +46547,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -45105,7 +46557,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -45115,7 +46567,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -45125,7 +46577,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -45135,7 +46587,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -45145,7 +46597,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -45155,7 +46607,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -45165,7 +46617,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -45175,7 +46627,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -45185,7 +46637,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -45195,7 +46647,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -45205,7 +46657,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -45215,7 +46667,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -45225,7 +46677,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -45235,7 +46687,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -45245,7 +46697,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -45255,7 +46707,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -45265,7 +46717,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -45275,7 +46727,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -45285,7 +46737,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -45295,7 +46747,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -45305,7 +46757,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -45315,7 +46767,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -45325,7 +46777,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -45335,7 +46787,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -45345,7 +46797,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -45355,7 +46807,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Beauty/aesthetics training academy</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -45365,7 +46817,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Beauty/hair training academy</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -45375,7 +46827,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Creative &amp; marketing recruitment agency</t>
+          <t>Medical aesthetics/injectable training academy</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -45385,7 +46837,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Private dermatology &amp; women's health clinics</t>
+          <t>Yoga teacher training school</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -45395,7 +46847,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Private dermatology practice</t>
+          <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -45405,7 +46857,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Estate &amp; lettings agent</t>
+          <t>Private dermatology &amp; women's health clinics</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -45415,7 +46867,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Wedding venue (converted barn)</t>
+          <t>Private dermatology practice</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -45425,7 +46877,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Wedding venue (waterside barn &amp; estate)</t>
+          <t>Wedding venue (converted barn)</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -45435,7 +46887,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Wedding venue (thatched barn on working farm)</t>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -45445,7 +46897,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Wedding venue (working farm)</t>
+          <t>Wedding venue (thatched barn on working farm)</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -45455,7 +46907,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Wedding venue (restored historic barn)</t>
+          <t>Wedding venue (working farm)</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -45465,7 +46917,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Chartered IFA / wealth management</t>
+          <t>Wedding venue (restored historic barn)</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -45475,7 +46927,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Independent mortgage broker</t>
+          <t>Chartered IFA / wealth management</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -45485,7 +46937,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Independent financial planning</t>
+          <t>Independent mortgage broker</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -45495,7 +46947,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Chartered independent financial planners</t>
+          <t>Independent financial planning</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -45505,7 +46957,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Veterinary practice (small independent group)</t>
+          <t>Chartered independent financial planners</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -45515,7 +46967,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, family, private client)</t>
+          <t>Veterinary practice (small independent group)</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -45525,7 +46977,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, private client)</t>
+          <t>Law firm (conveyancing, family, private client)</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -45535,7 +46987,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Conveyancing solicitors</t>
+          <t>Law firm (conveyancing, private client)</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -45545,7 +46997,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Law firm (residential &amp; commercial property)</t>
+          <t>Conveyancing solicitors</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -45555,7 +47007,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing, private client, family)</t>
+          <t>Law firm (residential &amp; commercial property)</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -45565,7 +47017,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Solar &amp; heat pump installer</t>
+          <t>Law firm (conveyancing, private client, family)</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -45575,7 +47027,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Solar PV &amp; electrical installer</t>
+          <t>Solar &amp; heat pump installer</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -45585,7 +47037,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Heat pump &amp; EV charger installer</t>
+          <t>Solar PV &amp; electrical installer</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -45595,7 +47047,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Solar PV &amp; EV charger installer</t>
+          <t>Heat pump &amp; EV charger installer</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -45605,7 +47057,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Electrical contractor &amp; solar installer</t>
+          <t>Solar PV &amp; EV charger installer</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -45615,7 +47067,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Solar PV installer</t>
+          <t>Electrical contractor &amp; solar installer</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -45625,7 +47077,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Classical Pilates studio</t>
+          <t>Solar PV installer</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -45635,7 +47087,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Pilates &amp; yoga studio (+ teacher training)</t>
+          <t>Classical Pilates studio</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -45645,7 +47097,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
+          <t>Pilates &amp; yoga studio (+ teacher training)</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -45655,7 +47107,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Women-only strength &amp; personal training studio</t>
+          <t>Yoga, barre &amp; Pilates studio (+ teacher training)</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -45665,7 +47117,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Immigration &amp; commercial law firm</t>
+          <t>Women-only strength &amp; personal training studio</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -45675,7 +47127,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Immigration law firm (UK/US)</t>
+          <t>Immigration &amp; commercial law firm</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -45685,7 +47137,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Private client law firm (wills, trusts, estates)</t>
+          <t>Immigration law firm (UK/US)</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -45695,7 +47147,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Private wealth &amp; estate planning law firm</t>
+          <t>Private client law firm (wills, trusts, estates)</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -45705,7 +47157,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Private wealth law firm (UHNW)</t>
+          <t>Private wealth &amp; estate planning law firm</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -45715,7 +47167,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Residential &amp; domiciliary care provider</t>
+          <t>Private wealth law firm (UHNW)</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -45725,7 +47177,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Outdoor 'Forest School' nursery</t>
+          <t>Residential &amp; domiciliary care provider</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -45735,7 +47187,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Day nursery group (3 sites)</t>
+          <t>Outdoor 'Forest School' nursery</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -45745,7 +47197,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Day nursery &amp; pre-school</t>
+          <t>Day nursery group (3 sites)</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -45755,7 +47207,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Chartered lifestyle financial planning</t>
+          <t>Day nursery &amp; pre-school</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -45765,7 +47217,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Chartered independent financial planning</t>
+          <t>Chartered lifestyle financial planning</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -45775,7 +47227,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>IT support &amp; managed services (MSP)</t>
+          <t>Chartered independent financial planning</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -45785,7 +47237,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Outsourced finance &amp; business consultancy</t>
+          <t>IT support &amp; managed services (MSP)</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -45795,7 +47247,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>IT support, hosting &amp; web development (MSP)</t>
+          <t>Outsourced finance &amp; business consultancy</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -45805,7 +47257,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>IT support (MSP)</t>
+          <t>IT support, hosting &amp; web development (MSP)</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -45815,7 +47267,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Executive coaching &amp; leadership training</t>
+          <t>IT support (MSP)</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -45825,7 +47277,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Lime plastering/render conservation specialist</t>
+          <t>Executive coaching &amp; leadership training</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -45835,7 +47287,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Lime plastering &amp; traditional render specialist</t>
+          <t>Lime plastering/render conservation specialist</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -45845,7 +47297,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sash window manufacture &amp; restoration</t>
+          <t>Lime plastering &amp; traditional render specialist</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -45855,7 +47307,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Bespoke joinery (sash windows, doors, cabinetry)</t>
+          <t>Sash window manufacture &amp; restoration</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -45865,7 +47317,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Bespoke joinery for listed/conservation buildings</t>
+          <t>Bespoke joinery (sash windows, doors, cabinetry)</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -45875,10 +47327,120 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
+          <t>Bespoke joinery for listed/conservation buildings</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>Conservation/heritage builder</t>
         </is>
       </c>
-      <c r="B227" t="n">
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Chiropractic clinic</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Physiotherapy clinic (3 locations)</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Luxury home builder &amp; developer</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Electrical contractor</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Dental practice (specialist, implants, aesthetics)</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Dental practice (general, cosmetic, surgical)</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Dental practice (holistic, implants, orthodontics)</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Architecture, interior design &amp; build practice</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (face, body, skin)</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Medical aesthetics clinic</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$514</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T508"/>
+  <dimension ref="A1:T514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45072,8 +45072,548 @@
       </c>
       <c r="T508" s="3" t="inlineStr"/>
     </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>Litchfields</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; lettings agent</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="inlineStr">
+        <is>
+          <t>Highgate &amp; Hampstead Garden Suburb, London</t>
+        </is>
+      </c>
+      <c r="D509" s="3" t="inlineStr">
+        <is>
+          <t>https://www.litchfields.com</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>highgate@litchfields.com</t>
+        </is>
+      </c>
+      <c r="F509" s="3" t="inlineStr">
+        <is>
+          <t>020 8348 8000</t>
+        </is>
+      </c>
+      <c r="G509" s="3" t="inlineStr">
+        <is>
+          <t>Independent, privately owned (est. 1989)</t>
+        </is>
+      </c>
+      <c r="H509" s="3" t="inlineStr"/>
+      <c r="I509" s="3" t="inlineStr"/>
+      <c r="J509" s="3" t="inlineStr">
+        <is>
+          <t>36-year independent multi-office agent covering Highgate/Hampstead Garden Suburb/Crouch End; commissions on premium North London property sales are substantial</t>
+        </is>
+      </c>
+      <c r="K509" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L509" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M509" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N509" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O509" s="3" t="inlineStr">
+        <is>
+          <t>36-year trading history; multi-office expansion</t>
+        </is>
+      </c>
+      <c r="P509" s="3" t="inlineStr">
+        <is>
+          <t>36-year heritage not yet the AI-cited answer for 'estate agent Highgate'</t>
+        </is>
+      </c>
+      <c r="Q509" s="3" t="inlineStr">
+        <is>
+          <t>'36 years, run like a family business - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R509" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S509" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T509" s="3" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>Day Morris Estate Agents</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>Estate &amp; lettings agent</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>Hampstead &amp; Highgate, London</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>https://daymorris.co.uk</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>hampstead@daymorris.co.uk</t>
+        </is>
+      </c>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>020 7482 4282</t>
+        </is>
+      </c>
+      <c r="G510" s="3" t="inlineStr">
+        <is>
+          <t>Steven Day &amp; John Morris (Founders, est. 1989)</t>
+        </is>
+      </c>
+      <c r="H510" s="3" t="inlineStr"/>
+      <c r="I510" s="3" t="inlineStr"/>
+      <c r="J510" s="3" t="inlineStr">
+        <is>
+          <t>36-year independent agency founded by two of Hampstead's most respected property professionals; commissions on premium North London property sales are substantial</t>
+        </is>
+      </c>
+      <c r="K510" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L510" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M510" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N510" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O510" s="3" t="inlineStr">
+        <is>
+          <t>36-year heritage; founders' local reputation</t>
+        </is>
+      </c>
+      <c r="P510" s="3" t="inlineStr">
+        <is>
+          <t>36-year founder reputation not yet the AI-cited answer for 'estate agent Hampstead'</t>
+        </is>
+      </c>
+      <c r="Q510" s="3" t="inlineStr">
+        <is>
+          <t>'Founded by two of Hampstead's most respected agents - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R510" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S510" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T510" s="3" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="3" t="inlineStr">
+        <is>
+          <t>Pembridge Dental</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>Dental practice (general, cosmetic, implants)</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="inlineStr">
+        <is>
+          <t>Notting Hill, West London</t>
+        </is>
+      </c>
+      <c r="D511" s="3" t="inlineStr">
+        <is>
+          <t>https://pembridgedental.co.uk</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F511" s="3" t="inlineStr"/>
+      <c r="G511" s="3" t="inlineStr">
+        <is>
+          <t>Dr Ardalan Eghtedar BDS MFDS RCS(Edin) (Principal Dentist, practice est. 1986)</t>
+        </is>
+      </c>
+      <c r="H511" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/aeghtedar</t>
+        </is>
+      </c>
+      <c r="I511" s="3" t="inlineStr"/>
+      <c r="J511" s="3" t="inlineStr">
+        <is>
+          <t>39-year long-established private dental practice serving Kensington/Holland Park/Bayswater/Chelsea; private treatment fees run into thousands per patient, especially implants</t>
+        </is>
+      </c>
+      <c r="K511" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L511" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M511" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N511" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O511" s="3" t="inlineStr">
+        <is>
+          <t>39-year trading history; extensive patient reviews</t>
+        </is>
+      </c>
+      <c r="P511" s="3" t="inlineStr">
+        <is>
+          <t>39-year heritage not yet the AI-cited answer for 'dentist Notting Hill'</t>
+        </is>
+      </c>
+      <c r="Q511" s="3" t="inlineStr">
+        <is>
+          <t>'39 years serving Notting Hill and Kensington - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R511" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S511" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T511" s="3" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="3" t="inlineStr">
+        <is>
+          <t>Pilates Plus London</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>Pilates, osteopathy &amp; functional medicine clinic</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>Blackheath &amp; Greenwich, London</t>
+        </is>
+      </c>
+      <c r="D512" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pilatespluslondon.co.uk</t>
+        </is>
+      </c>
+      <c r="E512" s="3" t="inlineStr">
+        <is>
+          <t>pilatespluss@hotmail.co.uk</t>
+        </is>
+      </c>
+      <c r="F512" s="3" t="inlineStr">
+        <is>
+          <t>020 3305 5563</t>
+        </is>
+      </c>
+      <c r="G512" s="3" t="inlineStr">
+        <is>
+          <t>Galina Bell (Founder, Registered Osteopath, est. 20+ years ago)</t>
+        </is>
+      </c>
+      <c r="H512" s="3" t="inlineStr"/>
+      <c r="I512" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/pilatespluslondon</t>
+        </is>
+      </c>
+      <c r="J512" s="3" t="inlineStr">
+        <is>
+          <t>20+ year multi-discipline clinic combining Pilates, osteopathy, acupuncture and functional medicine; class packages and treatment fees worth hundreds to thousands per client per year</t>
+        </is>
+      </c>
+      <c r="K512" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L512" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M512" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N512" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O512" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 20+ year trading history; multi-discipline offering</t>
+        </is>
+      </c>
+      <c r="P512" s="3" t="inlineStr">
+        <is>
+          <t>Multi-discipline offering (Pilates + osteopathy + functional medicine) not yet the AI-cited answer for 'Pilates Blackheath'</t>
+        </is>
+      </c>
+      <c r="Q512" s="3" t="inlineStr">
+        <is>
+          <t>'One clinic for Pilates, osteopathy and functional medicine - own that exact AEO multi-discipline positioning'</t>
+        </is>
+      </c>
+      <c r="R512" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S512" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T512" s="3" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="3" t="inlineStr">
+        <is>
+          <t>Godfrey &amp; Barr</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
+      <c r="C513" s="3" t="inlineStr">
+        <is>
+          <t>Hampstead Garden Suburb, London</t>
+        </is>
+      </c>
+      <c r="D513" s="3" t="inlineStr">
+        <is>
+          <t>https://www.godfreyandbarr.com</t>
+        </is>
+      </c>
+      <c r="E513" s="3" t="inlineStr">
+        <is>
+          <t>enquire@godfreyandbarr.com</t>
+        </is>
+      </c>
+      <c r="F513" s="3" t="inlineStr">
+        <is>
+          <t>020 8458 9119</t>
+        </is>
+      </c>
+      <c r="G513" s="3" t="inlineStr">
+        <is>
+          <t>Ian Godfrey &amp; Jonathan Barr (Founders, est. 1991)</t>
+        </is>
+      </c>
+      <c r="H513" s="3" t="inlineStr"/>
+      <c r="I513" s="3" t="inlineStr"/>
+      <c r="J513" s="3" t="inlineStr">
+        <is>
+          <t>34-year fully independent residential estate agent covering Hampstead Garden Suburb; commissions on premium North London property sales are substantial</t>
+        </is>
+      </c>
+      <c r="K513" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L513" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M513" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N513" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O513" s="3" t="inlineStr">
+        <is>
+          <t>34-year trading history; press features (Fabric Magazine)</t>
+        </is>
+      </c>
+      <c r="P513" s="3" t="inlineStr">
+        <is>
+          <t>34-year heritage and press coverage not yet the AI-cited answer for 'estate agent Hampstead Garden Suburb'</t>
+        </is>
+      </c>
+      <c r="Q513" s="3" t="inlineStr">
+        <is>
+          <t>'34 years, fully independent, featured in Fabric Magazine - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R513" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S513" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T513" s="3" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="3" t="inlineStr">
+        <is>
+          <t>Studio Duggan</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>Interior design studio</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>Notting Hill, London (projects incl. Islington)</t>
+        </is>
+      </c>
+      <c r="D514" s="3" t="inlineStr">
+        <is>
+          <t>https://www.studioduggan.com</t>
+        </is>
+      </c>
+      <c r="E514" s="3" t="inlineStr">
+        <is>
+          <t>info@studioduggan.com</t>
+        </is>
+      </c>
+      <c r="F514" s="3" t="inlineStr">
+        <is>
+          <t>020 3642 3120</t>
+        </is>
+      </c>
+      <c r="G514" s="3" t="inlineStr">
+        <is>
+          <t>Tiffany Duggan (Founder, est. 2011, ex-Elle Decoration/Livingetc stylist)</t>
+        </is>
+      </c>
+      <c r="H514" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/tiffany-duggan-b97bb148</t>
+        </is>
+      </c>
+      <c r="I514" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/studioduggan</t>
+        </is>
+      </c>
+      <c r="J514" s="3" t="inlineStr">
+        <is>
+          <t>14-year high-end residential/boutique-commercial interior design studio founded by a former Elle Decoration/Livingetc stylist; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K514" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L514" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M514" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N514" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O514" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence; press-editorial founder background = strong PR asset</t>
+        </is>
+      </c>
+      <c r="P514" s="3" t="inlineStr">
+        <is>
+          <t>Editorial-press founder pedigree not yet the AI-cited answer for 'interior designer Notting Hill'</t>
+        </is>
+      </c>
+      <c r="Q514" s="3" t="inlineStr">
+        <is>
+          <t>'Founded by a former Elle Decoration stylist - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R514" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S514" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T514" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T508"/>
+  <autoFilter ref="A1:T514"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45084,7 +45624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B238"/>
+  <dimension ref="A1:B240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -45104,7 +45644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5">
@@ -45121,7 +45661,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -45247,7 +45787,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Osteopathy clinic</t>
+          <t>Interior design studio</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -45257,7 +45797,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Recruitment agency</t>
+          <t>Osteopathy clinic</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -45267,7 +45807,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT support / MSP</t>
+          <t>Recruitment agency</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -45277,27 +45817,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Interior design studio</t>
+          <t>IT support / MSP</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Estate &amp; lettings agent</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -45307,7 +45847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -45317,7 +45857,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -45327,7 +45867,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -45337,7 +45877,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -45347,7 +45887,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -45357,7 +45897,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -45367,7 +45907,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -45377,7 +45917,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -45387,7 +45927,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kitchen &amp; bathroom design</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -45397,7 +45937,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Architecture practice</t>
+          <t>Kitchen &amp; bathroom design</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -45407,7 +45947,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Home care agency</t>
+          <t>Architecture practice</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -45417,17 +45957,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Home care agency</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -45437,7 +45977,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -45447,7 +45987,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -45457,7 +45997,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -45467,7 +46007,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -45477,7 +46017,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -45487,7 +46027,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -45497,7 +46037,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -45507,7 +46047,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -45517,7 +46057,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -45527,7 +46067,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -45537,7 +46077,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -45547,7 +46087,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -45557,7 +46097,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -45567,7 +46107,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -45577,7 +46117,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -45587,7 +46127,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -45597,7 +46137,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -45607,7 +46147,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -45617,7 +46157,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -45627,7 +46167,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Private GP practice</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -45637,7 +46177,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aesthetics clinic (non-surgical)</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -45647,7 +46187,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Estate &amp; lettings agent</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -47441,6 +47981,26 @@
         </is>
       </c>
       <c r="B238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Dental practice (general, cosmetic, implants)</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Pilates, osteopathy &amp; functional medicine clinic</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$518</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T514"/>
+  <dimension ref="A1:T518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45612,8 +45612,360 @@
       </c>
       <c r="T514" s="3" t="inlineStr"/>
     </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>The Grove Vets</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>Veterinary practice</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>Henleaze, Bristol</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thegrovevet.com</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>info@thegrovevet.com</t>
+        </is>
+      </c>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>0117 252 0545</t>
+        </is>
+      </c>
+      <c r="G515" s="3" t="inlineStr">
+        <is>
+          <t>Andy Valenzia &amp; Amy Valenzia (Founders, vets since 2008)</t>
+        </is>
+      </c>
+      <c r="H515" s="3" t="inlineStr"/>
+      <c r="I515" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/grovevetbristol; facebook.com/grovevetbristol</t>
+        </is>
+      </c>
+      <c r="J515" s="3" t="inlineStr">
+        <is>
+          <t>Vet-owned family-run practice explicitly marketed as independent; consultation/treatment fees plus repeat annual health-plan clients</t>
+        </is>
+      </c>
+      <c r="K515" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L515" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M515" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N515" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O515" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P515" s="3" t="inlineStr">
+        <is>
+          <t>'Independent veterinary centre' positioning not yet the AI-cited trust signal for 'vet Bristol'</t>
+        </is>
+      </c>
+      <c r="Q515" s="3" t="inlineStr">
+        <is>
+          <t>'Vet-owned, family-run, proudly independent - own that exact AEO trust signal in Bristol'</t>
+        </is>
+      </c>
+      <c r="R515" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S515" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T515" s="3" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="inlineStr">
+        <is>
+          <t>Mortgage Gold</t>
+        </is>
+      </c>
+      <c r="B516" s="4" t="inlineStr">
+        <is>
+          <t>Independent mortgage broker</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>Bath (+ Bristol)</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mortgagegold.co.uk</t>
+        </is>
+      </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F516" s="4" t="inlineStr"/>
+      <c r="G516" s="4" t="inlineStr">
+        <is>
+          <t>Guy Maloney &amp; Clarissa Bellavia (Founders)</t>
+        </is>
+      </c>
+      <c r="H516" s="4" t="inlineStr"/>
+      <c r="I516" s="4" t="inlineStr"/>
+      <c r="J516" s="4" t="inlineStr">
+        <is>
+          <t>Fees-free, whole-of-market independent mortgage broker serving Bath and Bristol; commission per completed mortgage recurs with remortgage clients</t>
+        </is>
+      </c>
+      <c r="K516" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L516" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M516" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N516" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O516" s="4" t="inlineStr">
+        <is>
+          <t>'Fees-free' whole-of-market marketing positioning</t>
+        </is>
+      </c>
+      <c r="P516" s="4" t="inlineStr">
+        <is>
+          <t>'Fees-free' positioning not yet the AI-cited answer for 'mortgage broker Bath'</t>
+        </is>
+      </c>
+      <c r="Q516" s="4" t="inlineStr">
+        <is>
+          <t>'Fees-free, whole-of-market - own that exact AEO trust signal in Bath'</t>
+        </is>
+      </c>
+      <c r="R516" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S516" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T516" s="4" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr">
+        <is>
+          <t>Gate Street Barn</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (barn on working farm)</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>Bramley, nr Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>https://gatestreet.co.uk</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>info@gatestreetbarn.com</t>
+        </is>
+      </c>
+      <c r="F517" s="3" t="inlineStr"/>
+      <c r="G517" s="3" t="inlineStr">
+        <is>
+          <t>Third-generation family farm owners</t>
+        </is>
+      </c>
+      <c r="H517" s="3" t="inlineStr"/>
+      <c r="I517" s="3" t="inlineStr"/>
+      <c r="J517" s="3" t="inlineStr">
+        <is>
+          <t>180-acre third-generation family-run regenerative farm hosting countryside weddings; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K517" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L517" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M517" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N517" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O517" s="3" t="inlineStr">
+        <is>
+          <t>Regenerative-farming/biodiversity marketing angle = active PR positioning</t>
+        </is>
+      </c>
+      <c r="P517" s="3" t="inlineStr">
+        <is>
+          <t>Third-generation regenerative-farm story not yet the AI-cited answer for 'barn wedding venue Surrey'</t>
+        </is>
+      </c>
+      <c r="Q517" s="3" t="inlineStr">
+        <is>
+          <t>'A third-generation regenerative farm - own that exact AEO story in Surrey weddings'</t>
+        </is>
+      </c>
+      <c r="R517" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S517" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T517" s="3" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="3" t="inlineStr">
+        <is>
+          <t>Jenners Barn</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>Wedding venue (Cotswold stone barn)</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>Whelford, nr Fairford, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D518" s="3" t="inlineStr">
+        <is>
+          <t>https://jennersbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="E518" s="3" t="inlineStr">
+        <is>
+          <t>hello@jennersbarn.co.uk</t>
+        </is>
+      </c>
+      <c r="F518" s="3" t="inlineStr">
+        <is>
+          <t>07886 037224</t>
+        </is>
+      </c>
+      <c r="G518" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned and run</t>
+        </is>
+      </c>
+      <c r="H518" s="3" t="inlineStr"/>
+      <c r="I518" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/Jennersbarn</t>
+        </is>
+      </c>
+      <c r="J518" s="3" t="inlineStr">
+        <is>
+          <t>Family-owned Cotswold stone barn venue near Fairford/Lechlade/Cirencester with flexible planning freedom; bookings run into thousands to tens of thousands per event</t>
+        </is>
+      </c>
+      <c r="K518" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L518" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M518" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N518" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O518" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence</t>
+        </is>
+      </c>
+      <c r="P518" s="3" t="inlineStr">
+        <is>
+          <t>Flexible-planning positioning not yet the AI-cited answer for 'barn wedding venue Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q518" s="3" t="inlineStr">
+        <is>
+          <t>'Freedom to plan your own unique day - own that exact AEO positioning in the Cotswolds'</t>
+        </is>
+      </c>
+      <c r="R518" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S518" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T518" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T514"/>
+  <autoFilter ref="A1:T518"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45624,7 +45976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B240"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -45644,7 +45996,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5">
@@ -45957,7 +46309,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Home care agency</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -45967,17 +46319,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Home care agency</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -45987,7 +46339,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -45997,7 +46349,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -46007,7 +46359,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -46017,7 +46369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -46027,7 +46379,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -46037,7 +46389,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -46047,7 +46399,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -46057,7 +46409,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -46067,7 +46419,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -46077,7 +46429,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -46087,7 +46439,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -46097,7 +46449,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -46107,7 +46459,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -46117,7 +46469,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -46127,7 +46479,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -46137,7 +46489,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -46147,7 +46499,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -46157,7 +46509,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -46167,7 +46519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -46177,7 +46529,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Private GP practice</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -46187,7 +46539,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aesthetics clinic (non-surgical)</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -46197,7 +46549,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Driving school &amp; ADI instructor training</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -46207,7 +46559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Veterinary practice</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -46217,7 +46569,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Reformer Pilates studio</t>
+          <t>Independent mortgage broker</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -46227,7 +46579,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Home care &amp; live-in care agency</t>
+          <t>Reformer Pilates studio</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -46237,7 +46589,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Private tuition (primary/11+)</t>
+          <t>Home care &amp; live-in care agency</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -46247,7 +46599,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Independent Chartered financial planning</t>
+          <t>Private tuition (primary/11+)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -46257,7 +46609,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Roofing contractor</t>
+          <t>Independent Chartered financial planning</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -46267,17 +46619,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Roofing contractor</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -46287,7 +46639,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -46297,7 +46649,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -46307,7 +46659,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -46317,7 +46669,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -46327,7 +46679,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Mortgage broker / financial adviser</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -46337,7 +46689,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Architects (RIBA chartered)</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -46347,7 +46699,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Recruitment agency (IT/data)</t>
+          <t>Recruitment agency (tech/startups)</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -46357,7 +46709,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Independent vet (24/7 emergency)</t>
+          <t>Recruitment agency (IT/data)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -46367,7 +46719,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Letting &amp; estate agent</t>
+          <t>Independent vet (24/7 emergency)</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -46377,7 +46729,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cosmetic clinic (injectables)</t>
+          <t>Letting &amp; estate agent</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -46387,7 +46739,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cosmetic/anti-ageing clinic</t>
+          <t>Cosmetic clinic (injectables)</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -46397,7 +46749,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Yoga &amp; reformer pilates studio</t>
+          <t>Cosmetic/anti-ageing clinic</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -46407,7 +46759,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Reformer pilates studio</t>
+          <t>Yoga &amp; reformer pilates studio</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -46417,7 +46769,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wealth management</t>
+          <t>Reformer pilates studio</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -46427,7 +46779,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Private tuition &amp; education consultancy</t>
+          <t>Wealth management</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -46437,7 +46789,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Private tuition &amp; education consultancy</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -46447,7 +46799,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Design &amp; build / home renovation</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -46457,7 +46809,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Builders / building contractor</t>
+          <t>Design &amp; build / home renovation</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -46467,7 +46819,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Home care / live-in care</t>
+          <t>Builders / building contractor</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -46477,7 +46829,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Private day nurseries</t>
+          <t>Home care / live-in care</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -46487,7 +46839,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Personal training &amp; wellness studio</t>
+          <t>Private day nurseries</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -46497,7 +46849,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mortgage &amp; insurance broker</t>
+          <t>Personal training &amp; wellness studio</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -46507,7 +46859,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business consultancy</t>
+          <t>Mortgage &amp; insurance broker</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -46517,7 +46869,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Interior designer (period homes)</t>
+          <t>Business consultancy</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -46527,7 +46879,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Landscape design &amp; build</t>
+          <t>Interior designer (period homes)</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -46537,7 +46889,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Landscape design &amp; build</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -46547,7 +46899,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Garden design &amp; landscaping</t>
+          <t>Interior designer</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -46557,7 +46909,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Legal recruitment</t>
+          <t>Garden design &amp; landscaping</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -46567,7 +46919,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Independent gym &amp; health club</t>
+          <t>Legal recruitment</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -46577,7 +46929,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Independent gym</t>
+          <t>Independent gym &amp; health club</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -46587,7 +46939,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Physiotherapy (sports)</t>
+          <t>Independent gym</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -46597,7 +46949,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Letting agent / property management</t>
+          <t>Physiotherapy (sports)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -46607,7 +46959,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Skin clinic</t>
+          <t>Letting agent / property management</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -46617,7 +46969,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tutoring company</t>
+          <t>Skin clinic</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -46627,7 +46979,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tutorial college &amp; exam centre</t>
+          <t>Tutoring company</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -46637,7 +46989,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Employment law (disability discrimination)</t>
+          <t>Tutorial college &amp; exam centre</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -46647,7 +46999,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating</t>
+          <t>Employment law (disability discrimination)</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -46657,7 +47009,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Plumbing &amp; heating</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -46667,7 +47019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sports physio &amp; massage</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -46677,7 +47029,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Chartered surveyors (party wall/building)</t>
+          <t>Sports physio &amp; massage</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -46687,7 +47039,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Chartered surveyors</t>
+          <t>Chartered surveyors (party wall/building)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -46697,7 +47049,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Chartered building surveyors</t>
+          <t>Chartered surveyors</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -46707,7 +47059,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Osteopathy clinics</t>
+          <t>Chartered building surveyors</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -46717,7 +47069,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Builders / renovations</t>
+          <t>Osteopathy clinics</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -46727,7 +47079,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Private nursery schools</t>
+          <t>Builders / renovations</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -46737,7 +47089,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Private day nursery</t>
+          <t>Private nursery schools</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -46747,7 +47099,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Private GP (membership model)</t>
+          <t>Private day nursery</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -46757,7 +47109,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sash window restoration</t>
+          <t>Private GP (membership model)</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -46767,7 +47119,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Personal training (1:1)</t>
+          <t>Sash window restoration</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -46777,7 +47129,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Personal training &amp; nutrition coaching</t>
+          <t>Personal training (1:1)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -46787,7 +47139,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Private nursery/pre-prep school</t>
+          <t>Personal training &amp; nutrition coaching</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -46797,7 +47149,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Independent nursery (Montessori)</t>
+          <t>Private nursery/pre-prep school</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -46807,7 +47159,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Live-in care agency</t>
+          <t>Independent nursery (Montessori)</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -46817,7 +47169,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Law firm (conveyancing/family)</t>
+          <t>Live-in care agency</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -46827,7 +47179,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Architect &amp; interior designer</t>
+          <t>Law firm (conveyancing/family)</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -46837,7 +47189,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Architects / project management</t>
+          <t>Architect &amp; interior designer</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -46847,7 +47199,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; clinical Pilates</t>
+          <t>Architects / project management</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -46857,7 +47209,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Aesthetics &amp; skin clinic</t>
+          <t>Physiotherapy &amp; clinical Pilates</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -46867,7 +47219,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IFA / financial planning</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -46877,7 +47229,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Wealth management &amp; employee benefits</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -46887,7 +47239,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dermatology clinic</t>
+          <t>Wealth management &amp; employee benefits</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -46897,7 +47249,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Pilates studio (multi-site)</t>
+          <t>Dermatology clinic</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -46907,7 +47259,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Private nursery (Montessori, multi-site)</t>
+          <t>Pilates studio (multi-site)</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -46917,7 +47269,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Law firm (wills &amp; probate)</t>
+          <t>Private nursery (Montessori, multi-site)</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -46927,7 +47279,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Business/technical consultancy</t>
+          <t>Law firm (wills &amp; probate)</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -46937,7 +47289,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Private/NHS dentist</t>
+          <t>Business/technical consultancy</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -46947,7 +47299,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Removals company</t>
+          <t>Private/NHS dentist</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -46957,7 +47309,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Driveways &amp; landscaping</t>
+          <t>Removals company</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -46967,7 +47319,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Wedding &amp; event venue</t>
+          <t>Driveways &amp; landscaping</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -46977,7 +47329,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IFA &amp; mortgage broker</t>
+          <t>Wedding &amp; event venue</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -46987,7 +47339,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Wedding photography &amp; videography</t>
+          <t>IFA &amp; mortgage broker</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -46997,7 +47349,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Commercial property litigation law firm</t>
+          <t>Wedding photography &amp; videography</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -47007,7 +47359,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Recruitment agency (boutique)</t>
+          <t>Commercial property litigation law firm</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -47017,7 +47369,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Home cinema &amp; smart home installer</t>
+          <t>Recruitment agency (boutique)</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -47027,7 +47379,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Home cinema installer</t>
+          <t>Home cinema &amp; smart home installer</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -47037,7 +47389,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Curtains, blinds &amp; upholstery</t>
+          <t>Home cinema installer</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -47047,7 +47399,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Bespoke curtains &amp; soft furnishings</t>
+          <t>Curtains, blinds &amp; upholstery</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -47057,7 +47409,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Wine merchant</t>
+          <t>Bespoke curtains &amp; soft furnishings</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -47067,7 +47419,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Education consultancy (school placement)</t>
+          <t>Wine merchant</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -47077,7 +47429,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Estate agent &amp; surveyors</t>
+          <t>Education consultancy (school placement)</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -47087,7 +47439,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Independent financial adviser</t>
+          <t>Estate agent &amp; surveyors</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -47097,7 +47449,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial planners</t>
+          <t>Independent financial adviser</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -47107,7 +47459,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Private GP &amp; dermatology</t>
+          <t>Chartered accountants &amp; financial planners</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -47117,7 +47469,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Architects (heritage specialism)</t>
+          <t>Private GP &amp; dermatology</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -47127,7 +47479,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Private cosmetic dentist / implants</t>
+          <t>Architects (heritage specialism)</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -47137,7 +47489,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Heating engineer / plumbing</t>
+          <t>Private cosmetic dentist / implants</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -47147,7 +47499,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Estate agent (boutique)</t>
+          <t>Heating engineer / plumbing</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -47157,7 +47509,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Independent vet (mixed practice)</t>
+          <t>Estate agent (boutique)</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -47167,7 +47519,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Private dentist / cosmetic</t>
+          <t>Independent vet (mixed practice)</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -47177,7 +47529,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Chartered accountants &amp; financial advisers</t>
+          <t>Private dentist / cosmetic</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -47187,7 +47539,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Healthcare recruitment agency</t>
+          <t>Chartered accountants &amp; financial advisers</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -47197,7 +47549,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Executive search / headhunting</t>
+          <t>Healthcare recruitment agency</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -47207,7 +47559,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>First aid &amp; health &amp; safety training</t>
+          <t>Executive search / headhunting</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -47217,7 +47569,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Teaching &amp; education recruitment agency</t>
+          <t>First aid &amp; health &amp; safety training</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -47227,7 +47579,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Supply teaching agency</t>
+          <t>Teaching &amp; education recruitment agency</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -47237,7 +47589,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Hospitality staffing agency</t>
+          <t>Supply teaching agency</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -47247,7 +47599,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Finance &amp; accountancy recruitment agency</t>
+          <t>Hospitality staffing agency</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -47257,7 +47609,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Accounting &amp; finance recruitment agency</t>
+          <t>Finance &amp; accountancy recruitment agency</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -47267,7 +47619,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Forklift &amp; plant operator training</t>
+          <t>Accounting &amp; finance recruitment agency</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -47277,7 +47629,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Forklift training</t>
+          <t>Forklift &amp; plant operator training</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -47287,7 +47639,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Language school</t>
+          <t>Forklift training</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -47297,7 +47649,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Engineering &amp; manufacturing recruitment</t>
+          <t>Language school</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -47307,7 +47659,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Business &amp; sales coaching</t>
+          <t>Engineering &amp; manufacturing recruitment</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -47317,7 +47669,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Engineering &amp; energy recruitment</t>
+          <t>Business &amp; sales coaching</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -47327,7 +47679,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Tech recruitment agency</t>
+          <t>Engineering &amp; energy recruitment</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -47337,7 +47689,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data/tech/AI recruitment agency</t>
+          <t>Tech recruitment agency</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -47347,7 +47699,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Beauty/aesthetics training academy</t>
+          <t>Data/tech/AI recruitment agency</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -47357,7 +47709,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Beauty/hair training academy</t>
+          <t>Beauty/aesthetics training academy</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -47367,7 +47719,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Medical aesthetics/injectable training academy</t>
+          <t>Beauty/hair training academy</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -47377,7 +47729,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Yoga teacher training school</t>
+          <t>Medical aesthetics/injectable training academy</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -47387,7 +47739,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Creative &amp; marketing recruitment agency</t>
+          <t>Yoga teacher training school</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -47397,7 +47749,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Private dermatology &amp; women's health clinics</t>
+          <t>Creative &amp; marketing recruitment agency</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -47407,7 +47759,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Private dermatology practice</t>
+          <t>Private dermatology &amp; women's health clinics</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -47417,7 +47769,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Wedding venue (converted barn)</t>
+          <t>Private dermatology practice</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -47427,7 +47779,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Wedding venue (waterside barn &amp; estate)</t>
+          <t>Wedding venue (converted barn)</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -47437,7 +47789,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Wedding venue (thatched barn on working farm)</t>
+          <t>Wedding venue (waterside barn &amp; estate)</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -47447,7 +47799,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Wedding venue (working farm)</t>
+          <t>Wedding venue (thatched barn on working farm)</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -47457,7 +47809,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Wedding venue (restored historic barn)</t>
+          <t>Wedding venue (working farm)</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -47467,7 +47819,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Chartered IFA / wealth management</t>
+          <t>Wedding venue (restored historic barn)</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -47477,7 +47829,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Independent mortgage broker</t>
+          <t>Chartered IFA / wealth management</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -48001,6 +48353,26 @@
         </is>
       </c>
       <c r="B240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Wedding venue (barn on working farm)</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Wedding venue (Cotswold stone barn)</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$518</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$522</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T518"/>
+  <dimension ref="A1:T522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -45964,8 +45964,368 @@
       </c>
       <c r="T518" s="3" t="inlineStr"/>
     </row>
+    <row r="519">
+      <c r="A519" s="3" t="inlineStr">
+        <is>
+          <t>Cedar Trust Care Homes</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>Care home group (residential, nursing, dementia)</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t>Cheltenham, Tewkesbury &amp; Gloucester (5 homes)</t>
+        </is>
+      </c>
+      <c r="D519" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cedartrust.co.uk</t>
+        </is>
+      </c>
+      <c r="E519" s="3" t="inlineStr">
+        <is>
+          <t>info@cedartrust.co.uk</t>
+        </is>
+      </c>
+      <c r="F519" s="3" t="inlineStr">
+        <is>
+          <t>01242 525 087</t>
+        </is>
+      </c>
+      <c r="G519" s="3" t="inlineStr">
+        <is>
+          <t>Antony D. Cronk (Managing Director, opened first home 1986)</t>
+        </is>
+      </c>
+      <c r="H519" s="3" t="inlineStr"/>
+      <c r="I519" s="3" t="inlineStr"/>
+      <c r="J519" s="3" t="inlineStr">
+        <is>
+          <t>39-year family-owned care home group with 5 homes across Gloucestershire; care fees run into thousands per month per resident, recurring</t>
+        </is>
+      </c>
+      <c r="K519" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L519" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M519" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N519" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O519" s="3" t="inlineStr">
+        <is>
+          <t>39-year trading history; 5-site regional footprint</t>
+        </is>
+      </c>
+      <c r="P519" s="3" t="inlineStr">
+        <is>
+          <t>5-site footprint not matched by per-town AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q519" s="3" t="inlineStr">
+        <is>
+          <t>Per-site AEO content to own Cheltenham/Tewkesbury/Gloucester 'care home near me' searches separately</t>
+        </is>
+      </c>
+      <c r="R519" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S519" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T519" s="3" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="inlineStr">
+        <is>
+          <t>Northleach Court Care Home</t>
+        </is>
+      </c>
+      <c r="B520" s="4" t="inlineStr">
+        <is>
+          <t>Care home (nursing, dementia, residential)</t>
+        </is>
+      </c>
+      <c r="C520" s="4" t="inlineStr">
+        <is>
+          <t>Northleach, nr Cheltenham &amp; Cirencester</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="inlineStr">
+        <is>
+          <t>https://www.northleachcourtcarehome.com</t>
+        </is>
+      </c>
+      <c r="E520" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F520" s="4" t="inlineStr">
+        <is>
+          <t>01451 861447</t>
+        </is>
+      </c>
+      <c r="G520" s="4" t="inlineStr">
+        <is>
+          <t>Family-run, independently owned</t>
+        </is>
+      </c>
+      <c r="H520" s="4" t="inlineStr"/>
+      <c r="I520" s="4" t="inlineStr"/>
+      <c r="J520" s="4" t="inlineStr">
+        <is>
+          <t>Family-run independent Cotswolds care home with CQC Good rating, 'home from home' positioning; care fees run into thousands per month per resident, recurring</t>
+        </is>
+      </c>
+      <c r="K520" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L520" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M520" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N520" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O520" s="4" t="inlineStr">
+        <is>
+          <t>CQC Good rating</t>
+        </is>
+      </c>
+      <c r="P520" s="4" t="inlineStr">
+        <is>
+          <t>'Home from home' family positioning not yet the AI-cited answer for 'care home Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q520" s="4" t="inlineStr">
+        <is>
+          <t>'A true home from home, family-run - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R520" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S520" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T520" s="4" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="3" t="inlineStr">
+        <is>
+          <t>Newlands Care (Newlands of Stow)</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>Care home (exclusive residential care)</t>
+        </is>
+      </c>
+      <c r="C521" s="3" t="inlineStr">
+        <is>
+          <t>Stow-on-the-Wold, Cotswolds</t>
+        </is>
+      </c>
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>https://newlands.care</t>
+        </is>
+      </c>
+      <c r="E521" s="3" t="inlineStr">
+        <is>
+          <t>enquiries@newlandsofstow.co.uk</t>
+        </is>
+      </c>
+      <c r="F521" s="3" t="inlineStr">
+        <is>
+          <t>01451 885277</t>
+        </is>
+      </c>
+      <c r="G521" s="3" t="inlineStr">
+        <is>
+          <t>Amar Sheikh (Founder, family ties spanning 30+ years)</t>
+        </is>
+      </c>
+      <c r="H521" s="3" t="inlineStr"/>
+      <c r="I521" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/NewlandsofStow</t>
+        </is>
+      </c>
+      <c r="J521" s="3" t="inlineStr">
+        <is>
+          <t>Exclusive Cotswolds care residence built on 30+ years of family history in care; care fees run into thousands per month per resident, recurring</t>
+        </is>
+      </c>
+      <c r="K521" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L521" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M521" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N521" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O521" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 30+ year family heritage; 'exclusive' premium positioning</t>
+        </is>
+      </c>
+      <c r="P521" s="3" t="inlineStr">
+        <is>
+          <t>Premium/exclusive positioning and family heritage not yet the AI-cited answer for 'care home Cotswolds'</t>
+        </is>
+      </c>
+      <c r="Q521" s="3" t="inlineStr">
+        <is>
+          <t>'30+ years of family care history, now an exclusive Cotswold residence - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R521" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S521" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T521" s="3" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="inlineStr">
+        <is>
+          <t>Jolley Consultancy</t>
+        </is>
+      </c>
+      <c r="B522" s="4" t="inlineStr">
+        <is>
+          <t>Business consultancy (small business support)</t>
+        </is>
+      </c>
+      <c r="C522" s="4" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D522" s="4" t="inlineStr">
+        <is>
+          <t>https://jolleyconsultancy.com</t>
+        </is>
+      </c>
+      <c r="E522" s="4" t="inlineStr">
+        <is>
+          <t>jolley.consultancy@gmail.com</t>
+        </is>
+      </c>
+      <c r="F522" s="4" t="inlineStr">
+        <is>
+          <t>07718 587 526</t>
+        </is>
+      </c>
+      <c r="G522" s="4" t="inlineStr">
+        <is>
+          <t>Anna Jolley (Founder)</t>
+        </is>
+      </c>
+      <c r="H522" s="4" t="inlineStr"/>
+      <c r="I522" s="4" t="inlineStr">
+        <is>
+          <t>instagram.com/jolleyconsultancy; facebook.com/Jolley.Consultancy</t>
+        </is>
+      </c>
+      <c r="J522" s="4" t="inlineStr">
+        <is>
+          <t>Affordable one-to-one business consultancy for small, local Guildford businesses; monthly retained consultancy fees recur across a client's growth</t>
+        </is>
+      </c>
+      <c r="K522" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L522" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M522" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N522" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O522" s="4" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence</t>
+        </is>
+      </c>
+      <c r="P522" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'business consultant Guildford' searches not yet AI-answer dominated by this consultancy</t>
+        </is>
+      </c>
+      <c r="Q522" s="4" t="inlineStr">
+        <is>
+          <t>'Own the AI-cited answer for small-business support in Guildford'</t>
+        </is>
+      </c>
+      <c r="R522" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S522" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T522" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T518"/>
+  <autoFilter ref="A1:T522"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45976,7 +46336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -45996,7 +46356,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5">
@@ -48373,6 +48733,46 @@
         </is>
       </c>
       <c r="B242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Care home group (residential, nursing, dementia)</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Care home (nursing, dementia, residential)</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Care home (exclusive residential care)</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Business consultancy (small business support)</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$522</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$524</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T522"/>
+  <dimension ref="A1:T524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -46324,8 +46324,184 @@
       </c>
       <c r="T522" s="4" t="inlineStr"/>
     </row>
+    <row r="523">
+      <c r="A523" s="3" t="inlineStr">
+        <is>
+          <t>Randall &amp; Payne</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; tax advisers</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>Shurdington, Cheltenham</t>
+        </is>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randall-payne.co.uk</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>info@randall-payne.co.uk</t>
+        </is>
+      </c>
+      <c r="F523" s="3" t="inlineStr">
+        <is>
+          <t>01242 776000</t>
+        </is>
+      </c>
+      <c r="G523" s="3" t="inlineStr">
+        <is>
+          <t>Independently owned LLP</t>
+        </is>
+      </c>
+      <c r="H523" s="3" t="inlineStr"/>
+      <c r="I523" s="3" t="inlineStr"/>
+      <c r="J523" s="3" t="inlineStr">
+        <is>
+          <t>Independently owned chartered accountancy and tax advisory firm working with clients across Gloucestershire and internationally; ongoing accountancy/advisory retainers recur across a client's business lifetime</t>
+        </is>
+      </c>
+      <c r="K523" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L523" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M523" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N523" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O523" s="3" t="inlineStr">
+        <is>
+          <t>ICAEW listing; established multi-decade regional reputation</t>
+        </is>
+      </c>
+      <c r="P523" s="3" t="inlineStr">
+        <is>
+          <t>Established reputation not yet the AI-cited answer for 'accountant Cheltenham'</t>
+        </is>
+      </c>
+      <c r="Q523" s="3" t="inlineStr">
+        <is>
+          <t>'Independently owned chartered accountants serving Gloucestershire - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R523" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S523" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T523" s="3" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="inlineStr">
+        <is>
+          <t>Andy Walton &amp; Co</t>
+        </is>
+      </c>
+      <c r="B524" s="4" t="inlineStr">
+        <is>
+          <t>Chartered accountants (small business)</t>
+        </is>
+      </c>
+      <c r="C524" s="4" t="inlineStr">
+        <is>
+          <t>Dorchester-on-Thames, nr Wallingford, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D524" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oxford-accountant.co.uk</t>
+        </is>
+      </c>
+      <c r="E524" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F524" s="4" t="inlineStr"/>
+      <c r="G524" s="4" t="inlineStr">
+        <is>
+          <t>Andy Walton (Founder, est. 2005)</t>
+        </is>
+      </c>
+      <c r="H524" s="4" t="inlineStr"/>
+      <c r="I524" s="4" t="inlineStr"/>
+      <c r="J524" s="4" t="inlineStr">
+        <is>
+          <t>20-year small-business chartered accountancy practice founded as an alternative to expensive high-street accountants; ongoing accountancy/tax retainers recur across a client's business lifetime</t>
+        </is>
+      </c>
+      <c r="K524" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L524" s="4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M524" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N524" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O524" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P524" s="4" t="inlineStr">
+        <is>
+          <t>20-year affordable-alternative positioning not yet the AI-cited answer for 'small business accountant Oxfordshire'</t>
+        </is>
+      </c>
+      <c r="Q524" s="4" t="inlineStr">
+        <is>
+          <t>'The affordable alternative to expensive high-street accountants for 20 years - own that AEO positioning'</t>
+        </is>
+      </c>
+      <c r="R524" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S524" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T524" s="4" t="inlineStr">
+        <is>
+          <t>Phone number removed from site due to nuisance calls - use contact form</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T522"/>
+  <autoFilter ref="A1:T524"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46336,7 +46512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B246"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -46356,7 +46532,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5">
@@ -48773,6 +48949,26 @@
         </is>
       </c>
       <c r="B246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Chartered accountants &amp; tax advisers</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Chartered accountants (small business)</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$532</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T524"/>
+  <dimension ref="A1:T532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -46500,8 +46500,732 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="3" t="inlineStr">
+        <is>
+          <t>Fern &amp; Pine Garden Design Studio</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>Garden &amp; landscape design studio</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t>Brighton/Sussex (+ Surrey, Kent, Cotswolds)</t>
+        </is>
+      </c>
+      <c r="D525" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fernandpine.com</t>
+        </is>
+      </c>
+      <c r="E525" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F525" s="3" t="inlineStr">
+        <is>
+          <t>01273 906 912</t>
+        </is>
+      </c>
+      <c r="G525" s="3" t="inlineStr">
+        <is>
+          <t>Alick Nee (Founder, Society of Garden Designers Pre-Registered Member)</t>
+        </is>
+      </c>
+      <c r="H525" s="3" t="inlineStr"/>
+      <c r="I525" s="3" t="inlineStr"/>
+      <c r="J525" s="3" t="inlineStr">
+        <is>
+          <t>Boutique garden design/landscape architecture studio working on £25k-£250k+ project budgets across Sussex/Surrey/Kent/Cotswolds; project fees run into tens of thousands to hundreds of thousands</t>
+        </is>
+      </c>
+      <c r="K525" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L525" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M525" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N525" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O525" s="3" t="inlineStr">
+        <is>
+          <t>Houzz presence; wide multi-county coverage</t>
+        </is>
+      </c>
+      <c r="P525" s="3" t="inlineStr">
+        <is>
+          <t>Wide geographic coverage not matched by per-region AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q525" s="3" t="inlineStr">
+        <is>
+          <t>Per-region AEO content to own Sussex/Surrey/Kent/Cotswolds 'garden designer' searches separately</t>
+        </is>
+      </c>
+      <c r="R525" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S525" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T525" s="3" t="inlineStr">
+        <is>
+          <t>High project budgets (£25k-£250k+) - strong AEO opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="inlineStr">
+        <is>
+          <t>The Landscape Design Studio</t>
+        </is>
+      </c>
+      <c r="B526" s="4" t="inlineStr">
+        <is>
+          <t>Landscape &amp; garden design studio</t>
+        </is>
+      </c>
+      <c r="C526" s="4" t="inlineStr">
+        <is>
+          <t>Bromley, Kent (serving South London/Surrey)</t>
+        </is>
+      </c>
+      <c r="D526" s="4" t="inlineStr">
+        <is>
+          <t>https://thelandscapedesignstudio.co.uk</t>
+        </is>
+      </c>
+      <c r="E526" s="4" t="inlineStr">
+        <is>
+          <t>info@thelandscapedesignstudio.com</t>
+        </is>
+      </c>
+      <c r="F526" s="4" t="inlineStr">
+        <is>
+          <t>0203 538 8655</t>
+        </is>
+      </c>
+      <c r="G526" s="4" t="inlineStr">
+        <is>
+          <t>Chris Benson (Founder)</t>
+        </is>
+      </c>
+      <c r="H526" s="4" t="inlineStr"/>
+      <c r="I526" s="4" t="inlineStr"/>
+      <c r="J526" s="4" t="inlineStr">
+        <is>
+          <t>Independent landscape design studio serving Kent/South London/Surrey; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K526" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L526" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M526" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N526" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O526" s="4" t="inlineStr">
+        <is>
+          <t>Houzz presence</t>
+        </is>
+      </c>
+      <c r="P526" s="4" t="inlineStr">
+        <is>
+          <t>Generic 'garden designer Kent' searches not yet AI-answer dominated by this studio</t>
+        </is>
+      </c>
+      <c r="Q526" s="4" t="inlineStr">
+        <is>
+          <t>Own a specific Kent/South London AEO niche vs bigger regional landscape firms</t>
+        </is>
+      </c>
+      <c r="R526" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S526" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T526" s="4" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon Tutors</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>Private tuition (A-Level/IB/GCSE/KS3)</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon, SW London</t>
+        </is>
+      </c>
+      <c r="D527" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wimbledon-tutors.co.uk</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F527" s="3" t="inlineStr"/>
+      <c r="G527" s="3" t="inlineStr">
+        <is>
+          <t>Sara, Tom, Win &amp; Jacki Davis (Partner-led team, ex-independent-school teachers/examiners)</t>
+        </is>
+      </c>
+      <c r="H527" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jacki-davis-9518738a</t>
+        </is>
+      </c>
+      <c r="I527" s="3" t="inlineStr"/>
+      <c r="J527" s="3" t="inlineStr">
+        <is>
+          <t>Small partner-led tutoring practice staffed entirely by former top independent-school teachers and examiners; per-session tuition fees recur weekly across a family's school years</t>
+        </is>
+      </c>
+      <c r="K527" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L527" s="3" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="M527" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N527" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O527" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P527" s="3" t="inlineStr">
+        <is>
+          <t>Elite ex-teacher credentials not yet the AI-cited answer for 'tutor Wimbledon'</t>
+        </is>
+      </c>
+      <c r="Q527" s="3" t="inlineStr">
+        <is>
+          <t>'Every tutor is a former top independent-school teacher or examiner - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R527" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S527" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T527" s="3" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Apstar Tutoring</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>Private tuition (maths, 7+ to Oxbridge entry)</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>Dulwich, South London</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apstartutoring.com</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr"/>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>Aidin &amp; Jonathan (Co-founders, current Dulwich College maths teachers &amp; exam board examiners, est. 2023)</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr"/>
+      <c r="I528" s="2" t="inlineStr"/>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>New tutoring practice founded by two working Dulwich College teachers/AQA-Pearson examiners, already claiming 2,000+ students; per-session tuition fees recur weekly, especially around exam season</t>
+        </is>
+      </c>
+      <c r="K528" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N528" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O528" s="2" t="inlineStr">
+        <is>
+          <t>Founders are working exam-board examiners = exceptional credibility asset</t>
+        </is>
+      </c>
+      <c r="P528" s="2" t="inlineStr">
+        <is>
+          <t>New but rapidly-growing (2,000+ students) practice not yet the AI-cited answer for 'maths tutor Dulwich'</t>
+        </is>
+      </c>
+      <c r="Q528" s="2" t="inlineStr">
+        <is>
+          <t>'Taught by working Dulwich College teachers and exam board examiners - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R528" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S528" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T528" s="2" t="inlineStr">
+        <is>
+          <t>Founders are practising exam-board examiners - exceptional AEO credibility hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="inlineStr">
+        <is>
+          <t>Dulwich Tutor</t>
+        </is>
+      </c>
+      <c r="B529" s="4" t="inlineStr">
+        <is>
+          <t>Private tuition (ages 3-16)</t>
+        </is>
+      </c>
+      <c r="C529" s="4" t="inlineStr">
+        <is>
+          <t>Dulwich Village, South London</t>
+        </is>
+      </c>
+      <c r="D529" s="4" t="inlineStr">
+        <is>
+          <t>https://dulwich-tutor.co.uk</t>
+        </is>
+      </c>
+      <c r="E529" s="4" t="inlineStr">
+        <is>
+          <t>info@dulwichtutors.com</t>
+        </is>
+      </c>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>0208 653 3502</t>
+        </is>
+      </c>
+      <c r="G529" s="4" t="inlineStr">
+        <is>
+          <t>Female founder, 14+ years teaching experience (name not publicly disclosed)</t>
+        </is>
+      </c>
+      <c r="H529" s="4" t="inlineStr"/>
+      <c r="I529" s="4" t="inlineStr"/>
+      <c r="J529" s="4" t="inlineStr">
+        <is>
+          <t>Long-standing owner-operated tutoring agency for maths/English/exam prep across independent and state school curricula; per-session tuition fees recur weekly across a family's school years</t>
+        </is>
+      </c>
+      <c r="K529" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L529" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M529" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N529" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O529" s="4" t="inlineStr">
+        <is>
+          <t>None visible</t>
+        </is>
+      </c>
+      <c r="P529" s="4" t="inlineStr">
+        <is>
+          <t>14+ years of experience not yet the AI-cited answer for 'tutor Dulwich'</t>
+        </is>
+      </c>
+      <c r="Q529" s="4" t="inlineStr">
+        <is>
+          <t>'14+ years of trusted local tutoring in Dulwich - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R529" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S529" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T529" s="4" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="3" t="inlineStr">
+        <is>
+          <t>Crown Kindergartens</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>Day nursery</t>
+        </is>
+      </c>
+      <c r="C530" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon, SW19</t>
+        </is>
+      </c>
+      <c r="D530" s="3" t="inlineStr">
+        <is>
+          <t>https://www.crownkindergartens.co.uk</t>
+        </is>
+      </c>
+      <c r="E530" s="3" t="inlineStr">
+        <is>
+          <t>info@crownkindergartens.co.uk</t>
+        </is>
+      </c>
+      <c r="F530" s="3" t="inlineStr">
+        <is>
+          <t>020 8540 8820</t>
+        </is>
+      </c>
+      <c r="G530" s="3" t="inlineStr">
+        <is>
+          <t>Family-run since 1974</t>
+        </is>
+      </c>
+      <c r="H530" s="3" t="inlineStr"/>
+      <c r="I530" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/CrownKindergarten</t>
+        </is>
+      </c>
+      <c r="J530" s="3" t="inlineStr">
+        <is>
+          <t>51-year family-run Wimbledon nursery with a rare large private garden, Ofsted Good in all areas; nursery fees run into thousands per year per child</t>
+        </is>
+      </c>
+      <c r="K530" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L530" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M530" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N530" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O530" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; 51-year trading history; Ofsted Good across all areas</t>
+        </is>
+      </c>
+      <c r="P530" s="3" t="inlineStr">
+        <is>
+          <t>51-year heritage not yet the AI-cited answer for 'nursery Wimbledon'</t>
+        </is>
+      </c>
+      <c r="Q530" s="3" t="inlineStr">
+        <is>
+          <t>'51 years and Ofsted Good in every area - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R530" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S530" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T530" s="3" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>Under the Willow</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>Montessori-inspired day nursery</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>Dulwich/Herne Hill, SE21</t>
+        </is>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>https://www.underthewillow.co.uk</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>headteacher@underthewillow.co.uk</t>
+        </is>
+      </c>
+      <c r="F531" s="3" t="inlineStr">
+        <is>
+          <t>020 8761 7972</t>
+        </is>
+      </c>
+      <c r="G531" s="3" t="inlineStr">
+        <is>
+          <t>Mary Haynes (Founder/Owner, est. 2012)</t>
+        </is>
+      </c>
+      <c r="H531" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/maryhaynes</t>
+        </is>
+      </c>
+      <c r="I531" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/Under-The-Willow-163852547114079</t>
+        </is>
+      </c>
+      <c r="J531" s="3" t="inlineStr">
+        <is>
+          <t>13-year eco-friendly Montessori nursery, Ofsted Good (2022); nursery fees run into thousands per year per child</t>
+        </is>
+      </c>
+      <c r="K531" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L531" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M531" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N531" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O531" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; Montessori niche positioning; Ofsted Good</t>
+        </is>
+      </c>
+      <c r="P531" s="3" t="inlineStr">
+        <is>
+          <t>Montessori/eco-friendly niche positioning not yet the AI-cited answer for 'Montessori nursery Dulwich'</t>
+        </is>
+      </c>
+      <c r="Q531" s="3" t="inlineStr">
+        <is>
+          <t>'The eco-friendly Montessori choice in Dulwich - own that exact AEO niche positioning'</t>
+        </is>
+      </c>
+      <c r="R531" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S531" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T531" s="3" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="3" t="inlineStr">
+        <is>
+          <t>Alexander House Nursery</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>Day nursery (STEAM-focused, 3 sites)</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon, Wandsworth &amp; Battersea Reach, SW London</t>
+        </is>
+      </c>
+      <c r="D532" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alexanderhousenursery.com</t>
+        </is>
+      </c>
+      <c r="E532" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon@alexanderhousenursery.com</t>
+        </is>
+      </c>
+      <c r="F532" s="3" t="inlineStr">
+        <is>
+          <t>0208 240 0299</t>
+        </is>
+      </c>
+      <c r="G532" s="3" t="inlineStr">
+        <is>
+          <t>Family-run, founder has 30+ years' childcare experience</t>
+        </is>
+      </c>
+      <c r="H532" s="3" t="inlineStr"/>
+      <c r="I532" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/alexanderhousenursery; facebook.com/alexanderhousenursery</t>
+        </is>
+      </c>
+      <c r="J532" s="3" t="inlineStr">
+        <is>
+          <t>3-site independent family-run nursery group with a STEAM curriculum niche; nursery fees run into thousands per year per child across 3 locations</t>
+        </is>
+      </c>
+      <c r="K532" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L532" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M532" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N532" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O532" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook/TikTok presence = active marketing; STEAM niche positioning</t>
+        </is>
+      </c>
+      <c r="P532" s="3" t="inlineStr">
+        <is>
+          <t>3-site footprint and STEAM niche not matched by per-site AI-search dominance</t>
+        </is>
+      </c>
+      <c r="Q532" s="3" t="inlineStr">
+        <is>
+          <t>Per-site AEO content to own Wimbledon/Wandsworth/Battersea 'STEAM nursery' searches separately</t>
+        </is>
+      </c>
+      <c r="R532" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S532" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T532" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T524"/>
+  <autoFilter ref="A1:T532"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46512,7 +47236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -46532,7 +47256,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5">
@@ -48969,6 +49693,86 @@
         </is>
       </c>
       <c r="B248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Garden &amp; landscape design studio</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Landscape &amp; garden design studio</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Private tuition (A-Level/IB/GCSE/KS3)</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Private tuition (maths, 7+ to Oxbridge entry)</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Private tuition (ages 3-16)</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Day nursery</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Montessori-inspired day nursery</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Day nursery (STEAM-focused, 3 sites)</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
         <v>1</v>
       </c>
     </row>

--- a/prospects/aeora_prospects.xlsx
+++ b/prospects/aeora_prospects.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$532</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$T$552</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T532"/>
+  <dimension ref="A1:T552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -47224,8 +47224,1896 @@
       </c>
       <c r="T532" s="3" t="inlineStr"/>
     </row>
+    <row r="533">
+      <c r="A533" s="3" t="inlineStr">
+        <is>
+          <t>Michael Jones Architects</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>Architecture practice (residential/commercial)</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="inlineStr">
+        <is>
+          <t>Richmond, Surrey</t>
+        </is>
+      </c>
+      <c r="D533" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mjarchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="E533" s="3" t="inlineStr">
+        <is>
+          <t>studio@mjarchitects.co.uk</t>
+        </is>
+      </c>
+      <c r="F533" s="3" t="inlineStr">
+        <is>
+          <t>020 8948 1863</t>
+        </is>
+      </c>
+      <c r="G533" s="3" t="inlineStr">
+        <is>
+          <t>Michael Jones (Founder, est. 1990)</t>
+        </is>
+      </c>
+      <c r="H533" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/michael-jones-architects-limited</t>
+        </is>
+      </c>
+      <c r="I533" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/MJArchitectsLtd</t>
+        </is>
+      </c>
+      <c r="J533" s="3" t="inlineStr">
+        <is>
+          <t>35-year established RIBA chartered Richmond practice spanning private residences to commercial developments; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K533" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L533" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M533" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N533" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O533" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; 35-year trading history; award-winning portfolio</t>
+        </is>
+      </c>
+      <c r="P533" s="3" t="inlineStr">
+        <is>
+          <t>35-year heritage not yet the AI-cited answer for 'architect Richmond'</t>
+        </is>
+      </c>
+      <c r="Q533" s="3" t="inlineStr">
+        <is>
+          <t>'35 years of award-winning architecture in Richmond - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R533" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S533" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T533" s="3" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>50 Degrees North Architects</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>Architecture practice (residential extensions/retrofit)</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>Richmond, Surrey</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.50degrees.co.uk</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>info@50degrees.co.uk</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>020 8744 2337</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>Leigh Bowen (Founder, ARB/RIBA, est. ~2006, worked on BedZED zero-carbon housing)</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/50-degrees-north-design-consultants-ltd</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/50degreesnortharchitects</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>19-year RIBA chartered practice founded by a pioneer of the BedZED zero-carbon housing project; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K534" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L534" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N534" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O534" s="2" t="inlineStr">
+        <is>
+          <t>Instagram (3,100+ followers); LinkedIn presence; BedZED pioneer credential = strong authority asset</t>
+        </is>
+      </c>
+      <c r="P534" s="2" t="inlineStr">
+        <is>
+          <t>BedZED pioneer credential not yet the AI-cited answer for 'sustainable architect Richmond'</t>
+        </is>
+      </c>
+      <c r="Q534" s="2" t="inlineStr">
+        <is>
+          <t>'Worked on the pioneering BedZED zero-carbon project - own that exact AEO authority signal'</t>
+        </is>
+      </c>
+      <c r="R534" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S534" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T534" s="2" t="inlineStr">
+        <is>
+          <t>BedZED pioneer credential - exceptional AEO hook for sustainability-focused clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Tania Azadian Interiors</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>Luxury interior design</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>Wimbledon Village, London</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taniaazadianinteriors.com</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>info@taniaazadianinteriors.com</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>07946 533380</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>Tania Azadian (Founder, ex-Kelly Hoppen Senior Designer, est. 2016)</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/tania-azadian; linkedin.com/company/tania-azadian-interiors-ltd</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>instagram.com/tania_azadian_interiors; facebook.com/taniaazadianinteriors</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>One of only a few BIID Registered designers in Wimbledon, founder sits on the BIID council; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K535" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L535" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N535" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O535" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram/Facebook presence; BIID council position; ex-Kelly Hoppen pedigree</t>
+        </is>
+      </c>
+      <c r="P535" s="2" t="inlineStr">
+        <is>
+          <t>BIID council position and Kelly Hoppen pedigree not yet the AI-cited trust signal for 'interior designer Wimbledon'</t>
+        </is>
+      </c>
+      <c r="Q535" s="2" t="inlineStr">
+        <is>
+          <t>'A BIID council member and ex-Kelly Hoppen designer - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R535" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S535" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T535" s="2" t="inlineStr">
+        <is>
+          <t>BIID council position + Kelly Hoppen pedigree - exceptional AEO credibility hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="3" t="inlineStr">
+        <is>
+          <t>Gomm Studio</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>Boutique interior design</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon Village, London</t>
+        </is>
+      </c>
+      <c r="D536" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gommstudio.com</t>
+        </is>
+      </c>
+      <c r="E536" s="3" t="inlineStr">
+        <is>
+          <t>office@gommstudio.com</t>
+        </is>
+      </c>
+      <c r="F536" s="3" t="inlineStr"/>
+      <c r="G536" s="3" t="inlineStr">
+        <is>
+          <t>Louise Gomm (Founder, BIID registered, KLC-trained, est. 2015)</t>
+        </is>
+      </c>
+      <c r="H536" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/louise-gomm-86507152</t>
+        </is>
+      </c>
+      <c r="I536" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com/gommstudio</t>
+        </is>
+      </c>
+      <c r="J536" s="3" t="inlineStr">
+        <is>
+          <t>10-year award-winning family-run boutique studio for residential/commercial clients; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K536" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L536" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M536" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N536" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O536" s="3" t="inlineStr">
+        <is>
+          <t>Facebook presence; press feature (Humphrey Munson Q&amp;A); award-winning</t>
+        </is>
+      </c>
+      <c r="P536" s="3" t="inlineStr">
+        <is>
+          <t>Press feature and award-winning status not yet the AI-cited answer for 'interior designer Wimbledon'</t>
+        </is>
+      </c>
+      <c r="Q536" s="3" t="inlineStr">
+        <is>
+          <t>'Award-winning and featured in the press - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R536" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S536" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T536" s="3" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="3" t="inlineStr">
+        <is>
+          <t>Anna Auzins Interiors</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>Boutique residential interior design</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>Wimbledon, London</t>
+        </is>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>https://www.annaauzins.co.uk</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F537" s="3" t="inlineStr"/>
+      <c r="G537" s="3" t="inlineStr">
+        <is>
+          <t>Anna Auzins (Founder, KLC-trained, est. 2008)</t>
+        </is>
+      </c>
+      <c r="H537" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/anna-auzins-0a590b14</t>
+        </is>
+      </c>
+      <c r="I537" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/annaauzins; facebook.com/AnnaAuzinsInteriors</t>
+        </is>
+      </c>
+      <c r="J537" s="3" t="inlineStr">
+        <is>
+          <t>17-year boutique interior design studio with a distinctive people-first design approach, press-featured (Hayche/H Furniture); project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K537" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L537" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M537" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N537" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O537" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn/Instagram/Facebook presence; 17-year trading history; press feature</t>
+        </is>
+      </c>
+      <c r="P537" s="3" t="inlineStr">
+        <is>
+          <t>17-year heritage and press feature not yet the AI-cited answer for 'interior designer Wimbledon'</t>
+        </is>
+      </c>
+      <c r="Q537" s="3" t="inlineStr">
+        <is>
+          <t>'17 years of people-first interior design in Wimbledon - own that AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R537" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S537" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T537" s="3" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>Studio Belle Interior Design</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="inlineStr">
+        <is>
+          <t>High-end interior design</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="inlineStr">
+        <is>
+          <t>Wimbledon Village, London</t>
+        </is>
+      </c>
+      <c r="D538" s="4" t="inlineStr">
+        <is>
+          <t>https://www.studiobelle.co.uk</t>
+        </is>
+      </c>
+      <c r="E538" s="4" t="inlineStr">
+        <is>
+          <t>jessica@studiobelle.co.uk</t>
+        </is>
+      </c>
+      <c r="F538" s="4" t="inlineStr"/>
+      <c r="G538" s="4" t="inlineStr">
+        <is>
+          <t>Jessica Bell (Founder, est. 2021)</t>
+        </is>
+      </c>
+      <c r="H538" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jessica-bell-5b722290</t>
+        </is>
+      </c>
+      <c r="I538" s="4" t="inlineStr"/>
+      <c r="J538" s="4" t="inlineStr">
+        <is>
+          <t>Growing independent studio for high-end London residential/commercial projects; project fees run into tens of thousands per client</t>
+        </is>
+      </c>
+      <c r="K538" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L538" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M538" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N538" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O538" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn presence</t>
+        </is>
+      </c>
+      <c r="P538" s="4" t="inlineStr">
+        <is>
+          <t>New but growing studio - ground-floor opportunity to own local AEO search before bigger studios do</t>
+        </is>
+      </c>
+      <c r="Q538" s="4" t="inlineStr">
+        <is>
+          <t>'A rising name in Wimbledon interior design - be the AI-cited answer before competitors catch on'</t>
+        </is>
+      </c>
+      <c r="R538" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S538" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T538" s="4" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="3" t="inlineStr">
+        <is>
+          <t>Verse Medical Aesthetics</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (injectables, skin)</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>https://www.versemedicalaesthetics.com</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>marta@versemedicalaesthetics.com</t>
+        </is>
+      </c>
+      <c r="F539" s="3" t="inlineStr">
+        <is>
+          <t>07476 695696</t>
+        </is>
+      </c>
+      <c r="G539" s="3" t="inlineStr">
+        <is>
+          <t>Marta (Founder, NMC-registered nurse, V300 Independent Prescriber, ex-lawyer)</t>
+        </is>
+      </c>
+      <c r="H539" s="3" t="inlineStr"/>
+      <c r="I539" s="3" t="inlineStr"/>
+      <c r="J539" s="3" t="inlineStr">
+        <is>
+          <t>Nurse-led injectables/skin clinic founded by a former Polish lawyer/barrister who retrained as a nurse prescriber; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K539" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L539" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M539" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N539" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O539" s="3" t="inlineStr">
+        <is>
+          <t>Unusual ex-lawyer founder story = strong PR asset</t>
+        </is>
+      </c>
+      <c r="P539" s="3" t="inlineStr">
+        <is>
+          <t>Unique career-change founder story not yet the AI-cited answer for 'aesthetics clinic Guildford'</t>
+        </is>
+      </c>
+      <c r="Q539" s="3" t="inlineStr">
+        <is>
+          <t>'From barrister to nurse prescriber - own that exact AEO founder story'</t>
+        </is>
+      </c>
+      <c r="R539" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S539" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T539" s="3" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Optimise Aesthetics</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>Aesthetics, wellness &amp; weight-loss clinic</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.optimiseaesthetics.com</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>07581 375192</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>Dr Louise Bye (Founder, GP/eye surgeon, est. 2019)</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/dr-louise-bye-235bbb330</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/optimiseaesthetics</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>CQC-registered, award-winning doctor-led clinic founded by a dual-qualified GP and eye surgeon; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L540" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N540" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O540" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; CQC registration; award-winning</t>
+        </is>
+      </c>
+      <c r="P540" s="2" t="inlineStr">
+        <is>
+          <t>Dual-qualification founder credential not yet the AI-cited trust signal for 'aesthetics clinic Guildford'</t>
+        </is>
+      </c>
+      <c r="Q540" s="2" t="inlineStr">
+        <is>
+          <t>'Led by a GP and eye surgeon, CQC-registered - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R540" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S540" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T540" s="2" t="inlineStr">
+        <is>
+          <t>Dual medical qualification founder - exceptional AEO credibility hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr">
+        <is>
+          <t>First Aesthetics (Guildford)</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics &amp; skin clinic</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>Guildford, Surrey</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>https://firstaesthetics.co.uk</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F541" s="3" t="inlineStr"/>
+      <c r="G541" s="3" t="inlineStr">
+        <is>
+          <t>Dr Bib &amp; Dr Shova (Co-founders, Harley Street-trained, 40+ yrs combined experience)</t>
+        </is>
+      </c>
+      <c r="H541" s="3" t="inlineStr"/>
+      <c r="I541" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/dr.bib.guildford</t>
+        </is>
+      </c>
+      <c r="J541" s="3" t="inlineStr">
+        <is>
+          <t>Harley Street-trained doctor-led clinic with a co-founder holding both a medical and law degree; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K541" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L541" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M541" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N541" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O541" s="3" t="inlineStr">
+        <is>
+          <t>Instagram presence; Harley Street training pedigree</t>
+        </is>
+      </c>
+      <c r="P541" s="3" t="inlineStr">
+        <is>
+          <t>Harley Street pedigree not yet the AI-cited answer for 'Botox clinic Guildford'</t>
+        </is>
+      </c>
+      <c r="Q541" s="3" t="inlineStr">
+        <is>
+          <t>'Harley Street-trained doctors, now in Guildford - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R541" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S541" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T541" s="3" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Dr Paulina Charlesworth Aesthetics</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>GP-led aesthetics &amp; longevity clinic</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>Underriver, Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>https://drcharlesworth.co.uk</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>01732 682439</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>Dr Paulina Charlesworth MBBS MRCGP (Founder, ~10 years trading)</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/dr-paulina-charlesworth-mbbs-mrcgp-9b748a296</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/charlesworthclinic</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>American Board Certified GP-led aesthetics/anti-ageing clinic trained across UK/California/Paris; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L542" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N542" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O542" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; American Board Certification; ~10-year trading history</t>
+        </is>
+      </c>
+      <c r="P542" s="2" t="inlineStr">
+        <is>
+          <t>International board certification not yet the AI-cited trust signal for 'aesthetics clinic Sevenoaks'</t>
+        </is>
+      </c>
+      <c r="Q542" s="2" t="inlineStr">
+        <is>
+          <t>'American Board Certified in Anti-Ageing Medicine - own that exact AEO credibility signal'</t>
+        </is>
+      </c>
+      <c r="R542" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S542" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T542" s="2" t="inlineStr">
+        <is>
+          <t>International board certification - exceptional AEO credibility hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="3" t="inlineStr">
+        <is>
+          <t>Greenhouse Aesthetics</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics clinic (30+ treatments)</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="inlineStr">
+        <is>
+          <t>Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D543" s="3" t="inlineStr">
+        <is>
+          <t>https://www.greenhouseaesthetics.com</t>
+        </is>
+      </c>
+      <c r="E543" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F543" s="3" t="inlineStr"/>
+      <c r="G543" s="3" t="inlineStr">
+        <is>
+          <t>Tanya Garcia (Owner/Clinical Director, ex-Guy's Hospital dental training, ~5 years trading)</t>
+        </is>
+      </c>
+      <c r="H543" s="3" t="inlineStr"/>
+      <c r="I543" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/thegreenhouseaesthetics; facebook.com/thegreenhouseaesthetics</t>
+        </is>
+      </c>
+      <c r="J543" s="3" t="inlineStr">
+        <is>
+          <t>5-star rated clinic offering 30+ treatments, founded by a Guy's Hospital-trained practitioner; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K543" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L543" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M543" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N543" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O543" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence; 5-star rating</t>
+        </is>
+      </c>
+      <c r="P543" s="3" t="inlineStr">
+        <is>
+          <t>5-star rating not yet the AI-cited trust signal for 'aesthetics clinic Sevenoaks'</t>
+        </is>
+      </c>
+      <c r="Q543" s="3" t="inlineStr">
+        <is>
+          <t>'5-star rated across 30+ treatments - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R543" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S543" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T543" s="3" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>Lumen Skin Clinic</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetics &amp; functional medicine clinic</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="inlineStr">
+        <is>
+          <t>Sevenoaks, Kent</t>
+        </is>
+      </c>
+      <c r="D544" s="3" t="inlineStr">
+        <is>
+          <t>https://lumenskinclinic.co.uk</t>
+        </is>
+      </c>
+      <c r="E544" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F544" s="3" t="inlineStr">
+        <is>
+          <t>01732 252770</t>
+        </is>
+      </c>
+      <c r="G544" s="3" t="inlineStr">
+        <is>
+          <t>Iwona Taylor (Founder, Registered Nurse Prescriber, dermatology-trained at Guy's &amp; St Thomas's)</t>
+        </is>
+      </c>
+      <c r="H544" s="3" t="inlineStr"/>
+      <c r="I544" s="3" t="inlineStr">
+        <is>
+          <t>instagram.com/lumen_skin_clinic; facebook.com/Lumenskinclinic</t>
+        </is>
+      </c>
+      <c r="J544" s="3" t="inlineStr">
+        <is>
+          <t>Nurse-led clinic combining aesthetic treatments with functional medicine, trained under a renowned Harley Street dermatologist; repeat treatment clients, premium per-session fees</t>
+        </is>
+      </c>
+      <c r="K544" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L544" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M544" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N544" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O544" s="3" t="inlineStr">
+        <is>
+          <t>Instagram/Facebook presence; dermatology + functional medicine dual specialism</t>
+        </is>
+      </c>
+      <c r="P544" s="3" t="inlineStr">
+        <is>
+          <t>Dual dermatology/functional-medicine specialism not yet the AI-cited answer for 'skin clinic Sevenoaks'</t>
+        </is>
+      </c>
+      <c r="Q544" s="3" t="inlineStr">
+        <is>
+          <t>'Dermatology training plus functional medicine - own that exact AEO dual-specialism positioning'</t>
+        </is>
+      </c>
+      <c r="R544" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S544" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T544" s="3" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr">
+        <is>
+          <t>Brigstow Independent Financial Planning</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>IFA / financial planning</t>
+        </is>
+      </c>
+      <c r="C545" s="3" t="inlineStr">
+        <is>
+          <t>Downend, Bristol</t>
+        </is>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>https://www.brigstowifp.co.uk</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>info@brigstowifp.co.uk</t>
+        </is>
+      </c>
+      <c r="F545" s="3" t="inlineStr">
+        <is>
+          <t>07894 708855</t>
+        </is>
+      </c>
+      <c r="G545" s="3" t="inlineStr">
+        <is>
+          <t>Giles &amp; Dean (Co-founders, Chartered Financial Planners, 25+ yrs experience, left Close Brothers-owned network in 2024)</t>
+        </is>
+      </c>
+      <c r="H545" s="3" t="inlineStr"/>
+      <c r="I545" s="3" t="inlineStr"/>
+      <c r="J545" s="3" t="inlineStr">
+        <is>
+          <t>Founders deliberately left a bank-owned advice network to return to true independence, naming the firm after Bristol's Old English name; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K545" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L545" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M545" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N545" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O545" s="3" t="inlineStr">
+        <is>
+          <t>Deliberate 'return to independence' founder story = strong trust narrative</t>
+        </is>
+      </c>
+      <c r="P545" s="3" t="inlineStr">
+        <is>
+          <t>'Left a bank-owned network to go independent' story not yet the AI-cited answer for 'IFA Bristol'</t>
+        </is>
+      </c>
+      <c r="Q545" s="3" t="inlineStr">
+        <is>
+          <t>'We left a bank-owned network to be truly independent again - own that exact AEO trust story'</t>
+        </is>
+      </c>
+      <c r="R545" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S545" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T545" s="3" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="3" t="inlineStr">
+        <is>
+          <t>Sunrise Independent Financial Advisers</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>IFA / ethical &amp; sustainable investment advice</t>
+        </is>
+      </c>
+      <c r="C546" s="3" t="inlineStr">
+        <is>
+          <t>Clifton, Bristol</t>
+        </is>
+      </c>
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sunrise-ifa.co.uk</t>
+        </is>
+      </c>
+      <c r="E546" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F546" s="3" t="inlineStr">
+        <is>
+          <t>0117 244 3862</t>
+        </is>
+      </c>
+      <c r="G546" s="3" t="inlineStr">
+        <is>
+          <t>Guy Roper FPFS (Founder, Fellow of the Personal Finance Society - PFS's highest qualification level, est. 2019)</t>
+        </is>
+      </c>
+      <c r="H546" s="3" t="inlineStr"/>
+      <c r="I546" s="3" t="inlineStr"/>
+      <c r="J546" s="3" t="inlineStr">
+        <is>
+          <t>Ethical/sustainable-investment focused IFA led by a Fellow of the PFS (the profession's top qualification tier); ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K546" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L546" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M546" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N546" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O546" s="3" t="inlineStr">
+        <is>
+          <t>PFS Fellowship = highest national qualification tier; ethical-investment niche</t>
+        </is>
+      </c>
+      <c r="P546" s="3" t="inlineStr">
+        <is>
+          <t>PFS Fellowship and ethical-investment niche not yet the AI-cited answer for 'ethical IFA Bristol'</t>
+        </is>
+      </c>
+      <c r="Q546" s="3" t="inlineStr">
+        <is>
+          <t>'A Fellow of the Personal Finance Society specialising in ethical investing - own that exact AEO niche'</t>
+        </is>
+      </c>
+      <c r="R546" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S546" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T546" s="3" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>Combined Financial Strategies (CFS)</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>IFA / financial planning</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cfsorg.com</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>info@cfsorg.com</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>01225 471462</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>Jonothan McColgan (Founder, Chartered Financial Planner, UK Financial Adviser of the Year winner)</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jonothanmccolgan</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/combinedfinancialstrategies</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>Founder is a national award-winning adviser and regular FT/Times/Telegraph/Mail on Sunday commentator; ongoing wealth-management fees run into thousands annually per client</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L547" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N547" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O547" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; national press commentator status; UK Adviser of the Year award</t>
+        </is>
+      </c>
+      <c r="P547" s="2" t="inlineStr">
+        <is>
+          <t>National press-commentator status not yet the AI-cited answer for 'financial adviser Bath'</t>
+        </is>
+      </c>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>'Quoted in the FT and the Times, UK Adviser of the Year - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R547" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S547" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T547" s="2" t="inlineStr">
+        <is>
+          <t>National press commentator + top industry award - exceptional AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="3" t="inlineStr">
+        <is>
+          <t>Mhairi Cameron Consulting</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>Leadership &amp; organisational development consultancy</t>
+        </is>
+      </c>
+      <c r="C548" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="D548" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mhairicameronconsulting.co.uk</t>
+        </is>
+      </c>
+      <c r="E548" s="3" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F548" s="3" t="inlineStr">
+        <is>
+          <t>07711 764128</t>
+        </is>
+      </c>
+      <c r="G548" s="3" t="inlineStr">
+        <is>
+          <t>Mhairi Cameron (Founder/Director, est. 2003, ICF member)</t>
+        </is>
+      </c>
+      <c r="H548" s="3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/mhairi-cameron-13426010</t>
+        </is>
+      </c>
+      <c r="I548" s="3" t="inlineStr"/>
+      <c r="J548" s="3" t="inlineStr">
+        <is>
+          <t>22-year executive coaching/organisational-change consultancy with UK, Europe, Africa and Australia client experience; monthly retained consultancy fees recur across a client's leadership development</t>
+        </is>
+      </c>
+      <c r="K548" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L548" s="3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M548" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N548" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O548" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn presence; 22-year trading history; international client base</t>
+        </is>
+      </c>
+      <c r="P548" s="3" t="inlineStr">
+        <is>
+          <t>22-year international track record not yet the AI-cited answer for 'executive coach Bristol'</t>
+        </is>
+      </c>
+      <c r="Q548" s="3" t="inlineStr">
+        <is>
+          <t>'22 years coaching leaders across 4 continents - own that AEO trust signal in Bristol'</t>
+        </is>
+      </c>
+      <c r="R548" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S548" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T548" s="3" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Huntington &amp; Langham Estate</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>Care home group (residential, nursing, dementia)</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>Hindhead, Surrey (2 homes on a 30-acre estate)</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.huntingtonlangham.estate</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@huntingtonhouse.co.uk</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>01428 604600</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>Hoare family (4th generation, Charlie &amp; Sarah Hoare, since 1977)</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/huntington-langham</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/huntingtonandlangham; instagram.com/huntingtonlanghamestate</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>48-year, four-generation family-owned care estate with 2 CQC Good-rated homes on 30 acres; care fees run into thousands per month per resident, recurring</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L549" s="2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N549" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O549" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook/Instagram presence; 48-year 4-generation family history; CQC Good x2</t>
+        </is>
+      </c>
+      <c r="P549" s="2" t="inlineStr">
+        <is>
+          <t>48-year, 4-generation family story not yet the AI-cited answer for 'care home Surrey'</t>
+        </is>
+      </c>
+      <c r="Q549" s="2" t="inlineStr">
+        <is>
+          <t>'Four generations of the same family, 48 years of care - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R549" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S549" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="inlineStr">
+        <is>
+          <t>4-generation family heritage on a 30-acre estate - exceptional AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Everycare Central Surrey</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>Home care agency</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>Merrow, Guildford, Surrey (Guildford/Woking/Leatherhead/Bookham/Godalming)</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.everycare.co.uk/centralsurrey</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>centralsurrey@everycare.co.uk</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>01483 536266</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>Pauline Herring (Founder, est. 2012), now run by daughter Serena Coates</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/everycare-central-surrey-ltd</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/EverycareCentralSurrey</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>13-year mother-to-daughter family care agency, CQC Good, finalist and 'Most Trusted Home Care Provider - Surrey' award winner; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L550" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N550" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O550" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; national award win; CQC Good</t>
+        </is>
+      </c>
+      <c r="P550" s="2" t="inlineStr">
+        <is>
+          <t>'Most Trusted' award win not yet the AI-cited answer for 'home care Guildford'</t>
+        </is>
+      </c>
+      <c r="Q550" s="2" t="inlineStr">
+        <is>
+          <t>'Voted Surrey's Most Trusted Home Care Provider - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R550" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S550" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="inlineStr">
+        <is>
+          <t>National 'Most Trusted' award - strong AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Azure Care</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>Home care &amp; live-in care agency</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>Chatham, Kent (Medway)</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.azurecare.co.uk</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>hello@azurecare.co.uk</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>01634 968300</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>Kiran Gill &amp; Parvinder Dusanj (Co-founders, est. 2019)</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/azurecare</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>facebook.com/AzureCareLtd</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>The only CQC Outstanding-rated home care provider in Medway; care packages worth thousands per month per client</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L551" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N551" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O551" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn/Facebook presence; sole CQC Outstanding rating in Medway; local press coverage (Kent Online)</t>
+        </is>
+      </c>
+      <c r="P551" s="2" t="inlineStr">
+        <is>
+          <t>Sole-Outstanding-in-Medway status not yet the AI-cited trust signal for 'home care Medway'</t>
+        </is>
+      </c>
+      <c r="Q551" s="2" t="inlineStr">
+        <is>
+          <t>'The only Outstanding-rated home care provider in Medway - own that exact AEO trust signal'</t>
+        </is>
+      </c>
+      <c r="R551" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S551" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T551" s="2" t="inlineStr">
+        <is>
+          <t>Sole CQC Outstanding rating in the entire Medway area - exceptional AEO hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>Birchwood House &amp; Birchwood Care Services</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="inlineStr">
+        <is>
+          <t>Residential care home + domiciliary care agency</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>Speldhurst, Tunbridge Wells, Kent (+ Tonbridge/Sevenoaks)</t>
+        </is>
+      </c>
+      <c r="D552" s="4" t="inlineStr">
+        <is>
+          <t>https://www.birchwoodhouse.org.uk</t>
+        </is>
+      </c>
+      <c r="E552" s="4" t="inlineStr">
+        <is>
+          <t>via website contact form</t>
+        </is>
+      </c>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>01892 863710</t>
+        </is>
+      </c>
+      <c r="G552" s="4" t="inlineStr">
+        <is>
+          <t>Kiran Patel (Founder, ~30 years ago), now run by son Niral Patel</t>
+        </is>
+      </c>
+      <c r="H552" s="4" t="inlineStr"/>
+      <c r="I552" s="4" t="inlineStr">
+        <is>
+          <t>facebook.com/BirchwoodCare</t>
+        </is>
+      </c>
+      <c r="J552" s="4" t="inlineStr">
+        <is>
+          <t>30-year, two-generation family care home with a linked domiciliary care arm covering Tunbridge Wells/Tonbridge/Sevenoaks; care fees run into thousands per month per resident/client</t>
+        </is>
+      </c>
+      <c r="K552" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L552" s="4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="M552" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N552" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O552" s="4" t="inlineStr">
+        <is>
+          <t>Facebook presence; 30-year, 2-generation family history</t>
+        </is>
+      </c>
+      <c r="P552" s="4" t="inlineStr">
+        <is>
+          <t>Domiciliary arm rated 'Requires improvement' after recovering from special measures - reputation-repair opportunity alongside AEO</t>
+        </is>
+      </c>
+      <c r="Q552" s="4" t="inlineStr">
+        <is>
+          <t>'Recovering and rebuilding trust after a tough period - own the AEO narrative of your comeback'</t>
+        </is>
+      </c>
+      <c r="R552" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S552" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="T552" s="4" t="inlineStr">
+        <is>
+          <t>Domiciliary care arm rated 'Requires improvement' (recovering from special measures) - reputation/SEO opportunity, but flag pain point honestly in outreach</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T532"/>
+  <autoFilter ref="A1:T552"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47236,7 +49124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -47256,7 +49144,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>531</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5">
@@ -47449,17 +49337,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Law firm</t>
+          <t>Home care agency</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Letting agent</t>
+          <t>Law firm</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -47469,7 +49357,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Private tuition agency</t>
+          <t>Letting agent</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -47479,7 +49367,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Electrician</t>
+          <t>Private tuition agency</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -47489,7 +49377,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Personal training studio</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -47499,7 +49387,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Family law firm</t>
+          <t>Personal training studio</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -47509,7 +49397,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chiropractor</t>
+          <t>Family law firm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -47519,7 +49407,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Immigration law firm</t>
+          <t>Chiropractor</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -47529,7 +49417,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Independent optician</t>
+          <t>Immigration law firm</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -47539,7 +49427,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pilates studio</t>
+          <t>IFA / financial planning</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -47549,7 +49437,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kitchen &amp; bathroom design</t>
+          <t>Independent optician</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -47559,7 +49447,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Architecture practice</t>
+          <t>Pilates studio</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -47569,7 +49457,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Veterinary practice</t>
+          <t>Kitchen &amp; bathroom design</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -47579,7 +49467,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Home care agency</t>
+          <t>Architecture practice</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -47589,27 +49477,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Financial adviser / wealth management</t>
+          <t>Veterinary practice</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Roofer</t>
+          <t>Home care &amp; live-in care agency</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating / boilers</t>
+          <t>Financial adviser / wealth management</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -47619,7 +49507,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Event &amp; wedding caterer</t>
+          <t>Roofer</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -47629,7 +49517,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Estate agent (premium)</t>
+          <t>Plumbing &amp; heating / boilers</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -47639,7 +49527,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Orthodontist</t>
+          <t>Event &amp; wedding caterer</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -47649,7 +49537,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Employment law firm</t>
+          <t>Estate agent (premium)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -47659,7 +49547,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Event management agency</t>
+          <t>Orthodontist</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -47669,7 +49557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Design &amp; build</t>
+          <t>Employment law firm</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -47679,7 +49567,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IFA / wealth management</t>
+          <t>Event management agency</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -47689,7 +49577,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wealth management / IFA</t>
+          <t>Design &amp; build</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -47699,7 +49587,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Architects &amp; interior design</t>
+          <t>IFA / wealth management</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -47709,7 +49597,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Funeral directors</t>
+          <t>Aesthetics &amp; skin clinic</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -47719,7 +49607,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Garden rooms / outbuildings</t>
+          <t>Wealth management / IFA</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -47729,7 +49617,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Personal training gym</t>
+          <t>Architects &amp; interior design</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -47739,7 +49627,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Estate agent &amp; chartered surveyors</t>
+          <t>Funeral directors</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -47749,7 +49637,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Wedding &amp; event caterer</t>
+          <t>Garden rooms / outbuildings</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -47759,7 +49647,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Personal training</t>
+          <t>Personal training gym</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -47769,7 +49657,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Construction recruitment agency</t>
+          <t>Estate agent &amp; chartered surveyors</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -47779,7 +49667,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Legal recruitment agency</t>
+          <t>Wedding &amp; event caterer</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -47789,7 +49677,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HGV driver training</t>
+          <t>Personal training</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -47799,7 +49687,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Private GP practice</t>
+          <t>Construction recruitment agency</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -47809,7 +49697,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aesthetics clinic (non-surgical)</t>
+          <t>Legal recruitment agency</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -47819,7 +49707,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Driving school &amp; ADI instructor training</t>
+          <t>HGV driver training</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -47829,7 +49717,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Independent mortgage broker</t>
+          <t>Private GP practice</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -47839,7 +49727,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Reformer Pilates studio</t>
+          <t>Aesthetics clinic (non-surgical)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -47849,7 +49737,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Home care &amp; live-in care agency</t>
+          <t>Driving school &amp; ADI instructor training</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -47859,7 +49747,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Private tuition (primary/11+)</t>
+          <t>Independent mortgage broker</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -47869,7 +49757,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Independent Chartered financial planning</t>
+          <t>Reformer Pilates studio</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -47879,7 +49767,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Roofing contractor</t>
+          <t>Private tuition (primary/11+)</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -47889,37 +49777,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dentist / Orthodontics</t>
+          <t>Independent Chartered financial planning</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist dental/implant clinic</t>
+          <t>Roofing contractor</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Boutique corporate law firm</t>
+          <t>Care home group (residential, nursing, dementia)</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cosmetic/aesthetics clinic</t>
+          <t>Dentist / Orthodontics</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -47929,7 +49817,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Skin &amp; laser clinic</t>
+          <t>Specialist dental/implant clinic</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -47939,7 +49827,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mortgage broker / financial adviser</t>
+          <t>Boutique corporate law firm</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -47949,7 +49837,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Architects (RIBA chartered)</t>
+          <t>Cosmetic/aesthetics clinic</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -47959,7 +49847,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Recruitment agency (tech/startups)</t>
+          <t>Skin &amp; laser clinic</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -47969,7 +49857,7 @@
     <row r="76">
       <c r="A76" t="inline